--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{486CE867-83B2-4C72-BBD8-7D51D220FDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{738E663D-B019-4E02-A952-830ECEC2E249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4B246B51-0414-4298-9B05-397516E9385D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{8D152B1C-E3BE-4609-A2B8-4623FDE6A808}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11485" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11647" uniqueCount="1026">
   <si>
     <t>날짜</t>
   </si>
@@ -3503,7 +3503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1414C1B-EB23-431A-A369-9550664800F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D113FB47-0220-434E-BB04-02BB658B912F}">
   <dimension ref="A1:V344"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4976,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>2</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>2</v>
@@ -8716,7 +8716,7 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O77">
         <v>4</v>
@@ -8831,13 +8831,13 @@
         <v>270</v>
       </c>
       <c r="G79">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -8846,16 +8846,16 @@
         <v>282</v>
       </c>
       <c r="L79">
+        <v>3</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
         <v>2</v>
       </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>1</v>
-      </c>
       <c r="O79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P79" t="s">
         <v>17</v>
@@ -9872,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="N94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94">
         <v>1</v>
@@ -11300,7 +11300,7 @@
         <v>1</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115">
         <v>5</v>
@@ -12163,13 +12163,13 @@
         <v>240</v>
       </c>
       <c r="G128">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -12178,16 +12178,16 @@
         <v>282</v>
       </c>
       <c r="L128">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M128">
         <v>11</v>
       </c>
       <c r="N128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O128">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P128" t="s">
         <v>17</v>
@@ -12252,7 +12252,7 @@
         <v>7</v>
       </c>
       <c r="N129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O129">
         <v>14</v>
@@ -12320,7 +12320,7 @@
         <v>5</v>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O130">
         <v>4</v>
@@ -12435,31 +12435,31 @@
         <v>235</v>
       </c>
       <c r="G132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J132">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K132" t="s">
         <v>270</v>
       </c>
       <c r="L132">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M132">
         <v>12</v>
       </c>
       <c r="N132">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O132">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P132" t="s">
         <v>17</v>
@@ -12524,7 +12524,7 @@
         <v>9</v>
       </c>
       <c r="N133">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O133">
         <v>28</v>
@@ -12571,22 +12571,22 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K134" t="s">
         <v>270</v>
       </c>
       <c r="L134">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M134">
         <v>8</v>
@@ -12595,7 +12595,7 @@
         <v>3</v>
       </c>
       <c r="O134">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P134" t="s">
         <v>17</v>
@@ -12639,13 +12639,13 @@
         <v>250</v>
       </c>
       <c r="G135">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -12654,16 +12654,16 @@
         <v>282</v>
       </c>
       <c r="L135">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M135">
         <v>2</v>
       </c>
       <c r="N135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O135">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P135" t="s">
         <v>17</v>
@@ -12728,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="N136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136">
         <v>8</v>
@@ -12843,13 +12843,13 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -12858,16 +12858,16 @@
         <v>282</v>
       </c>
       <c r="L138">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M138">
         <v>2</v>
       </c>
       <c r="N138">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O138">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P138" t="s">
         <v>17</v>
@@ -12979,13 +12979,13 @@
         <v>250</v>
       </c>
       <c r="G140">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H140">
         <v>0</v>
       </c>
       <c r="I140">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -12994,16 +12994,16 @@
         <v>282</v>
       </c>
       <c r="L140">
+        <v>10</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140">
         <v>9</v>
-      </c>
-      <c r="M140">
-        <v>1</v>
-      </c>
-      <c r="N140">
-        <v>2</v>
-      </c>
-      <c r="O140">
-        <v>8</v>
       </c>
       <c r="P140" t="s">
         <v>17</v>
@@ -13455,13 +13455,13 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -13470,7 +13470,7 @@
         <v>282</v>
       </c>
       <c r="L147">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M147">
         <v>3</v>
@@ -13479,7 +13479,7 @@
         <v>5</v>
       </c>
       <c r="O147">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P147" t="s">
         <v>17</v>
@@ -13523,13 +13523,13 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -13538,16 +13538,16 @@
         <v>282</v>
       </c>
       <c r="L148">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M148">
         <v>3</v>
       </c>
       <c r="N148">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O148">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P148" t="s">
         <v>17</v>
@@ -13727,13 +13727,13 @@
         <v>255</v>
       </c>
       <c r="G151">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -13742,16 +13742,16 @@
         <v>282</v>
       </c>
       <c r="L151">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M151">
         <v>0</v>
       </c>
       <c r="N151">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O151">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P151" t="s">
         <v>17</v>
@@ -14156,7 +14156,7 @@
         <v>0</v>
       </c>
       <c r="N157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157">
         <v>1</v>
@@ -14224,7 +14224,7 @@
         <v>0</v>
       </c>
       <c r="N158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O158">
         <v>2</v>
@@ -14496,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="N162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O162">
         <v>1</v>
@@ -15229,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -15247,7 +15247,7 @@
         <v>3</v>
       </c>
       <c r="O173">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P173" t="s">
         <v>17</v>
@@ -15433,7 +15433,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -15451,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="O176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P176" t="s">
         <v>17</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -15859,7 +15859,7 @@
         <v>3</v>
       </c>
       <c r="O182">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P182" t="s">
         <v>17</v>
@@ -15924,7 +15924,7 @@
         <v>4</v>
       </c>
       <c r="N183">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O183">
         <v>9</v>
@@ -15971,13 +15971,13 @@
         <v>245</v>
       </c>
       <c r="G184">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -15986,16 +15986,16 @@
         <v>282</v>
       </c>
       <c r="L184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M184">
         <v>1</v>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P184" t="s">
         <v>17</v>
@@ -16651,13 +16651,13 @@
         <v>245</v>
       </c>
       <c r="G194">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
       <c r="I194">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -16666,16 +16666,16 @@
         <v>282</v>
       </c>
       <c r="L194">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M194">
         <v>14</v>
       </c>
       <c r="N194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O194">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P194" t="s">
         <v>17</v>
@@ -16787,13 +16787,13 @@
         <v>255</v>
       </c>
       <c r="G196">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H196">
         <v>0</v>
       </c>
       <c r="I196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -16802,16 +16802,16 @@
         <v>282</v>
       </c>
       <c r="L196">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M196">
         <v>7</v>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P196" t="s">
         <v>17</v>
@@ -16876,7 +16876,7 @@
         <v>0</v>
       </c>
       <c r="N197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O197">
         <v>2</v>
@@ -18236,7 +18236,7 @@
         <v>6</v>
       </c>
       <c r="N217">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O217">
         <v>6</v>
@@ -18351,13 +18351,13 @@
         <v>245</v>
       </c>
       <c r="G219">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J219">
         <v>0</v>
@@ -18366,16 +18366,16 @@
         <v>282</v>
       </c>
       <c r="L219">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M219">
         <v>3</v>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O219">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P219" t="s">
         <v>17</v>
@@ -18419,13 +18419,13 @@
         <v>250</v>
       </c>
       <c r="G220">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H220">
         <v>0</v>
       </c>
       <c r="I220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -18434,16 +18434,16 @@
         <v>282</v>
       </c>
       <c r="L220">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M220">
         <v>2</v>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P220" t="s">
         <v>17</v>
@@ -18969,7 +18969,7 @@
         <v>0</v>
       </c>
       <c r="I228">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5</v>
       </c>
       <c r="O228">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P228" t="s">
         <v>17</v>
@@ -19052,7 +19052,7 @@
         <v>10</v>
       </c>
       <c r="N229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229">
         <v>11</v>
@@ -19238,7 +19238,7 @@
         <v>0</v>
       </c>
       <c r="I232">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -19256,7 +19256,7 @@
         <v>1</v>
       </c>
       <c r="O232">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P232" t="s">
         <v>124</v>
@@ -19291,13 +19291,13 @@
         <v>123</v>
       </c>
       <c r="G233">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J233">
         <v>0</v>
@@ -19306,16 +19306,16 @@
         <v>282</v>
       </c>
       <c r="L233">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M233">
         <v>1</v>
       </c>
       <c r="N233">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O233">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P233" t="s">
         <v>124</v>
@@ -19489,7 +19489,7 @@
         <v>0</v>
       </c>
       <c r="N236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O236">
         <v>4</v>
@@ -19533,7 +19533,7 @@
         <v>0</v>
       </c>
       <c r="I237">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J237">
         <v>0</v>
@@ -19551,7 +19551,7 @@
         <v>0</v>
       </c>
       <c r="O237">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P237" t="s">
         <v>124</v>
@@ -19763,13 +19763,13 @@
         <v>123</v>
       </c>
       <c r="G241">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H241">
         <v>0</v>
       </c>
       <c r="I241">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -19778,16 +19778,16 @@
         <v>282</v>
       </c>
       <c r="L241">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M241">
         <v>0</v>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P241" t="s">
         <v>124</v>
@@ -20005,7 +20005,7 @@
         <v>0</v>
       </c>
       <c r="I245">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -20023,7 +20023,7 @@
         <v>8</v>
       </c>
       <c r="O245">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P245" t="s">
         <v>124</v>
@@ -20138,7 +20138,7 @@
         <v>1</v>
       </c>
       <c r="N247">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O247">
         <v>15</v>
@@ -20315,7 +20315,7 @@
         <v>1</v>
       </c>
       <c r="N250">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O250">
         <v>11</v>
@@ -20536,7 +20536,7 @@
         <v>0</v>
       </c>
       <c r="I254">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -20554,7 +20554,7 @@
         <v>1</v>
       </c>
       <c r="O254">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P254" t="s">
         <v>124</v>
@@ -20961,7 +20961,7 @@
         <v>0</v>
       </c>
       <c r="N261">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O261">
         <v>27</v>
@@ -20999,10 +20999,10 @@
         <v>191</v>
       </c>
       <c r="G262">
-        <v>5950</v>
+        <v>5948</v>
       </c>
       <c r="I262">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -21011,16 +21011,16 @@
         <v>282</v>
       </c>
       <c r="L262">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M262">
         <v>0</v>
       </c>
       <c r="N262">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O262">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P262" t="s">
         <v>182</v>
@@ -24692,8 +24692,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BA441C-4B31-4E15-973A-772DDD89CC76}">
-  <dimension ref="A1:K1237"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800A25F-3B69-4336-8B5A-3BA0F6383161}">
+  <dimension ref="A1:K1260"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -67989,6 +67989,811 @@
       </c>
       <c r="K1237">
         <v>35900</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1238" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1238">
+        <v>245</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1238">
+        <v>1</v>
+      </c>
+      <c r="J1238" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1238">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1239" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1239">
+        <v>235</v>
+      </c>
+      <c r="H1239" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1239">
+        <v>1</v>
+      </c>
+      <c r="J1239" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1239">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1240" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1240">
+        <v>255</v>
+      </c>
+      <c r="H1240" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1240">
+        <v>1</v>
+      </c>
+      <c r="J1240" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1240">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1241" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1241">
+        <v>255</v>
+      </c>
+      <c r="H1241" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1241">
+        <v>1</v>
+      </c>
+      <c r="J1241" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1241">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1242" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1242">
+        <v>240</v>
+      </c>
+      <c r="H1242" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1242">
+        <v>1</v>
+      </c>
+      <c r="J1242" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1242">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1243" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1243">
+        <v>250</v>
+      </c>
+      <c r="H1243" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1243">
+        <v>1</v>
+      </c>
+      <c r="J1243" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1243">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1244" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1244">
+        <v>245</v>
+      </c>
+      <c r="H1244" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1244">
+        <v>1</v>
+      </c>
+      <c r="J1244" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1244">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1245" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1245">
+        <v>235</v>
+      </c>
+      <c r="H1245" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1245">
+        <v>1</v>
+      </c>
+      <c r="J1245" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1245">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1246" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1246">
+        <v>235</v>
+      </c>
+      <c r="H1246" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1246">
+        <v>1</v>
+      </c>
+      <c r="J1246" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1246">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1247" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1247">
+        <v>245</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1247">
+        <v>1</v>
+      </c>
+      <c r="J1247" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1247">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1248" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1248">
+        <v>250</v>
+      </c>
+      <c r="H1248" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1248">
+        <v>1</v>
+      </c>
+      <c r="J1248" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1248">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1249" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1249">
+        <v>240</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1249">
+        <v>1</v>
+      </c>
+      <c r="J1249" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1249">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1250" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1250">
+        <v>245</v>
+      </c>
+      <c r="H1250" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1250">
+        <v>1</v>
+      </c>
+      <c r="J1250" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1250">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1251" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1251">
+        <v>270</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1251">
+        <v>1</v>
+      </c>
+      <c r="J1251" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1251">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1252" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1252">
+        <v>240</v>
+      </c>
+      <c r="H1252" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1252">
+        <v>1</v>
+      </c>
+      <c r="J1252" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1252">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1253" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1253">
+        <v>255</v>
+      </c>
+      <c r="H1253" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1253">
+        <v>1</v>
+      </c>
+      <c r="J1253" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1253">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1254" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1254">
+        <v>250</v>
+      </c>
+      <c r="H1254" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1254">
+        <v>1</v>
+      </c>
+      <c r="J1254" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1254">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1255" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1255">
+        <v>240</v>
+      </c>
+      <c r="H1255" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1255">
+        <v>1</v>
+      </c>
+      <c r="J1255" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1255">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1256" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1256">
+        <v>240</v>
+      </c>
+      <c r="H1256" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1256">
+        <v>1</v>
+      </c>
+      <c r="J1256" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1256">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1257" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1257">
+        <v>240</v>
+      </c>
+      <c r="H1257" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1257">
+        <v>1</v>
+      </c>
+      <c r="J1257" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1257">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1258" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1258" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1258" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1258">
+        <v>2</v>
+      </c>
+      <c r="J1258" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1258">
+        <v>19800</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1259" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1259">
+        <v>0</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1259">
+        <v>1</v>
+      </c>
+      <c r="J1259" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1259">
+        <v>35900</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1260" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1260">
+        <v>0</v>
+      </c>
+      <c r="H1260" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1260">
+        <v>1</v>
+      </c>
+      <c r="J1260" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1260">
+        <v>42900</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{738E663D-B019-4E02-A952-830ECEC2E249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9AD33DB-6881-47BF-B9E5-57C8F2090B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{8D152B1C-E3BE-4609-A2B8-4623FDE6A808}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{CFCBF8CC-6E88-4D14-A1F1-00DDF440466A}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11647" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11812" uniqueCount="1026">
   <si>
     <t>날짜</t>
   </si>
@@ -837,6 +837,9 @@
     <t>BJW1170-BKSL255</t>
   </si>
   <si>
+    <t>BJW1133-WHRO250</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -2200,9 +2203,6 @@
   </si>
   <si>
     <t>U-BJW1133-133139</t>
-  </si>
-  <si>
-    <t>BJW1133-WHRO250</t>
   </si>
   <si>
     <t>BJW1133WHRO 바오지 여성 배드민턴화 화이트로즈 250</t>
@@ -3503,7 +3503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D113FB47-0220-434E-BB04-02BB658B912F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F3E14C-5CB8-4166-BC74-BB224187E3F8}">
   <dimension ref="A1:V344"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3512,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3527,52 +3527,52 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="V1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -3580,7 +3580,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2">
         <v>20</v>
@@ -3625,7 +3625,7 @@
         <v>17</v>
       </c>
       <c r="Q2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>59000</v>
       </c>
       <c r="U2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L3">
         <v>17</v>
@@ -3693,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="Q3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>59000</v>
       </c>
       <c r="U3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -3716,7 +3716,7 @@
         <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -3761,7 +3761,7 @@
         <v>17</v>
       </c>
       <c r="Q4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -3773,7 +3773,7 @@
         <v>59000</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -3811,7 +3811,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L5">
         <v>13</v>
@@ -3829,7 +3829,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>59000</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -3897,7 +3897,7 @@
         <v>17</v>
       </c>
       <c r="Q6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>59000</v>
       </c>
       <c r="U6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -3965,7 +3965,7 @@
         <v>17</v>
       </c>
       <c r="Q7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3977,7 +3977,7 @@
         <v>59000</v>
       </c>
       <c r="U7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -4033,7 +4033,7 @@
         <v>17</v>
       </c>
       <c r="Q8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>59000</v>
       </c>
       <c r="U8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         <v>154</v>
       </c>
       <c r="B9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -4101,7 +4101,7 @@
         <v>17</v>
       </c>
       <c r="Q9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>59000</v>
       </c>
       <c r="U9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>155</v>
       </c>
       <c r="B10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -4169,7 +4169,7 @@
         <v>17</v>
       </c>
       <c r="Q10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>59000</v>
       </c>
       <c r="U10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -4237,7 +4237,7 @@
         <v>17</v>
       </c>
       <c r="Q11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -4249,7 +4249,7 @@
         <v>59000</v>
       </c>
       <c r="U11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -4257,10 +4257,10 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C12" t="s">
         <v>249</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>79900</v>
       </c>
       <c r="U12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C13" t="s">
         <v>249</v>
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4385,7 +4385,7 @@
         <v>79900</v>
       </c>
       <c r="U13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C14" t="s">
         <v>249</v>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>79900</v>
       </c>
       <c r="U14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C15" t="s">
         <v>249</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>79900</v>
       </c>
       <c r="U15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
         <v>249</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>79900</v>
       </c>
       <c r="U16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C17" t="s">
         <v>249</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         <v>79900</v>
       </c>
       <c r="U17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C18" t="s">
         <v>249</v>
@@ -4695,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4725,7 +4725,7 @@
         <v>79900</v>
       </c>
       <c r="U18" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4733,10 +4733,10 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C19" t="s">
         <v>249</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>79900</v>
       </c>
       <c r="U19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C20" t="s">
         <v>249</v>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4861,7 +4861,7 @@
         <v>79900</v>
       </c>
       <c r="U20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C21" t="s">
         <v>249</v>
@@ -4899,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>79900</v>
       </c>
       <c r="U21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C22" t="s">
         <v>249</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L22">
         <v>2</v>
@@ -4997,7 +4997,7 @@
         <v>79900</v>
       </c>
       <c r="U22" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>253</v>
       </c>
       <c r="B23" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C23" t="s">
         <v>249</v>
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L23">
         <v>2</v>
@@ -5065,7 +5065,7 @@
         <v>79900</v>
       </c>
       <c r="U23" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B24" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C24" t="s">
         <v>249</v>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -5133,7 +5133,7 @@
         <v>79900</v>
       </c>
       <c r="U24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -5141,10 +5141,10 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B25" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C25" t="s">
         <v>249</v>
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>79900</v>
       </c>
       <c r="U25" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C26" t="s">
         <v>249</v>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         <v>79900</v>
       </c>
       <c r="U26" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C27" t="s">
         <v>249</v>
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L27">
         <v>2</v>
@@ -5337,7 +5337,7 @@
         <v>79900</v>
       </c>
       <c r="U27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C28" t="s">
         <v>249</v>
@@ -5375,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -5405,7 +5405,7 @@
         <v>79900</v>
       </c>
       <c r="U28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C29" t="s">
         <v>249</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>79900</v>
       </c>
       <c r="U29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C30" t="s">
         <v>249</v>
@@ -5511,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>79900</v>
       </c>
       <c r="U30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B31" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C31" t="s">
         <v>249</v>
@@ -5579,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -5609,7 +5609,7 @@
         <v>79900</v>
       </c>
       <c r="U31" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -5617,10 +5617,10 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C32" t="s">
         <v>249</v>
@@ -5647,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>79900</v>
       </c>
       <c r="U32" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C33" t="s">
         <v>249</v>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -5745,7 +5745,7 @@
         <v>79900</v>
       </c>
       <c r="U33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -5753,10 +5753,10 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B34" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C34" t="s">
         <v>249</v>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         <v>79900</v>
       </c>
       <c r="U34" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C35" t="s">
         <v>249</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -5881,7 +5881,7 @@
         <v>79900</v>
       </c>
       <c r="U35" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C36" t="s">
         <v>249</v>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>79900</v>
       </c>
       <c r="U36" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B37" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C37" t="s">
         <v>249</v>
@@ -5987,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>79900</v>
       </c>
       <c r="U37" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -6028,7 +6028,7 @@
         <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C38" t="s">
         <v>249</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -6085,7 +6085,7 @@
         <v>79900</v>
       </c>
       <c r="U38" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C39" t="s">
         <v>249</v>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -6153,7 +6153,7 @@
         <v>79900</v>
       </c>
       <c r="U39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -6161,10 +6161,10 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C40" t="s">
         <v>249</v>
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -6221,7 +6221,7 @@
         <v>79900</v>
       </c>
       <c r="U40" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -6229,10 +6229,10 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C41" t="s">
         <v>249</v>
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>79900</v>
       </c>
       <c r="U41" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C42" t="s">
         <v>249</v>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -6357,7 +6357,7 @@
         <v>79900</v>
       </c>
       <c r="U42" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -6365,10 +6365,10 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B43" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C43" t="s">
         <v>249</v>
@@ -6395,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         <v>79900</v>
       </c>
       <c r="U43" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C44" t="s">
         <v>249</v>
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>79900</v>
       </c>
       <c r="U44" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C45" t="s">
         <v>249</v>
@@ -6531,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>79900</v>
       </c>
       <c r="U45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6569,10 +6569,10 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C46" t="s">
         <v>249</v>
@@ -6599,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>79900</v>
       </c>
       <c r="U46" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -6637,10 +6637,10 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" t="s">
         <v>249</v>
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -6697,7 +6697,7 @@
         <v>79900</v>
       </c>
       <c r="U47" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C48" t="s">
         <v>249</v>
@@ -6735,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>79900</v>
       </c>
       <c r="U48" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -6773,10 +6773,10 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C49" t="s">
         <v>249</v>
@@ -6803,7 +6803,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -6833,7 +6833,7 @@
         <v>79900</v>
       </c>
       <c r="U49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C50" t="s">
         <v>249</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -6901,7 +6901,7 @@
         <v>79900</v>
       </c>
       <c r="U50" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B51" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C51" t="s">
         <v>249</v>
@@ -6939,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -6969,7 +6969,7 @@
         <v>79900</v>
       </c>
       <c r="U51" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -6977,16 +6977,16 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C52" t="s">
         <v>249</v>
       </c>
       <c r="D52" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>79900</v>
       </c>
       <c r="U52" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -7045,16 +7045,16 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C53" t="s">
         <v>249</v>
       </c>
       <c r="D53" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -7105,7 +7105,7 @@
         <v>79900</v>
       </c>
       <c r="U53" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="V53">
         <v>0</v>
@@ -7113,16 +7113,16 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C54" t="s">
         <v>249</v>
       </c>
       <c r="D54" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E54" t="s">
         <v>16</v>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         <v>79900</v>
       </c>
       <c r="U54" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="V54">
         <v>0</v>
@@ -7181,16 +7181,16 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C55" t="s">
         <v>249</v>
       </c>
       <c r="D55" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
@@ -7211,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -7241,7 +7241,7 @@
         <v>79900</v>
       </c>
       <c r="U55" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="V55">
         <v>0</v>
@@ -7249,16 +7249,16 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C56" t="s">
         <v>249</v>
       </c>
       <c r="D56" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>79900</v>
       </c>
       <c r="U56" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="V56">
         <v>0</v>
@@ -7317,16 +7317,16 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C57" t="s">
         <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -7377,7 +7377,7 @@
         <v>79900</v>
       </c>
       <c r="U57" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="V57">
         <v>0</v>
@@ -7385,16 +7385,16 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B58" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C58" t="s">
         <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E58" t="s">
         <v>16</v>
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>79900</v>
       </c>
       <c r="U58" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="V58">
         <v>0</v>
@@ -7453,16 +7453,16 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C59" t="s">
         <v>249</v>
       </c>
       <c r="D59" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -7513,7 +7513,7 @@
         <v>79900</v>
       </c>
       <c r="U59" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -7521,16 +7521,16 @@
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B60" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C60" t="s">
         <v>249</v>
       </c>
       <c r="D60" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         <v>79900</v>
       </c>
       <c r="U60" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -7589,16 +7589,16 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C61" t="s">
         <v>249</v>
       </c>
       <c r="D61" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -7649,7 +7649,7 @@
         <v>79900</v>
       </c>
       <c r="U61" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -7657,16 +7657,16 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C62" t="s">
         <v>249</v>
       </c>
       <c r="D62" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
@@ -7687,7 +7687,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -7717,7 +7717,7 @@
         <v>79900</v>
       </c>
       <c r="U62" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -7725,16 +7725,16 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C63" t="s">
         <v>249</v>
       </c>
       <c r="D63" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -7785,7 +7785,7 @@
         <v>79900</v>
       </c>
       <c r="U63" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -7793,16 +7793,16 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C64" t="s">
         <v>249</v>
       </c>
       <c r="D64" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -7853,7 +7853,7 @@
         <v>79900</v>
       </c>
       <c r="U64" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -7861,16 +7861,16 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C65" t="s">
         <v>249</v>
       </c>
       <c r="D65" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
@@ -7891,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -7921,7 +7921,7 @@
         <v>79900</v>
       </c>
       <c r="U65" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -7929,16 +7929,16 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B66" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C66" t="s">
         <v>249</v>
       </c>
       <c r="D66" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>79900</v>
       </c>
       <c r="U66" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="V66">
         <v>0</v>
@@ -8000,7 +8000,7 @@
         <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L67">
         <v>12</v>
@@ -8045,7 +8045,7 @@
         <v>17</v>
       </c>
       <c r="Q67" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -8057,7 +8057,7 @@
         <v>69000</v>
       </c>
       <c r="U67" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="V67">
         <v>0</v>
@@ -8068,7 +8068,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -8095,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L68">
         <v>14</v>
@@ -8113,7 +8113,7 @@
         <v>17</v>
       </c>
       <c r="Q68" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -8125,7 +8125,7 @@
         <v>69000</v>
       </c>
       <c r="U68" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="V68">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -8163,7 +8163,7 @@
         <v>18</v>
       </c>
       <c r="K69" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L69">
         <v>28</v>
@@ -8181,7 +8181,7 @@
         <v>17</v>
       </c>
       <c r="Q69" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -8193,7 +8193,7 @@
         <v>69000</v>
       </c>
       <c r="U69" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -8231,7 +8231,7 @@
         <v>4</v>
       </c>
       <c r="K70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L70">
         <v>14</v>
@@ -8249,7 +8249,7 @@
         <v>17</v>
       </c>
       <c r="Q70" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -8261,7 +8261,7 @@
         <v>69000</v>
       </c>
       <c r="U70" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="V70">
         <v>0</v>
@@ -8272,7 +8272,7 @@
         <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -8299,7 +8299,7 @@
         <v>4</v>
       </c>
       <c r="K71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L71">
         <v>8</v>
@@ -8317,7 +8317,7 @@
         <v>17</v>
       </c>
       <c r="Q71" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         <v>69000</v>
       </c>
       <c r="U71" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="V71">
         <v>0</v>
@@ -8337,10 +8337,10 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C72" t="s">
         <v>25</v>
@@ -8367,7 +8367,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -8385,7 +8385,7 @@
         <v>17</v>
       </c>
       <c r="Q72" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -8397,7 +8397,7 @@
         <v>69000</v>
       </c>
       <c r="U72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="V72">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>119</v>
       </c>
       <c r="B73" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C73" t="s">
         <v>25</v>
@@ -8429,13 +8429,13 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L73">
         <v>4</v>
@@ -8447,13 +8447,13 @@
         <v>0</v>
       </c>
       <c r="O73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P73" t="s">
         <v>17</v>
       </c>
       <c r="Q73" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -8465,7 +8465,7 @@
         <v>69000</v>
       </c>
       <c r="U73" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="V73">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C74" t="s">
         <v>25</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         <v>17</v>
       </c>
       <c r="Q74" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -8533,7 +8533,7 @@
         <v>69000</v>
       </c>
       <c r="U74" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -8544,7 +8544,7 @@
         <v>184</v>
       </c>
       <c r="B75" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" t="s">
         <v>25</v>
@@ -8571,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -8589,7 +8589,7 @@
         <v>17</v>
       </c>
       <c r="Q75" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>69000</v>
       </c>
       <c r="U75" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -8612,7 +8612,7 @@
         <v>262</v>
       </c>
       <c r="B76" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C76" t="s">
         <v>25</v>
@@ -8639,7 +8639,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L76">
         <v>1</v>
@@ -8657,7 +8657,7 @@
         <v>17</v>
       </c>
       <c r="Q76" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>69000</v>
       </c>
       <c r="U76" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="V76">
         <v>0</v>
@@ -8680,7 +8680,7 @@
         <v>186</v>
       </c>
       <c r="B77" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C77" t="s">
         <v>25</v>
@@ -8707,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L77">
         <v>4</v>
@@ -8725,7 +8725,7 @@
         <v>17</v>
       </c>
       <c r="Q77" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -8737,7 +8737,7 @@
         <v>69000</v>
       </c>
       <c r="U77" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="V77">
         <v>0</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C78" t="s">
         <v>25</v>
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -8793,7 +8793,7 @@
         <v>17</v>
       </c>
       <c r="Q78" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -8805,7 +8805,7 @@
         <v>69000</v>
       </c>
       <c r="U78" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>233</v>
       </c>
       <c r="B79" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C79" t="s">
         <v>25</v>
@@ -8843,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L79">
         <v>3</v>
@@ -8861,7 +8861,7 @@
         <v>17</v>
       </c>
       <c r="Q79" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -8873,7 +8873,7 @@
         <v>69000</v>
       </c>
       <c r="U79" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -8884,7 +8884,7 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C80" t="s">
         <v>25</v>
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -8929,7 +8929,7 @@
         <v>17</v>
       </c>
       <c r="Q80" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -8941,7 +8941,7 @@
         <v>69000</v>
       </c>
       <c r="U80" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -8952,7 +8952,7 @@
         <v>222</v>
       </c>
       <c r="B81" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C81" t="s">
         <v>25</v>
@@ -8979,7 +8979,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L81">
         <v>2</v>
@@ -8997,7 +8997,7 @@
         <v>17</v>
       </c>
       <c r="Q81" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -9009,7 +9009,7 @@
         <v>69000</v>
       </c>
       <c r="U81" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="V81">
         <v>0</v>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B82" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C82" t="s">
         <v>25</v>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -9065,7 +9065,7 @@
         <v>17</v>
       </c>
       <c r="Q82" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -9077,7 +9077,7 @@
         <v>69000</v>
       </c>
       <c r="U82" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="V82">
         <v>0</v>
@@ -9085,10 +9085,10 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B83" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C83" t="s">
         <v>25</v>
@@ -9115,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>17</v>
       </c>
       <c r="Q83" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -9145,7 +9145,7 @@
         <v>69000</v>
       </c>
       <c r="U83" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="V83">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C84" t="s">
         <v>25</v>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L84">
         <v>1</v>
@@ -9201,7 +9201,7 @@
         <v>17</v>
       </c>
       <c r="Q84" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -9213,7 +9213,7 @@
         <v>69000</v>
       </c>
       <c r="U84" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="V84">
         <v>0</v>
@@ -9221,10 +9221,10 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B85" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C85" t="s">
         <v>25</v>
@@ -9251,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>17</v>
       </c>
       <c r="Q85" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -9281,7 +9281,7 @@
         <v>69000</v>
       </c>
       <c r="U85" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -9292,7 +9292,7 @@
         <v>226</v>
       </c>
       <c r="B86" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C86" t="s">
         <v>25</v>
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L86">
         <v>1</v>
@@ -9337,7 +9337,7 @@
         <v>17</v>
       </c>
       <c r="Q86" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -9349,7 +9349,7 @@
         <v>69000</v>
       </c>
       <c r="U86" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -9357,10 +9357,10 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C87" t="s">
         <v>25</v>
@@ -9387,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -9405,7 +9405,7 @@
         <v>17</v>
       </c>
       <c r="Q87" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>69000</v>
       </c>
       <c r="U87" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="V87">
         <v>0</v>
@@ -9428,7 +9428,7 @@
         <v>107</v>
       </c>
       <c r="B88" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C88" t="s">
         <v>25</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L88">
         <v>3</v>
@@ -9473,7 +9473,7 @@
         <v>17</v>
       </c>
       <c r="Q88" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -9485,7 +9485,7 @@
         <v>69000</v>
       </c>
       <c r="U88" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="V88">
         <v>0</v>
@@ -9496,7 +9496,7 @@
         <v>214</v>
       </c>
       <c r="B89" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C89" t="s">
         <v>25</v>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L89">
         <v>3</v>
@@ -9541,7 +9541,7 @@
         <v>17</v>
       </c>
       <c r="Q89" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -9553,7 +9553,7 @@
         <v>69000</v>
       </c>
       <c r="U89" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L90">
         <v>3</v>
@@ -9609,7 +9609,7 @@
         <v>17</v>
       </c>
       <c r="Q90" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -9621,7 +9621,7 @@
         <v>69000</v>
       </c>
       <c r="U90" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="V90">
         <v>0</v>
@@ -9629,10 +9629,10 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B91" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C91" t="s">
         <v>25</v>
@@ -9659,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -9677,7 +9677,7 @@
         <v>17</v>
       </c>
       <c r="Q91" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>69000</v>
       </c>
       <c r="U91" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="V91">
         <v>0</v>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C92" t="s">
         <v>25</v>
@@ -9727,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -9745,7 +9745,7 @@
         <v>17</v>
       </c>
       <c r="Q92" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>69000</v>
       </c>
       <c r="U92" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="V92">
         <v>0</v>
@@ -9768,7 +9768,7 @@
         <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C93" t="s">
         <v>25</v>
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -9813,7 +9813,7 @@
         <v>17</v>
       </c>
       <c r="Q93" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -9825,7 +9825,7 @@
         <v>69000</v>
       </c>
       <c r="U93" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="V93">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>260</v>
       </c>
       <c r="B94" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C94" t="s">
         <v>25</v>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L94">
         <v>1</v>
@@ -9881,7 +9881,7 @@
         <v>17</v>
       </c>
       <c r="Q94" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -9893,7 +9893,7 @@
         <v>69000</v>
       </c>
       <c r="U94" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="V94">
         <v>0</v>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C95" t="s">
         <v>25</v>
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -9949,7 +9949,7 @@
         <v>17</v>
       </c>
       <c r="Q95" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -9961,7 +9961,7 @@
         <v>69000</v>
       </c>
       <c r="U95" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="V95">
         <v>0</v>
@@ -9972,7 +9972,7 @@
         <v>228</v>
       </c>
       <c r="B96" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C96" t="s">
         <v>25</v>
@@ -9999,7 +9999,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L96">
         <v>3</v>
@@ -10017,7 +10017,7 @@
         <v>17</v>
       </c>
       <c r="Q96" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -10029,7 +10029,7 @@
         <v>69000</v>
       </c>
       <c r="U96" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="V96">
         <v>0</v>
@@ -10037,10 +10037,10 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C97" t="s">
         <v>25</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -10085,7 +10085,7 @@
         <v>17</v>
       </c>
       <c r="Q97" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -10097,7 +10097,7 @@
         <v>69000</v>
       </c>
       <c r="U97" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="V97">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C98" t="s">
         <v>25</v>
@@ -10135,7 +10135,7 @@
         <v>4</v>
       </c>
       <c r="K98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L98">
         <v>10</v>
@@ -10153,7 +10153,7 @@
         <v>17</v>
       </c>
       <c r="Q98" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>69000</v>
       </c>
       <c r="U98" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="V98">
         <v>0</v>
@@ -10176,7 +10176,7 @@
         <v>160</v>
       </c>
       <c r="B99" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C99" t="s">
         <v>25</v>
@@ -10203,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L99">
         <v>4</v>
@@ -10221,7 +10221,7 @@
         <v>17</v>
       </c>
       <c r="Q99" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -10233,7 +10233,7 @@
         <v>69000</v>
       </c>
       <c r="U99" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="V99">
         <v>0</v>
@@ -10244,7 +10244,7 @@
         <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C100" t="s">
         <v>25</v>
@@ -10271,7 +10271,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L100">
         <v>5</v>
@@ -10289,7 +10289,7 @@
         <v>17</v>
       </c>
       <c r="Q100" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -10301,7 +10301,7 @@
         <v>69000</v>
       </c>
       <c r="U100" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="V100">
         <v>0</v>
@@ -10309,10 +10309,10 @@
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C101" t="s">
         <v>25</v>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -10357,7 +10357,7 @@
         <v>17</v>
       </c>
       <c r="Q101" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -10369,7 +10369,7 @@
         <v>69000</v>
       </c>
       <c r="U101" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="V101">
         <v>0</v>
@@ -10377,10 +10377,10 @@
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B102" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C102" t="s">
         <v>25</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -10425,7 +10425,7 @@
         <v>17</v>
       </c>
       <c r="Q102" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -10437,7 +10437,7 @@
         <v>69000</v>
       </c>
       <c r="U102" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="V102">
         <v>0</v>
@@ -10448,7 +10448,7 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C103" t="s">
         <v>25</v>
@@ -10463,37 +10463,37 @@
         <v>265</v>
       </c>
       <c r="G103">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
       <c r="I103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M103">
         <v>0</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P103" t="s">
         <v>17</v>
       </c>
       <c r="Q103" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -10505,7 +10505,7 @@
         <v>69000</v>
       </c>
       <c r="U103" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="V103">
         <v>0</v>
@@ -10516,7 +10516,7 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C104" t="s">
         <v>25</v>
@@ -10531,37 +10531,37 @@
         <v>270</v>
       </c>
       <c r="G104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H104">
         <v>0</v>
       </c>
       <c r="I104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M104">
         <v>0</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P104" t="s">
         <v>17</v>
       </c>
       <c r="Q104" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -10573,7 +10573,7 @@
         <v>69000</v>
       </c>
       <c r="U104" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="V104">
         <v>0</v>
@@ -10581,10 +10581,10 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B105" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C105" t="s">
         <v>25</v>
@@ -10611,7 +10611,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         <v>17</v>
       </c>
       <c r="Q105" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>69000</v>
       </c>
       <c r="U105" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V105">
         <v>0</v>
@@ -10652,7 +10652,7 @@
         <v>58</v>
       </c>
       <c r="B106" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C106" t="s">
         <v>25</v>
@@ -10679,7 +10679,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L106">
         <v>2</v>
@@ -10697,7 +10697,7 @@
         <v>17</v>
       </c>
       <c r="Q106" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -10709,7 +10709,7 @@
         <v>69000</v>
       </c>
       <c r="U106" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="V106">
         <v>0</v>
@@ -10717,10 +10717,10 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B107" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C107" t="s">
         <v>25</v>
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>17</v>
       </c>
       <c r="Q107" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -10777,7 +10777,7 @@
         <v>69000</v>
       </c>
       <c r="U107" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="V107">
         <v>0</v>
@@ -10788,7 +10788,7 @@
         <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C108" t="s">
         <v>25</v>
@@ -10815,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -10833,7 +10833,7 @@
         <v>17</v>
       </c>
       <c r="Q108" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>69000</v>
       </c>
       <c r="U108" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="V108">
         <v>0</v>
@@ -10856,7 +10856,7 @@
         <v>37</v>
       </c>
       <c r="B109" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C109" t="s">
         <v>25</v>
@@ -10883,7 +10883,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -10901,7 +10901,7 @@
         <v>17</v>
       </c>
       <c r="Q109" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -10913,7 +10913,7 @@
         <v>69000</v>
       </c>
       <c r="U109" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="V109">
         <v>0</v>
@@ -10921,10 +10921,10 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B110" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C110" t="s">
         <v>25</v>
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>17</v>
       </c>
       <c r="Q110" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -10981,7 +10981,7 @@
         <v>69000</v>
       </c>
       <c r="U110" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="V110">
         <v>0</v>
@@ -10989,10 +10989,10 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B111" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C111" t="s">
         <v>25</v>
@@ -11019,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -11037,7 +11037,7 @@
         <v>17</v>
       </c>
       <c r="Q111" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -11049,7 +11049,7 @@
         <v>69000</v>
       </c>
       <c r="U111" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="V111">
         <v>0</v>
@@ -11060,7 +11060,7 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C112" t="s">
         <v>25</v>
@@ -11087,7 +11087,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L112">
         <v>5</v>
@@ -11105,7 +11105,7 @@
         <v>17</v>
       </c>
       <c r="Q112" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -11117,7 +11117,7 @@
         <v>69000</v>
       </c>
       <c r="U112" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="V112">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>97</v>
       </c>
       <c r="B113" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C113" t="s">
         <v>25</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L113">
         <v>11</v>
@@ -11173,7 +11173,7 @@
         <v>17</v>
       </c>
       <c r="Q113" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -11185,7 +11185,7 @@
         <v>69000</v>
       </c>
       <c r="U113" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="V113">
         <v>0</v>
@@ -11196,7 +11196,7 @@
         <v>108</v>
       </c>
       <c r="B114" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C114" t="s">
         <v>25</v>
@@ -11223,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L114">
         <v>14</v>
@@ -11241,7 +11241,7 @@
         <v>17</v>
       </c>
       <c r="Q114" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -11253,7 +11253,7 @@
         <v>69000</v>
       </c>
       <c r="U114" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="V114">
         <v>0</v>
@@ -11264,7 +11264,7 @@
         <v>59</v>
       </c>
       <c r="B115" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C115" t="s">
         <v>25</v>
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L115">
         <v>7</v>
@@ -11309,7 +11309,7 @@
         <v>17</v>
       </c>
       <c r="Q115" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -11321,7 +11321,7 @@
         <v>69000</v>
       </c>
       <c r="U115" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="V115">
         <v>0</v>
@@ -11332,7 +11332,7 @@
         <v>102</v>
       </c>
       <c r="B116" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C116" t="s">
         <v>25</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L116">
         <v>5</v>
@@ -11377,7 +11377,7 @@
         <v>17</v>
       </c>
       <c r="Q116" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>69000</v>
       </c>
       <c r="U116" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="V116">
         <v>0</v>
@@ -11400,7 +11400,7 @@
         <v>38</v>
       </c>
       <c r="B117" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C117" t="s">
         <v>25</v>
@@ -11427,7 +11427,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L117">
         <v>9</v>
@@ -11445,7 +11445,7 @@
         <v>17</v>
       </c>
       <c r="Q117" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -11457,7 +11457,7 @@
         <v>69000</v>
       </c>
       <c r="U117" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="V117">
         <v>0</v>
@@ -11468,7 +11468,7 @@
         <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C118" t="s">
         <v>25</v>
@@ -11489,13 +11489,13 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L118">
         <v>5</v>
@@ -11507,13 +11507,13 @@
         <v>0</v>
       </c>
       <c r="O118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P118" t="s">
         <v>17</v>
       </c>
       <c r="Q118" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>69000</v>
       </c>
       <c r="U118" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V118">
         <v>0</v>
@@ -11536,7 +11536,7 @@
         <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C119" t="s">
         <v>25</v>
@@ -11563,7 +11563,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L119">
         <v>5</v>
@@ -11581,7 +11581,7 @@
         <v>17</v>
       </c>
       <c r="Q119" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -11593,7 +11593,7 @@
         <v>69000</v>
       </c>
       <c r="U119" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="V119">
         <v>0</v>
@@ -11604,7 +11604,7 @@
         <v>82</v>
       </c>
       <c r="B120" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C120" t="s">
         <v>25</v>
@@ -11631,7 +11631,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L120">
         <v>4</v>
@@ -11649,7 +11649,7 @@
         <v>17</v>
       </c>
       <c r="Q120" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -11661,7 +11661,7 @@
         <v>69000</v>
       </c>
       <c r="U120" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="V120">
         <v>0</v>
@@ -11672,7 +11672,7 @@
         <v>98</v>
       </c>
       <c r="B121" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C121" t="s">
         <v>25</v>
@@ -11699,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -11717,7 +11717,7 @@
         <v>17</v>
       </c>
       <c r="Q121" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -11729,7 +11729,7 @@
         <v>69000</v>
       </c>
       <c r="U121" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="V121">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C122" t="s">
         <v>25</v>
@@ -11755,37 +11755,37 @@
         <v>260</v>
       </c>
       <c r="G122">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M122">
         <v>2</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P122" t="s">
         <v>17</v>
       </c>
       <c r="Q122" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -11797,7 +11797,7 @@
         <v>69000</v>
       </c>
       <c r="U122" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="V122">
         <v>0</v>
@@ -11808,7 +11808,7 @@
         <v>118</v>
       </c>
       <c r="B123" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C123" t="s">
         <v>25</v>
@@ -11835,7 +11835,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L123">
         <v>3</v>
@@ -11853,7 +11853,7 @@
         <v>17</v>
       </c>
       <c r="Q123" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -11865,7 +11865,7 @@
         <v>69000</v>
       </c>
       <c r="U123" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="V123">
         <v>0</v>
@@ -11876,7 +11876,7 @@
         <v>96</v>
       </c>
       <c r="B124" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C124" t="s">
         <v>25</v>
@@ -11903,7 +11903,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L124">
         <v>3</v>
@@ -11921,7 +11921,7 @@
         <v>17</v>
       </c>
       <c r="Q124" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -11933,7 +11933,7 @@
         <v>69000</v>
       </c>
       <c r="U124" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="V124">
         <v>0</v>
@@ -11944,7 +11944,7 @@
         <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C125" t="s">
         <v>25</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L125">
         <v>2</v>
@@ -11989,7 +11989,7 @@
         <v>17</v>
       </c>
       <c r="Q125" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -12001,7 +12001,7 @@
         <v>69000</v>
       </c>
       <c r="U125" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="V125">
         <v>0</v>
@@ -12012,7 +12012,7 @@
         <v>64</v>
       </c>
       <c r="B126" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C126" t="s">
         <v>25</v>
@@ -12039,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L126">
         <v>5</v>
@@ -12057,7 +12057,7 @@
         <v>17</v>
       </c>
       <c r="Q126" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -12069,7 +12069,7 @@
         <v>69000</v>
       </c>
       <c r="U126" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="V126">
         <v>0</v>
@@ -12080,7 +12080,7 @@
         <v>83</v>
       </c>
       <c r="B127" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
@@ -12107,7 +12107,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L127">
         <v>11</v>
@@ -12125,7 +12125,7 @@
         <v>17</v>
       </c>
       <c r="Q127" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -12137,7 +12137,7 @@
         <v>74000</v>
       </c>
       <c r="U127" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="V127">
         <v>0</v>
@@ -12148,7 +12148,7 @@
         <v>70</v>
       </c>
       <c r="B128" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C128" t="s">
         <v>19</v>
@@ -12175,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L128">
         <v>24</v>
@@ -12184,7 +12184,7 @@
         <v>11</v>
       </c>
       <c r="N128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O128">
         <v>11</v>
@@ -12193,7 +12193,7 @@
         <v>17</v>
       </c>
       <c r="Q128" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -12205,7 +12205,7 @@
         <v>74000</v>
       </c>
       <c r="U128" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="V128">
         <v>0</v>
@@ -12216,7 +12216,7 @@
         <v>75</v>
       </c>
       <c r="B129" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C129" t="s">
         <v>19</v>
@@ -12243,7 +12243,7 @@
         <v>9</v>
       </c>
       <c r="K129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L129">
         <v>20</v>
@@ -12252,7 +12252,7 @@
         <v>7</v>
       </c>
       <c r="N129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O129">
         <v>14</v>
@@ -12261,7 +12261,7 @@
         <v>17</v>
       </c>
       <c r="Q129" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -12273,7 +12273,7 @@
         <v>74000</v>
       </c>
       <c r="U129" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="V129">
         <v>0</v>
@@ -12284,7 +12284,7 @@
         <v>81</v>
       </c>
       <c r="B130" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C130" t="s">
         <v>19</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L130">
         <v>10</v>
@@ -12329,7 +12329,7 @@
         <v>17</v>
       </c>
       <c r="Q130" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -12341,7 +12341,7 @@
         <v>74000</v>
       </c>
       <c r="U130" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="V130">
         <v>0</v>
@@ -12352,7 +12352,7 @@
         <v>78</v>
       </c>
       <c r="B131" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C131" t="s">
         <v>19</v>
@@ -12379,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L131">
         <v>3</v>
@@ -12397,7 +12397,7 @@
         <v>17</v>
       </c>
       <c r="Q131" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -12409,7 +12409,7 @@
         <v>74000</v>
       </c>
       <c r="U131" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="V131">
         <v>0</v>
@@ -12420,7 +12420,7 @@
         <v>21</v>
       </c>
       <c r="B132" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C132" t="s">
         <v>19</v>
@@ -12435,22 +12435,22 @@
         <v>235</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J132">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K132" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L132">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M132">
         <v>12</v>
@@ -12459,13 +12459,13 @@
         <v>8</v>
       </c>
       <c r="O132">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P132" t="s">
         <v>17</v>
       </c>
       <c r="Q132" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -12477,7 +12477,7 @@
         <v>74000</v>
       </c>
       <c r="U132" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="V132">
         <v>0</v>
@@ -12488,7 +12488,7 @@
         <v>79</v>
       </c>
       <c r="B133" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C133" t="s">
         <v>19</v>
@@ -12503,37 +12503,37 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J133">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K133" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L133">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M133">
         <v>9</v>
       </c>
       <c r="N133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O133">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P133" t="s">
         <v>17</v>
       </c>
       <c r="Q133" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -12545,7 +12545,7 @@
         <v>74000</v>
       </c>
       <c r="U133" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="V133">
         <v>0</v>
@@ -12556,7 +12556,7 @@
         <v>62</v>
       </c>
       <c r="B134" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C134" t="s">
         <v>19</v>
@@ -12571,37 +12571,37 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J134">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K134" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L134">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M134">
         <v>8</v>
       </c>
       <c r="N134">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O134">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P134" t="s">
         <v>17</v>
       </c>
       <c r="Q134" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -12613,7 +12613,7 @@
         <v>74000</v>
       </c>
       <c r="U134" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="V134">
         <v>0</v>
@@ -12624,7 +12624,7 @@
         <v>76</v>
       </c>
       <c r="B135" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C135" t="s">
         <v>19</v>
@@ -12639,37 +12639,37 @@
         <v>250</v>
       </c>
       <c r="G135">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L135">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M135">
         <v>2</v>
       </c>
       <c r="N135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O135">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P135" t="s">
         <v>17</v>
       </c>
       <c r="Q135" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -12681,7 +12681,7 @@
         <v>74000</v>
       </c>
       <c r="U135" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="V135">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>86</v>
       </c>
       <c r="B136" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C136" t="s">
         <v>19</v>
@@ -12719,7 +12719,7 @@
         <v>7</v>
       </c>
       <c r="K136" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L136">
         <v>9</v>
@@ -12737,7 +12737,7 @@
         <v>17</v>
       </c>
       <c r="Q136" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -12749,7 +12749,7 @@
         <v>74000</v>
       </c>
       <c r="U136" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="V136">
         <v>0</v>
@@ -12760,7 +12760,7 @@
         <v>90</v>
       </c>
       <c r="B137" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C137" t="s">
         <v>19</v>
@@ -12787,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L137">
         <v>9</v>
@@ -12805,7 +12805,7 @@
         <v>17</v>
       </c>
       <c r="Q137" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>69000</v>
       </c>
       <c r="U137" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="V137">
         <v>0</v>
@@ -12828,7 +12828,7 @@
         <v>163</v>
       </c>
       <c r="B138" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C138" t="s">
         <v>19</v>
@@ -12855,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L138">
         <v>15</v>
@@ -12873,7 +12873,7 @@
         <v>17</v>
       </c>
       <c r="Q138" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>69000</v>
       </c>
       <c r="U138" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="V138">
         <v>0</v>
@@ -12896,7 +12896,7 @@
         <v>167</v>
       </c>
       <c r="B139" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C139" t="s">
         <v>19</v>
@@ -12923,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L139">
         <v>6</v>
@@ -12941,7 +12941,7 @@
         <v>17</v>
       </c>
       <c r="Q139" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>69000</v>
       </c>
       <c r="U139" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="V139">
         <v>0</v>
@@ -12964,7 +12964,7 @@
         <v>105</v>
       </c>
       <c r="B140" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C140" t="s">
         <v>19</v>
@@ -12979,37 +12979,37 @@
         <v>250</v>
       </c>
       <c r="G140">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H140">
         <v>0</v>
       </c>
       <c r="I140">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L140">
+        <v>11</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>4</v>
+      </c>
+      <c r="O140">
         <v>10</v>
       </c>
-      <c r="M140">
-        <v>1</v>
-      </c>
-      <c r="N140">
-        <v>3</v>
-      </c>
-      <c r="O140">
-        <v>9</v>
-      </c>
       <c r="P140" t="s">
         <v>17</v>
       </c>
       <c r="Q140" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -13021,7 +13021,7 @@
         <v>69000</v>
       </c>
       <c r="U140" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="V140">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>164</v>
       </c>
       <c r="B141" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C141" t="s">
         <v>19</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L141">
         <v>6</v>
@@ -13077,7 +13077,7 @@
         <v>17</v>
       </c>
       <c r="Q141" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -13089,7 +13089,7 @@
         <v>69000</v>
       </c>
       <c r="U141" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V141">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>92</v>
       </c>
       <c r="B142" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C142" t="s">
         <v>19</v>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L142">
         <v>2</v>
@@ -13145,7 +13145,7 @@
         <v>17</v>
       </c>
       <c r="Q142" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -13157,7 +13157,7 @@
         <v>69000</v>
       </c>
       <c r="U142" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="V142">
         <v>0</v>
@@ -13168,7 +13168,7 @@
         <v>168</v>
       </c>
       <c r="B143" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C143" t="s">
         <v>19</v>
@@ -13195,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L143">
         <v>5</v>
@@ -13213,7 +13213,7 @@
         <v>17</v>
       </c>
       <c r="Q143" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -13225,7 +13225,7 @@
         <v>69000</v>
       </c>
       <c r="U143" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="V143">
         <v>0</v>
@@ -13236,7 +13236,7 @@
         <v>172</v>
       </c>
       <c r="B144" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C144" t="s">
         <v>19</v>
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -13281,7 +13281,7 @@
         <v>17</v>
       </c>
       <c r="Q144" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>69000</v>
       </c>
       <c r="U144" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="V144">
         <v>0</v>
@@ -13304,7 +13304,7 @@
         <v>234</v>
       </c>
       <c r="B145" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C145" t="s">
         <v>19</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L145">
         <v>1</v>
@@ -13349,7 +13349,7 @@
         <v>17</v>
       </c>
       <c r="Q145" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>69000</v>
       </c>
       <c r="U145" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="V145">
         <v>0</v>
@@ -13372,7 +13372,7 @@
         <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C146" t="s">
         <v>19</v>
@@ -13399,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L146">
         <v>1</v>
@@ -13417,7 +13417,7 @@
         <v>17</v>
       </c>
       <c r="Q146" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>69000</v>
       </c>
       <c r="U146" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="V146">
         <v>0</v>
@@ -13440,7 +13440,7 @@
         <v>173</v>
       </c>
       <c r="B147" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C147" t="s">
         <v>19</v>
@@ -13455,37 +13455,37 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L147">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M147">
         <v>3</v>
       </c>
       <c r="N147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O147">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P147" t="s">
         <v>17</v>
       </c>
       <c r="Q147" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -13497,7 +13497,7 @@
         <v>69000</v>
       </c>
       <c r="U147" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="V147">
         <v>0</v>
@@ -13508,7 +13508,7 @@
         <v>113</v>
       </c>
       <c r="B148" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C148" t="s">
         <v>19</v>
@@ -13535,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L148">
         <v>23</v>
@@ -13553,7 +13553,7 @@
         <v>17</v>
       </c>
       <c r="Q148" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -13565,7 +13565,7 @@
         <v>69000</v>
       </c>
       <c r="U148" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="V148">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>161</v>
       </c>
       <c r="B149" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C149" t="s">
         <v>19</v>
@@ -13603,7 +13603,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L149">
         <v>11</v>
@@ -13612,7 +13612,7 @@
         <v>3</v>
       </c>
       <c r="N149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O149">
         <v>11</v>
@@ -13621,7 +13621,7 @@
         <v>17</v>
       </c>
       <c r="Q149" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -13633,7 +13633,7 @@
         <v>69000</v>
       </c>
       <c r="U149" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="V149">
         <v>0</v>
@@ -13644,7 +13644,7 @@
         <v>106</v>
       </c>
       <c r="B150" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C150" t="s">
         <v>19</v>
@@ -13671,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L150">
         <v>11</v>
@@ -13680,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="N150">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O150">
         <v>9</v>
@@ -13689,7 +13689,7 @@
         <v>17</v>
       </c>
       <c r="Q150" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -13701,7 +13701,7 @@
         <v>69000</v>
       </c>
       <c r="U150" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="V150">
         <v>0</v>
@@ -13712,7 +13712,7 @@
         <v>117</v>
       </c>
       <c r="B151" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C151" t="s">
         <v>19</v>
@@ -13727,22 +13727,22 @@
         <v>255</v>
       </c>
       <c r="G151">
+        <v>11</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>11</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151" t="s">
+        <v>283</v>
+      </c>
+      <c r="L151">
         <v>12</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>10</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151" t="s">
-        <v>282</v>
-      </c>
-      <c r="L151">
-        <v>11</v>
       </c>
       <c r="M151">
         <v>0</v>
@@ -13751,13 +13751,13 @@
         <v>7</v>
       </c>
       <c r="O151">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P151" t="s">
         <v>17</v>
       </c>
       <c r="Q151" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -13769,7 +13769,7 @@
         <v>69000</v>
       </c>
       <c r="U151" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="V151">
         <v>0</v>
@@ -13777,10 +13777,10 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B152" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C152" t="s">
         <v>249</v>
@@ -13807,7 +13807,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -13837,7 +13837,7 @@
         <v>0</v>
       </c>
       <c r="U152" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="V152">
         <v>0</v>
@@ -13845,10 +13845,10 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B153" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C153" t="s">
         <v>249</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -13905,7 +13905,7 @@
         <v>0</v>
       </c>
       <c r="U153" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="V153">
         <v>0</v>
@@ -13913,10 +13913,10 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B154" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C154" t="s">
         <v>249</v>
@@ -13943,7 +13943,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -13973,7 +13973,7 @@
         <v>0</v>
       </c>
       <c r="U154" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="V154">
         <v>0</v>
@@ -13981,10 +13981,10 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B155" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C155" t="s">
         <v>249</v>
@@ -14011,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -14041,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="U155" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="V155">
         <v>0</v>
@@ -14049,10 +14049,10 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B156" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C156" t="s">
         <v>249</v>
@@ -14079,7 +14079,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="U156" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="V156">
         <v>0</v>
@@ -14120,7 +14120,7 @@
         <v>257</v>
       </c>
       <c r="B157" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C157" t="s">
         <v>249</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L157">
         <v>1</v>
@@ -14177,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="U157" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="V157">
         <v>0</v>
@@ -14188,7 +14188,7 @@
         <v>256</v>
       </c>
       <c r="B158" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C158" t="s">
         <v>249</v>
@@ -14215,7 +14215,7 @@
         <v>1</v>
       </c>
       <c r="K158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L158">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         <v>0</v>
       </c>
       <c r="U158" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="V158">
         <v>0</v>
@@ -14253,10 +14253,10 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B159" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C159" t="s">
         <v>249</v>
@@ -14283,7 +14283,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -14313,7 +14313,7 @@
         <v>0</v>
       </c>
       <c r="U159" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="V159">
         <v>0</v>
@@ -14321,10 +14321,10 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B160" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C160" t="s">
         <v>249</v>
@@ -14351,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -14381,7 +14381,7 @@
         <v>0</v>
       </c>
       <c r="U160" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="V160">
         <v>0</v>
@@ -14389,10 +14389,10 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B161" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C161" t="s">
         <v>249</v>
@@ -14419,7 +14419,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="U161" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="V161">
         <v>0</v>
@@ -14460,7 +14460,7 @@
         <v>251</v>
       </c>
       <c r="B162" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C162" t="s">
         <v>249</v>
@@ -14487,7 +14487,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L162">
         <v>1</v>
@@ -14517,7 +14517,7 @@
         <v>0</v>
       </c>
       <c r="U162" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="V162">
         <v>0</v>
@@ -14525,10 +14525,10 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B163" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C163" t="s">
         <v>249</v>
@@ -14555,7 +14555,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -14585,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="U163" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="V163">
         <v>0</v>
@@ -14593,10 +14593,10 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B164" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C164" t="s">
         <v>249</v>
@@ -14623,7 +14623,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="U164" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="V164">
         <v>0</v>
@@ -14661,10 +14661,10 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B165" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C165" t="s">
         <v>249</v>
@@ -14691,7 +14691,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -14721,7 +14721,7 @@
         <v>0</v>
       </c>
       <c r="U165" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="V165">
         <v>0</v>
@@ -14729,10 +14729,10 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B166" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C166" t="s">
         <v>249</v>
@@ -14759,7 +14759,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -14789,7 +14789,7 @@
         <v>0</v>
       </c>
       <c r="U166" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="V166">
         <v>0</v>
@@ -14797,10 +14797,10 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B167" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C167" t="s">
         <v>249</v>
@@ -14827,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -14857,7 +14857,7 @@
         <v>0</v>
       </c>
       <c r="U167" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="V167">
         <v>0</v>
@@ -14865,10 +14865,10 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B168" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C168" t="s">
         <v>249</v>
@@ -14895,7 +14895,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -14925,7 +14925,7 @@
         <v>0</v>
       </c>
       <c r="U168" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="V168">
         <v>0</v>
@@ -14933,10 +14933,10 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B169" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C169" t="s">
         <v>249</v>
@@ -14963,7 +14963,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -14993,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="U169" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="V169">
         <v>0</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>720</v>
+        <v>265</v>
       </c>
       <c r="B170" t="s">
         <v>721</v>
@@ -15019,31 +15019,31 @@
         <v>250</v>
       </c>
       <c r="G170">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170">
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P170" t="s">
         <v>17</v>
@@ -15099,7 +15099,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -15167,7 +15167,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L172">
         <v>11</v>
@@ -15235,7 +15235,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L173">
         <v>12</v>
@@ -15244,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="N173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O173">
         <v>9</v>
@@ -15303,7 +15303,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L174">
         <v>7</v>
@@ -15359,22 +15359,22 @@
         <v>250</v>
       </c>
       <c r="G175">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H175">
         <v>0</v>
       </c>
       <c r="I175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J175">
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M175">
         <v>2</v>
@@ -15383,7 +15383,7 @@
         <v>3</v>
       </c>
       <c r="O175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P175" t="s">
         <v>17</v>
@@ -15439,7 +15439,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L176">
         <v>4</v>
@@ -15507,7 +15507,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L177">
         <v>4</v>
@@ -15516,7 +15516,7 @@
         <v>2</v>
       </c>
       <c r="N177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O177">
         <v>4</v>
@@ -15575,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L178">
         <v>5</v>
@@ -15643,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L179">
         <v>3</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L180">
         <v>5</v>
@@ -15779,7 +15779,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L181">
         <v>1</v>
@@ -15847,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L182">
         <v>12</v>
@@ -15856,7 +15856,7 @@
         <v>4</v>
       </c>
       <c r="N182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O182">
         <v>10</v>
@@ -15915,7 +15915,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L183">
         <v>10</v>
@@ -15983,7 +15983,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L184">
         <v>5</v>
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L185">
         <v>6</v>
@@ -16119,7 +16119,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -16187,7 +16187,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L187">
         <v>12</v>
@@ -16255,7 +16255,7 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L188">
         <v>15</v>
@@ -16323,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L189">
         <v>10</v>
@@ -16391,7 +16391,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L190">
         <v>9</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L191">
         <v>2</v>
@@ -16527,7 +16527,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L192">
         <v>16</v>
@@ -16595,7 +16595,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L193">
         <v>33</v>
@@ -16663,7 +16663,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L194">
         <v>30</v>
@@ -16731,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L195">
         <v>20</v>
@@ -16799,7 +16799,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L196">
         <v>10</v>
@@ -16867,7 +16867,7 @@
         <v>1</v>
       </c>
       <c r="K197" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L197">
         <v>2</v>
@@ -16935,7 +16935,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L198">
         <v>9</v>
@@ -17003,7 +17003,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L199">
         <v>6</v>
@@ -17071,7 +17071,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -17139,7 +17139,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -17207,7 +17207,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L202">
         <v>1</v>
@@ -17275,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -17343,7 +17343,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L204">
         <v>2</v>
@@ -17411,7 +17411,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L205">
         <v>4</v>
@@ -17479,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -17547,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -17615,7 +17615,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -17683,7 +17683,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L210">
         <v>6</v>
@@ -17819,7 +17819,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L211">
         <v>2</v>
@@ -17887,7 +17887,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -17955,7 +17955,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L213">
         <v>3</v>
@@ -18023,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L214">
         <v>2</v>
@@ -18091,7 +18091,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -18159,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L216">
         <v>1</v>
@@ -18227,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L217">
         <v>10</v>
@@ -18295,7 +18295,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L218">
         <v>7</v>
@@ -18363,7 +18363,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L219">
         <v>9</v>
@@ -18431,7 +18431,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L220">
         <v>6</v>
@@ -18499,7 +18499,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L221">
         <v>3</v>
@@ -18567,7 +18567,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L222">
         <v>3</v>
@@ -18623,31 +18623,31 @@
         <v>240</v>
       </c>
       <c r="G223">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="L223">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M223">
         <v>8</v>
       </c>
       <c r="N223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P223" t="s">
         <v>17</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K224" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L224">
         <v>23</v>
@@ -18771,7 +18771,7 @@
         <v>4</v>
       </c>
       <c r="K225" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L225">
         <v>17</v>
@@ -18780,7 +18780,7 @@
         <v>8</v>
       </c>
       <c r="N225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O225">
         <v>11</v>
@@ -18839,7 +18839,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -18907,7 +18907,7 @@
         <v>8</v>
       </c>
       <c r="K227" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L227">
         <v>25</v>
@@ -18916,7 +18916,7 @@
         <v>12</v>
       </c>
       <c r="N227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O227">
         <v>20</v>
@@ -18975,7 +18975,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L228">
         <v>28</v>
@@ -18984,7 +18984,7 @@
         <v>12</v>
       </c>
       <c r="N228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O228">
         <v>19</v>
@@ -19043,7 +19043,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L229">
         <v>17</v>
@@ -19111,7 +19111,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L230">
         <v>11</v>
@@ -19179,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L231">
         <v>2</v>
@@ -19244,7 +19244,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L232">
         <v>16</v>
@@ -19291,31 +19291,31 @@
         <v>123</v>
       </c>
       <c r="G233">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J233">
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L233">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M233">
         <v>1</v>
       </c>
       <c r="N233">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O233">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P233" t="s">
         <v>124</v>
@@ -19362,7 +19362,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L234">
         <v>6</v>
@@ -19421,7 +19421,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L235">
         <v>11</v>
@@ -19468,31 +19468,31 @@
         <v>123</v>
       </c>
       <c r="G236">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H236">
         <v>0</v>
       </c>
       <c r="I236">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J236">
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L236">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M236">
         <v>0</v>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O236">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P236" t="s">
         <v>124</v>
@@ -19539,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L237">
         <v>7</v>
@@ -19586,31 +19586,31 @@
         <v>123</v>
       </c>
       <c r="G238">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H238">
         <v>0</v>
       </c>
       <c r="I238">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J238">
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L238">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M238">
         <v>1</v>
       </c>
       <c r="N238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O238">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P238" t="s">
         <v>124</v>
@@ -19657,7 +19657,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L239">
         <v>5</v>
@@ -19716,7 +19716,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L240">
         <v>5</v>
@@ -19775,7 +19775,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L241">
         <v>12</v>
@@ -19834,7 +19834,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L242">
         <v>20</v>
@@ -19893,7 +19893,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L243">
         <v>2</v>
@@ -19952,7 +19952,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L244">
         <v>14</v>
@@ -20011,7 +20011,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L245">
         <v>19</v>
@@ -20070,7 +20070,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L246">
         <v>9</v>
@@ -20129,7 +20129,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L247">
         <v>15</v>
@@ -20188,7 +20188,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L248">
         <v>5</v>
@@ -20247,7 +20247,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L249">
         <v>9</v>
@@ -20294,31 +20294,31 @@
         <v>123</v>
       </c>
       <c r="G250">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J250">
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L250">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M250">
         <v>1</v>
       </c>
       <c r="N250">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O250">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P250" t="s">
         <v>124</v>
@@ -20365,7 +20365,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L251">
         <v>13</v>
@@ -20424,7 +20424,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L252">
         <v>11</v>
@@ -20433,7 +20433,7 @@
         <v>1</v>
       </c>
       <c r="N252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O252">
         <v>11</v>
@@ -20483,7 +20483,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L253">
         <v>32</v>
@@ -20542,7 +20542,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L254">
         <v>16</v>
@@ -20589,31 +20589,31 @@
         <v>123</v>
       </c>
       <c r="G255">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H255">
         <v>0</v>
       </c>
       <c r="I255">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J255">
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L255">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M255">
         <v>0</v>
       </c>
       <c r="N255">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O255">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P255" t="s">
         <v>124</v>
@@ -20660,7 +20660,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L256">
         <v>13</v>
@@ -20719,7 +20719,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L257">
         <v>4</v>
@@ -20778,7 +20778,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L258">
         <v>11</v>
@@ -20837,7 +20837,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L259">
         <v>12</v>
@@ -20887,28 +20887,28 @@
         <v>194</v>
       </c>
       <c r="G260">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="I260">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J260">
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L260">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M260">
         <v>0</v>
       </c>
       <c r="N260">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O260">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P260" t="s">
         <v>182</v>
@@ -20943,28 +20943,28 @@
         <v>181</v>
       </c>
       <c r="G261">
-        <v>1973</v>
+        <v>1956</v>
       </c>
       <c r="I261">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J261">
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L261">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="M261">
         <v>0</v>
       </c>
       <c r="N261">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="O261">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="P261" t="s">
         <v>182</v>
@@ -20999,28 +20999,28 @@
         <v>191</v>
       </c>
       <c r="G262">
-        <v>5948</v>
+        <v>5939</v>
       </c>
       <c r="I262">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J262">
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L262">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M262">
         <v>0</v>
       </c>
       <c r="N262">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O262">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="P262" t="s">
         <v>182</v>
@@ -21055,28 +21055,28 @@
         <v>193</v>
       </c>
       <c r="G263">
-        <v>1915</v>
+        <v>1909</v>
       </c>
       <c r="I263">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J263">
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L263">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M263">
         <v>4</v>
       </c>
       <c r="N263">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O263">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P263" t="s">
         <v>182</v>
@@ -21117,7 +21117,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L264">
         <v>1</v>
@@ -21167,7 +21167,7 @@
         <v>0</v>
       </c>
       <c r="K265" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L265">
         <v>1</v>
@@ -21217,7 +21217,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L266">
         <v>1</v>
@@ -21264,7 +21264,7 @@
         <v>0</v>
       </c>
       <c r="K267" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L267">
         <v>1</v>
@@ -21311,7 +21311,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L268">
         <v>1</v>
@@ -21358,7 +21358,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L269">
         <v>1</v>
@@ -21405,7 +21405,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L270">
         <v>1</v>
@@ -21452,7 +21452,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L271">
         <v>1</v>
@@ -21496,7 +21496,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -21584,7 +21584,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -21628,7 +21628,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -21672,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -21716,7 +21716,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -21760,7 +21760,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -21848,7 +21848,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -21892,7 +21892,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -21936,7 +21936,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -21980,7 +21980,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -22024,7 +22024,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L284">
         <v>0</v>
@@ -22068,7 +22068,7 @@
         <v>0</v>
       </c>
       <c r="K285" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L285">
         <v>0</v>
@@ -22112,7 +22112,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L286">
         <v>0</v>
@@ -22156,7 +22156,7 @@
         <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L287">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L288">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L289">
         <v>0</v>
@@ -22288,7 +22288,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L290">
         <v>0</v>
@@ -22332,7 +22332,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L291">
         <v>0</v>
@@ -22376,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L292">
         <v>0</v>
@@ -22420,7 +22420,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L293">
         <v>0</v>
@@ -22464,7 +22464,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L294">
         <v>0</v>
@@ -22508,7 +22508,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L295">
         <v>0</v>
@@ -22552,7 +22552,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L296">
         <v>0</v>
@@ -22596,7 +22596,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L297">
         <v>0</v>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L298">
         <v>0</v>
@@ -22684,7 +22684,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L299">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L300">
         <v>0</v>
@@ -22772,7 +22772,7 @@
         <v>0</v>
       </c>
       <c r="K301" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L301">
         <v>0</v>
@@ -22816,7 +22816,7 @@
         <v>0</v>
       </c>
       <c r="K302" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L302">
         <v>0</v>
@@ -22860,7 +22860,7 @@
         <v>0</v>
       </c>
       <c r="K303" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L303">
         <v>0</v>
@@ -22904,7 +22904,7 @@
         <v>0</v>
       </c>
       <c r="K304" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L304">
         <v>0</v>
@@ -22948,7 +22948,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L305">
         <v>0</v>
@@ -22992,7 +22992,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L306">
         <v>0</v>
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L307">
         <v>0</v>
@@ -23080,7 +23080,7 @@
         <v>0</v>
       </c>
       <c r="K308" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L308">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>0</v>
       </c>
       <c r="K309" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L309">
         <v>0</v>
@@ -23168,7 +23168,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L310">
         <v>0</v>
@@ -23212,7 +23212,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L311">
         <v>0</v>
@@ -23256,7 +23256,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L312">
         <v>0</v>
@@ -23300,7 +23300,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L313">
         <v>0</v>
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L314">
         <v>0</v>
@@ -23388,7 +23388,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L315">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L316">
         <v>0</v>
@@ -23476,7 +23476,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L317">
         <v>0</v>
@@ -23520,7 +23520,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L318">
         <v>0</v>
@@ -23564,7 +23564,7 @@
         <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L319">
         <v>0</v>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L320">
         <v>0</v>
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L321">
         <v>0</v>
@@ -23696,7 +23696,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L322">
         <v>0</v>
@@ -23740,7 +23740,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L323">
         <v>0</v>
@@ -23784,7 +23784,7 @@
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L324">
         <v>0</v>
@@ -23828,7 +23828,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L325">
         <v>0</v>
@@ -23872,7 +23872,7 @@
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L326">
         <v>0</v>
@@ -23916,7 +23916,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L327">
         <v>0</v>
@@ -23960,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L328">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L329">
         <v>0</v>
@@ -24048,7 +24048,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L330">
         <v>0</v>
@@ -24092,7 +24092,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L331">
         <v>0</v>
@@ -24136,7 +24136,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L332">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L333">
         <v>0</v>
@@ -24224,7 +24224,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L334">
         <v>0</v>
@@ -24268,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L335">
         <v>0</v>
@@ -24312,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L336">
         <v>0</v>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L337">
         <v>0</v>
@@ -24400,7 +24400,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L338">
         <v>0</v>
@@ -24444,7 +24444,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L339">
         <v>0</v>
@@ -24488,7 +24488,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L340">
         <v>0</v>
@@ -24532,7 +24532,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L341">
         <v>0</v>
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="K342" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L342">
         <v>0</v>
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L343">
         <v>0</v>
@@ -24664,7 +24664,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L344">
         <v>0</v>
@@ -24692,8 +24692,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800A25F-3B69-4336-8B5A-3BA0F6383161}">
-  <dimension ref="A1:K1260"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAC31B6-36A2-4375-9C91-A16B35C290D0}">
+  <dimension ref="A1:K1283"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -68794,6 +68794,811 @@
       </c>
       <c r="K1260">
         <v>42900</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1261" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1261" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1261" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1261">
+        <v>3</v>
+      </c>
+      <c r="J1261" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1261">
+        <v>20700</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1262" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1262" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1262" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1262">
+        <v>17</v>
+      </c>
+      <c r="J1262" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1262">
+        <v>142800</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1263" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1263" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1263">
+        <v>9</v>
+      </c>
+      <c r="J1263" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1263">
+        <v>89100</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1264" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1264" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1264">
+        <v>6</v>
+      </c>
+      <c r="J1264" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1264">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1265" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1265">
+        <v>0</v>
+      </c>
+      <c r="H1265" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1265">
+        <v>1</v>
+      </c>
+      <c r="J1265" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1265">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1266" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1266">
+        <v>0</v>
+      </c>
+      <c r="H1266" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1266">
+        <v>3</v>
+      </c>
+      <c r="J1266" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1266">
+        <v>119700</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1267" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1267">
+        <v>0</v>
+      </c>
+      <c r="H1267" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1267">
+        <v>3</v>
+      </c>
+      <c r="J1267" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1267">
+        <v>128700</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1268" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1268">
+        <v>0</v>
+      </c>
+      <c r="H1268" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1268">
+        <v>1</v>
+      </c>
+      <c r="J1268" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1268">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1269" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1269" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1269">
+        <v>250</v>
+      </c>
+      <c r="H1269" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1269">
+        <v>1</v>
+      </c>
+      <c r="J1269" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1270" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1270" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1270">
+        <v>240</v>
+      </c>
+      <c r="H1270" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1270">
+        <v>1</v>
+      </c>
+      <c r="J1270" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1270">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1271" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1271">
+        <v>240</v>
+      </c>
+      <c r="H1271" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1271">
+        <v>1</v>
+      </c>
+      <c r="J1271" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1271">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1272" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1272">
+        <v>250</v>
+      </c>
+      <c r="H1272" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1272">
+        <v>1</v>
+      </c>
+      <c r="J1272" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1272">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1273" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1273">
+        <v>250</v>
+      </c>
+      <c r="H1273" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1273">
+        <v>1</v>
+      </c>
+      <c r="J1273" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1273">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1274" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1274">
+        <v>235</v>
+      </c>
+      <c r="H1274" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1274">
+        <v>1</v>
+      </c>
+      <c r="J1274" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1274">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1275" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1275">
+        <v>255</v>
+      </c>
+      <c r="H1275" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1275">
+        <v>1</v>
+      </c>
+      <c r="J1275" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1275">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1276" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1276">
+        <v>260</v>
+      </c>
+      <c r="H1276" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1276">
+        <v>1</v>
+      </c>
+      <c r="J1276" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1276">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1277" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1277">
+        <v>250</v>
+      </c>
+      <c r="H1277" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1277">
+        <v>1</v>
+      </c>
+      <c r="J1277" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1277">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1278" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1278">
+        <v>245</v>
+      </c>
+      <c r="H1278" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1278">
+        <v>1</v>
+      </c>
+      <c r="J1278" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1278">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1279" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1279" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1279">
+        <v>245</v>
+      </c>
+      <c r="H1279" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1279">
+        <v>1</v>
+      </c>
+      <c r="J1279" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1279">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1280" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1280" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1280">
+        <v>235</v>
+      </c>
+      <c r="H1280" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1280">
+        <v>1</v>
+      </c>
+      <c r="J1280" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1280">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1281" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1281" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1281">
+        <v>265</v>
+      </c>
+      <c r="H1281" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1281">
+        <v>1</v>
+      </c>
+      <c r="J1281" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1281">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1282" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1282" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1282">
+        <v>270</v>
+      </c>
+      <c r="H1282" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1282">
+        <v>1</v>
+      </c>
+      <c r="J1282" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1282">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1283" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1283" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1283">
+        <v>0</v>
+      </c>
+      <c r="H1283" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1283">
+        <v>1</v>
+      </c>
+      <c r="J1283" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1283">
+        <v>35900</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5688D50F-FAA6-4BA4-BD08-3A609C9C0A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DAE50FA-DA87-48A7-99CD-2526A4CDD2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{A493FDF1-50B2-45AB-B2C2-7BDBC64634AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{D11318CC-187B-4384-B14C-597319100051}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12057" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12183" uniqueCount="1093">
   <si>
     <t>날짜</t>
   </si>
@@ -915,7 +915,7 @@
     <t>정상</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ed60ec093ce86cf1be9ab7d6a21dccad.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/1efc4f23c48af75a7ddba48c413c1a80.jpg</t>
   </si>
   <si>
     <t>U-BJM946-120041</t>
@@ -948,7 +948,7 @@
     <t>BJM946NV 바오지 남성 데일리화 네이비 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ccea15f086483595f221192f06cf1d08.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/5500ad5711a08c68d5a74e04f265c442.jpg</t>
   </si>
   <si>
     <t>U-BJM946-180041</t>
@@ -984,6 +984,9 @@
     <t>BJM1133NV 바오지 남성 배드민턴화 네이비 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/e9422c34b90f865e4e5c66938e2ac580.jpg</t>
+  </si>
+  <si>
     <t>U-BJM1133-180041</t>
   </si>
   <si>
@@ -1029,6 +1032,9 @@
     <t>BJM1133WHDB 바오지 남성 배드민턴화 화이트딥블루 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/e6bd42a96692d710f84a765bbd2cc894.jpg</t>
+  </si>
+  <si>
     <t>U-BJM1133-132241</t>
   </si>
   <si>
@@ -1065,6 +1071,9 @@
     <t>BJM1133WHGY 바오지 남성 배드민턴화 화이트그레이 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/424e418e8e9d2ec22079e68941402bcc.jpg</t>
+  </si>
+  <si>
     <t>U-BJM1133-132341</t>
   </si>
   <si>
@@ -1104,6 +1113,9 @@
     <t>BJM1133WHRD 바오지 남성 배드민턴화 화이트레드 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/ac3dcc9f691a2d693abecdf3e1555691.jpg</t>
+  </si>
+  <si>
     <t>U-BJM1133-131541</t>
   </si>
   <si>
@@ -1143,6 +1155,9 @@
     <t>BJM845OR 바오지 남성 배드민턴화 오렌지 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/5d3d2e3ec680243a8e434f38c1676330.jpg</t>
+  </si>
+  <si>
     <t>U-BJM845-240041</t>
   </si>
   <si>
@@ -1188,6 +1203,9 @@
     <t>BJM845RD 바오지 남성 배드민턴화 레드 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/07d660af5d39c6d09ee54acb05ed8ead.jpg</t>
+  </si>
+  <si>
     <t>U-BJM845-150041</t>
   </si>
   <si>
@@ -1230,6 +1248,9 @@
     <t>BJM845DBL 바오지 남성 배드민턴화 딥블루 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/fb7a2f8e59b1ec0cf5b471771806047b.jpg</t>
+  </si>
+  <si>
     <t>U-BJM845-220041</t>
   </si>
   <si>
@@ -1275,6 +1296,9 @@
     <t>BJM845WHNV 바오지 남성 배드민턴화 화이트네이비 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/4715a703918cb5fc87825282375f06c8.jpg</t>
+  </si>
+  <si>
     <t>U-BJM845-131841</t>
   </si>
   <si>
@@ -1323,6 +1347,9 @@
     <t>BJM943</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/68d35db609de240e485588c370a087ff.jpg</t>
+  </si>
+  <si>
     <t>U-BJM943-220041</t>
   </si>
   <si>
@@ -1368,6 +1395,9 @@
     <t>BJM943ORRD 바오지 남성 배드민턴화 오렌지레드 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/5b2614bf5ab0fb5fdaa68677f6dd2473.jpg</t>
+  </si>
+  <si>
     <t>U-BJM943-241541</t>
   </si>
   <si>
@@ -1413,6 +1443,9 @@
     <t>BJM943RDWH 바오지 남성 배드민턴화 레드화이트 260</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/7c05705056b3cd58692a47b84c329633.jpg</t>
+  </si>
+  <si>
     <t>U-BJM943-151341</t>
   </si>
   <si>
@@ -1455,7 +1488,7 @@
     <t>BJM898GNBK 바오지 남성 기능화 그린블랙 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/43ad30e6dfa6829e2e9197096e51ddbc.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260508/236c84aa0218c2bb59ba5ae921718652.jpg</t>
   </si>
   <si>
     <t>U-BJM898-261241</t>
@@ -1491,7 +1524,7 @@
     <t>BJM931WHGN 바오지 남성 러닝화 화이트그린 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/202cd5f60e9b6aefbdcdb821150f0847.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260508/4f1a9f787f8ab49427ba485b27cdd0b8.jpg</t>
   </si>
   <si>
     <t>U-BJM931-132641</t>
@@ -1524,7 +1557,7 @@
     <t>BJM931BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/d591f0085a95e682f634c5a2e7c3181c.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260508/20f0d1631c1ba274f454e3744f4570bb.jpg</t>
   </si>
   <si>
     <t>U-BJM931-120041</t>
@@ -1563,7 +1596,7 @@
     <t>BJM931GYOR 바오지 남성 러닝화 그레이오렌지 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260508/84fef7d7356edf7395a30196bcb089fb.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260508/929a59a7b3e834f6a1d80e83ee1996f2.jpg</t>
   </si>
   <si>
     <t>U-BJM931-232441</t>
@@ -1605,7 +1638,7 @@
     <t>DPM641APGY 바오지 남성 러닝화 살구그레이 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/97a7c69842b4c63abef188facb775e4f.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/7890accc94172c0aa71b646efcb53446.jpg</t>
   </si>
   <si>
     <t>U-DPM641-142341</t>
@@ -1644,7 +1677,7 @@
     <t>DPM641WHOR 바오지 남성 러닝화 화이트오렌지 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/2fb441bfd755361bb19ba77de2bee0eb.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/4033ef1a63ca16479d547e1111d8600e.jpg</t>
   </si>
   <si>
     <t>U-DPM641-132441</t>
@@ -1683,7 +1716,7 @@
     <t>DPM644APCO 바오지 남성 러닝화 살구커피 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/1003a283213e42fbe9e16752fcc3c555.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/547899f7c84c1d3db7a316388aea3b5b.jpg</t>
   </si>
   <si>
     <t>U-DPM644-141641</t>
@@ -1722,7 +1755,7 @@
     <t>DPM644BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/42d5aa739d3370e66e2d8d12d782c91f.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/585f2f523a109913035d9594a4f07542.jpg</t>
   </si>
   <si>
     <t>U-DPM644-120041</t>
@@ -1761,7 +1794,7 @@
     <t>DPM644GY 바오지 남성 러닝화 그레이 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/1dfc43085ae67e133658c892b5be798c.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/33ae257330ad59add6838c0f87b16e1a.jpg</t>
   </si>
   <si>
     <t>U-DPM644-230041</t>
@@ -1800,7 +1833,7 @@
     <t>DPM647BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/29c3aba06cac20436d2a9481f20bbad1.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/342a5147ed63968bbec1394bae307411.jpg</t>
   </si>
   <si>
     <t>U-DPM647-120041</t>
@@ -1833,7 +1866,7 @@
     <t>DPM647GY 바오지 남성 러닝화 그레이 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/5cf5621395426e457cc806b96bf53033.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/22f955ce9d961d940a4b0828872eb2f0.jpg</t>
   </si>
   <si>
     <t>U-DPM647-230041</t>
@@ -1866,7 +1899,7 @@
     <t>DPM647WHGN 바오지 남성 러닝화 화이트그린 260</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/f8c179a789e8e0012ab7e17ef5146546.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/6692af4ccbbe44fc71aa751db2cf3a2b.jpg</t>
   </si>
   <si>
     <t>U-DPM647-132641</t>
@@ -1899,7 +1932,7 @@
     <t>BJW1090PK 바오지 여성 데일리화 핑크 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/0bdbdba1a835ef083473109fd9b5acba.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/59bb21dc2bf0fbddd6319aafabf3f71a.jpg</t>
   </si>
   <si>
     <t>U-BJW1090-250037</t>
@@ -1932,7 +1965,7 @@
     <t>BJW1090WH 바오지 여성 데일리화 화이트 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/2b72ca06ab6cf20c097ea9cfeb1af19e.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/a9229d232d93e8a663c1411b7bf4658a.jpg</t>
   </si>
   <si>
     <t>U-BJW1090-130037</t>
@@ -1965,7 +1998,7 @@
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/620fa2b989fb7b735c6460f8db0f7193.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/58a6b88b1d7f31c29f725fa70257826d.jpg</t>
   </si>
   <si>
     <t>U-BJW1179-123037</t>
@@ -1998,7 +2031,7 @@
     <t>BJW1179GDWH 바오지 여성 데일리화 골드화이트 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/7d0830bae29f3498109786ad117520e8.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/9591d8e44d0cf50eaca7b97c70b95e9a.jpg</t>
   </si>
   <si>
     <t>U-BJW1179-291337</t>
@@ -2031,7 +2064,7 @@
     <t>BJW1179GY 바오지 여성 데일리화 그레이 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/12a6c4024daa1596ee483d4862903d60.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/73d5f8b6452a15158dd37d825c51f36e.jpg</t>
   </si>
   <si>
     <t>U-BJW1179-230037</t>
@@ -2067,6 +2100,9 @@
     <t>BJW1133NV 바오지 여성 배드민턴화 네이비 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/b9428d7323bf9653261d4a385786b139.jpg</t>
+  </si>
+  <si>
     <t>U-BJW1133-180037</t>
   </si>
   <si>
@@ -2109,6 +2145,9 @@
     <t>BJW1133WHGY 바오지 여성 배드민턴화 화이트그레이 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/2d999094f258518d4236c1ede6c3f995.jpg</t>
+  </si>
+  <si>
     <t>U-BJW1133-132337</t>
   </si>
   <si>
@@ -2148,6 +2187,9 @@
     <t>BJW1133WHLB 바오지 여성 배드민턴화 화이트연블루 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/f745d55054d0186c1ae4587e68795ae3.jpg</t>
+  </si>
+  <si>
     <t>U-BJW1133-131937</t>
   </si>
   <si>
@@ -2190,6 +2232,9 @@
     <t>BJW1133WHRO 바오지 여성 배드민턴화 화이트로즈 235</t>
   </si>
   <si>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260824/3a363c00c19972c91df5c908b1982dea.jpg</t>
+  </si>
+  <si>
     <t>U-BJW1133-133137</t>
   </si>
   <si>
@@ -2226,7 +2271,7 @@
     <t>BJW1170APPU 바오지 여성 러닝화 살구퍼플 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ded5fe5f89146731f189af9a78a1c34f.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/4680474a2d32f26f5fa61fdb8ef1a1ec.jpg</t>
   </si>
   <si>
     <t>U-BJW1170-142737</t>
@@ -2259,7 +2304,7 @@
     <t>BJW1170BKSL 바오지 여성 러닝화 블랙실버 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/6947c2358efbd9544338290c72785d21.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/a0ee1226a76d4f8cd2e51adf60d874df.jpg</t>
   </si>
   <si>
     <t>U-BJW1170-123037</t>
@@ -2292,7 +2337,7 @@
     <t>BJW1170SLAP 바오지 여성 러닝화 실버살구 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/a9e2643d92235d24aa5d0935b68b8ce3.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/49f4d153913f51feb059b9e22b76c33b.jpg</t>
   </si>
   <si>
     <t>U-BJW1170-301437</t>
@@ -2325,7 +2370,7 @@
     <t>DPW770AP 바오지 여성 러닝화 살구색 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/ff3edade5789b88dba27e58f0944169f.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/187ddf25b06a1c6bce15949f8c1d3d9f.jpg</t>
   </si>
   <si>
     <t>U-DPW770-140037</t>
@@ -2358,7 +2403,7 @@
     <t>DPW770BK 바오지 여성 러닝화 블랙 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/2bbe2bf75567d644f2750688699c32c8.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/4002aa39833c060fd5a7cfad76b75d34.jpg</t>
   </si>
   <si>
     <t>U-DPW770-120037</t>
@@ -2391,7 +2436,7 @@
     <t>DPW770PK 바오지 여성 러닝화 핑크 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/4a9e9eefa715a7f595a6e88108550bd0.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/8d9b3ae8aea890773765f11f018a15f1.jpg</t>
   </si>
   <si>
     <t>U-DPW770-250037</t>
@@ -2427,7 +2472,7 @@
     <t>DPW771AP 바오지 여성 러닝화 살구색 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/dc33a9225d366e06d103fce2d7323dfb.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/b5fd641d934d50aac3dbbd4b8d89cec0.jpg</t>
   </si>
   <si>
     <t>U-DPW771-140037</t>
@@ -2463,7 +2508,7 @@
     <t>DPW771BK 바오지 여성 러닝화 블랙 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/fc7ca9ac124b00497e04f2f57b93b418.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/b990f51bc42b2bcf9d1de0bf2e6ce91a.jpg</t>
   </si>
   <si>
     <t>U-DPW771-120037</t>
@@ -2502,7 +2547,7 @@
     <t>DPW771LBL 바오지 여성 러닝화 연블루 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/9e874b053bcd998829e1022dcc741b05.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/a1876503cd6888bb0ff60fd6b7bc0ba8.jpg</t>
   </si>
   <si>
     <t>U-DPW771-190037</t>
@@ -2535,7 +2580,7 @@
     <t>ECW304BK 바오지 여성 러닝화 블랙 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/f14b3d8b9788081c9a2818d0240e9afd.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/cb74ebdae15978e91de264e3646c335f.jpg</t>
   </si>
   <si>
     <t>U-ECW304-120037</t>
@@ -2568,7 +2613,7 @@
     <t>ECW304WHLB 바오지 여성 러닝화 화이트연블루 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/7b1a3261a7072d73059e3bd136f32308.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/2b9e911557a288c100ecb774ccc6c2bf.jpg</t>
   </si>
   <si>
     <t>U-ECW304-131937</t>
@@ -2601,7 +2646,7 @@
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 235</t>
   </si>
   <si>
-    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/4cd2c11a8558ddc90574b8e9d521c30b.jpg</t>
+    <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/small/20260511/8b98fda8a19bc2e17d607900f838a782.jpg</t>
   </si>
   <si>
     <t>U-ECW304-132537</t>
@@ -2631,24 +2676,126 @@
     <t>U-ECW304-132541</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/b13ebe10a75eb72cbd176fd22d01df92.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/big/202607/f03c4d3eecac8598e9a94cbb8a5b9efb.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/f7e9f1a91588dd4707f6e6c277768157.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/3f00a18c2bdc72fd27a213d9e04c7671.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/5f66942aa9dcec57730c5a243396b5fc.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/48791b0250f8cdc30a6f3cf9ecd3b17a.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/1f51ad007dfb2a00ca0ed50ddca75ff6.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/a65a51aec843470c7d431e28b974dd39.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/c94cb4db7099fb0275f7272b7c008c20.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/642a2f8220376120934732546bd7c8c0.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/dd9f76d594fc152d7b850542f5447955.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/big/202607/5bc759f63e3221445b0badc20d6a2fc0.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/71000f231eef10f7204350a3f29d6e1d.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/c2c5015133f6a9af7521f463f1c92f44.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/big/202607/f446282c93d0604b95f3de878ef79dda.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/5df7d2d1866622f8a74e075e757cdae9.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/6fd2bc03ae444ecfee90290b8241bf35.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/ac3fb9ab1f237944bbdbae2ebdcbb60c.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/9393ac4427dd761266f87b4fbd2f72da.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/dcb1ae80b2d1cb9e8a3eee3cea3dc87e.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/big/202607/c6190cfc915c686bf13bc27d264e7f20.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/5163aba01c35d8e3718d761dc797ef7f.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/3069a1daa0e2127d52c02347fa38f743.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/3c7ea2e22333a52ee8073113468e779c.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/b28b73df2a2bffb4d989dd208b0b82fa.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/24c294f3d16fe1056f8b192e2a83c3bd.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202607/0b92ab1dc963b7c063d992b7085c67d6.jpg</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/big/202607/1cb89489d53889f643f581f0016a4a8d.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 클리어겔 롤형 테이프 1m</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202607/b5e8b47627891bee80c077452ca0fff4.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 클리어겔 롤형 테이프 1.5m</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202607/86a3d03b20db0229b05c2daf5fcc7a12.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 클리어겔 롤형 테이프 3m</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202607/a5159ce34cde057bba387435d17d0020.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 클리어겔 원형 스티커</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202607/d91619dfcb8b61b59b4175d4a637d9d8.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 실리콘 자석 거치대 블랙</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202609/19869e70fbf514d4e67973c9ffa663f6.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 실리콘 자석 거치대 그레이</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202609/7082d88f0fd288335b9de702a2c6da66.jpg</t>
+  </si>
+  <si>
     <t>볼트겔 흡착 실리콘 부착패드 24 핑크</t>
   </si>
   <si>
@@ -2694,10 +2841,16 @@
     <t>뷰엔아미고 49%</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/big/202608/d7895ca785b55efcaaebc4c5aba63c3b.jpg</t>
+  </si>
+  <si>
     <t>BUAG-112020</t>
   </si>
   <si>
-    <t>뷰엔아미고 경량 타프 330 스카이</t>
+    <t>뷰엔아미고 경량 타프 330 탄</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202609/6b55ed98ced519f7a02d83efb3d4a51b.jpg</t>
   </si>
   <si>
     <t>BUAG-112030</t>
@@ -2706,6 +2859,9 @@
     <t>뷰엔아미고 경량 타프 330 네이비</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/0088afae2d5ede2f5163e9c59b86b2be.jpg</t>
+  </si>
+  <si>
     <t>BUAG-121012</t>
   </si>
   <si>
@@ -2715,42 +2871,63 @@
     <t>텐트</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202608/d6903de8faf9fe0bcf53ac6962759ecf.jpg</t>
+  </si>
+  <si>
     <t>BUAG-121022</t>
   </si>
   <si>
     <t>뷰엔아미고 오토 텐트 4 그레이</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/b8d040c5db8fcf1cbc3886712bce6209.jpg</t>
+  </si>
+  <si>
     <t>BUAG-121032</t>
   </si>
   <si>
     <t>뷰엔아미고 오토 텐트 4 블랙</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/3b1df62aa6373bbfc4cb8aff6b7143be.jpg</t>
+  </si>
+  <si>
     <t>BUAG-131012</t>
   </si>
   <si>
     <t>뷰엔아미고 팝업 텐트 3P 오렌지</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/1cee831ea3795a775140f6baedfb6085.jpg</t>
+  </si>
+  <si>
     <t>BUAG-131022</t>
   </si>
   <si>
     <t>뷰엔아미고 팝업 텐트 3P 라이트베이지</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202609/129325e51b4c0a7b9308f08f78c222e7.jpg</t>
+  </si>
+  <si>
     <t>BUAG-131032</t>
   </si>
   <si>
     <t>뷰엔아미고 팝업 텐트 3P 카키</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/5faa53973c2f0a235faa951c8a38f7be.jpg</t>
+  </si>
+  <si>
     <t>BUAG-131042</t>
   </si>
   <si>
     <t>뷰엔아미고 팝업 텐트 3P 라이트그레이</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/2501061472783ded849a645f1a8f22be.jpg</t>
+  </si>
+  <si>
     <t>BUAG-131052</t>
   </si>
   <si>
@@ -2763,6 +2940,9 @@
     <t>뷰엔아미고 백패킹 하이커 2P 오렌지</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202608/e5b3963da5ae277ee193245a33d0e953.jpg</t>
+  </si>
+  <si>
     <t>BUAG-151011</t>
   </si>
   <si>
@@ -2778,18 +2958,27 @@
     <t>애견텐트 P 레드 S</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/66840064ba7551ae92d1da8a09f9ef4f.jpg</t>
+  </si>
+  <si>
     <t>BUAG-151031</t>
   </si>
   <si>
     <t>애견텐트 P 라임 S</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202608/f572abe28dcc14228d7dd27c14d11213.jpg</t>
+  </si>
+  <si>
     <t>BUAG-151012</t>
   </si>
   <si>
     <t>애견텐트 P 오렌지 M</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/373fb4faf7d2be2987f178e41b456092.jpg</t>
+  </si>
+  <si>
     <t>BUAG-151022</t>
   </si>
   <si>
@@ -2808,12 +2997,18 @@
     <t>애견텐트 P 다크브라운 M</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202608/c8261dc0878da00ae4f87d32100ad707.jpg</t>
+  </si>
+  <si>
     <t>BUAG-151052</t>
   </si>
   <si>
     <t>애견텐트 P 브라운 M</t>
   </si>
   <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/9babeca900a539bd3c00359b649e3f7e.jpg</t>
+  </si>
+  <si>
     <t>BUAG-151013</t>
   </si>
   <si>
@@ -2836,6 +3031,9 @@
   </si>
   <si>
     <t>애견텐트 P 카키 L</t>
+  </si>
+  <si>
+    <t>https://idoogenkorea.cafe24.com/web/product/small/202608/21813b1588993306777bb07ce651de86.jpg</t>
   </si>
   <si>
     <t>BUAG-163010</t>
@@ -3506,7 +3704,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B616BFE8-4456-4EB6-838F-FD895AD81B70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFCDFA-D993-4FA1-A980-3BBB4678E1B8}">
   <dimension ref="A1:V344"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4307,8 +4505,8 @@
       <c r="P12" t="s">
         <v>17</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
+      <c r="Q12" t="s">
+        <v>314</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -4320,7 +4518,7 @@
         <v>79000</v>
       </c>
       <c r="U12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -4328,10 +4526,10 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C13" t="s">
         <v>249</v>
@@ -4375,8 +4573,8 @@
       <c r="P13" t="s">
         <v>17</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
+      <c r="Q13" t="s">
+        <v>314</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4388,7 +4586,7 @@
         <v>79000</v>
       </c>
       <c r="U13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -4396,10 +4594,10 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C14" t="s">
         <v>249</v>
@@ -4443,8 +4641,8 @@
       <c r="P14" t="s">
         <v>17</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
+      <c r="Q14" t="s">
+        <v>314</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4456,7 +4654,7 @@
         <v>79000</v>
       </c>
       <c r="U14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4464,10 +4662,10 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C15" t="s">
         <v>249</v>
@@ -4511,8 +4709,8 @@
       <c r="P15" t="s">
         <v>17</v>
       </c>
-      <c r="Q15">
-        <v>0</v>
+      <c r="Q15" t="s">
+        <v>314</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4524,7 +4722,7 @@
         <v>79000</v>
       </c>
       <c r="U15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4532,10 +4730,10 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C16" t="s">
         <v>249</v>
@@ -4579,8 +4777,8 @@
       <c r="P16" t="s">
         <v>17</v>
       </c>
-      <c r="Q16">
-        <v>0</v>
+      <c r="Q16" t="s">
+        <v>314</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4592,7 +4790,7 @@
         <v>79000</v>
       </c>
       <c r="U16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4600,10 +4798,10 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C17" t="s">
         <v>249</v>
@@ -4647,8 +4845,8 @@
       <c r="P17" t="s">
         <v>17</v>
       </c>
-      <c r="Q17">
-        <v>0</v>
+      <c r="Q17" t="s">
+        <v>330</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4660,7 +4858,7 @@
         <v>79000</v>
       </c>
       <c r="U17" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4671,7 +4869,7 @@
         <v>268</v>
       </c>
       <c r="B18" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C18" t="s">
         <v>249</v>
@@ -4715,8 +4913,8 @@
       <c r="P18" t="s">
         <v>17</v>
       </c>
-      <c r="Q18">
-        <v>0</v>
+      <c r="Q18" t="s">
+        <v>330</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -4728,7 +4926,7 @@
         <v>79000</v>
       </c>
       <c r="U18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4739,7 +4937,7 @@
         <v>269</v>
       </c>
       <c r="B19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C19" t="s">
         <v>249</v>
@@ -4783,8 +4981,8 @@
       <c r="P19" t="s">
         <v>17</v>
       </c>
-      <c r="Q19">
-        <v>0</v>
+      <c r="Q19" t="s">
+        <v>330</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -4796,7 +4994,7 @@
         <v>79000</v>
       </c>
       <c r="U19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -4804,10 +5002,10 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B20" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C20" t="s">
         <v>249</v>
@@ -4851,8 +5049,8 @@
       <c r="P20" t="s">
         <v>17</v>
       </c>
-      <c r="Q20">
-        <v>0</v>
+      <c r="Q20" t="s">
+        <v>330</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -4864,7 +5062,7 @@
         <v>79000</v>
       </c>
       <c r="U20" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -4872,10 +5070,10 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C21" t="s">
         <v>249</v>
@@ -4919,8 +5117,8 @@
       <c r="P21" t="s">
         <v>17</v>
       </c>
-      <c r="Q21">
-        <v>0</v>
+      <c r="Q21" t="s">
+        <v>330</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -4932,7 +5130,7 @@
         <v>79000</v>
       </c>
       <c r="U21" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -4943,7 +5141,7 @@
         <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C22" t="s">
         <v>249</v>
@@ -4987,8 +5185,8 @@
       <c r="P22" t="s">
         <v>17</v>
       </c>
-      <c r="Q22">
-        <v>0</v>
+      <c r="Q22" t="s">
+        <v>343</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -5000,7 +5198,7 @@
         <v>79000</v>
       </c>
       <c r="U22" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5011,7 +5209,7 @@
         <v>253</v>
       </c>
       <c r="B23" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C23" t="s">
         <v>249</v>
@@ -5055,8 +5253,8 @@
       <c r="P23" t="s">
         <v>17</v>
       </c>
-      <c r="Q23">
-        <v>0</v>
+      <c r="Q23" t="s">
+        <v>343</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -5068,7 +5266,7 @@
         <v>79000</v>
       </c>
       <c r="U23" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5076,10 +5274,10 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C24" t="s">
         <v>249</v>
@@ -5123,8 +5321,8 @@
       <c r="P24" t="s">
         <v>17</v>
       </c>
-      <c r="Q24">
-        <v>0</v>
+      <c r="Q24" t="s">
+        <v>343</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -5136,7 +5334,7 @@
         <v>79000</v>
       </c>
       <c r="U24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -5144,10 +5342,10 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B25" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C25" t="s">
         <v>249</v>
@@ -5191,8 +5389,8 @@
       <c r="P25" t="s">
         <v>17</v>
       </c>
-      <c r="Q25">
-        <v>0</v>
+      <c r="Q25" t="s">
+        <v>343</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -5204,7 +5402,7 @@
         <v>79000</v>
       </c>
       <c r="U25" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -5212,10 +5410,10 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B26" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C26" t="s">
         <v>249</v>
@@ -5259,8 +5457,8 @@
       <c r="P26" t="s">
         <v>17</v>
       </c>
-      <c r="Q26">
-        <v>0</v>
+      <c r="Q26" t="s">
+        <v>343</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -5272,7 +5470,7 @@
         <v>79000</v>
       </c>
       <c r="U26" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -5283,7 +5481,7 @@
         <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C27" t="s">
         <v>249</v>
@@ -5327,8 +5525,8 @@
       <c r="P27" t="s">
         <v>17</v>
       </c>
-      <c r="Q27">
-        <v>0</v>
+      <c r="Q27" t="s">
+        <v>357</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -5340,7 +5538,7 @@
         <v>79000</v>
       </c>
       <c r="U27" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -5351,7 +5549,7 @@
         <v>266</v>
       </c>
       <c r="B28" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C28" t="s">
         <v>249</v>
@@ -5395,8 +5593,8 @@
       <c r="P28" t="s">
         <v>17</v>
       </c>
-      <c r="Q28">
-        <v>0</v>
+      <c r="Q28" t="s">
+        <v>357</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -5408,7 +5606,7 @@
         <v>79000</v>
       </c>
       <c r="U28" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -5416,10 +5614,10 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B29" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C29" t="s">
         <v>249</v>
@@ -5463,8 +5661,8 @@
       <c r="P29" t="s">
         <v>17</v>
       </c>
-      <c r="Q29">
-        <v>0</v>
+      <c r="Q29" t="s">
+        <v>357</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -5476,7 +5674,7 @@
         <v>79000</v>
       </c>
       <c r="U29" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -5487,7 +5685,7 @@
         <v>267</v>
       </c>
       <c r="B30" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C30" t="s">
         <v>249</v>
@@ -5531,8 +5729,8 @@
       <c r="P30" t="s">
         <v>17</v>
       </c>
-      <c r="Q30">
-        <v>0</v>
+      <c r="Q30" t="s">
+        <v>357</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -5544,7 +5742,7 @@
         <v>79000</v>
       </c>
       <c r="U30" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -5552,10 +5750,10 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B31" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C31" t="s">
         <v>249</v>
@@ -5599,8 +5797,8 @@
       <c r="P31" t="s">
         <v>17</v>
       </c>
-      <c r="Q31">
-        <v>0</v>
+      <c r="Q31" t="s">
+        <v>357</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -5612,7 +5810,7 @@
         <v>79000</v>
       </c>
       <c r="U31" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -5620,10 +5818,10 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B32" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C32" t="s">
         <v>249</v>
@@ -5667,8 +5865,8 @@
       <c r="P32" t="s">
         <v>17</v>
       </c>
-      <c r="Q32">
-        <v>0</v>
+      <c r="Q32" t="s">
+        <v>371</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -5680,7 +5878,7 @@
         <v>79000</v>
       </c>
       <c r="U32" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -5688,10 +5886,10 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B33" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
         <v>249</v>
@@ -5735,8 +5933,8 @@
       <c r="P33" t="s">
         <v>17</v>
       </c>
-      <c r="Q33">
-        <v>0</v>
+      <c r="Q33" t="s">
+        <v>371</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -5748,7 +5946,7 @@
         <v>79000</v>
       </c>
       <c r="U33" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -5756,10 +5954,10 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B34" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C34" t="s">
         <v>249</v>
@@ -5803,8 +6001,8 @@
       <c r="P34" t="s">
         <v>17</v>
       </c>
-      <c r="Q34">
-        <v>0</v>
+      <c r="Q34" t="s">
+        <v>371</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -5816,7 +6014,7 @@
         <v>79000</v>
       </c>
       <c r="U34" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -5824,10 +6022,10 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B35" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C35" t="s">
         <v>249</v>
@@ -5871,8 +6069,8 @@
       <c r="P35" t="s">
         <v>17</v>
       </c>
-      <c r="Q35">
-        <v>0</v>
+      <c r="Q35" t="s">
+        <v>371</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -5884,7 +6082,7 @@
         <v>79000</v>
       </c>
       <c r="U35" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -5892,10 +6090,10 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B36" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C36" t="s">
         <v>249</v>
@@ -5939,8 +6137,8 @@
       <c r="P36" t="s">
         <v>17</v>
       </c>
-      <c r="Q36">
-        <v>0</v>
+      <c r="Q36" t="s">
+        <v>371</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -5952,7 +6150,7 @@
         <v>79000</v>
       </c>
       <c r="U36" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -5960,10 +6158,10 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B37" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C37" t="s">
         <v>249</v>
@@ -6007,8 +6205,8 @@
       <c r="P37" t="s">
         <v>17</v>
       </c>
-      <c r="Q37">
-        <v>0</v>
+      <c r="Q37" t="s">
+        <v>387</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -6020,7 +6218,7 @@
         <v>79000</v>
       </c>
       <c r="U37" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -6031,7 +6229,7 @@
         <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C38" t="s">
         <v>249</v>
@@ -6075,8 +6273,8 @@
       <c r="P38" t="s">
         <v>17</v>
       </c>
-      <c r="Q38">
-        <v>0</v>
+      <c r="Q38" t="s">
+        <v>387</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -6088,7 +6286,7 @@
         <v>79000</v>
       </c>
       <c r="U38" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -6096,10 +6294,10 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B39" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C39" t="s">
         <v>249</v>
@@ -6143,8 +6341,8 @@
       <c r="P39" t="s">
         <v>17</v>
       </c>
-      <c r="Q39">
-        <v>0</v>
+      <c r="Q39" t="s">
+        <v>387</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -6156,7 +6354,7 @@
         <v>79000</v>
       </c>
       <c r="U39" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -6164,10 +6362,10 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C40" t="s">
         <v>249</v>
@@ -6211,8 +6409,8 @@
       <c r="P40" t="s">
         <v>17</v>
       </c>
-      <c r="Q40">
-        <v>0</v>
+      <c r="Q40" t="s">
+        <v>387</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -6224,7 +6422,7 @@
         <v>79000</v>
       </c>
       <c r="U40" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -6232,10 +6430,10 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C41" t="s">
         <v>249</v>
@@ -6279,8 +6477,8 @@
       <c r="P41" t="s">
         <v>17</v>
       </c>
-      <c r="Q41">
-        <v>0</v>
+      <c r="Q41" t="s">
+        <v>387</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -6292,7 +6490,7 @@
         <v>79000</v>
       </c>
       <c r="U41" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -6300,10 +6498,10 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B42" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C42" t="s">
         <v>249</v>
@@ -6347,8 +6545,8 @@
       <c r="P42" t="s">
         <v>17</v>
       </c>
-      <c r="Q42">
-        <v>0</v>
+      <c r="Q42" t="s">
+        <v>402</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -6360,7 +6558,7 @@
         <v>79000</v>
       </c>
       <c r="U42" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -6368,10 +6566,10 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C43" t="s">
         <v>249</v>
@@ -6415,8 +6613,8 @@
       <c r="P43" t="s">
         <v>17</v>
       </c>
-      <c r="Q43">
-        <v>0</v>
+      <c r="Q43" t="s">
+        <v>402</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -6428,7 +6626,7 @@
         <v>79000</v>
       </c>
       <c r="U43" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -6436,10 +6634,10 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C44" t="s">
         <v>249</v>
@@ -6483,8 +6681,8 @@
       <c r="P44" t="s">
         <v>17</v>
       </c>
-      <c r="Q44">
-        <v>0</v>
+      <c r="Q44" t="s">
+        <v>402</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -6496,7 +6694,7 @@
         <v>79000</v>
       </c>
       <c r="U44" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -6504,10 +6702,10 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C45" t="s">
         <v>249</v>
@@ -6551,8 +6749,8 @@
       <c r="P45" t="s">
         <v>17</v>
       </c>
-      <c r="Q45">
-        <v>0</v>
+      <c r="Q45" t="s">
+        <v>402</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -6564,7 +6762,7 @@
         <v>79000</v>
       </c>
       <c r="U45" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6572,10 +6770,10 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B46" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C46" t="s">
         <v>249</v>
@@ -6619,8 +6817,8 @@
       <c r="P46" t="s">
         <v>17</v>
       </c>
-      <c r="Q46">
-        <v>0</v>
+      <c r="Q46" t="s">
+        <v>402</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -6632,7 +6830,7 @@
         <v>79000</v>
       </c>
       <c r="U46" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -6640,10 +6838,10 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C47" t="s">
         <v>249</v>
@@ -6687,8 +6885,8 @@
       <c r="P47" t="s">
         <v>17</v>
       </c>
-      <c r="Q47">
-        <v>0</v>
+      <c r="Q47" t="s">
+        <v>418</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -6700,7 +6898,7 @@
         <v>79000</v>
       </c>
       <c r="U47" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -6708,10 +6906,10 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C48" t="s">
         <v>249</v>
@@ -6755,8 +6953,8 @@
       <c r="P48" t="s">
         <v>17</v>
       </c>
-      <c r="Q48">
-        <v>0</v>
+      <c r="Q48" t="s">
+        <v>418</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -6768,7 +6966,7 @@
         <v>79000</v>
       </c>
       <c r="U48" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -6776,10 +6974,10 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C49" t="s">
         <v>249</v>
@@ -6823,8 +7021,8 @@
       <c r="P49" t="s">
         <v>17</v>
       </c>
-      <c r="Q49">
-        <v>0</v>
+      <c r="Q49" t="s">
+        <v>418</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -6836,7 +7034,7 @@
         <v>79000</v>
       </c>
       <c r="U49" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -6844,10 +7042,10 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C50" t="s">
         <v>249</v>
@@ -6891,8 +7089,8 @@
       <c r="P50" t="s">
         <v>17</v>
       </c>
-      <c r="Q50">
-        <v>0</v>
+      <c r="Q50" t="s">
+        <v>418</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -6904,7 +7102,7 @@
         <v>79000</v>
       </c>
       <c r="U50" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -6912,10 +7110,10 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C51" t="s">
         <v>249</v>
@@ -6959,8 +7157,8 @@
       <c r="P51" t="s">
         <v>17</v>
       </c>
-      <c r="Q51">
-        <v>0</v>
+      <c r="Q51" t="s">
+        <v>418</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -6972,7 +7170,7 @@
         <v>79000</v>
       </c>
       <c r="U51" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -6980,16 +7178,16 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C52" t="s">
         <v>249</v>
       </c>
       <c r="D52" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
@@ -7027,8 +7225,8 @@
       <c r="P52" t="s">
         <v>17</v>
       </c>
-      <c r="Q52">
-        <v>0</v>
+      <c r="Q52" t="s">
+        <v>435</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -7040,7 +7238,7 @@
         <v>79000</v>
       </c>
       <c r="U52" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -7048,16 +7246,16 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C53" t="s">
         <v>249</v>
       </c>
       <c r="D53" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -7095,8 +7293,8 @@
       <c r="P53" t="s">
         <v>17</v>
       </c>
-      <c r="Q53">
-        <v>0</v>
+      <c r="Q53" t="s">
+        <v>435</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -7108,7 +7306,7 @@
         <v>79000</v>
       </c>
       <c r="U53" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="V53">
         <v>0</v>
@@ -7116,16 +7314,16 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C54" t="s">
         <v>249</v>
       </c>
       <c r="D54" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E54" t="s">
         <v>16</v>
@@ -7163,8 +7361,8 @@
       <c r="P54" t="s">
         <v>17</v>
       </c>
-      <c r="Q54">
-        <v>0</v>
+      <c r="Q54" t="s">
+        <v>435</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -7176,7 +7374,7 @@
         <v>79000</v>
       </c>
       <c r="U54" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="V54">
         <v>0</v>
@@ -7184,16 +7382,16 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C55" t="s">
         <v>249</v>
       </c>
       <c r="D55" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
@@ -7231,8 +7429,8 @@
       <c r="P55" t="s">
         <v>17</v>
       </c>
-      <c r="Q55">
-        <v>0</v>
+      <c r="Q55" t="s">
+        <v>435</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -7244,7 +7442,7 @@
         <v>79000</v>
       </c>
       <c r="U55" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="V55">
         <v>0</v>
@@ -7252,16 +7450,16 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C56" t="s">
         <v>249</v>
       </c>
       <c r="D56" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
@@ -7299,8 +7497,8 @@
       <c r="P56" t="s">
         <v>17</v>
       </c>
-      <c r="Q56">
-        <v>0</v>
+      <c r="Q56" t="s">
+        <v>435</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -7312,7 +7510,7 @@
         <v>79000</v>
       </c>
       <c r="U56" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="V56">
         <v>0</v>
@@ -7320,16 +7518,16 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C57" t="s">
         <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -7367,8 +7565,8 @@
       <c r="P57" t="s">
         <v>17</v>
       </c>
-      <c r="Q57">
-        <v>0</v>
+      <c r="Q57" t="s">
+        <v>451</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -7380,7 +7578,7 @@
         <v>79000</v>
       </c>
       <c r="U57" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="V57">
         <v>0</v>
@@ -7388,16 +7586,16 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="C58" t="s">
         <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E58" t="s">
         <v>16</v>
@@ -7435,8 +7633,8 @@
       <c r="P58" t="s">
         <v>17</v>
       </c>
-      <c r="Q58">
-        <v>0</v>
+      <c r="Q58" t="s">
+        <v>451</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -7448,7 +7646,7 @@
         <v>79000</v>
       </c>
       <c r="U58" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="V58">
         <v>0</v>
@@ -7456,16 +7654,16 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="B59" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="C59" t="s">
         <v>249</v>
       </c>
       <c r="D59" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -7503,8 +7701,8 @@
       <c r="P59" t="s">
         <v>17</v>
       </c>
-      <c r="Q59">
-        <v>0</v>
+      <c r="Q59" t="s">
+        <v>451</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -7516,7 +7714,7 @@
         <v>79000</v>
       </c>
       <c r="U59" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -7524,16 +7722,16 @@
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B60" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C60" t="s">
         <v>249</v>
       </c>
       <c r="D60" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -7571,8 +7769,8 @@
       <c r="P60" t="s">
         <v>17</v>
       </c>
-      <c r="Q60">
-        <v>0</v>
+      <c r="Q60" t="s">
+        <v>451</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -7584,7 +7782,7 @@
         <v>79000</v>
       </c>
       <c r="U60" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -7592,16 +7790,16 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C61" t="s">
         <v>249</v>
       </c>
       <c r="D61" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -7639,8 +7837,8 @@
       <c r="P61" t="s">
         <v>17</v>
       </c>
-      <c r="Q61">
-        <v>0</v>
+      <c r="Q61" t="s">
+        <v>451</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -7652,7 +7850,7 @@
         <v>79000</v>
       </c>
       <c r="U61" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -7660,16 +7858,16 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C62" t="s">
         <v>249</v>
       </c>
       <c r="D62" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
@@ -7707,8 +7905,8 @@
       <c r="P62" t="s">
         <v>17</v>
       </c>
-      <c r="Q62">
-        <v>0</v>
+      <c r="Q62" t="s">
+        <v>467</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -7720,7 +7918,7 @@
         <v>79000</v>
       </c>
       <c r="U62" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -7728,16 +7926,16 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C63" t="s">
         <v>249</v>
       </c>
       <c r="D63" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
@@ -7775,8 +7973,8 @@
       <c r="P63" t="s">
         <v>17</v>
       </c>
-      <c r="Q63">
-        <v>0</v>
+      <c r="Q63" t="s">
+        <v>467</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -7788,7 +7986,7 @@
         <v>79000</v>
       </c>
       <c r="U63" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -7796,16 +7994,16 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C64" t="s">
         <v>249</v>
       </c>
       <c r="D64" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -7843,8 +8041,8 @@
       <c r="P64" t="s">
         <v>17</v>
       </c>
-      <c r="Q64">
-        <v>0</v>
+      <c r="Q64" t="s">
+        <v>467</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -7856,7 +8054,7 @@
         <v>79000</v>
       </c>
       <c r="U64" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -7864,16 +8062,16 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C65" t="s">
         <v>249</v>
       </c>
       <c r="D65" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
@@ -7911,8 +8109,8 @@
       <c r="P65" t="s">
         <v>17</v>
       </c>
-      <c r="Q65">
-        <v>0</v>
+      <c r="Q65" t="s">
+        <v>467</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -7924,7 +8122,7 @@
         <v>79000</v>
       </c>
       <c r="U65" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -7932,16 +8130,16 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B66" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C66" t="s">
         <v>249</v>
       </c>
       <c r="D66" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -7979,8 +8177,8 @@
       <c r="P66" t="s">
         <v>17</v>
       </c>
-      <c r="Q66">
-        <v>0</v>
+      <c r="Q66" t="s">
+        <v>467</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -7992,7 +8190,7 @@
         <v>79000</v>
       </c>
       <c r="U66" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="V66">
         <v>0</v>
@@ -8003,7 +8201,7 @@
         <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -8048,7 +8246,7 @@
         <v>17</v>
       </c>
       <c r="Q67" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -8060,7 +8258,7 @@
         <v>69000</v>
       </c>
       <c r="U67" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="V67">
         <v>0</v>
@@ -8071,7 +8269,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -8116,7 +8314,7 @@
         <v>17</v>
       </c>
       <c r="Q68" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -8128,7 +8326,7 @@
         <v>69000</v>
       </c>
       <c r="U68" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="V68">
         <v>0</v>
@@ -8139,7 +8337,7 @@
         <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -8184,7 +8382,7 @@
         <v>17</v>
       </c>
       <c r="Q69" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -8196,7 +8394,7 @@
         <v>69000</v>
       </c>
       <c r="U69" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -8207,7 +8405,7 @@
         <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -8252,7 +8450,7 @@
         <v>17</v>
       </c>
       <c r="Q70" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -8264,7 +8462,7 @@
         <v>69000</v>
       </c>
       <c r="U70" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="V70">
         <v>0</v>
@@ -8275,7 +8473,7 @@
         <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -8320,7 +8518,7 @@
         <v>17</v>
       </c>
       <c r="Q71" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -8332,7 +8530,7 @@
         <v>69000</v>
       </c>
       <c r="U71" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="V71">
         <v>0</v>
@@ -8340,10 +8538,10 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C72" t="s">
         <v>25</v>
@@ -8388,7 +8586,7 @@
         <v>17</v>
       </c>
       <c r="Q72" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -8400,7 +8598,7 @@
         <v>69000</v>
       </c>
       <c r="U72" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="V72">
         <v>0</v>
@@ -8411,7 +8609,7 @@
         <v>119</v>
       </c>
       <c r="B73" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C73" t="s">
         <v>25</v>
@@ -8456,7 +8654,7 @@
         <v>17</v>
       </c>
       <c r="Q73" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -8468,7 +8666,7 @@
         <v>69000</v>
       </c>
       <c r="U73" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="V73">
         <v>0</v>
@@ -8479,7 +8677,7 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="C74" t="s">
         <v>25</v>
@@ -8524,7 +8722,7 @@
         <v>17</v>
       </c>
       <c r="Q74" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -8536,7 +8734,7 @@
         <v>69000</v>
       </c>
       <c r="U74" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -8547,7 +8745,7 @@
         <v>184</v>
       </c>
       <c r="B75" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C75" t="s">
         <v>25</v>
@@ -8592,7 +8790,7 @@
         <v>17</v>
       </c>
       <c r="Q75" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -8604,7 +8802,7 @@
         <v>69000</v>
       </c>
       <c r="U75" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -8615,7 +8813,7 @@
         <v>262</v>
       </c>
       <c r="B76" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C76" t="s">
         <v>25</v>
@@ -8660,7 +8858,7 @@
         <v>17</v>
       </c>
       <c r="Q76" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -8672,7 +8870,7 @@
         <v>69000</v>
       </c>
       <c r="U76" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="V76">
         <v>0</v>
@@ -8683,7 +8881,7 @@
         <v>186</v>
       </c>
       <c r="B77" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="C77" t="s">
         <v>25</v>
@@ -8728,7 +8926,7 @@
         <v>17</v>
       </c>
       <c r="Q77" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -8740,7 +8938,7 @@
         <v>69000</v>
       </c>
       <c r="U77" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="V77">
         <v>0</v>
@@ -8748,10 +8946,10 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B78" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C78" t="s">
         <v>25</v>
@@ -8796,7 +8994,7 @@
         <v>17</v>
       </c>
       <c r="Q78" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -8808,7 +9006,7 @@
         <v>69000</v>
       </c>
       <c r="U78" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -8819,7 +9017,7 @@
         <v>233</v>
       </c>
       <c r="B79" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="C79" t="s">
         <v>25</v>
@@ -8864,7 +9062,7 @@
         <v>17</v>
       </c>
       <c r="Q79" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -8876,7 +9074,7 @@
         <v>69000</v>
       </c>
       <c r="U79" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -8887,7 +9085,7 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C80" t="s">
         <v>25</v>
@@ -8932,7 +9130,7 @@
         <v>17</v>
       </c>
       <c r="Q80" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -8944,7 +9142,7 @@
         <v>69000</v>
       </c>
       <c r="U80" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -8955,7 +9153,7 @@
         <v>222</v>
       </c>
       <c r="B81" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C81" t="s">
         <v>25</v>
@@ -9000,7 +9198,7 @@
         <v>17</v>
       </c>
       <c r="Q81" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -9012,7 +9210,7 @@
         <v>69000</v>
       </c>
       <c r="U81" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="V81">
         <v>0</v>
@@ -9020,10 +9218,10 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B82" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="C82" t="s">
         <v>25</v>
@@ -9068,7 +9266,7 @@
         <v>17</v>
       </c>
       <c r="Q82" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -9080,7 +9278,7 @@
         <v>69000</v>
       </c>
       <c r="U82" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="V82">
         <v>0</v>
@@ -9088,10 +9286,10 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B83" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="C83" t="s">
         <v>25</v>
@@ -9136,7 +9334,7 @@
         <v>17</v>
       </c>
       <c r="Q83" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -9148,7 +9346,7 @@
         <v>69000</v>
       </c>
       <c r="U83" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="V83">
         <v>0</v>
@@ -9159,7 +9357,7 @@
         <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="C84" t="s">
         <v>25</v>
@@ -9204,7 +9402,7 @@
         <v>17</v>
       </c>
       <c r="Q84" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -9216,7 +9414,7 @@
         <v>69000</v>
       </c>
       <c r="U84" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="V84">
         <v>0</v>
@@ -9224,10 +9422,10 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B85" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="C85" t="s">
         <v>25</v>
@@ -9272,7 +9470,7 @@
         <v>17</v>
       </c>
       <c r="Q85" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -9284,7 +9482,7 @@
         <v>69000</v>
       </c>
       <c r="U85" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -9295,7 +9493,7 @@
         <v>226</v>
       </c>
       <c r="B86" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="C86" t="s">
         <v>25</v>
@@ -9340,7 +9538,7 @@
         <v>17</v>
       </c>
       <c r="Q86" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -9352,7 +9550,7 @@
         <v>69000</v>
       </c>
       <c r="U86" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -9360,10 +9558,10 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B87" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="C87" t="s">
         <v>25</v>
@@ -9408,7 +9606,7 @@
         <v>17</v>
       </c>
       <c r="Q87" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -9420,7 +9618,7 @@
         <v>69000</v>
       </c>
       <c r="U87" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="V87">
         <v>0</v>
@@ -9431,7 +9629,7 @@
         <v>107</v>
       </c>
       <c r="B88" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="C88" t="s">
         <v>25</v>
@@ -9476,7 +9674,7 @@
         <v>17</v>
       </c>
       <c r="Q88" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -9488,7 +9686,7 @@
         <v>69000</v>
       </c>
       <c r="U88" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="V88">
         <v>0</v>
@@ -9499,7 +9697,7 @@
         <v>214</v>
       </c>
       <c r="B89" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="C89" t="s">
         <v>25</v>
@@ -9544,7 +9742,7 @@
         <v>17</v>
       </c>
       <c r="Q89" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -9556,7 +9754,7 @@
         <v>69000</v>
       </c>
       <c r="U89" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -9567,7 +9765,7 @@
         <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
@@ -9612,7 +9810,7 @@
         <v>17</v>
       </c>
       <c r="Q90" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -9624,7 +9822,7 @@
         <v>69000</v>
       </c>
       <c r="U90" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="V90">
         <v>0</v>
@@ -9632,10 +9830,10 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B91" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="C91" t="s">
         <v>25</v>
@@ -9680,7 +9878,7 @@
         <v>17</v>
       </c>
       <c r="Q91" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -9692,7 +9890,7 @@
         <v>69000</v>
       </c>
       <c r="U91" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="V91">
         <v>0</v>
@@ -9700,10 +9898,10 @@
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="B92" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="C92" t="s">
         <v>25</v>
@@ -9748,7 +9946,7 @@
         <v>17</v>
       </c>
       <c r="Q92" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -9760,7 +9958,7 @@
         <v>69000</v>
       </c>
       <c r="U92" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="V92">
         <v>0</v>
@@ -9771,7 +9969,7 @@
         <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="C93" t="s">
         <v>25</v>
@@ -9816,7 +10014,7 @@
         <v>17</v>
       </c>
       <c r="Q93" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -9828,7 +10026,7 @@
         <v>69000</v>
       </c>
       <c r="U93" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="V93">
         <v>0</v>
@@ -9839,7 +10037,7 @@
         <v>260</v>
       </c>
       <c r="B94" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="C94" t="s">
         <v>25</v>
@@ -9884,7 +10082,7 @@
         <v>17</v>
       </c>
       <c r="Q94" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -9896,7 +10094,7 @@
         <v>69000</v>
       </c>
       <c r="U94" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="V94">
         <v>0</v>
@@ -9904,10 +10102,10 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B95" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="C95" t="s">
         <v>25</v>
@@ -9952,7 +10150,7 @@
         <v>17</v>
       </c>
       <c r="Q95" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -9964,7 +10162,7 @@
         <v>69000</v>
       </c>
       <c r="U95" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="V95">
         <v>0</v>
@@ -9975,7 +10173,7 @@
         <v>228</v>
       </c>
       <c r="B96" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C96" t="s">
         <v>25</v>
@@ -10020,7 +10218,7 @@
         <v>17</v>
       </c>
       <c r="Q96" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -10032,7 +10230,7 @@
         <v>69000</v>
       </c>
       <c r="U96" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="V96">
         <v>0</v>
@@ -10040,10 +10238,10 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="C97" t="s">
         <v>25</v>
@@ -10088,7 +10286,7 @@
         <v>17</v>
       </c>
       <c r="Q97" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -10100,7 +10298,7 @@
         <v>69000</v>
       </c>
       <c r="U97" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="V97">
         <v>0</v>
@@ -10111,7 +10309,7 @@
         <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C98" t="s">
         <v>25</v>
@@ -10156,7 +10354,7 @@
         <v>17</v>
       </c>
       <c r="Q98" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -10168,7 +10366,7 @@
         <v>69000</v>
       </c>
       <c r="U98" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="V98">
         <v>0</v>
@@ -10179,7 +10377,7 @@
         <v>160</v>
       </c>
       <c r="B99" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="C99" t="s">
         <v>25</v>
@@ -10224,7 +10422,7 @@
         <v>17</v>
       </c>
       <c r="Q99" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -10236,7 +10434,7 @@
         <v>69000</v>
       </c>
       <c r="U99" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="V99">
         <v>0</v>
@@ -10247,7 +10445,7 @@
         <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="C100" t="s">
         <v>25</v>
@@ -10292,7 +10490,7 @@
         <v>17</v>
       </c>
       <c r="Q100" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -10304,7 +10502,7 @@
         <v>69000</v>
       </c>
       <c r="U100" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="V100">
         <v>0</v>
@@ -10312,10 +10510,10 @@
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B101" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C101" t="s">
         <v>25</v>
@@ -10360,7 +10558,7 @@
         <v>17</v>
       </c>
       <c r="Q101" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -10372,7 +10570,7 @@
         <v>69000</v>
       </c>
       <c r="U101" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="V101">
         <v>0</v>
@@ -10380,10 +10578,10 @@
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B102" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="C102" t="s">
         <v>25</v>
@@ -10428,7 +10626,7 @@
         <v>17</v>
       </c>
       <c r="Q102" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -10440,7 +10638,7 @@
         <v>69000</v>
       </c>
       <c r="U102" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="V102">
         <v>0</v>
@@ -10451,7 +10649,7 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="C103" t="s">
         <v>25</v>
@@ -10496,7 +10694,7 @@
         <v>17</v>
       </c>
       <c r="Q103" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -10508,7 +10706,7 @@
         <v>69000</v>
       </c>
       <c r="U103" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="V103">
         <v>0</v>
@@ -10519,7 +10717,7 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="C104" t="s">
         <v>25</v>
@@ -10564,7 +10762,7 @@
         <v>17</v>
       </c>
       <c r="Q104" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -10576,7 +10774,7 @@
         <v>69000</v>
       </c>
       <c r="U104" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="V104">
         <v>0</v>
@@ -10584,10 +10782,10 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="B105" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="C105" t="s">
         <v>25</v>
@@ -10632,7 +10830,7 @@
         <v>17</v>
       </c>
       <c r="Q105" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -10644,7 +10842,7 @@
         <v>69000</v>
       </c>
       <c r="U105" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="V105">
         <v>0</v>
@@ -10655,7 +10853,7 @@
         <v>58</v>
       </c>
       <c r="B106" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="C106" t="s">
         <v>25</v>
@@ -10700,7 +10898,7 @@
         <v>17</v>
       </c>
       <c r="Q106" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -10712,7 +10910,7 @@
         <v>69000</v>
       </c>
       <c r="U106" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="V106">
         <v>0</v>
@@ -10720,10 +10918,10 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="C107" t="s">
         <v>25</v>
@@ -10768,7 +10966,7 @@
         <v>17</v>
       </c>
       <c r="Q107" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -10780,7 +10978,7 @@
         <v>69000</v>
       </c>
       <c r="U107" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="V107">
         <v>0</v>
@@ -10791,7 +10989,7 @@
         <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C108" t="s">
         <v>25</v>
@@ -10836,7 +11034,7 @@
         <v>17</v>
       </c>
       <c r="Q108" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -10848,7 +11046,7 @@
         <v>69000</v>
       </c>
       <c r="U108" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="V108">
         <v>0</v>
@@ -10859,7 +11057,7 @@
         <v>37</v>
       </c>
       <c r="B109" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="C109" t="s">
         <v>25</v>
@@ -10904,7 +11102,7 @@
         <v>17</v>
       </c>
       <c r="Q109" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -10916,7 +11114,7 @@
         <v>69000</v>
       </c>
       <c r="U109" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="V109">
         <v>0</v>
@@ -10924,10 +11122,10 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="B110" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="C110" t="s">
         <v>25</v>
@@ -10972,7 +11170,7 @@
         <v>17</v>
       </c>
       <c r="Q110" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -10984,7 +11182,7 @@
         <v>69000</v>
       </c>
       <c r="U110" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="V110">
         <v>0</v>
@@ -10992,10 +11190,10 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B111" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="C111" t="s">
         <v>25</v>
@@ -11040,7 +11238,7 @@
         <v>17</v>
       </c>
       <c r="Q111" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -11052,7 +11250,7 @@
         <v>69000</v>
       </c>
       <c r="U111" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="V111">
         <v>0</v>
@@ -11063,7 +11261,7 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="C112" t="s">
         <v>25</v>
@@ -11108,7 +11306,7 @@
         <v>17</v>
       </c>
       <c r="Q112" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -11120,7 +11318,7 @@
         <v>69000</v>
       </c>
       <c r="U112" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="V112">
         <v>0</v>
@@ -11131,7 +11329,7 @@
         <v>97</v>
       </c>
       <c r="B113" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="C113" t="s">
         <v>25</v>
@@ -11176,7 +11374,7 @@
         <v>17</v>
       </c>
       <c r="Q113" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -11188,7 +11386,7 @@
         <v>69000</v>
       </c>
       <c r="U113" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="V113">
         <v>0</v>
@@ -11199,7 +11397,7 @@
         <v>108</v>
       </c>
       <c r="B114" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="C114" t="s">
         <v>25</v>
@@ -11244,7 +11442,7 @@
         <v>17</v>
       </c>
       <c r="Q114" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -11256,7 +11454,7 @@
         <v>69000</v>
       </c>
       <c r="U114" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="V114">
         <v>0</v>
@@ -11267,7 +11465,7 @@
         <v>59</v>
       </c>
       <c r="B115" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="C115" t="s">
         <v>25</v>
@@ -11312,7 +11510,7 @@
         <v>17</v>
       </c>
       <c r="Q115" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -11324,7 +11522,7 @@
         <v>69000</v>
       </c>
       <c r="U115" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="V115">
         <v>0</v>
@@ -11335,7 +11533,7 @@
         <v>102</v>
       </c>
       <c r="B116" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="C116" t="s">
         <v>25</v>
@@ -11380,7 +11578,7 @@
         <v>17</v>
       </c>
       <c r="Q116" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -11392,7 +11590,7 @@
         <v>69000</v>
       </c>
       <c r="U116" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="V116">
         <v>0</v>
@@ -11403,7 +11601,7 @@
         <v>38</v>
       </c>
       <c r="B117" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="C117" t="s">
         <v>25</v>
@@ -11448,7 +11646,7 @@
         <v>17</v>
       </c>
       <c r="Q117" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -11460,7 +11658,7 @@
         <v>69000</v>
       </c>
       <c r="U117" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="V117">
         <v>0</v>
@@ -11471,7 +11669,7 @@
         <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="C118" t="s">
         <v>25</v>
@@ -11516,7 +11714,7 @@
         <v>17</v>
       </c>
       <c r="Q118" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -11528,7 +11726,7 @@
         <v>69000</v>
       </c>
       <c r="U118" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="V118">
         <v>0</v>
@@ -11539,7 +11737,7 @@
         <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="C119" t="s">
         <v>25</v>
@@ -11584,7 +11782,7 @@
         <v>17</v>
       </c>
       <c r="Q119" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -11596,7 +11794,7 @@
         <v>69000</v>
       </c>
       <c r="U119" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="V119">
         <v>0</v>
@@ -11607,7 +11805,7 @@
         <v>82</v>
       </c>
       <c r="B120" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="C120" t="s">
         <v>25</v>
@@ -11652,7 +11850,7 @@
         <v>17</v>
       </c>
       <c r="Q120" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -11664,7 +11862,7 @@
         <v>69000</v>
       </c>
       <c r="U120" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="V120">
         <v>0</v>
@@ -11675,7 +11873,7 @@
         <v>98</v>
       </c>
       <c r="B121" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="C121" t="s">
         <v>25</v>
@@ -11720,7 +11918,7 @@
         <v>17</v>
       </c>
       <c r="Q121" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -11732,7 +11930,7 @@
         <v>69000</v>
       </c>
       <c r="U121" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="V121">
         <v>0</v>
@@ -11743,7 +11941,7 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="C122" t="s">
         <v>25</v>
@@ -11788,7 +11986,7 @@
         <v>17</v>
       </c>
       <c r="Q122" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -11800,7 +11998,7 @@
         <v>69000</v>
       </c>
       <c r="U122" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="V122">
         <v>0</v>
@@ -11811,7 +12009,7 @@
         <v>118</v>
       </c>
       <c r="B123" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="C123" t="s">
         <v>25</v>
@@ -11856,7 +12054,7 @@
         <v>17</v>
       </c>
       <c r="Q123" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -11868,7 +12066,7 @@
         <v>69000</v>
       </c>
       <c r="U123" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="V123">
         <v>0</v>
@@ -11879,7 +12077,7 @@
         <v>96</v>
       </c>
       <c r="B124" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="C124" t="s">
         <v>25</v>
@@ -11924,7 +12122,7 @@
         <v>17</v>
       </c>
       <c r="Q124" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -11936,7 +12134,7 @@
         <v>69000</v>
       </c>
       <c r="U124" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="V124">
         <v>0</v>
@@ -11947,7 +12145,7 @@
         <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="C125" t="s">
         <v>25</v>
@@ -11992,7 +12190,7 @@
         <v>17</v>
       </c>
       <c r="Q125" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -12004,7 +12202,7 @@
         <v>69000</v>
       </c>
       <c r="U125" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="V125">
         <v>0</v>
@@ -12015,7 +12213,7 @@
         <v>64</v>
       </c>
       <c r="B126" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="C126" t="s">
         <v>25</v>
@@ -12060,7 +12258,7 @@
         <v>17</v>
       </c>
       <c r="Q126" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -12072,7 +12270,7 @@
         <v>69000</v>
       </c>
       <c r="U126" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="V126">
         <v>0</v>
@@ -12083,7 +12281,7 @@
         <v>83</v>
       </c>
       <c r="B127" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
@@ -12104,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -12119,16 +12317,16 @@
         <v>6</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O127">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P127" t="s">
         <v>17</v>
       </c>
       <c r="Q127" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -12140,7 +12338,7 @@
         <v>74000</v>
       </c>
       <c r="U127" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="V127">
         <v>0</v>
@@ -12151,7 +12349,7 @@
         <v>70</v>
       </c>
       <c r="B128" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="C128" t="s">
         <v>19</v>
@@ -12196,7 +12394,7 @@
         <v>17</v>
       </c>
       <c r="Q128" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -12208,7 +12406,7 @@
         <v>74000</v>
       </c>
       <c r="U128" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="V128">
         <v>0</v>
@@ -12219,7 +12417,7 @@
         <v>75</v>
       </c>
       <c r="B129" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="C129" t="s">
         <v>19</v>
@@ -12264,7 +12462,7 @@
         <v>17</v>
       </c>
       <c r="Q129" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -12276,7 +12474,7 @@
         <v>74000</v>
       </c>
       <c r="U129" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="V129">
         <v>0</v>
@@ -12287,7 +12485,7 @@
         <v>81</v>
       </c>
       <c r="B130" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="C130" t="s">
         <v>19</v>
@@ -12332,7 +12530,7 @@
         <v>17</v>
       </c>
       <c r="Q130" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -12344,7 +12542,7 @@
         <v>74000</v>
       </c>
       <c r="U130" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="V130">
         <v>0</v>
@@ -12355,7 +12553,7 @@
         <v>78</v>
       </c>
       <c r="B131" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="C131" t="s">
         <v>19</v>
@@ -12400,7 +12598,7 @@
         <v>17</v>
       </c>
       <c r="Q131" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -12412,7 +12610,7 @@
         <v>74000</v>
       </c>
       <c r="U131" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="V131">
         <v>0</v>
@@ -12423,7 +12621,7 @@
         <v>21</v>
       </c>
       <c r="B132" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="C132" t="s">
         <v>19</v>
@@ -12459,7 +12657,7 @@
         <v>12</v>
       </c>
       <c r="N132">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O132">
         <v>26</v>
@@ -12468,7 +12666,7 @@
         <v>17</v>
       </c>
       <c r="Q132" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -12480,7 +12678,7 @@
         <v>74000</v>
       </c>
       <c r="U132" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="V132">
         <v>0</v>
@@ -12491,7 +12689,7 @@
         <v>79</v>
       </c>
       <c r="B133" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="C133" t="s">
         <v>19</v>
@@ -12527,7 +12725,7 @@
         <v>9</v>
       </c>
       <c r="N133">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O133">
         <v>30</v>
@@ -12536,7 +12734,7 @@
         <v>17</v>
       </c>
       <c r="Q133" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -12548,7 +12746,7 @@
         <v>74000</v>
       </c>
       <c r="U133" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="V133">
         <v>0</v>
@@ -12559,7 +12757,7 @@
         <v>62</v>
       </c>
       <c r="B134" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="C134" t="s">
         <v>19</v>
@@ -12604,7 +12802,7 @@
         <v>17</v>
       </c>
       <c r="Q134" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -12616,7 +12814,7 @@
         <v>74000</v>
       </c>
       <c r="U134" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="V134">
         <v>0</v>
@@ -12627,7 +12825,7 @@
         <v>76</v>
       </c>
       <c r="B135" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="C135" t="s">
         <v>19</v>
@@ -12663,7 +12861,7 @@
         <v>2</v>
       </c>
       <c r="N135">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O135">
         <v>17</v>
@@ -12672,7 +12870,7 @@
         <v>17</v>
       </c>
       <c r="Q135" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -12684,7 +12882,7 @@
         <v>74000</v>
       </c>
       <c r="U135" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="V135">
         <v>0</v>
@@ -12695,7 +12893,7 @@
         <v>86</v>
       </c>
       <c r="B136" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="C136" t="s">
         <v>19</v>
@@ -12740,7 +12938,7 @@
         <v>17</v>
       </c>
       <c r="Q136" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -12752,7 +12950,7 @@
         <v>74000</v>
       </c>
       <c r="U136" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="V136">
         <v>0</v>
@@ -12763,7 +12961,7 @@
         <v>90</v>
       </c>
       <c r="B137" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="C137" t="s">
         <v>19</v>
@@ -12799,7 +12997,7 @@
         <v>2</v>
       </c>
       <c r="N137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137">
         <v>8</v>
@@ -12808,7 +13006,7 @@
         <v>17</v>
       </c>
       <c r="Q137" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -12820,7 +13018,7 @@
         <v>69000</v>
       </c>
       <c r="U137" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="V137">
         <v>0</v>
@@ -12831,7 +13029,7 @@
         <v>163</v>
       </c>
       <c r="B138" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="C138" t="s">
         <v>19</v>
@@ -12867,7 +13065,7 @@
         <v>2</v>
       </c>
       <c r="N138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O138">
         <v>15</v>
@@ -12876,7 +13074,7 @@
         <v>17</v>
       </c>
       <c r="Q138" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -12888,7 +13086,7 @@
         <v>69000</v>
       </c>
       <c r="U138" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="V138">
         <v>0</v>
@@ -12899,7 +13097,7 @@
         <v>167</v>
       </c>
       <c r="B139" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="C139" t="s">
         <v>19</v>
@@ -12944,7 +13142,7 @@
         <v>17</v>
       </c>
       <c r="Q139" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -12956,7 +13154,7 @@
         <v>69000</v>
       </c>
       <c r="U139" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="V139">
         <v>0</v>
@@ -12967,7 +13165,7 @@
         <v>105</v>
       </c>
       <c r="B140" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="C140" t="s">
         <v>19</v>
@@ -13003,7 +13201,7 @@
         <v>1</v>
       </c>
       <c r="N140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O140">
         <v>10</v>
@@ -13012,7 +13210,7 @@
         <v>17</v>
       </c>
       <c r="Q140" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -13024,7 +13222,7 @@
         <v>69000</v>
       </c>
       <c r="U140" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="V140">
         <v>0</v>
@@ -13035,7 +13233,7 @@
         <v>164</v>
       </c>
       <c r="B141" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="C141" t="s">
         <v>19</v>
@@ -13080,7 +13278,7 @@
         <v>17</v>
       </c>
       <c r="Q141" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -13092,7 +13290,7 @@
         <v>69000</v>
       </c>
       <c r="U141" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="V141">
         <v>0</v>
@@ -13103,7 +13301,7 @@
         <v>92</v>
       </c>
       <c r="B142" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="C142" t="s">
         <v>19</v>
@@ -13148,7 +13346,7 @@
         <v>17</v>
       </c>
       <c r="Q142" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -13160,7 +13358,7 @@
         <v>69000</v>
       </c>
       <c r="U142" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="V142">
         <v>0</v>
@@ -13171,7 +13369,7 @@
         <v>168</v>
       </c>
       <c r="B143" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="C143" t="s">
         <v>19</v>
@@ -13207,7 +13405,7 @@
         <v>2</v>
       </c>
       <c r="N143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O143">
         <v>5</v>
@@ -13216,7 +13414,7 @@
         <v>17</v>
       </c>
       <c r="Q143" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -13228,7 +13426,7 @@
         <v>69000</v>
       </c>
       <c r="U143" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="V143">
         <v>0</v>
@@ -13239,7 +13437,7 @@
         <v>172</v>
       </c>
       <c r="B144" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="C144" t="s">
         <v>19</v>
@@ -13284,7 +13482,7 @@
         <v>17</v>
       </c>
       <c r="Q144" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -13296,7 +13494,7 @@
         <v>69000</v>
       </c>
       <c r="U144" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="V144">
         <v>0</v>
@@ -13307,7 +13505,7 @@
         <v>234</v>
       </c>
       <c r="B145" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="C145" t="s">
         <v>19</v>
@@ -13352,7 +13550,7 @@
         <v>17</v>
       </c>
       <c r="Q145" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -13364,7 +13562,7 @@
         <v>69000</v>
       </c>
       <c r="U145" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="V145">
         <v>0</v>
@@ -13375,7 +13573,7 @@
         <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="C146" t="s">
         <v>19</v>
@@ -13420,7 +13618,7 @@
         <v>17</v>
       </c>
       <c r="Q146" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -13432,7 +13630,7 @@
         <v>69000</v>
       </c>
       <c r="U146" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="V146">
         <v>0</v>
@@ -13443,7 +13641,7 @@
         <v>173</v>
       </c>
       <c r="B147" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="C147" t="s">
         <v>19</v>
@@ -13479,7 +13677,7 @@
         <v>3</v>
       </c>
       <c r="N147">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O147">
         <v>16</v>
@@ -13488,7 +13686,7 @@
         <v>17</v>
       </c>
       <c r="Q147" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -13500,7 +13698,7 @@
         <v>69000</v>
       </c>
       <c r="U147" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="V147">
         <v>0</v>
@@ -13511,7 +13709,7 @@
         <v>113</v>
       </c>
       <c r="B148" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="C148" t="s">
         <v>19</v>
@@ -13532,7 +13730,7 @@
         <v>0</v>
       </c>
       <c r="I148">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -13550,13 +13748,13 @@
         <v>6</v>
       </c>
       <c r="O148">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P148" t="s">
         <v>17</v>
       </c>
       <c r="Q148" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -13568,7 +13766,7 @@
         <v>69000</v>
       </c>
       <c r="U148" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="V148">
         <v>0</v>
@@ -13579,7 +13777,7 @@
         <v>161</v>
       </c>
       <c r="B149" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="C149" t="s">
         <v>19</v>
@@ -13615,7 +13813,7 @@
         <v>3</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O149">
         <v>11</v>
@@ -13624,7 +13822,7 @@
         <v>17</v>
       </c>
       <c r="Q149" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -13636,7 +13834,7 @@
         <v>69000</v>
       </c>
       <c r="U149" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="V149">
         <v>0</v>
@@ -13647,7 +13845,7 @@
         <v>106</v>
       </c>
       <c r="B150" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="C150" t="s">
         <v>19</v>
@@ -13683,7 +13881,7 @@
         <v>0</v>
       </c>
       <c r="N150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O150">
         <v>9</v>
@@ -13692,7 +13890,7 @@
         <v>17</v>
       </c>
       <c r="Q150" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -13704,7 +13902,7 @@
         <v>69000</v>
       </c>
       <c r="U150" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="V150">
         <v>0</v>
@@ -13715,7 +13913,7 @@
         <v>117</v>
       </c>
       <c r="B151" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="C151" t="s">
         <v>19</v>
@@ -13751,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="N151">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O151">
         <v>11</v>
@@ -13760,7 +13958,7 @@
         <v>17</v>
       </c>
       <c r="Q151" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -13772,7 +13970,7 @@
         <v>69000</v>
       </c>
       <c r="U151" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="V151">
         <v>0</v>
@@ -13780,10 +13978,10 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="B152" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="C152" t="s">
         <v>249</v>
@@ -13827,8 +14025,8 @@
       <c r="P152" t="s">
         <v>17</v>
       </c>
-      <c r="Q152">
-        <v>0</v>
+      <c r="Q152" t="s">
+        <v>686</v>
       </c>
       <c r="R152">
         <v>0</v>
@@ -13840,7 +14038,7 @@
         <v>79000</v>
       </c>
       <c r="U152" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="V152">
         <v>0</v>
@@ -13848,10 +14046,10 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="B153" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="C153" t="s">
         <v>249</v>
@@ -13895,8 +14093,8 @@
       <c r="P153" t="s">
         <v>17</v>
       </c>
-      <c r="Q153">
-        <v>0</v>
+      <c r="Q153" t="s">
+        <v>686</v>
       </c>
       <c r="R153">
         <v>0</v>
@@ -13908,7 +14106,7 @@
         <v>79000</v>
       </c>
       <c r="U153" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="V153">
         <v>0</v>
@@ -13916,10 +14114,10 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="B154" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="C154" t="s">
         <v>249</v>
@@ -13963,8 +14161,8 @@
       <c r="P154" t="s">
         <v>17</v>
       </c>
-      <c r="Q154">
-        <v>0</v>
+      <c r="Q154" t="s">
+        <v>686</v>
       </c>
       <c r="R154">
         <v>0</v>
@@ -13976,7 +14174,7 @@
         <v>79000</v>
       </c>
       <c r="U154" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="V154">
         <v>0</v>
@@ -13984,10 +14182,10 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="B155" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="C155" t="s">
         <v>249</v>
@@ -14031,8 +14229,8 @@
       <c r="P155" t="s">
         <v>17</v>
       </c>
-      <c r="Q155">
-        <v>0</v>
+      <c r="Q155" t="s">
+        <v>686</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -14044,7 +14242,7 @@
         <v>79000</v>
       </c>
       <c r="U155" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="V155">
         <v>0</v>
@@ -14052,10 +14250,10 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="B156" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="C156" t="s">
         <v>249</v>
@@ -14099,8 +14297,8 @@
       <c r="P156" t="s">
         <v>17</v>
       </c>
-      <c r="Q156">
-        <v>0</v>
+      <c r="Q156" t="s">
+        <v>686</v>
       </c>
       <c r="R156">
         <v>0</v>
@@ -14112,7 +14310,7 @@
         <v>79000</v>
       </c>
       <c r="U156" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="V156">
         <v>0</v>
@@ -14123,7 +14321,7 @@
         <v>257</v>
       </c>
       <c r="B157" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="C157" t="s">
         <v>249</v>
@@ -14167,8 +14365,8 @@
       <c r="P157" t="s">
         <v>17</v>
       </c>
-      <c r="Q157">
-        <v>0</v>
+      <c r="Q157" t="s">
+        <v>701</v>
       </c>
       <c r="R157">
         <v>0</v>
@@ -14180,7 +14378,7 @@
         <v>79000</v>
       </c>
       <c r="U157" t="s">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="V157">
         <v>0</v>
@@ -14191,7 +14389,7 @@
         <v>256</v>
       </c>
       <c r="B158" t="s">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="C158" t="s">
         <v>249</v>
@@ -14235,8 +14433,8 @@
       <c r="P158" t="s">
         <v>17</v>
       </c>
-      <c r="Q158">
-        <v>0</v>
+      <c r="Q158" t="s">
+        <v>701</v>
       </c>
       <c r="R158">
         <v>0</v>
@@ -14248,7 +14446,7 @@
         <v>79000</v>
       </c>
       <c r="U158" t="s">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="V158">
         <v>0</v>
@@ -14256,10 +14454,10 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="B159" t="s">
-        <v>693</v>
+        <v>706</v>
       </c>
       <c r="C159" t="s">
         <v>249</v>
@@ -14303,8 +14501,8 @@
       <c r="P159" t="s">
         <v>17</v>
       </c>
-      <c r="Q159">
-        <v>0</v>
+      <c r="Q159" t="s">
+        <v>701</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -14316,7 +14514,7 @@
         <v>79000</v>
       </c>
       <c r="U159" t="s">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="V159">
         <v>0</v>
@@ -14324,10 +14522,10 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="B160" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="C160" t="s">
         <v>249</v>
@@ -14371,8 +14569,8 @@
       <c r="P160" t="s">
         <v>17</v>
       </c>
-      <c r="Q160">
-        <v>0</v>
+      <c r="Q160" t="s">
+        <v>701</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -14384,7 +14582,7 @@
         <v>79000</v>
       </c>
       <c r="U160" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="V160">
         <v>0</v>
@@ -14392,10 +14590,10 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="B161" t="s">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="C161" t="s">
         <v>249</v>
@@ -14439,8 +14637,8 @@
       <c r="P161" t="s">
         <v>17</v>
       </c>
-      <c r="Q161">
-        <v>0</v>
+      <c r="Q161" t="s">
+        <v>701</v>
       </c>
       <c r="R161">
         <v>0</v>
@@ -14452,7 +14650,7 @@
         <v>79000</v>
       </c>
       <c r="U161" t="s">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="V161">
         <v>0</v>
@@ -14463,7 +14661,7 @@
         <v>251</v>
       </c>
       <c r="B162" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="C162" t="s">
         <v>249</v>
@@ -14507,8 +14705,8 @@
       <c r="P162" t="s">
         <v>17</v>
       </c>
-      <c r="Q162">
-        <v>0</v>
+      <c r="Q162" t="s">
+        <v>715</v>
       </c>
       <c r="R162">
         <v>0</v>
@@ -14520,7 +14718,7 @@
         <v>79000</v>
       </c>
       <c r="U162" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="V162">
         <v>0</v>
@@ -14528,10 +14726,10 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="B163" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="C163" t="s">
         <v>249</v>
@@ -14575,8 +14773,8 @@
       <c r="P163" t="s">
         <v>17</v>
       </c>
-      <c r="Q163">
-        <v>0</v>
+      <c r="Q163" t="s">
+        <v>715</v>
       </c>
       <c r="R163">
         <v>0</v>
@@ -14588,7 +14786,7 @@
         <v>79000</v>
       </c>
       <c r="U163" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="V163">
         <v>0</v>
@@ -14596,10 +14794,10 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="B164" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="C164" t="s">
         <v>249</v>
@@ -14643,8 +14841,8 @@
       <c r="P164" t="s">
         <v>17</v>
       </c>
-      <c r="Q164">
-        <v>0</v>
+      <c r="Q164" t="s">
+        <v>715</v>
       </c>
       <c r="R164">
         <v>0</v>
@@ -14656,7 +14854,7 @@
         <v>79000</v>
       </c>
       <c r="U164" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="V164">
         <v>0</v>
@@ -14664,10 +14862,10 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>709</v>
+        <v>723</v>
       </c>
       <c r="B165" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="C165" t="s">
         <v>249</v>
@@ -14711,8 +14909,8 @@
       <c r="P165" t="s">
         <v>17</v>
       </c>
-      <c r="Q165">
-        <v>0</v>
+      <c r="Q165" t="s">
+        <v>715</v>
       </c>
       <c r="R165">
         <v>0</v>
@@ -14724,7 +14922,7 @@
         <v>79000</v>
       </c>
       <c r="U165" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="V165">
         <v>0</v>
@@ -14732,10 +14930,10 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="B166" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="C166" t="s">
         <v>249</v>
@@ -14779,8 +14977,8 @@
       <c r="P166" t="s">
         <v>17</v>
       </c>
-      <c r="Q166">
-        <v>0</v>
+      <c r="Q166" t="s">
+        <v>715</v>
       </c>
       <c r="R166">
         <v>0</v>
@@ -14792,7 +14990,7 @@
         <v>79000</v>
       </c>
       <c r="U166" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="V166">
         <v>0</v>
@@ -14803,7 +15001,7 @@
         <v>270</v>
       </c>
       <c r="B167" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="C167" t="s">
         <v>249</v>
@@ -14847,8 +15045,8 @@
       <c r="P167" t="s">
         <v>17</v>
       </c>
-      <c r="Q167">
-        <v>0</v>
+      <c r="Q167" t="s">
+        <v>730</v>
       </c>
       <c r="R167">
         <v>0</v>
@@ -14860,7 +15058,7 @@
         <v>79000</v>
       </c>
       <c r="U167" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="V167">
         <v>0</v>
@@ -14868,10 +15066,10 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="B168" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="C168" t="s">
         <v>249</v>
@@ -14915,8 +15113,8 @@
       <c r="P168" t="s">
         <v>17</v>
       </c>
-      <c r="Q168">
-        <v>0</v>
+      <c r="Q168" t="s">
+        <v>730</v>
       </c>
       <c r="R168">
         <v>0</v>
@@ -14928,7 +15126,7 @@
         <v>79000</v>
       </c>
       <c r="U168" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="V168">
         <v>0</v>
@@ -14939,7 +15137,7 @@
         <v>271</v>
       </c>
       <c r="B169" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="C169" t="s">
         <v>249</v>
@@ -14983,8 +15181,8 @@
       <c r="P169" t="s">
         <v>17</v>
       </c>
-      <c r="Q169">
-        <v>0</v>
+      <c r="Q169" t="s">
+        <v>730</v>
       </c>
       <c r="R169">
         <v>0</v>
@@ -14996,7 +15194,7 @@
         <v>79000</v>
       </c>
       <c r="U169" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="V169">
         <v>0</v>
@@ -15007,7 +15205,7 @@
         <v>265</v>
       </c>
       <c r="B170" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="C170" t="s">
         <v>249</v>
@@ -15051,8 +15249,8 @@
       <c r="P170" t="s">
         <v>17</v>
       </c>
-      <c r="Q170">
-        <v>0</v>
+      <c r="Q170" t="s">
+        <v>730</v>
       </c>
       <c r="R170">
         <v>0</v>
@@ -15064,7 +15262,7 @@
         <v>79000</v>
       </c>
       <c r="U170" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="V170">
         <v>0</v>
@@ -15072,10 +15270,10 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="B171" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="C171" t="s">
         <v>249</v>
@@ -15119,8 +15317,8 @@
       <c r="P171" t="s">
         <v>17</v>
       </c>
-      <c r="Q171">
-        <v>0</v>
+      <c r="Q171" t="s">
+        <v>730</v>
       </c>
       <c r="R171">
         <v>0</v>
@@ -15132,7 +15330,7 @@
         <v>79000</v>
       </c>
       <c r="U171" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="V171">
         <v>0</v>
@@ -15143,7 +15341,7 @@
         <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="C172" t="s">
         <v>25</v>
@@ -15188,7 +15386,7 @@
         <v>17</v>
       </c>
       <c r="Q172" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -15200,7 +15398,7 @@
         <v>69000</v>
       </c>
       <c r="U172" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="V172">
         <v>0</v>
@@ -15211,7 +15409,7 @@
         <v>27</v>
       </c>
       <c r="B173" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="C173" t="s">
         <v>25</v>
@@ -15247,7 +15445,7 @@
         <v>1</v>
       </c>
       <c r="N173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O173">
         <v>10</v>
@@ -15256,7 +15454,7 @@
         <v>17</v>
       </c>
       <c r="Q173" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -15268,7 +15466,7 @@
         <v>69000</v>
       </c>
       <c r="U173" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="V173">
         <v>0</v>
@@ -15279,7 +15477,7 @@
         <v>114</v>
       </c>
       <c r="B174" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="C174" t="s">
         <v>25</v>
@@ -15324,7 +15522,7 @@
         <v>17</v>
       </c>
       <c r="Q174" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -15336,7 +15534,7 @@
         <v>69000</v>
       </c>
       <c r="U174" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="V174">
         <v>0</v>
@@ -15347,7 +15545,7 @@
         <v>165</v>
       </c>
       <c r="B175" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="C175" t="s">
         <v>25</v>
@@ -15392,7 +15590,7 @@
         <v>17</v>
       </c>
       <c r="Q175" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -15404,7 +15602,7 @@
         <v>69000</v>
       </c>
       <c r="U175" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="V175">
         <v>0</v>
@@ -15415,7 +15613,7 @@
         <v>112</v>
       </c>
       <c r="B176" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="C176" t="s">
         <v>25</v>
@@ -15460,7 +15658,7 @@
         <v>17</v>
       </c>
       <c r="Q176" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -15472,7 +15670,7 @@
         <v>69000</v>
       </c>
       <c r="U176" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="V176">
         <v>0</v>
@@ -15483,7 +15681,7 @@
         <v>157</v>
       </c>
       <c r="B177" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="C177" t="s">
         <v>25</v>
@@ -15528,7 +15726,7 @@
         <v>17</v>
       </c>
       <c r="Q177" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -15540,7 +15738,7 @@
         <v>69000</v>
       </c>
       <c r="U177" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="V177">
         <v>0</v>
@@ -15551,7 +15749,7 @@
         <v>143</v>
       </c>
       <c r="B178" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="C178" t="s">
         <v>25</v>
@@ -15572,7 +15770,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -15590,13 +15788,13 @@
         <v>0</v>
       </c>
       <c r="O178">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P178" t="s">
         <v>17</v>
       </c>
       <c r="Q178" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -15608,7 +15806,7 @@
         <v>69000</v>
       </c>
       <c r="U178" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="V178">
         <v>0</v>
@@ -15619,7 +15817,7 @@
         <v>183</v>
       </c>
       <c r="B179" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="C179" t="s">
         <v>25</v>
@@ -15664,7 +15862,7 @@
         <v>17</v>
       </c>
       <c r="Q179" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -15676,7 +15874,7 @@
         <v>69000</v>
       </c>
       <c r="U179" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="V179">
         <v>0</v>
@@ -15687,7 +15885,7 @@
         <v>111</v>
       </c>
       <c r="B180" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="C180" t="s">
         <v>25</v>
@@ -15732,7 +15930,7 @@
         <v>17</v>
       </c>
       <c r="Q180" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -15744,7 +15942,7 @@
         <v>69000</v>
       </c>
       <c r="U180" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="V180">
         <v>0</v>
@@ -15755,7 +15953,7 @@
         <v>264</v>
       </c>
       <c r="B181" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="C181" t="s">
         <v>25</v>
@@ -15800,7 +15998,7 @@
         <v>17</v>
       </c>
       <c r="Q181" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -15812,7 +16010,7 @@
         <v>69000</v>
       </c>
       <c r="U181" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="V181">
         <v>0</v>
@@ -15823,7 +16021,7 @@
         <v>28</v>
       </c>
       <c r="B182" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="C182" t="s">
         <v>25</v>
@@ -15868,7 +16066,7 @@
         <v>17</v>
       </c>
       <c r="Q182" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -15880,7 +16078,7 @@
         <v>69000</v>
       </c>
       <c r="U182" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="V182">
         <v>0</v>
@@ -15891,7 +16089,7 @@
         <v>29</v>
       </c>
       <c r="B183" t="s">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="C183" t="s">
         <v>25</v>
@@ -15936,7 +16134,7 @@
         <v>17</v>
       </c>
       <c r="Q183" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -15948,7 +16146,7 @@
         <v>69000</v>
       </c>
       <c r="U183" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="V183">
         <v>0</v>
@@ -15959,7 +16157,7 @@
         <v>159</v>
       </c>
       <c r="B184" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="C184" t="s">
         <v>25</v>
@@ -16004,7 +16202,7 @@
         <v>17</v>
       </c>
       <c r="Q184" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -16016,7 +16214,7 @@
         <v>69000</v>
       </c>
       <c r="U184" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="V184">
         <v>0</v>
@@ -16027,7 +16225,7 @@
         <v>109</v>
       </c>
       <c r="B185" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="C185" t="s">
         <v>25</v>
@@ -16072,7 +16270,7 @@
         <v>17</v>
       </c>
       <c r="Q185" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -16084,7 +16282,7 @@
         <v>69000</v>
       </c>
       <c r="U185" t="s">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="V185">
         <v>0</v>
@@ -16095,7 +16293,7 @@
         <v>162</v>
       </c>
       <c r="B186" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="C186" t="s">
         <v>25</v>
@@ -16140,7 +16338,7 @@
         <v>17</v>
       </c>
       <c r="Q186" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -16152,7 +16350,7 @@
         <v>69000</v>
       </c>
       <c r="U186" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="V186">
         <v>0</v>
@@ -16163,7 +16361,7 @@
         <v>40</v>
       </c>
       <c r="B187" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="C187" t="s">
         <v>25</v>
@@ -16208,7 +16406,7 @@
         <v>17</v>
       </c>
       <c r="Q187" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -16220,7 +16418,7 @@
         <v>69000</v>
       </c>
       <c r="U187" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="V187">
         <v>0</v>
@@ -16231,7 +16429,7 @@
         <v>42</v>
       </c>
       <c r="B188" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="C188" t="s">
         <v>25</v>
@@ -16276,7 +16474,7 @@
         <v>17</v>
       </c>
       <c r="Q188" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -16288,7 +16486,7 @@
         <v>69000</v>
       </c>
       <c r="U188" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="V188">
         <v>0</v>
@@ -16299,7 +16497,7 @@
         <v>43</v>
       </c>
       <c r="B189" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
       <c r="C189" t="s">
         <v>25</v>
@@ -16344,7 +16542,7 @@
         <v>17</v>
       </c>
       <c r="Q189" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -16356,7 +16554,7 @@
         <v>69000</v>
       </c>
       <c r="U189" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="V189">
         <v>0</v>
@@ -16367,7 +16565,7 @@
         <v>73</v>
       </c>
       <c r="B190" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="C190" t="s">
         <v>25</v>
@@ -16412,7 +16610,7 @@
         <v>17</v>
       </c>
       <c r="Q190" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -16424,7 +16622,7 @@
         <v>69000</v>
       </c>
       <c r="U190" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="V190">
         <v>0</v>
@@ -16435,7 +16633,7 @@
         <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="C191" t="s">
         <v>25</v>
@@ -16480,7 +16678,7 @@
         <v>17</v>
       </c>
       <c r="Q191" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -16492,7 +16690,7 @@
         <v>69000</v>
       </c>
       <c r="U191" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="V191">
         <v>0</v>
@@ -16503,7 +16701,7 @@
         <v>44</v>
       </c>
       <c r="B192" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="C192" t="s">
         <v>25</v>
@@ -16548,7 +16746,7 @@
         <v>17</v>
       </c>
       <c r="Q192" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -16560,7 +16758,7 @@
         <v>69000</v>
       </c>
       <c r="U192" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="V192">
         <v>0</v>
@@ -16571,7 +16769,7 @@
         <v>68</v>
       </c>
       <c r="B193" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="C193" t="s">
         <v>25</v>
@@ -16616,7 +16814,7 @@
         <v>17</v>
       </c>
       <c r="Q193" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -16628,7 +16826,7 @@
         <v>69000</v>
       </c>
       <c r="U193" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="V193">
         <v>0</v>
@@ -16639,7 +16837,7 @@
         <v>45</v>
       </c>
       <c r="B194" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="C194" t="s">
         <v>25</v>
@@ -16660,7 +16858,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -16678,13 +16876,13 @@
         <v>2</v>
       </c>
       <c r="O194">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P194" t="s">
         <v>17</v>
       </c>
       <c r="Q194" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -16696,7 +16894,7 @@
         <v>69000</v>
       </c>
       <c r="U194" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="V194">
         <v>0</v>
@@ -16707,7 +16905,7 @@
         <v>46</v>
       </c>
       <c r="B195" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="C195" t="s">
         <v>25</v>
@@ -16743,7 +16941,7 @@
         <v>8</v>
       </c>
       <c r="N195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O195">
         <v>10</v>
@@ -16752,7 +16950,7 @@
         <v>17</v>
       </c>
       <c r="Q195" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -16764,7 +16962,7 @@
         <v>69000</v>
       </c>
       <c r="U195" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="V195">
         <v>0</v>
@@ -16775,7 +16973,7 @@
         <v>66</v>
       </c>
       <c r="B196" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="C196" t="s">
         <v>25</v>
@@ -16820,7 +17018,7 @@
         <v>17</v>
       </c>
       <c r="Q196" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -16832,7 +17030,7 @@
         <v>69000</v>
       </c>
       <c r="U196" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="V196">
         <v>0</v>
@@ -16843,7 +17041,7 @@
         <v>246</v>
       </c>
       <c r="B197" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="C197" t="s">
         <v>25</v>
@@ -16888,7 +17086,7 @@
         <v>17</v>
       </c>
       <c r="Q197" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -16900,7 +17098,7 @@
         <v>69000</v>
       </c>
       <c r="U197" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="V197">
         <v>0</v>
@@ -16911,7 +17109,7 @@
         <v>74</v>
       </c>
       <c r="B198" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="C198" t="s">
         <v>25</v>
@@ -16956,7 +17154,7 @@
         <v>17</v>
       </c>
       <c r="Q198" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -16968,7 +17166,7 @@
         <v>69000</v>
       </c>
       <c r="U198" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="V198">
         <v>0</v>
@@ -16979,7 +17177,7 @@
         <v>69</v>
       </c>
       <c r="B199" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="C199" t="s">
         <v>25</v>
@@ -17024,7 +17222,7 @@
         <v>17</v>
       </c>
       <c r="Q199" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -17036,7 +17234,7 @@
         <v>69000</v>
       </c>
       <c r="U199" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="V199">
         <v>0</v>
@@ -17044,10 +17242,10 @@
     </row>
     <row r="200" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="B200" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="C200" t="s">
         <v>25</v>
@@ -17092,7 +17290,7 @@
         <v>17</v>
       </c>
       <c r="Q200" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -17104,7 +17302,7 @@
         <v>69000</v>
       </c>
       <c r="U200" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="V200">
         <v>0</v>
@@ -17115,7 +17313,7 @@
         <v>84</v>
       </c>
       <c r="B201" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="C201" t="s">
         <v>25</v>
@@ -17160,7 +17358,7 @@
         <v>17</v>
       </c>
       <c r="Q201" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -17172,7 +17370,7 @@
         <v>69000</v>
       </c>
       <c r="U201" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="V201">
         <v>0</v>
@@ -17183,7 +17381,7 @@
         <v>232</v>
       </c>
       <c r="B202" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="C202" t="s">
         <v>25</v>
@@ -17228,7 +17426,7 @@
         <v>17</v>
       </c>
       <c r="Q202" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -17240,7 +17438,7 @@
         <v>69000</v>
       </c>
       <c r="U202" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="V202">
         <v>0</v>
@@ -17251,7 +17449,7 @@
         <v>60</v>
       </c>
       <c r="B203" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="C203" t="s">
         <v>25</v>
@@ -17296,7 +17494,7 @@
         <v>17</v>
       </c>
       <c r="Q203" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -17308,7 +17506,7 @@
         <v>69000</v>
       </c>
       <c r="U203" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="V203">
         <v>0</v>
@@ -17319,7 +17517,7 @@
         <v>197</v>
       </c>
       <c r="B204" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="C204" t="s">
         <v>25</v>
@@ -17364,7 +17562,7 @@
         <v>17</v>
       </c>
       <c r="Q204" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -17376,7 +17574,7 @@
         <v>69000</v>
       </c>
       <c r="U204" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="V204">
         <v>0</v>
@@ -17387,7 +17585,7 @@
         <v>89</v>
       </c>
       <c r="B205" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="C205" t="s">
         <v>25</v>
@@ -17432,7 +17630,7 @@
         <v>17</v>
       </c>
       <c r="Q205" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -17444,7 +17642,7 @@
         <v>69000</v>
       </c>
       <c r="U205" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="V205">
         <v>0</v>
@@ -17452,10 +17650,10 @@
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="B206" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="C206" t="s">
         <v>25</v>
@@ -17500,7 +17698,7 @@
         <v>17</v>
       </c>
       <c r="Q206" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -17512,7 +17710,7 @@
         <v>69000</v>
       </c>
       <c r="U206" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="V206">
         <v>0</v>
@@ -17523,7 +17721,7 @@
         <v>202</v>
       </c>
       <c r="B207" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="C207" t="s">
         <v>25</v>
@@ -17568,7 +17766,7 @@
         <v>17</v>
       </c>
       <c r="Q207" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -17580,7 +17778,7 @@
         <v>69000</v>
       </c>
       <c r="U207" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="V207">
         <v>0</v>
@@ -17591,7 +17789,7 @@
         <v>199</v>
       </c>
       <c r="B208" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="C208" t="s">
         <v>25</v>
@@ -17636,7 +17834,7 @@
         <v>17</v>
       </c>
       <c r="Q208" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -17648,7 +17846,7 @@
         <v>69000</v>
       </c>
       <c r="U208" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="V208">
         <v>0</v>
@@ -17656,10 +17854,10 @@
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="B209" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="C209" t="s">
         <v>25</v>
@@ -17704,7 +17902,7 @@
         <v>17</v>
       </c>
       <c r="Q209" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -17716,7 +17914,7 @@
         <v>69000</v>
       </c>
       <c r="U209" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="V209">
         <v>0</v>
@@ -17727,7 +17925,7 @@
         <v>205</v>
       </c>
       <c r="B210" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="C210" t="s">
         <v>25</v>
@@ -17772,7 +17970,7 @@
         <v>17</v>
       </c>
       <c r="Q210" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -17784,7 +17982,7 @@
         <v>69000</v>
       </c>
       <c r="U210" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="V210">
         <v>0</v>
@@ -17795,7 +17993,7 @@
         <v>200</v>
       </c>
       <c r="B211" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="C211" t="s">
         <v>25</v>
@@ -17840,7 +18038,7 @@
         <v>17</v>
       </c>
       <c r="Q211" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -17852,7 +18050,7 @@
         <v>69000</v>
       </c>
       <c r="U211" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="V211">
         <v>0</v>
@@ -17860,10 +18058,10 @@
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="B212" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="C212" t="s">
         <v>25</v>
@@ -17908,7 +18106,7 @@
         <v>17</v>
       </c>
       <c r="Q212" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -17920,7 +18118,7 @@
         <v>69000</v>
       </c>
       <c r="U212" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="V212">
         <v>0</v>
@@ -17931,7 +18129,7 @@
         <v>201</v>
       </c>
       <c r="B213" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="C213" t="s">
         <v>25</v>
@@ -17976,7 +18174,7 @@
         <v>17</v>
       </c>
       <c r="Q213" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -17988,7 +18186,7 @@
         <v>69000</v>
       </c>
       <c r="U213" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="V213">
         <v>0</v>
@@ -17999,7 +18197,7 @@
         <v>47</v>
       </c>
       <c r="B214" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="C214" t="s">
         <v>25</v>
@@ -18044,7 +18242,7 @@
         <v>17</v>
       </c>
       <c r="Q214" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -18056,7 +18254,7 @@
         <v>69000</v>
       </c>
       <c r="U214" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="V214">
         <v>0</v>
@@ -18067,7 +18265,7 @@
         <v>110</v>
       </c>
       <c r="B215" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="C215" t="s">
         <v>25</v>
@@ -18112,7 +18310,7 @@
         <v>17</v>
       </c>
       <c r="Q215" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -18124,7 +18322,7 @@
         <v>69000</v>
       </c>
       <c r="U215" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="V215">
         <v>0</v>
@@ -18135,7 +18333,7 @@
         <v>229</v>
       </c>
       <c r="B216" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="C216" t="s">
         <v>25</v>
@@ -18180,7 +18378,7 @@
         <v>17</v>
       </c>
       <c r="Q216" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -18192,7 +18390,7 @@
         <v>69000</v>
       </c>
       <c r="U216" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="V216">
         <v>0</v>
@@ -18203,7 +18401,7 @@
         <v>72</v>
       </c>
       <c r="B217" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="C217" t="s">
         <v>25</v>
@@ -18239,7 +18437,7 @@
         <v>6</v>
       </c>
       <c r="N217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217">
         <v>6</v>
@@ -18248,7 +18446,7 @@
         <v>17</v>
       </c>
       <c r="Q217" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -18260,7 +18458,7 @@
         <v>69000</v>
       </c>
       <c r="U217" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="V217">
         <v>0</v>
@@ -18271,7 +18469,7 @@
         <v>100</v>
       </c>
       <c r="B218" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="C218" t="s">
         <v>25</v>
@@ -18316,7 +18514,7 @@
         <v>17</v>
       </c>
       <c r="Q218" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -18328,7 +18526,7 @@
         <v>69000</v>
       </c>
       <c r="U218" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="V218">
         <v>0</v>
@@ -18339,7 +18537,7 @@
         <v>104</v>
       </c>
       <c r="B219" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="C219" t="s">
         <v>25</v>
@@ -18384,7 +18582,7 @@
         <v>17</v>
       </c>
       <c r="Q219" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -18396,7 +18594,7 @@
         <v>69000</v>
       </c>
       <c r="U219" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="V219">
         <v>0</v>
@@ -18407,7 +18605,7 @@
         <v>99</v>
       </c>
       <c r="B220" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="C220" t="s">
         <v>25</v>
@@ -18452,7 +18650,7 @@
         <v>17</v>
       </c>
       <c r="Q220" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -18464,7 +18662,7 @@
         <v>69000</v>
       </c>
       <c r="U220" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="V220">
         <v>0</v>
@@ -18475,7 +18673,7 @@
         <v>227</v>
       </c>
       <c r="B221" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="C221" t="s">
         <v>25</v>
@@ -18520,7 +18718,7 @@
         <v>17</v>
       </c>
       <c r="Q221" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -18532,7 +18730,7 @@
         <v>69000</v>
       </c>
       <c r="U221" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="V221">
         <v>0</v>
@@ -18543,7 +18741,7 @@
         <v>80</v>
       </c>
       <c r="B222" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="C222" t="s">
         <v>25</v>
@@ -18588,7 +18786,7 @@
         <v>17</v>
       </c>
       <c r="Q222" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -18600,7 +18798,7 @@
         <v>69000</v>
       </c>
       <c r="U222" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="V222">
         <v>0</v>
@@ -18611,7 +18809,7 @@
         <v>87</v>
       </c>
       <c r="B223" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="C223" t="s">
         <v>25</v>
@@ -18656,7 +18854,7 @@
         <v>17</v>
       </c>
       <c r="Q223" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -18668,7 +18866,7 @@
         <v>69000</v>
       </c>
       <c r="U223" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="V223">
         <v>0</v>
@@ -18679,7 +18877,7 @@
         <v>49</v>
       </c>
       <c r="B224" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="C224" t="s">
         <v>25</v>
@@ -18715,7 +18913,7 @@
         <v>7</v>
       </c>
       <c r="N224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O224">
         <v>14</v>
@@ -18724,7 +18922,7 @@
         <v>17</v>
       </c>
       <c r="Q224" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -18736,7 +18934,7 @@
         <v>69000</v>
       </c>
       <c r="U224" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="V224">
         <v>0</v>
@@ -18747,7 +18945,7 @@
         <v>116</v>
       </c>
       <c r="B225" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="C225" t="s">
         <v>25</v>
@@ -18792,7 +18990,7 @@
         <v>17</v>
       </c>
       <c r="Q225" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -18804,7 +19002,7 @@
         <v>69000</v>
       </c>
       <c r="U225" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="V225">
         <v>0</v>
@@ -18815,7 +19013,7 @@
         <v>115</v>
       </c>
       <c r="B226" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="C226" t="s">
         <v>25</v>
@@ -18860,7 +19058,7 @@
         <v>17</v>
       </c>
       <c r="Q226" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -18872,7 +19070,7 @@
         <v>69000</v>
       </c>
       <c r="U226" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="V226">
         <v>0</v>
@@ -18883,7 +19081,7 @@
         <v>71</v>
       </c>
       <c r="B227" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="C227" t="s">
         <v>25</v>
@@ -18928,7 +19126,7 @@
         <v>17</v>
       </c>
       <c r="Q227" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -18940,7 +19138,7 @@
         <v>69000</v>
       </c>
       <c r="U227" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="V227">
         <v>0</v>
@@ -18951,7 +19149,7 @@
         <v>77</v>
       </c>
       <c r="B228" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="C228" t="s">
         <v>25</v>
@@ -18987,7 +19185,7 @@
         <v>12</v>
       </c>
       <c r="N228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O228">
         <v>19</v>
@@ -18996,7 +19194,7 @@
         <v>17</v>
       </c>
       <c r="Q228" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -19008,7 +19206,7 @@
         <v>69000</v>
       </c>
       <c r="U228" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="V228">
         <v>0</v>
@@ -19019,7 +19217,7 @@
         <v>51</v>
       </c>
       <c r="B229" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
       <c r="C229" t="s">
         <v>25</v>
@@ -19064,7 +19262,7 @@
         <v>17</v>
       </c>
       <c r="Q229" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -19076,7 +19274,7 @@
         <v>69000</v>
       </c>
       <c r="U229" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="V229">
         <v>0</v>
@@ -19087,7 +19285,7 @@
         <v>52</v>
       </c>
       <c r="B230" t="s">
-        <v>859</v>
+        <v>874</v>
       </c>
       <c r="C230" t="s">
         <v>25</v>
@@ -19132,7 +19330,7 @@
         <v>17</v>
       </c>
       <c r="Q230" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -19144,7 +19342,7 @@
         <v>69000</v>
       </c>
       <c r="U230" t="s">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="V230">
         <v>0</v>
@@ -19155,7 +19353,7 @@
         <v>158</v>
       </c>
       <c r="B231" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="C231" t="s">
         <v>25</v>
@@ -19200,7 +19398,7 @@
         <v>17</v>
       </c>
       <c r="Q231" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -19212,7 +19410,7 @@
         <v>69000</v>
       </c>
       <c r="U231" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="V231">
         <v>0</v>
@@ -19241,7 +19439,7 @@
         <v>0</v>
       </c>
       <c r="I232">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -19259,10 +19457,13 @@
         <v>1</v>
       </c>
       <c r="O232">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P232" t="s">
         <v>124</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>878</v>
       </c>
       <c r="S232">
         <v>35900</v>
@@ -19323,6 +19524,9 @@
       <c r="P233" t="s">
         <v>124</v>
       </c>
+      <c r="Q233" t="s">
+        <v>879</v>
+      </c>
       <c r="S233">
         <v>35900</v>
       </c>
@@ -19382,6 +19586,9 @@
       <c r="P234" t="s">
         <v>124</v>
       </c>
+      <c r="Q234" t="s">
+        <v>880</v>
+      </c>
       <c r="S234">
         <v>35900</v>
       </c>
@@ -19441,6 +19648,9 @@
       <c r="P235" t="s">
         <v>124</v>
       </c>
+      <c r="Q235" t="s">
+        <v>881</v>
+      </c>
       <c r="S235">
         <v>35900</v>
       </c>
@@ -19500,6 +19710,9 @@
       <c r="P236" t="s">
         <v>124</v>
       </c>
+      <c r="Q236" t="s">
+        <v>882</v>
+      </c>
       <c r="S236">
         <v>42900</v>
       </c>
@@ -19559,6 +19772,9 @@
       <c r="P237" t="s">
         <v>124</v>
       </c>
+      <c r="Q237" t="s">
+        <v>883</v>
+      </c>
       <c r="S237">
         <v>42900</v>
       </c>
@@ -19610,13 +19826,16 @@
         <v>1</v>
       </c>
       <c r="N238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O238">
         <v>7</v>
       </c>
       <c r="P238" t="s">
         <v>124</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>884</v>
       </c>
       <c r="S238">
         <v>42900</v>
@@ -19677,6 +19896,9 @@
       <c r="P239" t="s">
         <v>124</v>
       </c>
+      <c r="Q239" t="s">
+        <v>885</v>
+      </c>
       <c r="S239">
         <v>42900</v>
       </c>
@@ -19736,6 +19958,9 @@
       <c r="P240" t="s">
         <v>124</v>
       </c>
+      <c r="Q240" t="s">
+        <v>886</v>
+      </c>
       <c r="S240">
         <v>42900</v>
       </c>
@@ -19772,7 +19997,7 @@
         <v>0</v>
       </c>
       <c r="I241">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -19790,10 +20015,13 @@
         <v>1</v>
       </c>
       <c r="O241">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P241" t="s">
         <v>124</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>887</v>
       </c>
       <c r="S241">
         <v>42900</v>
@@ -19854,6 +20082,9 @@
       <c r="P242" t="s">
         <v>124</v>
       </c>
+      <c r="Q242" t="s">
+        <v>888</v>
+      </c>
       <c r="S242">
         <v>42900</v>
       </c>
@@ -19913,6 +20144,9 @@
       <c r="P243" t="s">
         <v>124</v>
       </c>
+      <c r="Q243" t="s">
+        <v>889</v>
+      </c>
       <c r="S243">
         <v>42900</v>
       </c>
@@ -19972,6 +20206,9 @@
       <c r="P244" t="s">
         <v>124</v>
       </c>
+      <c r="Q244" t="s">
+        <v>890</v>
+      </c>
       <c r="S244">
         <v>42900</v>
       </c>
@@ -20031,6 +20268,9 @@
       <c r="P245" t="s">
         <v>124</v>
       </c>
+      <c r="Q245" t="s">
+        <v>891</v>
+      </c>
       <c r="S245">
         <v>42900</v>
       </c>
@@ -20090,6 +20330,9 @@
       <c r="P246" t="s">
         <v>124</v>
       </c>
+      <c r="Q246" t="s">
+        <v>892</v>
+      </c>
       <c r="S246">
         <v>42900</v>
       </c>
@@ -20149,6 +20392,9 @@
       <c r="P247" t="s">
         <v>124</v>
       </c>
+      <c r="Q247" t="s">
+        <v>893</v>
+      </c>
       <c r="S247">
         <v>42900</v>
       </c>
@@ -20208,6 +20454,9 @@
       <c r="P248" t="s">
         <v>124</v>
       </c>
+      <c r="Q248" t="s">
+        <v>894</v>
+      </c>
       <c r="S248">
         <v>42900</v>
       </c>
@@ -20267,6 +20516,9 @@
       <c r="P249" t="s">
         <v>124</v>
       </c>
+      <c r="Q249" t="s">
+        <v>895</v>
+      </c>
       <c r="S249">
         <v>42900</v>
       </c>
@@ -20326,6 +20578,9 @@
       <c r="P250" t="s">
         <v>124</v>
       </c>
+      <c r="Q250" t="s">
+        <v>896</v>
+      </c>
       <c r="S250">
         <v>42900</v>
       </c>
@@ -20385,6 +20640,9 @@
       <c r="P251" t="s">
         <v>124</v>
       </c>
+      <c r="Q251" t="s">
+        <v>897</v>
+      </c>
       <c r="S251">
         <v>42900</v>
       </c>
@@ -20444,6 +20702,9 @@
       <c r="P252" t="s">
         <v>124</v>
       </c>
+      <c r="Q252" t="s">
+        <v>898</v>
+      </c>
       <c r="S252">
         <v>39900</v>
       </c>
@@ -20503,6 +20764,9 @@
       <c r="P253" t="s">
         <v>124</v>
       </c>
+      <c r="Q253" t="s">
+        <v>899</v>
+      </c>
       <c r="S253">
         <v>39900</v>
       </c>
@@ -20562,6 +20826,9 @@
       <c r="P254" t="s">
         <v>124</v>
       </c>
+      <c r="Q254" t="s">
+        <v>900</v>
+      </c>
       <c r="S254">
         <v>39900</v>
       </c>
@@ -20621,6 +20888,9 @@
       <c r="P255" t="s">
         <v>124</v>
       </c>
+      <c r="Q255" t="s">
+        <v>901</v>
+      </c>
       <c r="S255">
         <v>39900</v>
       </c>
@@ -20657,7 +20927,7 @@
         <v>0</v>
       </c>
       <c r="I256">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -20675,10 +20945,13 @@
         <v>0</v>
       </c>
       <c r="O256">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P256" t="s">
         <v>124</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>902</v>
       </c>
       <c r="S256">
         <v>33000</v>
@@ -20739,6 +21012,9 @@
       <c r="P257" t="s">
         <v>124</v>
       </c>
+      <c r="Q257" t="s">
+        <v>903</v>
+      </c>
       <c r="S257">
         <v>33000</v>
       </c>
@@ -20775,7 +21051,7 @@
         <v>0</v>
       </c>
       <c r="I258">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J258">
         <v>0</v>
@@ -20793,10 +21069,13 @@
         <v>1</v>
       </c>
       <c r="O258">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P258" t="s">
         <v>124</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>904</v>
       </c>
       <c r="S258">
         <v>33000</v>
@@ -20857,6 +21136,9 @@
       <c r="P259" t="s">
         <v>124</v>
       </c>
+      <c r="Q259" t="s">
+        <v>905</v>
+      </c>
       <c r="S259">
         <v>33000</v>
       </c>
@@ -20875,7 +21157,7 @@
         <v>178</v>
       </c>
       <c r="B260" t="s">
-        <v>863</v>
+        <v>906</v>
       </c>
       <c r="C260" t="s">
         <v>179</v>
@@ -20915,6 +21197,9 @@
       </c>
       <c r="P260" t="s">
         <v>182</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>907</v>
       </c>
       <c r="S260">
         <v>6900</v>
@@ -20931,7 +21216,7 @@
         <v>203</v>
       </c>
       <c r="B261" t="s">
-        <v>864</v>
+        <v>908</v>
       </c>
       <c r="C261" t="s">
         <v>179</v>
@@ -20971,6 +21256,9 @@
       </c>
       <c r="P261" t="s">
         <v>182</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>909</v>
       </c>
       <c r="S261">
         <v>8400</v>
@@ -20987,7 +21275,7 @@
         <v>189</v>
       </c>
       <c r="B262" t="s">
-        <v>865</v>
+        <v>910</v>
       </c>
       <c r="C262" t="s">
         <v>179</v>
@@ -21027,6 +21315,9 @@
       </c>
       <c r="P262" t="s">
         <v>182</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>911</v>
       </c>
       <c r="S262">
         <v>9900</v>
@@ -21043,7 +21334,7 @@
         <v>192</v>
       </c>
       <c r="B263" t="s">
-        <v>866</v>
+        <v>912</v>
       </c>
       <c r="C263" t="s">
         <v>179</v>
@@ -21076,13 +21367,16 @@
         <v>4</v>
       </c>
       <c r="N263">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O263">
         <v>91</v>
       </c>
       <c r="P263" t="s">
         <v>182</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>913</v>
       </c>
       <c r="S263">
         <v>8900</v>
@@ -21099,7 +21393,7 @@
         <v>235</v>
       </c>
       <c r="B264" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="C264" t="s">
         <v>236</v>
@@ -21136,6 +21430,9 @@
       </c>
       <c r="P264" t="s">
         <v>182</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>915</v>
       </c>
       <c r="S264">
         <v>5900</v>
@@ -21149,7 +21446,7 @@
         <v>237</v>
       </c>
       <c r="B265" t="s">
-        <v>868</v>
+        <v>916</v>
       </c>
       <c r="C265" t="s">
         <v>236</v>
@@ -21186,6 +21483,9 @@
       </c>
       <c r="P265" t="s">
         <v>182</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>917</v>
       </c>
       <c r="S265">
         <v>5900</v>
@@ -21199,7 +21499,7 @@
         <v>238</v>
       </c>
       <c r="B266" t="s">
-        <v>869</v>
+        <v>918</v>
       </c>
       <c r="C266" t="s">
         <v>236</v>
@@ -21246,7 +21546,7 @@
         <v>239</v>
       </c>
       <c r="B267" t="s">
-        <v>870</v>
+        <v>919</v>
       </c>
       <c r="C267" t="s">
         <v>236</v>
@@ -21293,7 +21593,7 @@
         <v>240</v>
       </c>
       <c r="B268" t="s">
-        <v>871</v>
+        <v>920</v>
       </c>
       <c r="C268" t="s">
         <v>236</v>
@@ -21340,7 +21640,7 @@
         <v>241</v>
       </c>
       <c r="B269" t="s">
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="C269" t="s">
         <v>236</v>
@@ -21387,7 +21687,7 @@
         <v>242</v>
       </c>
       <c r="B270" t="s">
-        <v>873</v>
+        <v>922</v>
       </c>
       <c r="C270" t="s">
         <v>236</v>
@@ -21434,7 +21734,7 @@
         <v>243</v>
       </c>
       <c r="B271" t="s">
-        <v>874</v>
+        <v>923</v>
       </c>
       <c r="C271" t="s">
         <v>236</v>
@@ -21478,13 +21778,13 @@
     </row>
     <row r="272" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>875</v>
+        <v>924</v>
       </c>
       <c r="B272" t="s">
-        <v>876</v>
+        <v>925</v>
       </c>
       <c r="C272" t="s">
-        <v>877</v>
+        <v>926</v>
       </c>
       <c r="E272" t="s">
         <v>123</v>
@@ -21522,13 +21822,13 @@
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>878</v>
+        <v>927</v>
       </c>
       <c r="B273" t="s">
-        <v>879</v>
+        <v>928</v>
       </c>
       <c r="C273" t="s">
-        <v>877</v>
+        <v>926</v>
       </c>
       <c r="E273" t="s">
         <v>123</v>
@@ -21566,13 +21866,13 @@
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>880</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s">
-        <v>881</v>
+        <v>930</v>
       </c>
       <c r="C274" t="s">
-        <v>882</v>
+        <v>931</v>
       </c>
       <c r="E274" t="s">
         <v>123</v>
@@ -21602,7 +21902,10 @@
         <v>0</v>
       </c>
       <c r="P274" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>933</v>
       </c>
       <c r="V274">
         <v>0</v>
@@ -21610,13 +21913,13 @@
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>884</v>
+        <v>934</v>
       </c>
       <c r="B275" t="s">
-        <v>885</v>
+        <v>935</v>
       </c>
       <c r="C275" t="s">
-        <v>882</v>
+        <v>931</v>
       </c>
       <c r="E275" t="s">
         <v>123</v>
@@ -21646,7 +21949,10 @@
         <v>0</v>
       </c>
       <c r="P275" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>936</v>
       </c>
       <c r="V275">
         <v>0</v>
@@ -21654,13 +21960,13 @@
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>886</v>
+        <v>937</v>
       </c>
       <c r="B276" t="s">
-        <v>887</v>
+        <v>938</v>
       </c>
       <c r="C276" t="s">
-        <v>882</v>
+        <v>931</v>
       </c>
       <c r="E276" t="s">
         <v>123</v>
@@ -21690,7 +21996,10 @@
         <v>0</v>
       </c>
       <c r="P276" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>939</v>
       </c>
       <c r="V276">
         <v>0</v>
@@ -21698,13 +22007,13 @@
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>888</v>
+        <v>940</v>
       </c>
       <c r="B277" t="s">
-        <v>889</v>
+        <v>941</v>
       </c>
       <c r="C277" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E277" t="s">
         <v>123</v>
@@ -21734,7 +22043,10 @@
         <v>0</v>
       </c>
       <c r="P277" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>943</v>
       </c>
       <c r="V277">
         <v>0</v>
@@ -21742,13 +22054,13 @@
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>891</v>
+        <v>944</v>
       </c>
       <c r="B278" t="s">
-        <v>892</v>
+        <v>945</v>
       </c>
       <c r="C278" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E278" t="s">
         <v>123</v>
@@ -21778,7 +22090,10 @@
         <v>0</v>
       </c>
       <c r="P278" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>946</v>
       </c>
       <c r="V278">
         <v>0</v>
@@ -21786,13 +22101,13 @@
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>893</v>
+        <v>947</v>
       </c>
       <c r="B279" t="s">
-        <v>894</v>
+        <v>948</v>
       </c>
       <c r="C279" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E279" t="s">
         <v>123</v>
@@ -21822,7 +22137,10 @@
         <v>0</v>
       </c>
       <c r="P279" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>949</v>
       </c>
       <c r="V279">
         <v>0</v>
@@ -21830,13 +22148,13 @@
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>895</v>
+        <v>950</v>
       </c>
       <c r="B280" t="s">
-        <v>896</v>
+        <v>951</v>
       </c>
       <c r="C280" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E280" t="s">
         <v>123</v>
@@ -21866,7 +22184,10 @@
         <v>0</v>
       </c>
       <c r="P280" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>952</v>
       </c>
       <c r="V280">
         <v>0</v>
@@ -21874,13 +22195,13 @@
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>897</v>
+        <v>953</v>
       </c>
       <c r="B281" t="s">
-        <v>898</v>
+        <v>954</v>
       </c>
       <c r="C281" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E281" t="s">
         <v>123</v>
@@ -21910,7 +22231,10 @@
         <v>0</v>
       </c>
       <c r="P281" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>955</v>
       </c>
       <c r="V281">
         <v>0</v>
@@ -21918,13 +22242,13 @@
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>899</v>
+        <v>956</v>
       </c>
       <c r="B282" t="s">
-        <v>900</v>
+        <v>957</v>
       </c>
       <c r="C282" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E282" t="s">
         <v>123</v>
@@ -21954,7 +22278,10 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>958</v>
       </c>
       <c r="V282">
         <v>0</v>
@@ -21962,13 +22289,13 @@
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>901</v>
+        <v>959</v>
       </c>
       <c r="B283" t="s">
-        <v>902</v>
+        <v>960</v>
       </c>
       <c r="C283" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E283" t="s">
         <v>123</v>
@@ -21998,7 +22325,10 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>961</v>
       </c>
       <c r="V283">
         <v>0</v>
@@ -22006,13 +22336,13 @@
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>903</v>
+        <v>962</v>
       </c>
       <c r="B284" t="s">
-        <v>904</v>
+        <v>963</v>
       </c>
       <c r="C284" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E284" t="s">
         <v>123</v>
@@ -22042,7 +22372,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V284">
         <v>0</v>
@@ -22050,13 +22380,13 @@
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>905</v>
+        <v>964</v>
       </c>
       <c r="B285" t="s">
-        <v>906</v>
+        <v>965</v>
       </c>
       <c r="C285" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="E285" t="s">
         <v>123</v>
@@ -22086,7 +22416,10 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>966</v>
       </c>
       <c r="V285">
         <v>0</v>
@@ -22094,13 +22427,13 @@
     </row>
     <row r="286" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>907</v>
+        <v>967</v>
       </c>
       <c r="B286" t="s">
-        <v>908</v>
+        <v>968</v>
       </c>
       <c r="C286" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E286" t="s">
         <v>123</v>
@@ -22130,7 +22463,7 @@
         <v>0</v>
       </c>
       <c r="P286" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V286">
         <v>0</v>
@@ -22138,13 +22471,13 @@
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>910</v>
+        <v>970</v>
       </c>
       <c r="B287" t="s">
-        <v>911</v>
+        <v>971</v>
       </c>
       <c r="C287" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E287" t="s">
         <v>123</v>
@@ -22174,7 +22507,10 @@
         <v>0</v>
       </c>
       <c r="P287" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>972</v>
       </c>
       <c r="V287">
         <v>0</v>
@@ -22182,13 +22518,13 @@
     </row>
     <row r="288" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>912</v>
+        <v>973</v>
       </c>
       <c r="B288" t="s">
-        <v>913</v>
+        <v>974</v>
       </c>
       <c r="C288" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E288" t="s">
         <v>123</v>
@@ -22218,7 +22554,10 @@
         <v>0</v>
       </c>
       <c r="P288" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>975</v>
       </c>
       <c r="V288">
         <v>0</v>
@@ -22226,13 +22565,13 @@
     </row>
     <row r="289" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>914</v>
+        <v>976</v>
       </c>
       <c r="B289" t="s">
-        <v>915</v>
+        <v>977</v>
       </c>
       <c r="C289" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E289" t="s">
         <v>123</v>
@@ -22262,7 +22601,10 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>978</v>
       </c>
       <c r="V289">
         <v>0</v>
@@ -22270,13 +22612,13 @@
     </row>
     <row r="290" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>916</v>
+        <v>979</v>
       </c>
       <c r="B290" t="s">
-        <v>917</v>
+        <v>980</v>
       </c>
       <c r="C290" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E290" t="s">
         <v>123</v>
@@ -22306,7 +22648,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V290">
         <v>0</v>
@@ -22314,13 +22656,13 @@
     </row>
     <row r="291" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>918</v>
+        <v>981</v>
       </c>
       <c r="B291" t="s">
-        <v>919</v>
+        <v>982</v>
       </c>
       <c r="C291" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E291" t="s">
         <v>123</v>
@@ -22350,7 +22692,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V291">
         <v>0</v>
@@ -22358,13 +22700,13 @@
     </row>
     <row r="292" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>920</v>
+        <v>983</v>
       </c>
       <c r="B292" t="s">
-        <v>921</v>
+        <v>984</v>
       </c>
       <c r="C292" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E292" t="s">
         <v>123</v>
@@ -22394,7 +22736,10 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>985</v>
       </c>
       <c r="V292">
         <v>0</v>
@@ -22402,13 +22747,13 @@
     </row>
     <row r="293" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>922</v>
+        <v>986</v>
       </c>
       <c r="B293" t="s">
-        <v>923</v>
+        <v>987</v>
       </c>
       <c r="C293" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E293" t="s">
         <v>123</v>
@@ -22438,7 +22783,10 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>988</v>
       </c>
       <c r="V293">
         <v>0</v>
@@ -22446,13 +22794,13 @@
     </row>
     <row r="294" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>924</v>
+        <v>989</v>
       </c>
       <c r="B294" t="s">
-        <v>925</v>
+        <v>990</v>
       </c>
       <c r="C294" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E294" t="s">
         <v>123</v>
@@ -22482,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V294">
         <v>0</v>
@@ -22490,13 +22838,13 @@
     </row>
     <row r="295" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>926</v>
+        <v>991</v>
       </c>
       <c r="B295" t="s">
-        <v>927</v>
+        <v>992</v>
       </c>
       <c r="C295" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E295" t="s">
         <v>123</v>
@@ -22526,7 +22874,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V295">
         <v>0</v>
@@ -22534,13 +22882,13 @@
     </row>
     <row r="296" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>928</v>
+        <v>993</v>
       </c>
       <c r="B296" t="s">
-        <v>929</v>
+        <v>994</v>
       </c>
       <c r="C296" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E296" t="s">
         <v>123</v>
@@ -22570,7 +22918,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V296">
         <v>0</v>
@@ -22578,13 +22926,13 @@
     </row>
     <row r="297" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>930</v>
+        <v>995</v>
       </c>
       <c r="B297" t="s">
-        <v>931</v>
+        <v>996</v>
       </c>
       <c r="C297" t="s">
-        <v>909</v>
+        <v>969</v>
       </c>
       <c r="E297" t="s">
         <v>123</v>
@@ -22614,7 +22962,10 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>883</v>
+        <v>932</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>997</v>
       </c>
       <c r="V297">
         <v>0</v>
@@ -22622,13 +22973,13 @@
     </row>
     <row r="298" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>932</v>
+        <v>998</v>
       </c>
       <c r="B298" t="s">
-        <v>933</v>
+        <v>999</v>
       </c>
       <c r="C298" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E298" t="s">
         <v>123</v>
@@ -22658,7 +23009,7 @@
         <v>0</v>
       </c>
       <c r="P298" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V298">
         <v>0</v>
@@ -22666,13 +23017,13 @@
     </row>
     <row r="299" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>935</v>
+        <v>1001</v>
       </c>
       <c r="B299" t="s">
-        <v>936</v>
+        <v>1002</v>
       </c>
       <c r="C299" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E299" t="s">
         <v>123</v>
@@ -22702,7 +23053,7 @@
         <v>0</v>
       </c>
       <c r="P299" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V299">
         <v>0</v>
@@ -22710,13 +23061,13 @@
     </row>
     <row r="300" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>937</v>
+        <v>1003</v>
       </c>
       <c r="B300" t="s">
-        <v>938</v>
+        <v>1004</v>
       </c>
       <c r="C300" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E300" t="s">
         <v>123</v>
@@ -22746,7 +23097,7 @@
         <v>0</v>
       </c>
       <c r="P300" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V300">
         <v>0</v>
@@ -22754,13 +23105,13 @@
     </row>
     <row r="301" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>939</v>
+        <v>1005</v>
       </c>
       <c r="B301" t="s">
-        <v>940</v>
+        <v>1006</v>
       </c>
       <c r="C301" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E301" t="s">
         <v>123</v>
@@ -22790,7 +23141,7 @@
         <v>0</v>
       </c>
       <c r="P301" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V301">
         <v>0</v>
@@ -22798,13 +23149,13 @@
     </row>
     <row r="302" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>941</v>
+        <v>1007</v>
       </c>
       <c r="B302" t="s">
-        <v>942</v>
+        <v>1008</v>
       </c>
       <c r="C302" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E302" t="s">
         <v>123</v>
@@ -22834,7 +23185,7 @@
         <v>0</v>
       </c>
       <c r="P302" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V302">
         <v>0</v>
@@ -22842,13 +23193,13 @@
     </row>
     <row r="303" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>943</v>
+        <v>1009</v>
       </c>
       <c r="B303" t="s">
-        <v>944</v>
+        <v>1010</v>
       </c>
       <c r="C303" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E303" t="s">
         <v>123</v>
@@ -22878,7 +23229,7 @@
         <v>0</v>
       </c>
       <c r="P303" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V303">
         <v>0</v>
@@ -22886,13 +23237,13 @@
     </row>
     <row r="304" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>945</v>
+        <v>1011</v>
       </c>
       <c r="B304" t="s">
-        <v>946</v>
+        <v>1012</v>
       </c>
       <c r="C304" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E304" t="s">
         <v>123</v>
@@ -22922,7 +23273,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V304">
         <v>0</v>
@@ -22930,13 +23281,13 @@
     </row>
     <row r="305" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>947</v>
+        <v>1013</v>
       </c>
       <c r="B305" t="s">
-        <v>948</v>
+        <v>1014</v>
       </c>
       <c r="C305" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E305" t="s">
         <v>123</v>
@@ -22966,7 +23317,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V305">
         <v>0</v>
@@ -22974,13 +23325,13 @@
     </row>
     <row r="306" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>949</v>
+        <v>1015</v>
       </c>
       <c r="B306" t="s">
-        <v>950</v>
+        <v>1016</v>
       </c>
       <c r="C306" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E306" t="s">
         <v>123</v>
@@ -23010,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V306">
         <v>0</v>
@@ -23018,13 +23369,13 @@
     </row>
     <row r="307" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>951</v>
+        <v>1017</v>
       </c>
       <c r="B307" t="s">
-        <v>952</v>
+        <v>1018</v>
       </c>
       <c r="C307" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E307" t="s">
         <v>123</v>
@@ -23054,7 +23405,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V307">
         <v>0</v>
@@ -23062,13 +23413,13 @@
     </row>
     <row r="308" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>953</v>
+        <v>1019</v>
       </c>
       <c r="B308" t="s">
-        <v>954</v>
+        <v>1020</v>
       </c>
       <c r="C308" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E308" t="s">
         <v>123</v>
@@ -23098,7 +23449,7 @@
         <v>0</v>
       </c>
       <c r="P308" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V308">
         <v>0</v>
@@ -23106,13 +23457,13 @@
     </row>
     <row r="309" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>955</v>
+        <v>1021</v>
       </c>
       <c r="B309" t="s">
-        <v>956</v>
+        <v>1022</v>
       </c>
       <c r="C309" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E309" t="s">
         <v>123</v>
@@ -23142,7 +23493,7 @@
         <v>0</v>
       </c>
       <c r="P309" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V309">
         <v>0</v>
@@ -23150,13 +23501,13 @@
     </row>
     <row r="310" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>957</v>
+        <v>1023</v>
       </c>
       <c r="B310" t="s">
-        <v>958</v>
+        <v>1024</v>
       </c>
       <c r="C310" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E310" t="s">
         <v>123</v>
@@ -23186,7 +23537,7 @@
         <v>0</v>
       </c>
       <c r="P310" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V310">
         <v>0</v>
@@ -23194,13 +23545,13 @@
     </row>
     <row r="311" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>959</v>
+        <v>1025</v>
       </c>
       <c r="B311" t="s">
-        <v>960</v>
+        <v>1026</v>
       </c>
       <c r="C311" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E311" t="s">
         <v>123</v>
@@ -23230,7 +23581,7 @@
         <v>0</v>
       </c>
       <c r="P311" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V311">
         <v>0</v>
@@ -23238,13 +23589,13 @@
     </row>
     <row r="312" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>961</v>
+        <v>1027</v>
       </c>
       <c r="B312" t="s">
-        <v>962</v>
+        <v>1028</v>
       </c>
       <c r="C312" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E312" t="s">
         <v>123</v>
@@ -23274,7 +23625,7 @@
         <v>0</v>
       </c>
       <c r="P312" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V312">
         <v>0</v>
@@ -23282,13 +23633,13 @@
     </row>
     <row r="313" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>963</v>
+        <v>1029</v>
       </c>
       <c r="B313" t="s">
-        <v>964</v>
+        <v>1030</v>
       </c>
       <c r="C313" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E313" t="s">
         <v>123</v>
@@ -23318,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="P313" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V313">
         <v>0</v>
@@ -23326,13 +23677,13 @@
     </row>
     <row r="314" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>965</v>
+        <v>1031</v>
       </c>
       <c r="B314" t="s">
-        <v>966</v>
+        <v>1032</v>
       </c>
       <c r="C314" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E314" t="s">
         <v>123</v>
@@ -23362,7 +23713,7 @@
         <v>0</v>
       </c>
       <c r="P314" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V314">
         <v>0</v>
@@ -23370,13 +23721,13 @@
     </row>
     <row r="315" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>967</v>
+        <v>1033</v>
       </c>
       <c r="B315" t="s">
-        <v>968</v>
+        <v>1034</v>
       </c>
       <c r="C315" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E315" t="s">
         <v>123</v>
@@ -23406,7 +23757,7 @@
         <v>0</v>
       </c>
       <c r="P315" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V315">
         <v>0</v>
@@ -23414,13 +23765,13 @@
     </row>
     <row r="316" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>969</v>
+        <v>1035</v>
       </c>
       <c r="B316" t="s">
-        <v>970</v>
+        <v>1036</v>
       </c>
       <c r="C316" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E316" t="s">
         <v>123</v>
@@ -23450,7 +23801,7 @@
         <v>0</v>
       </c>
       <c r="P316" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V316">
         <v>0</v>
@@ -23458,13 +23809,13 @@
     </row>
     <row r="317" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>971</v>
+        <v>1037</v>
       </c>
       <c r="B317" t="s">
-        <v>972</v>
+        <v>1038</v>
       </c>
       <c r="C317" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E317" t="s">
         <v>123</v>
@@ -23494,7 +23845,7 @@
         <v>0</v>
       </c>
       <c r="P317" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V317">
         <v>0</v>
@@ -23502,13 +23853,13 @@
     </row>
     <row r="318" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>973</v>
+        <v>1039</v>
       </c>
       <c r="B318" t="s">
-        <v>974</v>
+        <v>1040</v>
       </c>
       <c r="C318" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E318" t="s">
         <v>123</v>
@@ -23538,7 +23889,7 @@
         <v>0</v>
       </c>
       <c r="P318" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V318">
         <v>0</v>
@@ -23546,13 +23897,13 @@
     </row>
     <row r="319" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>975</v>
+        <v>1041</v>
       </c>
       <c r="B319" t="s">
-        <v>976</v>
+        <v>1042</v>
       </c>
       <c r="C319" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E319" t="s">
         <v>123</v>
@@ -23582,7 +23933,7 @@
         <v>0</v>
       </c>
       <c r="P319" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V319">
         <v>0</v>
@@ -23590,13 +23941,13 @@
     </row>
     <row r="320" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>977</v>
+        <v>1043</v>
       </c>
       <c r="B320" t="s">
-        <v>978</v>
+        <v>1044</v>
       </c>
       <c r="C320" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E320" t="s">
         <v>123</v>
@@ -23626,7 +23977,7 @@
         <v>0</v>
       </c>
       <c r="P320" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V320">
         <v>0</v>
@@ -23634,13 +23985,13 @@
     </row>
     <row r="321" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>979</v>
+        <v>1045</v>
       </c>
       <c r="B321" t="s">
-        <v>980</v>
+        <v>1046</v>
       </c>
       <c r="C321" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E321" t="s">
         <v>123</v>
@@ -23670,7 +24021,7 @@
         <v>0</v>
       </c>
       <c r="P321" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V321">
         <v>0</v>
@@ -23678,13 +24029,13 @@
     </row>
     <row r="322" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>981</v>
+        <v>1047</v>
       </c>
       <c r="B322" t="s">
-        <v>982</v>
+        <v>1048</v>
       </c>
       <c r="C322" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E322" t="s">
         <v>123</v>
@@ -23714,7 +24065,7 @@
         <v>0</v>
       </c>
       <c r="P322" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V322">
         <v>0</v>
@@ -23722,13 +24073,13 @@
     </row>
     <row r="323" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>983</v>
+        <v>1049</v>
       </c>
       <c r="B323" t="s">
-        <v>984</v>
+        <v>1050</v>
       </c>
       <c r="C323" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E323" t="s">
         <v>123</v>
@@ -23758,7 +24109,7 @@
         <v>0</v>
       </c>
       <c r="P323" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V323">
         <v>0</v>
@@ -23766,13 +24117,13 @@
     </row>
     <row r="324" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>985</v>
+        <v>1051</v>
       </c>
       <c r="B324" t="s">
-        <v>986</v>
+        <v>1052</v>
       </c>
       <c r="C324" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E324" t="s">
         <v>123</v>
@@ -23802,7 +24153,7 @@
         <v>0</v>
       </c>
       <c r="P324" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V324">
         <v>0</v>
@@ -23810,13 +24161,13 @@
     </row>
     <row r="325" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>987</v>
+        <v>1053</v>
       </c>
       <c r="B325" t="s">
-        <v>988</v>
+        <v>1054</v>
       </c>
       <c r="C325" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E325" t="s">
         <v>123</v>
@@ -23846,7 +24197,7 @@
         <v>0</v>
       </c>
       <c r="P325" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V325">
         <v>0</v>
@@ -23854,13 +24205,13 @@
     </row>
     <row r="326" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>989</v>
+        <v>1055</v>
       </c>
       <c r="B326" t="s">
-        <v>990</v>
+        <v>1056</v>
       </c>
       <c r="C326" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E326" t="s">
         <v>123</v>
@@ -23890,7 +24241,7 @@
         <v>0</v>
       </c>
       <c r="P326" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V326">
         <v>0</v>
@@ -23898,13 +24249,13 @@
     </row>
     <row r="327" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>991</v>
+        <v>1057</v>
       </c>
       <c r="B327" t="s">
-        <v>992</v>
+        <v>1058</v>
       </c>
       <c r="C327" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E327" t="s">
         <v>123</v>
@@ -23934,7 +24285,7 @@
         <v>0</v>
       </c>
       <c r="P327" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V327">
         <v>0</v>
@@ -23942,13 +24293,13 @@
     </row>
     <row r="328" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>993</v>
+        <v>1059</v>
       </c>
       <c r="B328" t="s">
-        <v>994</v>
+        <v>1060</v>
       </c>
       <c r="C328" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E328" t="s">
         <v>123</v>
@@ -23978,7 +24329,7 @@
         <v>0</v>
       </c>
       <c r="P328" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V328">
         <v>0</v>
@@ -23986,13 +24337,13 @@
     </row>
     <row r="329" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>995</v>
+        <v>1061</v>
       </c>
       <c r="B329" t="s">
-        <v>996</v>
+        <v>1062</v>
       </c>
       <c r="C329" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E329" t="s">
         <v>123</v>
@@ -24022,7 +24373,7 @@
         <v>0</v>
       </c>
       <c r="P329" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V329">
         <v>0</v>
@@ -24030,13 +24381,13 @@
     </row>
     <row r="330" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>997</v>
+        <v>1063</v>
       </c>
       <c r="B330" t="s">
-        <v>998</v>
+        <v>1064</v>
       </c>
       <c r="C330" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E330" t="s">
         <v>123</v>
@@ -24066,7 +24417,7 @@
         <v>0</v>
       </c>
       <c r="P330" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V330">
         <v>0</v>
@@ -24074,13 +24425,13 @@
     </row>
     <row r="331" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>999</v>
+        <v>1065</v>
       </c>
       <c r="B331" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C331" t="s">
         <v>1000</v>
-      </c>
-      <c r="C331" t="s">
-        <v>934</v>
       </c>
       <c r="E331" t="s">
         <v>123</v>
@@ -24110,7 +24461,7 @@
         <v>0</v>
       </c>
       <c r="P331" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V331">
         <v>0</v>
@@ -24118,13 +24469,13 @@
     </row>
     <row r="332" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>1001</v>
+        <v>1067</v>
       </c>
       <c r="B332" t="s">
-        <v>1002</v>
+        <v>1068</v>
       </c>
       <c r="C332" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E332" t="s">
         <v>123</v>
@@ -24154,7 +24505,7 @@
         <v>0</v>
       </c>
       <c r="P332" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V332">
         <v>0</v>
@@ -24162,13 +24513,13 @@
     </row>
     <row r="333" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>1003</v>
+        <v>1069</v>
       </c>
       <c r="B333" t="s">
-        <v>1004</v>
+        <v>1070</v>
       </c>
       <c r="C333" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E333" t="s">
         <v>123</v>
@@ -24198,7 +24549,7 @@
         <v>0</v>
       </c>
       <c r="P333" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V333">
         <v>0</v>
@@ -24206,13 +24557,13 @@
     </row>
     <row r="334" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>1005</v>
+        <v>1071</v>
       </c>
       <c r="B334" t="s">
-        <v>1006</v>
+        <v>1072</v>
       </c>
       <c r="C334" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E334" t="s">
         <v>123</v>
@@ -24242,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="P334" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V334">
         <v>0</v>
@@ -24250,13 +24601,13 @@
     </row>
     <row r="335" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>1007</v>
+        <v>1073</v>
       </c>
       <c r="B335" t="s">
-        <v>1008</v>
+        <v>1074</v>
       </c>
       <c r="C335" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E335" t="s">
         <v>123</v>
@@ -24286,7 +24637,7 @@
         <v>0</v>
       </c>
       <c r="P335" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V335">
         <v>0</v>
@@ -24294,13 +24645,13 @@
     </row>
     <row r="336" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>1009</v>
+        <v>1075</v>
       </c>
       <c r="B336" t="s">
-        <v>1010</v>
+        <v>1076</v>
       </c>
       <c r="C336" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E336" t="s">
         <v>123</v>
@@ -24330,7 +24681,7 @@
         <v>0</v>
       </c>
       <c r="P336" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V336">
         <v>0</v>
@@ -24338,13 +24689,13 @@
     </row>
     <row r="337" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>1011</v>
+        <v>1077</v>
       </c>
       <c r="B337" t="s">
-        <v>1012</v>
+        <v>1078</v>
       </c>
       <c r="C337" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E337" t="s">
         <v>123</v>
@@ -24374,7 +24725,7 @@
         <v>0</v>
       </c>
       <c r="P337" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V337">
         <v>0</v>
@@ -24382,13 +24733,13 @@
     </row>
     <row r="338" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>1013</v>
+        <v>1079</v>
       </c>
       <c r="B338" t="s">
-        <v>1014</v>
+        <v>1080</v>
       </c>
       <c r="C338" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E338" t="s">
         <v>123</v>
@@ -24418,7 +24769,7 @@
         <v>0</v>
       </c>
       <c r="P338" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V338">
         <v>0</v>
@@ -24426,13 +24777,13 @@
     </row>
     <row r="339" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>1015</v>
+        <v>1081</v>
       </c>
       <c r="B339" t="s">
-        <v>1016</v>
+        <v>1082</v>
       </c>
       <c r="C339" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E339" t="s">
         <v>123</v>
@@ -24462,7 +24813,7 @@
         <v>0</v>
       </c>
       <c r="P339" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V339">
         <v>0</v>
@@ -24470,13 +24821,13 @@
     </row>
     <row r="340" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>1017</v>
+        <v>1083</v>
       </c>
       <c r="B340" t="s">
-        <v>1018</v>
+        <v>1084</v>
       </c>
       <c r="C340" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E340" t="s">
         <v>123</v>
@@ -24506,7 +24857,7 @@
         <v>0</v>
       </c>
       <c r="P340" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V340">
         <v>0</v>
@@ -24514,13 +24865,13 @@
     </row>
     <row r="341" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>1019</v>
+        <v>1085</v>
       </c>
       <c r="B341" t="s">
-        <v>1020</v>
+        <v>1086</v>
       </c>
       <c r="C341" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E341" t="s">
         <v>123</v>
@@ -24550,7 +24901,7 @@
         <v>0</v>
       </c>
       <c r="P341" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V341">
         <v>0</v>
@@ -24558,13 +24909,13 @@
     </row>
     <row r="342" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>1021</v>
+        <v>1087</v>
       </c>
       <c r="B342" t="s">
-        <v>1022</v>
+        <v>1088</v>
       </c>
       <c r="C342" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E342" t="s">
         <v>123</v>
@@ -24594,7 +24945,7 @@
         <v>0</v>
       </c>
       <c r="P342" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V342">
         <v>0</v>
@@ -24602,13 +24953,13 @@
     </row>
     <row r="343" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>1023</v>
+        <v>1089</v>
       </c>
       <c r="B343" t="s">
-        <v>1024</v>
+        <v>1090</v>
       </c>
       <c r="C343" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E343" t="s">
         <v>123</v>
@@ -24638,7 +24989,7 @@
         <v>0</v>
       </c>
       <c r="P343" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V343">
         <v>0</v>
@@ -24646,13 +24997,13 @@
     </row>
     <row r="344" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1025</v>
+        <v>1091</v>
       </c>
       <c r="B344" t="s">
-        <v>1026</v>
+        <v>1092</v>
       </c>
       <c r="C344" t="s">
-        <v>934</v>
+        <v>1000</v>
       </c>
       <c r="E344" t="s">
         <v>123</v>
@@ -24682,7 +25033,7 @@
         <v>0</v>
       </c>
       <c r="P344" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="V344">
         <v>0</v>
@@ -24695,7 +25046,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C918FA4B-6E15-4AAF-BE7C-360F16688B9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE71E61-C426-47BA-A0A6-1B95CB33E89B}">
   <dimension ref="A1:K1318"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDC081C2-BA2D-4037-A8EF-82AC854EEA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC226D38-244E-487A-B88B-5461BEFD3EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{2633E1EB-8028-49D8-AD56-E79ECE751B49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{3467BDAE-609F-48A6-A432-907C3628AA73}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14084" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14415" uniqueCount="1103">
   <si>
     <t>날짜</t>
   </si>
@@ -3734,7 +3734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08BB3AD-0DC8-4D15-99D5-C0FDEF788376}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E899A796-F8CF-42ED-B237-E7ECC68D4A8F}">
   <dimension ref="A1:V348"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -10715,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>3</v>
@@ -10783,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="N104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104">
         <v>2</v>
@@ -11374,13 +11374,13 @@
         <v>265</v>
       </c>
       <c r="G113">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -11389,16 +11389,16 @@
         <v>345</v>
       </c>
       <c r="L113">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M113">
         <v>3</v>
       </c>
       <c r="N113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O113">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P113" t="s">
         <v>17</v>
@@ -12007,7 +12007,7 @@
         <v>2</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O122">
         <v>3</v>
@@ -12687,7 +12687,7 @@
         <v>12</v>
       </c>
       <c r="N132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132">
         <v>26</v>
@@ -12734,22 +12734,22 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J133">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K133" t="s">
         <v>333</v>
       </c>
       <c r="L133">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M133">
         <v>9</v>
@@ -12758,7 +12758,7 @@
         <v>8</v>
       </c>
       <c r="O133">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P133" t="s">
         <v>17</v>
@@ -12802,22 +12802,22 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J134">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K134" t="s">
         <v>333</v>
       </c>
       <c r="L134">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M134">
         <v>8</v>
@@ -12826,7 +12826,7 @@
         <v>9</v>
       </c>
       <c r="O134">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P134" t="s">
         <v>17</v>
@@ -12870,22 +12870,22 @@
         <v>250</v>
       </c>
       <c r="G135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J135">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K135" t="s">
         <v>333</v>
       </c>
       <c r="L135">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M135">
         <v>2</v>
@@ -12894,7 +12894,7 @@
         <v>11</v>
       </c>
       <c r="O135">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P135" t="s">
         <v>17</v>
@@ -13074,13 +13074,13 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -13089,16 +13089,16 @@
         <v>345</v>
       </c>
       <c r="L138">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M138">
         <v>2</v>
       </c>
       <c r="N138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O138">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P138" t="s">
         <v>17</v>
@@ -13231,7 +13231,7 @@
         <v>1</v>
       </c>
       <c r="N140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O140">
         <v>11</v>
@@ -13414,13 +13414,13 @@
         <v>240</v>
       </c>
       <c r="G143">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -13429,16 +13429,16 @@
         <v>345</v>
       </c>
       <c r="L143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M143">
         <v>2</v>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P143" t="s">
         <v>17</v>
@@ -13707,7 +13707,7 @@
         <v>3</v>
       </c>
       <c r="N147">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O147">
         <v>22</v>
@@ -13890,13 +13890,13 @@
         <v>250</v>
       </c>
       <c r="G150">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -13905,16 +13905,16 @@
         <v>345</v>
       </c>
       <c r="L150">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M150">
         <v>0</v>
       </c>
       <c r="N150">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O150">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P150" t="s">
         <v>17</v>
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="N151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O151">
         <v>13</v>
@@ -15271,7 +15271,7 @@
         <v>1</v>
       </c>
       <c r="N170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O170">
         <v>2</v>
@@ -15386,13 +15386,13 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -15401,16 +15401,16 @@
         <v>345</v>
       </c>
       <c r="L172">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M172">
         <v>2</v>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O172">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P172" t="s">
         <v>17</v>
@@ -15454,13 +15454,13 @@
         <v>240</v>
       </c>
       <c r="G173">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -15469,16 +15469,16 @@
         <v>345</v>
       </c>
       <c r="L173">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M173">
         <v>1</v>
       </c>
       <c r="N173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O173">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P173" t="s">
         <v>17</v>
@@ -15611,7 +15611,7 @@
         <v>2</v>
       </c>
       <c r="N175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O175">
         <v>9</v>
@@ -15794,13 +15794,13 @@
         <v>240</v>
       </c>
       <c r="G178">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
       <c r="I178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -15809,16 +15809,16 @@
         <v>345</v>
       </c>
       <c r="L178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M178">
         <v>1</v>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P178" t="s">
         <v>17</v>
@@ -18718,13 +18718,13 @@
         <v>255</v>
       </c>
       <c r="G221">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H221">
         <v>0</v>
       </c>
       <c r="I221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J221">
         <v>0</v>
@@ -18733,16 +18733,16 @@
         <v>345</v>
       </c>
       <c r="L221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M221">
         <v>0</v>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P221" t="s">
         <v>17</v>
@@ -18875,7 +18875,7 @@
         <v>8</v>
       </c>
       <c r="N223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O223">
         <v>17</v>
@@ -19262,13 +19262,13 @@
         <v>245</v>
       </c>
       <c r="G229">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -19277,16 +19277,16 @@
         <v>345</v>
       </c>
       <c r="L229">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M229">
         <v>10</v>
       </c>
       <c r="N229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O229">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P229" t="s">
         <v>17</v>
@@ -19546,7 +19546,7 @@
         <v>1</v>
       </c>
       <c r="N233">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O233">
         <v>44</v>
@@ -19732,7 +19732,7 @@
         <v>0</v>
       </c>
       <c r="N236">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O236">
         <v>10</v>
@@ -19856,7 +19856,7 @@
         <v>1</v>
       </c>
       <c r="N238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O238">
         <v>7</v>
@@ -20600,7 +20600,7 @@
         <v>1</v>
       </c>
       <c r="N250">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O250">
         <v>25</v>
@@ -20910,7 +20910,7 @@
         <v>0</v>
       </c>
       <c r="N255">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O255">
         <v>26</v>
@@ -21220,7 +21220,7 @@
         <v>0</v>
       </c>
       <c r="N260">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O260">
         <v>52</v>
@@ -21279,7 +21279,7 @@
         <v>0</v>
       </c>
       <c r="N261">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O261">
         <v>57</v>
@@ -21338,7 +21338,7 @@
         <v>0</v>
       </c>
       <c r="N262">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="O262">
         <v>80</v>
@@ -21397,7 +21397,7 @@
         <v>4</v>
       </c>
       <c r="N263">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O263">
         <v>97</v>
@@ -21541,10 +21541,10 @@
         <v>123</v>
       </c>
       <c r="G266">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I266">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -21553,16 +21553,16 @@
         <v>345</v>
       </c>
       <c r="L266">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M266">
         <v>0</v>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O266">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P266" t="s">
         <v>182</v>
@@ -21588,10 +21588,10 @@
         <v>123</v>
       </c>
       <c r="G267">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I267">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -21600,16 +21600,16 @@
         <v>345</v>
       </c>
       <c r="L267">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M267">
         <v>0</v>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O267">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P267" t="s">
         <v>182</v>
@@ -21635,10 +21635,10 @@
         <v>123</v>
       </c>
       <c r="G268">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I268">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J268">
         <v>0</v>
@@ -21647,16 +21647,16 @@
         <v>345</v>
       </c>
       <c r="L268">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M268">
         <v>0</v>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O268">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P268" t="s">
         <v>182</v>
@@ -21682,10 +21682,10 @@
         <v>123</v>
       </c>
       <c r="G269">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I269">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J269">
         <v>0</v>
@@ -21694,16 +21694,16 @@
         <v>345</v>
       </c>
       <c r="L269">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M269">
         <v>0</v>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O269">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P269" t="s">
         <v>182</v>
@@ -21729,10 +21729,10 @@
         <v>123</v>
       </c>
       <c r="G270">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I270">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J270">
         <v>0</v>
@@ -21741,16 +21741,16 @@
         <v>345</v>
       </c>
       <c r="L270">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M270">
         <v>0</v>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O270">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P270" t="s">
         <v>182</v>
@@ -21776,10 +21776,10 @@
         <v>123</v>
       </c>
       <c r="G271">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I271">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J271">
         <v>0</v>
@@ -21788,16 +21788,16 @@
         <v>345</v>
       </c>
       <c r="L271">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M271">
         <v>0</v>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O271">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P271" t="s">
         <v>182</v>
@@ -22422,28 +22422,28 @@
         <v>123</v>
       </c>
       <c r="G285">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="I285">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J285">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K285" t="s">
         <v>333</v>
       </c>
       <c r="L285">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M285">
         <v>0</v>
       </c>
       <c r="N285">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O285">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P285" t="s">
         <v>279</v>
@@ -23015,28 +23015,28 @@
         <v>123</v>
       </c>
       <c r="G298">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K298" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M298">
         <v>0</v>
       </c>
       <c r="N298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P298" t="s">
         <v>279</v>
@@ -23367,10 +23367,10 @@
         <v>123</v>
       </c>
       <c r="G306">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I306">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -23379,16 +23379,16 @@
         <v>345</v>
       </c>
       <c r="L306">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M306">
         <v>0</v>
       </c>
       <c r="N306">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O306">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P306" t="s">
         <v>279</v>
@@ -23411,10 +23411,10 @@
         <v>123</v>
       </c>
       <c r="G307">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I307">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -23423,16 +23423,16 @@
         <v>345</v>
       </c>
       <c r="L307">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M307">
         <v>0</v>
       </c>
       <c r="N307">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O307">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P307" t="s">
         <v>279</v>
@@ -23499,10 +23499,10 @@
         <v>123</v>
       </c>
       <c r="G309">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I309">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -23511,16 +23511,16 @@
         <v>345</v>
       </c>
       <c r="L309">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M309">
         <v>0</v>
       </c>
       <c r="N309">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O309">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P309" t="s">
         <v>279</v>
@@ -23631,10 +23631,10 @@
         <v>123</v>
       </c>
       <c r="G312">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I312">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -23643,16 +23643,16 @@
         <v>345</v>
       </c>
       <c r="L312">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M312">
         <v>0</v>
       </c>
       <c r="N312">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O312">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P312" t="s">
         <v>279</v>
@@ -23675,10 +23675,10 @@
         <v>123</v>
       </c>
       <c r="G313">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I313">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J313">
         <v>0</v>
@@ -23687,16 +23687,16 @@
         <v>345</v>
       </c>
       <c r="L313">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M313">
         <v>0</v>
       </c>
       <c r="N313">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O313">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P313" t="s">
         <v>279</v>
@@ -23719,10 +23719,10 @@
         <v>123</v>
       </c>
       <c r="G314">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I314">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J314">
         <v>0</v>
@@ -23731,16 +23731,16 @@
         <v>345</v>
       </c>
       <c r="L314">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M314">
         <v>0</v>
       </c>
       <c r="N314">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O314">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P314" t="s">
         <v>279</v>
@@ -23851,10 +23851,10 @@
         <v>123</v>
       </c>
       <c r="G317">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I317">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J317">
         <v>0</v>
@@ -23863,16 +23863,16 @@
         <v>345</v>
       </c>
       <c r="L317">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M317">
         <v>0</v>
       </c>
       <c r="N317">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O317">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P317" t="s">
         <v>279</v>
@@ -23939,10 +23939,10 @@
         <v>123</v>
       </c>
       <c r="G319">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I319">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J319">
         <v>0</v>
@@ -23951,16 +23951,16 @@
         <v>345</v>
       </c>
       <c r="L319">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M319">
         <v>0</v>
       </c>
       <c r="N319">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O319">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P319" t="s">
         <v>279</v>
@@ -23983,10 +23983,10 @@
         <v>123</v>
       </c>
       <c r="G320">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I320">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J320">
         <v>0</v>
@@ -23995,16 +23995,16 @@
         <v>345</v>
       </c>
       <c r="L320">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M320">
         <v>0</v>
       </c>
       <c r="N320">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O320">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P320" t="s">
         <v>279</v>
@@ -25083,28 +25083,28 @@
         <v>123</v>
       </c>
       <c r="G345">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="I345">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J345">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K345" t="s">
         <v>333</v>
       </c>
       <c r="L345">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M345">
         <v>0</v>
       </c>
       <c r="N345">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O345">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P345" t="s">
         <v>17</v>
@@ -25127,28 +25127,28 @@
         <v>123</v>
       </c>
       <c r="G346">
-        <v>-10</v>
+        <v>-21</v>
       </c>
       <c r="I346">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J346">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K346" t="s">
         <v>333</v>
       </c>
       <c r="L346">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M346">
         <v>0</v>
       </c>
       <c r="N346">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O346">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="P346" t="s">
         <v>17</v>
@@ -25171,28 +25171,28 @@
         <v>123</v>
       </c>
       <c r="G347">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="I347">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J347">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K347" t="s">
         <v>333</v>
       </c>
       <c r="L347">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M347">
         <v>0</v>
       </c>
       <c r="N347">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O347">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P347" t="s">
         <v>17</v>
@@ -25215,28 +25215,28 @@
         <v>123</v>
       </c>
       <c r="G348">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I348">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J348">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K348" t="s">
         <v>333</v>
       </c>
       <c r="L348">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M348">
         <v>0</v>
       </c>
       <c r="N348">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O348">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P348" t="s">
         <v>17</v>
@@ -25252,8 +25252,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E364771-F2B9-4405-9261-A2BFF4369783}">
-  <dimension ref="A1:K1605"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717A7C71-9FA7-4308-93AE-4A8811D9EFED}">
+  <dimension ref="A1:K1657"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -81339,6 +81339,1826 @@
       </c>
       <c r="K1605">
         <v>8900</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1606" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1606">
+        <v>0</v>
+      </c>
+      <c r="E1606" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1606" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1606">
+        <v>0</v>
+      </c>
+      <c r="H1606" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1606">
+        <v>1</v>
+      </c>
+      <c r="J1606" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1607" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1607">
+        <v>0</v>
+      </c>
+      <c r="E1607" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1607" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1607">
+        <v>0</v>
+      </c>
+      <c r="H1607" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1607">
+        <v>1</v>
+      </c>
+      <c r="J1607" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1608" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1608">
+        <v>0</v>
+      </c>
+      <c r="E1608" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1608" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1608">
+        <v>0</v>
+      </c>
+      <c r="H1608" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1608">
+        <v>1</v>
+      </c>
+      <c r="J1608" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1609" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1609">
+        <v>0</v>
+      </c>
+      <c r="E1609" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1609" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1609">
+        <v>0</v>
+      </c>
+      <c r="H1609" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1609">
+        <v>1</v>
+      </c>
+      <c r="J1609" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1610" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1610">
+        <v>0</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1610">
+        <v>0</v>
+      </c>
+      <c r="H1610" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1610">
+        <v>1</v>
+      </c>
+      <c r="J1610" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1611" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1611">
+        <v>0</v>
+      </c>
+      <c r="E1611" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1611" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1611">
+        <v>0</v>
+      </c>
+      <c r="H1611" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1611">
+        <v>1</v>
+      </c>
+      <c r="J1611" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1612" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1612">
+        <v>0</v>
+      </c>
+      <c r="E1612" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1612">
+        <v>0</v>
+      </c>
+      <c r="H1612" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1612">
+        <v>1</v>
+      </c>
+      <c r="J1612" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1613" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1613">
+        <v>0</v>
+      </c>
+      <c r="E1613" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1613" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1613">
+        <v>0</v>
+      </c>
+      <c r="H1613" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1613">
+        <v>1</v>
+      </c>
+      <c r="J1613" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1614" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1614">
+        <v>0</v>
+      </c>
+      <c r="E1614" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1614">
+        <v>0</v>
+      </c>
+      <c r="H1614" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1614">
+        <v>1</v>
+      </c>
+      <c r="J1614" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1615" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1615">
+        <v>0</v>
+      </c>
+      <c r="E1615" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1615">
+        <v>0</v>
+      </c>
+      <c r="H1615" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1615">
+        <v>1</v>
+      </c>
+      <c r="J1615" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1616" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1616">
+        <v>0</v>
+      </c>
+      <c r="E1616" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1616">
+        <v>0</v>
+      </c>
+      <c r="H1616" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1616">
+        <v>1</v>
+      </c>
+      <c r="J1616" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1617" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1617">
+        <v>0</v>
+      </c>
+      <c r="E1617" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1617">
+        <v>0</v>
+      </c>
+      <c r="H1617" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1617">
+        <v>1</v>
+      </c>
+      <c r="J1617" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1618" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1618">
+        <v>0</v>
+      </c>
+      <c r="E1618" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1618" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1618">
+        <v>0</v>
+      </c>
+      <c r="H1618" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1618">
+        <v>5</v>
+      </c>
+      <c r="J1618" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1619" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1619">
+        <v>0</v>
+      </c>
+      <c r="E1619" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1619">
+        <v>0</v>
+      </c>
+      <c r="H1619" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1619">
+        <v>5</v>
+      </c>
+      <c r="J1619" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1620" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1620">
+        <v>0</v>
+      </c>
+      <c r="E1620" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1620" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1620">
+        <v>0</v>
+      </c>
+      <c r="H1620" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1620">
+        <v>5</v>
+      </c>
+      <c r="J1620" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1621" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1621">
+        <v>0</v>
+      </c>
+      <c r="E1621" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1621" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1621">
+        <v>0</v>
+      </c>
+      <c r="H1621" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1621">
+        <v>5</v>
+      </c>
+      <c r="J1621" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1622" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1622">
+        <v>0</v>
+      </c>
+      <c r="E1622" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1622">
+        <v>0</v>
+      </c>
+      <c r="H1622" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1622">
+        <v>5</v>
+      </c>
+      <c r="J1622" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1623" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1623">
+        <v>0</v>
+      </c>
+      <c r="E1623" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1623" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1623">
+        <v>0</v>
+      </c>
+      <c r="H1623" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1623">
+        <v>5</v>
+      </c>
+      <c r="J1623" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1624" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1624">
+        <v>0</v>
+      </c>
+      <c r="E1624" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1624" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1624">
+        <v>0</v>
+      </c>
+      <c r="H1624" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1624">
+        <v>5</v>
+      </c>
+      <c r="J1624" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1625" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1625">
+        <v>0</v>
+      </c>
+      <c r="E1625" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1625">
+        <v>0</v>
+      </c>
+      <c r="H1625" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1625">
+        <v>5</v>
+      </c>
+      <c r="J1625" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1626" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1626">
+        <v>0</v>
+      </c>
+      <c r="E1626" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1626">
+        <v>0</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1626">
+        <v>5</v>
+      </c>
+      <c r="J1626" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1627" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1627">
+        <v>0</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1627">
+        <v>0</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1627">
+        <v>1</v>
+      </c>
+      <c r="J1627" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1628" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1628">
+        <v>0</v>
+      </c>
+      <c r="E1628" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1628">
+        <v>0</v>
+      </c>
+      <c r="H1628" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1628">
+        <v>1</v>
+      </c>
+      <c r="J1628" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1629" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1629">
+        <v>255</v>
+      </c>
+      <c r="H1629" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1629">
+        <v>1</v>
+      </c>
+      <c r="J1629" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1629">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1630" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1630">
+        <v>0</v>
+      </c>
+      <c r="E1630" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1630">
+        <v>0</v>
+      </c>
+      <c r="H1630" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1630">
+        <v>1</v>
+      </c>
+      <c r="J1630" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1631" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1631" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1631" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1631">
+        <v>250</v>
+      </c>
+      <c r="H1631" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1631">
+        <v>1</v>
+      </c>
+      <c r="J1631" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1631">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1632" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1632">
+        <v>0</v>
+      </c>
+      <c r="E1632" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1632" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1632">
+        <v>0</v>
+      </c>
+      <c r="H1632" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1632">
+        <v>1</v>
+      </c>
+      <c r="J1632" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1633" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1633" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1633">
+        <v>245</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1633">
+        <v>1</v>
+      </c>
+      <c r="J1633" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1633">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1634" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1634">
+        <v>0</v>
+      </c>
+      <c r="E1634" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1634">
+        <v>0</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1634">
+        <v>1</v>
+      </c>
+      <c r="J1634" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1635" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1635">
+        <v>240</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1635">
+        <v>1</v>
+      </c>
+      <c r="J1635" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1635">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1636" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1636">
+        <v>0</v>
+      </c>
+      <c r="E1636" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1636">
+        <v>0</v>
+      </c>
+      <c r="H1636" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1636">
+        <v>1</v>
+      </c>
+      <c r="J1636" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1637" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1637" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1637" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1637">
+        <v>250</v>
+      </c>
+      <c r="H1637" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1637">
+        <v>1</v>
+      </c>
+      <c r="J1637" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1637">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1638" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1638">
+        <v>0</v>
+      </c>
+      <c r="E1638" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1638" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1638">
+        <v>0</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1638">
+        <v>1</v>
+      </c>
+      <c r="J1638" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1639" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1639" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1639" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1639">
+        <v>240</v>
+      </c>
+      <c r="H1639" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1639">
+        <v>1</v>
+      </c>
+      <c r="J1639" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1639">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1640" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1640">
+        <v>0</v>
+      </c>
+      <c r="E1640" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1640" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1640">
+        <v>0</v>
+      </c>
+      <c r="H1640" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1640">
+        <v>1</v>
+      </c>
+      <c r="J1640" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1641" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1641" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1641" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1641">
+        <v>265</v>
+      </c>
+      <c r="H1641" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1641">
+        <v>1</v>
+      </c>
+      <c r="J1641" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1641">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1642" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1642">
+        <v>0</v>
+      </c>
+      <c r="E1642" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1642" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1642">
+        <v>0</v>
+      </c>
+      <c r="H1642" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1642">
+        <v>1</v>
+      </c>
+      <c r="J1642" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1643" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1643" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1643">
+        <v>245</v>
+      </c>
+      <c r="H1643" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1643">
+        <v>1</v>
+      </c>
+      <c r="J1643" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1643">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1644" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1644">
+        <v>0</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1644" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1644">
+        <v>0</v>
+      </c>
+      <c r="H1644" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1644">
+        <v>1</v>
+      </c>
+      <c r="J1644" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1645" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1645" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1645">
+        <v>235</v>
+      </c>
+      <c r="H1645" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1645">
+        <v>1</v>
+      </c>
+      <c r="J1645" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1645">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1646" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1646">
+        <v>0</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1646" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1646">
+        <v>0</v>
+      </c>
+      <c r="H1646" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1646">
+        <v>1</v>
+      </c>
+      <c r="J1646" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1647" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1647" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1647" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1647">
+        <v>240</v>
+      </c>
+      <c r="H1647" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1647">
+        <v>1</v>
+      </c>
+      <c r="J1647" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1647">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1648" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1648">
+        <v>0</v>
+      </c>
+      <c r="E1648" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1648" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1648">
+        <v>0</v>
+      </c>
+      <c r="H1648" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1648">
+        <v>1</v>
+      </c>
+      <c r="J1648" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1649" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1649" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1649" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1649">
+        <v>240</v>
+      </c>
+      <c r="H1649" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1649">
+        <v>1</v>
+      </c>
+      <c r="J1649" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1649">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1650" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1650" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1650" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1650">
+        <v>0</v>
+      </c>
+      <c r="H1650" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1650">
+        <v>10</v>
+      </c>
+      <c r="J1650" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1651" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1651" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1651" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1651">
+        <v>0</v>
+      </c>
+      <c r="H1651" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1651">
+        <v>10</v>
+      </c>
+      <c r="J1651" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1651">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1652" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1652" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1652" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1652">
+        <v>0</v>
+      </c>
+      <c r="H1652" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1652">
+        <v>10</v>
+      </c>
+      <c r="J1652" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1653" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1653" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1653" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1653">
+        <v>0</v>
+      </c>
+      <c r="H1653" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1653">
+        <v>10</v>
+      </c>
+      <c r="J1653" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1653">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1654" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1654" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1654" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1654">
+        <v>0</v>
+      </c>
+      <c r="H1654" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1654">
+        <v>10</v>
+      </c>
+      <c r="J1654" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1654">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1655" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1655" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1655" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1655">
+        <v>0</v>
+      </c>
+      <c r="H1655" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1655">
+        <v>10</v>
+      </c>
+      <c r="J1655" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1656" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1656" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1656" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1656">
+        <v>245</v>
+      </c>
+      <c r="H1656" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1656">
+        <v>1</v>
+      </c>
+      <c r="J1656" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1656">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1657" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1657" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1657" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1657">
+        <v>240</v>
+      </c>
+      <c r="H1657" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1657">
+        <v>1</v>
+      </c>
+      <c r="J1657" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1657">
+        <v>44900</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC226D38-244E-487A-B88B-5461BEFD3EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1BBC89-6E75-485B-A9DE-36509E320104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{3467BDAE-609F-48A6-A432-907C3628AA73}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{027AAE50-8570-450D-8313-9F2994500988}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14415" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14981" uniqueCount="1103">
   <si>
     <t>날짜</t>
   </si>
@@ -3734,7 +3734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E899A796-F8CF-42ED-B237-E7ECC68D4A8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6D4976-B18C-4BDC-9F45-77EBFBEF368A}">
   <dimension ref="A1:V348"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4642,31 +4642,31 @@
         <v>270</v>
       </c>
       <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>2</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" t="s">
         <v>17</v>
@@ -4710,31 +4710,31 @@
         <v>275</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="s">
         <v>17</v>
@@ -4935,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -5003,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19">
         <v>3</v>
@@ -5615,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -5662,13 +5662,13 @@
         <v>270</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5677,16 +5677,16 @@
         <v>345</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29" t="s">
         <v>17</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O30">
         <v>3</v>
@@ -8314,13 +8314,13 @@
         <v>265</v>
       </c>
       <c r="G68">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         <v>345</v>
       </c>
       <c r="L68">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -8338,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="O68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P68" t="s">
         <v>17</v>
@@ -8382,31 +8382,31 @@
         <v>270</v>
       </c>
       <c r="G69">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J69">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s">
         <v>333</v>
       </c>
       <c r="L69">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M69">
         <v>0</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P69" t="s">
         <v>17</v>
@@ -9130,13 +9130,13 @@
         <v>275</v>
       </c>
       <c r="G80">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -9145,16 +9145,16 @@
         <v>345</v>
       </c>
       <c r="L80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80">
         <v>0</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" t="s">
         <v>17</v>
@@ -9198,13 +9198,13 @@
         <v>280</v>
       </c>
       <c r="G81">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H81">
         <v>0</v>
       </c>
       <c r="I81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -9213,16 +9213,16 @@
         <v>345</v>
       </c>
       <c r="L81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M81">
         <v>0</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P81" t="s">
         <v>17</v>
@@ -9674,13 +9674,13 @@
         <v>265</v>
       </c>
       <c r="G88">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -9689,16 +9689,16 @@
         <v>345</v>
       </c>
       <c r="L88">
+        <v>5</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>2</v>
+      </c>
+      <c r="O88">
         <v>4</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>1</v>
-      </c>
-      <c r="O88">
-        <v>3</v>
       </c>
       <c r="P88" t="s">
         <v>17</v>
@@ -10360,10 +10360,10 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J98">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K98" t="s">
         <v>333</v>
@@ -10378,7 +10378,7 @@
         <v>2</v>
       </c>
       <c r="O98">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P98" t="s">
         <v>17</v>
@@ -10490,7 +10490,7 @@
         <v>275</v>
       </c>
       <c r="G100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -10499,19 +10499,19 @@
         <v>6</v>
       </c>
       <c r="J100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K100" t="s">
         <v>333</v>
       </c>
       <c r="L100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100">
         <v>6</v>
@@ -10768,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="O104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P104" t="s">
         <v>17</v>
@@ -11306,13 +11306,13 @@
         <v>260</v>
       </c>
       <c r="G112">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
       <c r="I112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -11321,16 +11321,16 @@
         <v>345</v>
       </c>
       <c r="L112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M112">
         <v>0</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P112" t="s">
         <v>17</v>
@@ -11448,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -11466,7 +11466,7 @@
         <v>1</v>
       </c>
       <c r="O114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P114" t="s">
         <v>17</v>
@@ -11516,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>1</v>
       </c>
       <c r="O115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P115" t="s">
         <v>17</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -11602,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="O116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P116" t="s">
         <v>17</v>
@@ -11646,31 +11646,31 @@
         <v>260</v>
       </c>
       <c r="G117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
       <c r="I117">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J117">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K117" t="s">
         <v>333</v>
       </c>
       <c r="L117">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M117">
         <v>1</v>
       </c>
       <c r="N117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O117">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P117" t="s">
         <v>17</v>
@@ -11782,13 +11782,13 @@
         <v>270</v>
       </c>
       <c r="G119">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
       <c r="I119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -11797,16 +11797,16 @@
         <v>345</v>
       </c>
       <c r="L119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M119">
         <v>0</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P119" t="s">
         <v>17</v>
@@ -12143,7 +12143,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124">
         <v>2</v>
@@ -12347,7 +12347,7 @@
         <v>6</v>
       </c>
       <c r="N127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O127">
         <v>7</v>
@@ -12394,31 +12394,31 @@
         <v>240</v>
       </c>
       <c r="G128">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J128">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K128" t="s">
         <v>333</v>
       </c>
       <c r="L128">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M128">
         <v>11</v>
       </c>
       <c r="N128">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O128">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P128" t="s">
         <v>17</v>
@@ -12468,10 +12468,10 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J129">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K129" t="s">
         <v>333</v>
@@ -12486,7 +12486,7 @@
         <v>3</v>
       </c>
       <c r="O129">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P129" t="s">
         <v>17</v>
@@ -12536,7 +12536,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -12551,10 +12551,10 @@
         <v>5</v>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P130" t="s">
         <v>17</v>
@@ -12734,7 +12734,7 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -12743,13 +12743,13 @@
         <v>35</v>
       </c>
       <c r="J133">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K133" t="s">
         <v>333</v>
       </c>
       <c r="L133">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M133">
         <v>9</v>
@@ -12802,7 +12802,7 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -12811,13 +12811,13 @@
         <v>31</v>
       </c>
       <c r="J134">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K134" t="s">
         <v>333</v>
       </c>
       <c r="L134">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M134">
         <v>8</v>
@@ -12870,13 +12870,13 @@
         <v>250</v>
       </c>
       <c r="G135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J135">
         <v>22</v>
@@ -12885,16 +12885,16 @@
         <v>333</v>
       </c>
       <c r="L135">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M135">
         <v>2</v>
       </c>
       <c r="N135">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O135">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P135" t="s">
         <v>17</v>
@@ -13006,7 +13006,7 @@
         <v>235</v>
       </c>
       <c r="G137">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -13021,13 +13021,13 @@
         <v>345</v>
       </c>
       <c r="L137">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M137">
         <v>2</v>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137">
         <v>8</v>
@@ -13074,13 +13074,13 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -13089,16 +13089,16 @@
         <v>345</v>
       </c>
       <c r="L138">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M138">
         <v>2</v>
       </c>
       <c r="N138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O138">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P138" t="s">
         <v>17</v>
@@ -13142,13 +13142,13 @@
         <v>245</v>
       </c>
       <c r="G139">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J139">
         <v>0</v>
@@ -13157,16 +13157,16 @@
         <v>345</v>
       </c>
       <c r="L139">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M139">
         <v>2</v>
       </c>
       <c r="N139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O139">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P139" t="s">
         <v>17</v>
@@ -13216,7 +13216,7 @@
         <v>0</v>
       </c>
       <c r="I140">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -13234,7 +13234,7 @@
         <v>1</v>
       </c>
       <c r="O140">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P140" t="s">
         <v>17</v>
@@ -13284,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J141">
         <v>0</v>
@@ -13299,10 +13299,10 @@
         <v>0</v>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P141" t="s">
         <v>17</v>
@@ -13414,13 +13414,13 @@
         <v>240</v>
       </c>
       <c r="G143">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -13429,16 +13429,16 @@
         <v>345</v>
       </c>
       <c r="L143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M143">
         <v>2</v>
       </c>
       <c r="N143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P143" t="s">
         <v>17</v>
@@ -13686,31 +13686,31 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J147">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K147" t="s">
         <v>333</v>
       </c>
       <c r="L147">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M147">
         <v>3</v>
       </c>
       <c r="N147">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O147">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P147" t="s">
         <v>17</v>
@@ -13754,13 +13754,13 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -13769,16 +13769,16 @@
         <v>345</v>
       </c>
       <c r="L148">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M148">
         <v>3</v>
       </c>
       <c r="N148">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O148">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P148" t="s">
         <v>17</v>
@@ -13822,13 +13822,13 @@
         <v>245</v>
       </c>
       <c r="G149">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -13837,16 +13837,16 @@
         <v>345</v>
       </c>
       <c r="L149">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M149">
         <v>3</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O149">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P149" t="s">
         <v>17</v>
@@ -13890,13 +13890,13 @@
         <v>250</v>
       </c>
       <c r="G150">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -13905,16 +13905,16 @@
         <v>345</v>
       </c>
       <c r="L150">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M150">
         <v>0</v>
       </c>
       <c r="N150">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O150">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P150" t="s">
         <v>17</v>
@@ -15067,7 +15067,7 @@
         <v>2</v>
       </c>
       <c r="N167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O167">
         <v>4</v>
@@ -15203,7 +15203,7 @@
         <v>2</v>
       </c>
       <c r="N169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O169">
         <v>4</v>
@@ -15386,13 +15386,13 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -15401,16 +15401,16 @@
         <v>345</v>
       </c>
       <c r="L172">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M172">
         <v>2</v>
       </c>
       <c r="N172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O172">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P172" t="s">
         <v>17</v>
@@ -15475,7 +15475,7 @@
         <v>1</v>
       </c>
       <c r="N173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O173">
         <v>12</v>
@@ -15522,7 +15522,7 @@
         <v>245</v>
       </c>
       <c r="G174">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -15537,13 +15537,13 @@
         <v>345</v>
       </c>
       <c r="L174">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M174">
         <v>1</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O174">
         <v>5</v>
@@ -15596,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -15614,7 +15614,7 @@
         <v>2</v>
       </c>
       <c r="O175">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P175" t="s">
         <v>17</v>
@@ -16072,7 +16072,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -16090,7 +16090,7 @@
         <v>1</v>
       </c>
       <c r="O182">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P182" t="s">
         <v>17</v>
@@ -16344,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="O186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P186" t="s">
         <v>17</v>
@@ -16548,7 +16548,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -16566,7 +16566,7 @@
         <v>0</v>
       </c>
       <c r="O189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P189" t="s">
         <v>17</v>
@@ -16746,13 +16746,13 @@
         <v>235</v>
       </c>
       <c r="G192">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -16761,16 +16761,16 @@
         <v>345</v>
       </c>
       <c r="L192">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M192">
         <v>8</v>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P192" t="s">
         <v>17</v>
@@ -16820,7 +16820,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -16838,7 +16838,7 @@
         <v>1</v>
       </c>
       <c r="O193">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P193" t="s">
         <v>17</v>
@@ -16971,7 +16971,7 @@
         <v>8</v>
       </c>
       <c r="N195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O195">
         <v>12</v>
@@ -17500,7 +17500,7 @@
         <v>0</v>
       </c>
       <c r="I203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="O203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P203" t="s">
         <v>17</v>
@@ -17787,7 +17787,7 @@
         <v>1</v>
       </c>
       <c r="N207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207">
         <v>2</v>
@@ -18928,10 +18928,10 @@
         <v>0</v>
       </c>
       <c r="I224">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K224" t="s">
         <v>333</v>
@@ -18946,7 +18946,7 @@
         <v>0</v>
       </c>
       <c r="O224">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P224" t="s">
         <v>17</v>
@@ -19194,13 +19194,13 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -19209,16 +19209,16 @@
         <v>345</v>
       </c>
       <c r="L228">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M228">
         <v>12</v>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O228">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P228" t="s">
         <v>17</v>
@@ -19262,13 +19262,13 @@
         <v>245</v>
       </c>
       <c r="G229">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -19277,7 +19277,7 @@
         <v>345</v>
       </c>
       <c r="L229">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M229">
         <v>10</v>
@@ -19286,7 +19286,7 @@
         <v>3</v>
       </c>
       <c r="O229">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P229" t="s">
         <v>17</v>
@@ -19351,7 +19351,7 @@
         <v>5</v>
       </c>
       <c r="N230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O230">
         <v>7</v>
@@ -19463,13 +19463,13 @@
         <v>123</v>
       </c>
       <c r="G232">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H232">
         <v>0</v>
       </c>
       <c r="I232">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -19478,16 +19478,16 @@
         <v>345</v>
       </c>
       <c r="L232">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M232">
         <v>1</v>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P232" t="s">
         <v>124</v>
@@ -19546,7 +19546,7 @@
         <v>1</v>
       </c>
       <c r="N233">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O233">
         <v>44</v>
@@ -19918,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="N239">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O239">
         <v>22</v>
@@ -20269,13 +20269,13 @@
         <v>123</v>
       </c>
       <c r="G245">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H245">
         <v>0</v>
       </c>
       <c r="I245">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -20284,16 +20284,16 @@
         <v>345</v>
       </c>
       <c r="L245">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M245">
         <v>2</v>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P245" t="s">
         <v>124</v>
@@ -20786,7 +20786,7 @@
         <v>3</v>
       </c>
       <c r="N253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O253">
         <v>33</v>
@@ -20951,13 +20951,13 @@
         <v>123</v>
       </c>
       <c r="G256">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H256">
         <v>0</v>
       </c>
       <c r="I256">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -20966,16 +20966,16 @@
         <v>345</v>
       </c>
       <c r="L256">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M256">
         <v>2</v>
       </c>
       <c r="N256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O256">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P256" t="s">
         <v>124</v>
@@ -21453,7 +21453,7 @@
         <v>0</v>
       </c>
       <c r="N264">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O264">
         <v>13</v>
@@ -21506,7 +21506,7 @@
         <v>0</v>
       </c>
       <c r="N265">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O265">
         <v>17</v>
@@ -22049,28 +22049,28 @@
         <v>123</v>
       </c>
       <c r="G277">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I277">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J277">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K277" t="s">
         <v>333</v>
       </c>
       <c r="L277">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M277">
         <v>0</v>
       </c>
       <c r="N277">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O277">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P277" t="s">
         <v>279</v>
@@ -22284,28 +22284,28 @@
         <v>123</v>
       </c>
       <c r="G282">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="I282">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J282">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K282" t="s">
         <v>333</v>
       </c>
       <c r="L282">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M282">
         <v>0</v>
       </c>
       <c r="N282">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O282">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P282" t="s">
         <v>279</v>
@@ -22331,28 +22331,28 @@
         <v>123</v>
       </c>
       <c r="G283">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="I283">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J283">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K283" t="s">
         <v>333</v>
       </c>
       <c r="L283">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M283">
         <v>0</v>
       </c>
       <c r="N283">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O283">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P283" t="s">
         <v>279</v>
@@ -22422,28 +22422,28 @@
         <v>123</v>
       </c>
       <c r="G285">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="I285">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J285">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K285" t="s">
         <v>333</v>
       </c>
       <c r="L285">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M285">
         <v>0</v>
       </c>
       <c r="N285">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O285">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P285" t="s">
         <v>279</v>
@@ -23015,28 +23015,28 @@
         <v>123</v>
       </c>
       <c r="G298">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I298">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J298">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K298" t="s">
         <v>333</v>
       </c>
       <c r="L298">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M298">
         <v>0</v>
       </c>
       <c r="N298">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O298">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P298" t="s">
         <v>279</v>
@@ -23059,28 +23059,28 @@
         <v>123</v>
       </c>
       <c r="G299">
+        <v>3</v>
+      </c>
+      <c r="I299">
+        <v>7</v>
+      </c>
+      <c r="J299">
         <v>4</v>
-      </c>
-      <c r="I299">
-        <v>6</v>
-      </c>
-      <c r="J299">
-        <v>2</v>
       </c>
       <c r="K299" t="s">
         <v>333</v>
       </c>
       <c r="L299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M299">
         <v>0</v>
       </c>
       <c r="N299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P299" t="s">
         <v>279</v>
@@ -23103,10 +23103,10 @@
         <v>123</v>
       </c>
       <c r="G300">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J300">
         <v>0</v>
@@ -23115,16 +23115,16 @@
         <v>345</v>
       </c>
       <c r="L300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M300">
         <v>0</v>
       </c>
       <c r="N300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P300" t="s">
         <v>279</v>
@@ -23147,28 +23147,28 @@
         <v>123</v>
       </c>
       <c r="G301">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I301">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J301">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K301" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L301">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M301">
         <v>0</v>
       </c>
       <c r="N301">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="O301">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="P301" t="s">
         <v>279</v>
@@ -23191,28 +23191,28 @@
         <v>123</v>
       </c>
       <c r="G302">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I302">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J302">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K302" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L302">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M302">
         <v>0</v>
       </c>
       <c r="N302">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O302">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="P302" t="s">
         <v>279</v>
@@ -23279,10 +23279,10 @@
         <v>123</v>
       </c>
       <c r="G304">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I304">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -23291,16 +23291,16 @@
         <v>345</v>
       </c>
       <c r="L304">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M304">
         <v>0</v>
       </c>
       <c r="N304">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O304">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P304" t="s">
         <v>279</v>
@@ -23499,28 +23499,28 @@
         <v>123</v>
       </c>
       <c r="G309">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I309">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J309">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K309" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L309">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M309">
         <v>0</v>
       </c>
       <c r="N309">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O309">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P309" t="s">
         <v>279</v>
@@ -23543,10 +23543,10 @@
         <v>123</v>
       </c>
       <c r="G310">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I310">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -23555,16 +23555,16 @@
         <v>345</v>
       </c>
       <c r="L310">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M310">
         <v>0</v>
       </c>
       <c r="N310">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O310">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P310" t="s">
         <v>279</v>
@@ -23675,10 +23675,10 @@
         <v>123</v>
       </c>
       <c r="G313">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I313">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J313">
         <v>0</v>
@@ -23687,16 +23687,16 @@
         <v>345</v>
       </c>
       <c r="L313">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M313">
         <v>0</v>
       </c>
       <c r="N313">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O313">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P313" t="s">
         <v>279</v>
@@ -23719,10 +23719,10 @@
         <v>123</v>
       </c>
       <c r="G314">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I314">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J314">
         <v>0</v>
@@ -23731,16 +23731,16 @@
         <v>345</v>
       </c>
       <c r="L314">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M314">
         <v>0</v>
       </c>
       <c r="N314">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O314">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P314" t="s">
         <v>279</v>
@@ -23983,10 +23983,10 @@
         <v>123</v>
       </c>
       <c r="G320">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I320">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J320">
         <v>0</v>
@@ -23995,16 +23995,16 @@
         <v>345</v>
       </c>
       <c r="L320">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M320">
         <v>0</v>
       </c>
       <c r="N320">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O320">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P320" t="s">
         <v>279</v>
@@ -25127,19 +25127,19 @@
         <v>123</v>
       </c>
       <c r="G346">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="I346">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J346">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="K346" t="s">
         <v>333</v>
       </c>
       <c r="L346">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M346">
         <v>0</v>
@@ -25148,7 +25148,7 @@
         <v>30</v>
       </c>
       <c r="O346">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="P346" t="s">
         <v>17</v>
@@ -25171,28 +25171,28 @@
         <v>123</v>
       </c>
       <c r="G347">
-        <v>-6</v>
+        <v>-19</v>
       </c>
       <c r="I347">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J347">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K347" t="s">
         <v>333</v>
       </c>
       <c r="L347">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M347">
         <v>0</v>
       </c>
       <c r="N347">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O347">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="P347" t="s">
         <v>17</v>
@@ -25233,7 +25233,7 @@
         <v>0</v>
       </c>
       <c r="N348">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O348">
         <v>15</v>
@@ -25252,8 +25252,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717A7C71-9FA7-4308-93AE-4A8811D9EFED}">
-  <dimension ref="A1:K1657"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{515F5B13-BD2A-4A64-BC32-3A315A2EF786}">
+  <dimension ref="A1:K1745"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -83159,6 +83159,3086 @@
       </c>
       <c r="K1657">
         <v>44900</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1658" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1658">
+        <v>0</v>
+      </c>
+      <c r="E1658" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1658" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1658">
+        <v>0</v>
+      </c>
+      <c r="H1658" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1658">
+        <v>12</v>
+      </c>
+      <c r="J1658" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1659" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1659">
+        <v>0</v>
+      </c>
+      <c r="E1659" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1659" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1659">
+        <v>0</v>
+      </c>
+      <c r="H1659" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1659">
+        <v>10</v>
+      </c>
+      <c r="J1659" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1660" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1660">
+        <v>0</v>
+      </c>
+      <c r="E1660" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1660" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1660">
+        <v>0</v>
+      </c>
+      <c r="H1660" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1660">
+        <v>1</v>
+      </c>
+      <c r="J1660" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1661" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1661">
+        <v>0</v>
+      </c>
+      <c r="E1661" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1661" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1661">
+        <v>0</v>
+      </c>
+      <c r="H1661" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1661">
+        <v>1</v>
+      </c>
+      <c r="J1661" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1662" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1662">
+        <v>0</v>
+      </c>
+      <c r="E1662" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1662" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1662">
+        <v>0</v>
+      </c>
+      <c r="H1662" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1662">
+        <v>1</v>
+      </c>
+      <c r="J1662" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1663" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1663">
+        <v>0</v>
+      </c>
+      <c r="E1663" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1663" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1663">
+        <v>0</v>
+      </c>
+      <c r="H1663" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1663">
+        <v>1</v>
+      </c>
+      <c r="J1663" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1664" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1664">
+        <v>0</v>
+      </c>
+      <c r="E1664" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1664" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1664">
+        <v>0</v>
+      </c>
+      <c r="H1664" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1664">
+        <v>1</v>
+      </c>
+      <c r="J1664" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1665" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1665">
+        <v>0</v>
+      </c>
+      <c r="E1665" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1665" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1665">
+        <v>0</v>
+      </c>
+      <c r="H1665" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1665">
+        <v>1</v>
+      </c>
+      <c r="J1665" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1666" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1666">
+        <v>0</v>
+      </c>
+      <c r="E1666" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1666" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1666">
+        <v>0</v>
+      </c>
+      <c r="H1666" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1666">
+        <v>1</v>
+      </c>
+      <c r="J1666" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1667" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1667">
+        <v>0</v>
+      </c>
+      <c r="E1667" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1667" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1667">
+        <v>0</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1667">
+        <v>4</v>
+      </c>
+      <c r="J1667" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1667">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1668" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1668">
+        <v>0</v>
+      </c>
+      <c r="E1668" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1668" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1668">
+        <v>0</v>
+      </c>
+      <c r="H1668" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1668">
+        <v>3</v>
+      </c>
+      <c r="J1668" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1669" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1669">
+        <v>0</v>
+      </c>
+      <c r="E1669" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1669" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1669">
+        <v>0</v>
+      </c>
+      <c r="H1669" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1669">
+        <v>2</v>
+      </c>
+      <c r="J1669" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1670" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1670">
+        <v>0</v>
+      </c>
+      <c r="E1670" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1670" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1670">
+        <v>0</v>
+      </c>
+      <c r="H1670" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1670">
+        <v>1</v>
+      </c>
+      <c r="J1670" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1671" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1671">
+        <v>0</v>
+      </c>
+      <c r="E1671" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1671" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1671">
+        <v>0</v>
+      </c>
+      <c r="H1671" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1671">
+        <v>1</v>
+      </c>
+      <c r="J1671" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1672" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1672">
+        <v>0</v>
+      </c>
+      <c r="E1672" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1672" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1672">
+        <v>0</v>
+      </c>
+      <c r="H1672" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1672">
+        <v>1</v>
+      </c>
+      <c r="J1672" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1673" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1673">
+        <v>0</v>
+      </c>
+      <c r="E1673" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1673" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1673">
+        <v>0</v>
+      </c>
+      <c r="H1673" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1673">
+        <v>1</v>
+      </c>
+      <c r="J1673" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1674" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1674">
+        <v>0</v>
+      </c>
+      <c r="E1674" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1674" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1674">
+        <v>0</v>
+      </c>
+      <c r="H1674" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1674">
+        <v>1</v>
+      </c>
+      <c r="J1674" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1675" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1675">
+        <v>0</v>
+      </c>
+      <c r="E1675" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1675" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1675">
+        <v>0</v>
+      </c>
+      <c r="H1675" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1675">
+        <v>1</v>
+      </c>
+      <c r="J1675" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1676" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1676">
+        <v>0</v>
+      </c>
+      <c r="E1676" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1676" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1676">
+        <v>0</v>
+      </c>
+      <c r="H1676" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1676">
+        <v>1</v>
+      </c>
+      <c r="J1676" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1676">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1677" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1677">
+        <v>0</v>
+      </c>
+      <c r="E1677" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1677" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1677">
+        <v>0</v>
+      </c>
+      <c r="H1677" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1677">
+        <v>1</v>
+      </c>
+      <c r="J1677" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1678" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1678">
+        <v>0</v>
+      </c>
+      <c r="E1678" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1678" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1678">
+        <v>0</v>
+      </c>
+      <c r="H1678" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1678">
+        <v>4</v>
+      </c>
+      <c r="J1678" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1679" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1679">
+        <v>0</v>
+      </c>
+      <c r="E1679" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1679" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1679">
+        <v>0</v>
+      </c>
+      <c r="H1679" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1679">
+        <v>1</v>
+      </c>
+      <c r="J1679" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1680" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1680">
+        <v>0</v>
+      </c>
+      <c r="E1680" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1680" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1680">
+        <v>0</v>
+      </c>
+      <c r="H1680" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1680">
+        <v>1</v>
+      </c>
+      <c r="J1680" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1681" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1681">
+        <v>0</v>
+      </c>
+      <c r="E1681" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1681" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1681">
+        <v>0</v>
+      </c>
+      <c r="H1681" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1681">
+        <v>1</v>
+      </c>
+      <c r="J1681" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1682" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1682">
+        <v>0</v>
+      </c>
+      <c r="E1682" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1682" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1682">
+        <v>0</v>
+      </c>
+      <c r="H1682" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1682">
+        <v>1</v>
+      </c>
+      <c r="J1682" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1683" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1683">
+        <v>0</v>
+      </c>
+      <c r="E1683" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1683" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1683">
+        <v>0</v>
+      </c>
+      <c r="H1683" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1683">
+        <v>1</v>
+      </c>
+      <c r="J1683" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1684" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1684">
+        <v>0</v>
+      </c>
+      <c r="E1684" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1684" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1684">
+        <v>0</v>
+      </c>
+      <c r="H1684" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1684">
+        <v>1</v>
+      </c>
+      <c r="J1684" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1685" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1685">
+        <v>0</v>
+      </c>
+      <c r="E1685" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1685" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1685">
+        <v>0</v>
+      </c>
+      <c r="H1685" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1685">
+        <v>1</v>
+      </c>
+      <c r="J1685" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1686" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1686">
+        <v>0</v>
+      </c>
+      <c r="E1686" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1686" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1686">
+        <v>0</v>
+      </c>
+      <c r="H1686" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1686">
+        <v>1</v>
+      </c>
+      <c r="J1686" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1687" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1687">
+        <v>0</v>
+      </c>
+      <c r="E1687" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1687" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1687">
+        <v>0</v>
+      </c>
+      <c r="H1687" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1687">
+        <v>1</v>
+      </c>
+      <c r="J1687" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1688" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1688" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1688" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1688">
+        <v>0</v>
+      </c>
+      <c r="H1688" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1688">
+        <v>1</v>
+      </c>
+      <c r="J1688" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1688">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1689" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1689" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1689" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1689">
+        <v>0</v>
+      </c>
+      <c r="H1689" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1689">
+        <v>1</v>
+      </c>
+      <c r="J1689" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1689">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1690" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1690">
+        <v>0</v>
+      </c>
+      <c r="E1690" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1690" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1690">
+        <v>0</v>
+      </c>
+      <c r="H1690" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1690">
+        <v>1</v>
+      </c>
+      <c r="J1690" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1691" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1691" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1691" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1691">
+        <v>275</v>
+      </c>
+      <c r="H1691" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1691">
+        <v>1</v>
+      </c>
+      <c r="J1691" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1691">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1692" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1692">
+        <v>0</v>
+      </c>
+      <c r="E1692" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1692" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1692">
+        <v>0</v>
+      </c>
+      <c r="H1692" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1692">
+        <v>1</v>
+      </c>
+      <c r="J1692" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1693" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1693" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1693" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1693">
+        <v>270</v>
+      </c>
+      <c r="H1693" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1693">
+        <v>1</v>
+      </c>
+      <c r="J1693" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1693">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1694" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1694">
+        <v>0</v>
+      </c>
+      <c r="E1694" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1694" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1694">
+        <v>0</v>
+      </c>
+      <c r="H1694" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1694">
+        <v>1</v>
+      </c>
+      <c r="J1694" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1695" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1695" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1695" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1695">
+        <v>240</v>
+      </c>
+      <c r="H1695" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1695">
+        <v>1</v>
+      </c>
+      <c r="J1695" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1695">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1696" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1696">
+        <v>0</v>
+      </c>
+      <c r="E1696" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1696" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1696">
+        <v>0</v>
+      </c>
+      <c r="H1696" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1696">
+        <v>1</v>
+      </c>
+      <c r="J1696" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1697" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1697" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1697" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1697">
+        <v>235</v>
+      </c>
+      <c r="H1697" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1697">
+        <v>1</v>
+      </c>
+      <c r="J1697" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1697">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1698" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1698">
+        <v>0</v>
+      </c>
+      <c r="E1698" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1698" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1698">
+        <v>0</v>
+      </c>
+      <c r="H1698" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1698">
+        <v>1</v>
+      </c>
+      <c r="J1698" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1699" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1699" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1699" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1699">
+        <v>245</v>
+      </c>
+      <c r="H1699" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1699">
+        <v>1</v>
+      </c>
+      <c r="J1699" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1699">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1700" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1700">
+        <v>0</v>
+      </c>
+      <c r="E1700" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1700" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1700">
+        <v>0</v>
+      </c>
+      <c r="H1700" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1700">
+        <v>1</v>
+      </c>
+      <c r="J1700" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1701" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1701" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1701" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1701">
+        <v>245</v>
+      </c>
+      <c r="H1701" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1701">
+        <v>1</v>
+      </c>
+      <c r="J1701" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1701">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1702" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1702">
+        <v>0</v>
+      </c>
+      <c r="E1702" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1702" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1702">
+        <v>0</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1702">
+        <v>1</v>
+      </c>
+      <c r="J1702" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1703" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1703" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1703" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1703">
+        <v>245</v>
+      </c>
+      <c r="H1703" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1703">
+        <v>1</v>
+      </c>
+      <c r="J1703" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1703">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1704" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1704">
+        <v>0</v>
+      </c>
+      <c r="E1704" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1704" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1704">
+        <v>0</v>
+      </c>
+      <c r="H1704" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1704">
+        <v>1</v>
+      </c>
+      <c r="J1704" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1705" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1705" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1705" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1705">
+        <v>245</v>
+      </c>
+      <c r="H1705" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1705">
+        <v>1</v>
+      </c>
+      <c r="J1705" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1705">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1706" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1706">
+        <v>0</v>
+      </c>
+      <c r="E1706" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1706" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1706">
+        <v>0</v>
+      </c>
+      <c r="H1706" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1706">
+        <v>1</v>
+      </c>
+      <c r="J1706" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1707" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1707" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1707" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1707">
+        <v>235</v>
+      </c>
+      <c r="H1707" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1707">
+        <v>1</v>
+      </c>
+      <c r="J1707" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1707">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1708" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1708">
+        <v>0</v>
+      </c>
+      <c r="E1708" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1708" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1708">
+        <v>0</v>
+      </c>
+      <c r="H1708" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1708">
+        <v>1</v>
+      </c>
+      <c r="J1708" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1708">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1709" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1709" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1709" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1709">
+        <v>245</v>
+      </c>
+      <c r="H1709" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1709">
+        <v>1</v>
+      </c>
+      <c r="J1709" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1709">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1710" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1710">
+        <v>0</v>
+      </c>
+      <c r="E1710" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1710" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1710">
+        <v>0</v>
+      </c>
+      <c r="H1710" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1710">
+        <v>1</v>
+      </c>
+      <c r="J1710" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1711" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1711" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1711" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1711">
+        <v>240</v>
+      </c>
+      <c r="H1711" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1711">
+        <v>1</v>
+      </c>
+      <c r="J1711" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1711">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1712" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1712">
+        <v>0</v>
+      </c>
+      <c r="E1712" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1712" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1712">
+        <v>0</v>
+      </c>
+      <c r="H1712" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1712">
+        <v>1</v>
+      </c>
+      <c r="J1712" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1713" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1713" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1713" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1713">
+        <v>240</v>
+      </c>
+      <c r="H1713" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1713">
+        <v>1</v>
+      </c>
+      <c r="J1713" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1713">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1714" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1714">
+        <v>0</v>
+      </c>
+      <c r="E1714" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1714" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1714">
+        <v>0</v>
+      </c>
+      <c r="H1714" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1714">
+        <v>1</v>
+      </c>
+      <c r="J1714" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1714">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1715" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1715" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1715" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1715">
+        <v>240</v>
+      </c>
+      <c r="H1715" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1715">
+        <v>1</v>
+      </c>
+      <c r="J1715" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1715">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1716" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1716">
+        <v>0</v>
+      </c>
+      <c r="E1716" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1716" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1716">
+        <v>0</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1716">
+        <v>1</v>
+      </c>
+      <c r="J1716" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1716">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1717" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1717" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1717" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1717">
+        <v>250</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1717">
+        <v>1</v>
+      </c>
+      <c r="J1717" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1717">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1718" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1718">
+        <v>0</v>
+      </c>
+      <c r="E1718" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1718" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1718">
+        <v>0</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1718">
+        <v>1</v>
+      </c>
+      <c r="J1718" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1719" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1719" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1719" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1719">
+        <v>235</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1719">
+        <v>1</v>
+      </c>
+      <c r="J1719" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1719">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1720" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1720">
+        <v>0</v>
+      </c>
+      <c r="E1720" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1720" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1720">
+        <v>0</v>
+      </c>
+      <c r="H1720" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1720">
+        <v>1</v>
+      </c>
+      <c r="J1720" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1720">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1721" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1721" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1721" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1721">
+        <v>280</v>
+      </c>
+      <c r="H1721" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1721">
+        <v>1</v>
+      </c>
+      <c r="J1721" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1721">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1722" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1722">
+        <v>0</v>
+      </c>
+      <c r="E1722" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1722" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1722">
+        <v>0</v>
+      </c>
+      <c r="H1722" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1722">
+        <v>1</v>
+      </c>
+      <c r="J1722" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1723" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1723" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1723" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1723">
+        <v>240</v>
+      </c>
+      <c r="H1723" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1723">
+        <v>1</v>
+      </c>
+      <c r="J1723" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1723">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1724" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1724">
+        <v>0</v>
+      </c>
+      <c r="E1724" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1724" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1724">
+        <v>0</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1724">
+        <v>1</v>
+      </c>
+      <c r="J1724" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1724">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1725" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1725" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1725" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1725">
+        <v>235</v>
+      </c>
+      <c r="H1725" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1725">
+        <v>1</v>
+      </c>
+      <c r="J1725" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1725">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1726">
+        <v>0</v>
+      </c>
+      <c r="E1726" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1726" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1726">
+        <v>0</v>
+      </c>
+      <c r="H1726" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1726">
+        <v>1</v>
+      </c>
+      <c r="J1726" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1726">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1727" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1727" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1727" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1727">
+        <v>240</v>
+      </c>
+      <c r="H1727" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1727">
+        <v>1</v>
+      </c>
+      <c r="J1727" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1727">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1728" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1728">
+        <v>0</v>
+      </c>
+      <c r="E1728" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1728" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1728">
+        <v>0</v>
+      </c>
+      <c r="H1728" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1728">
+        <v>1</v>
+      </c>
+      <c r="J1728" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1728">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1729" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1729" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1729" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1729">
+        <v>240</v>
+      </c>
+      <c r="H1729" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1729">
+        <v>1</v>
+      </c>
+      <c r="J1729" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1729">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1730" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1730" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1730" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1730">
+        <v>270</v>
+      </c>
+      <c r="H1730" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1730">
+        <v>1</v>
+      </c>
+      <c r="J1730" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1730">
+        <v>49900</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1731" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1731" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1731" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1731">
+        <v>250</v>
+      </c>
+      <c r="H1731" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1731">
+        <v>1</v>
+      </c>
+      <c r="J1731" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1731">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1732" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1732" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1732" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1732">
+        <v>270</v>
+      </c>
+      <c r="H1732" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1732">
+        <v>1</v>
+      </c>
+      <c r="J1732" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1732">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1733" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1733" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1733" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1733">
+        <v>265</v>
+      </c>
+      <c r="H1733" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1733">
+        <v>1</v>
+      </c>
+      <c r="J1733" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1733">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1734" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1734" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1734" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1734">
+        <v>270</v>
+      </c>
+      <c r="H1734" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1734">
+        <v>1</v>
+      </c>
+      <c r="J1734" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1734">
+        <v>49900</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1735" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1735" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1735" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1735">
+        <v>275</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1735">
+        <v>1</v>
+      </c>
+      <c r="J1735" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1735">
+        <v>49900</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1736" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1736" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1736" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1736">
+        <v>265</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1736">
+        <v>1</v>
+      </c>
+      <c r="J1736" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1736">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1737" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1737" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1737" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1737">
+        <v>245</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1737">
+        <v>1</v>
+      </c>
+      <c r="J1737" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1737">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1738" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1738" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1738" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1738">
+        <v>240</v>
+      </c>
+      <c r="H1738" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1738">
+        <v>1</v>
+      </c>
+      <c r="J1738" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1738">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1739" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1739" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1739" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1739">
+        <v>245</v>
+      </c>
+      <c r="H1739" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1739">
+        <v>1</v>
+      </c>
+      <c r="J1739" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1739">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1740" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1740" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1740" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1740">
+        <v>245</v>
+      </c>
+      <c r="H1740" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1740">
+        <v>1</v>
+      </c>
+      <c r="J1740" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1740">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1741" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1741" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1741" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1741">
+        <v>235</v>
+      </c>
+      <c r="H1741" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1741">
+        <v>1</v>
+      </c>
+      <c r="J1741" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1741">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1742" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1742" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1742" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1742">
+        <v>260</v>
+      </c>
+      <c r="H1742" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1742">
+        <v>1</v>
+      </c>
+      <c r="J1742" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1742">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1743" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1743" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1743" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1743">
+        <v>260</v>
+      </c>
+      <c r="H1743" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1743">
+        <v>1</v>
+      </c>
+      <c r="J1743" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1743">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1744" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1744" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1744" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1744">
+        <v>275</v>
+      </c>
+      <c r="H1744" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1744">
+        <v>1</v>
+      </c>
+      <c r="J1744" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1744">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1745" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1745" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1745" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1745">
+        <v>0</v>
+      </c>
+      <c r="H1745" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1745">
+        <v>1</v>
+      </c>
+      <c r="J1745" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1745">
+        <v>35900</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1BBC89-6E75-485B-A9DE-36509E320104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E572E8F5-9624-44E7-A17B-A35D6342E87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{027AAE50-8570-450D-8313-9F2994500988}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{772E659C-3C91-4EC3-9053-4A4BD7754CA3}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14981" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15316" uniqueCount="1103">
   <si>
     <t>날짜</t>
   </si>
@@ -3734,7 +3734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6D4976-B18C-4BDC-9F45-77EBFBEF368A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25593462-3BC2-4937-AB2C-7C77B903C8F0}">
   <dimension ref="A1:V348"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -5615,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -8314,13 +8314,13 @@
         <v>265</v>
       </c>
       <c r="G68">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -8329,16 +8329,16 @@
         <v>345</v>
       </c>
       <c r="L68">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P68" t="s">
         <v>17</v>
@@ -8654,13 +8654,13 @@
         <v>265</v>
       </c>
       <c r="G73">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>345</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M73">
         <v>0</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P73" t="s">
         <v>17</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O98">
         <v>9</v>
@@ -10443,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99">
         <v>4</v>
@@ -11312,7 +11312,7 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -11330,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="O112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P112" t="s">
         <v>17</v>
@@ -11395,7 +11395,7 @@
         <v>3</v>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O113">
         <v>10</v>
@@ -11448,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -11466,7 +11466,7 @@
         <v>1</v>
       </c>
       <c r="O114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P114" t="s">
         <v>17</v>
@@ -11531,7 +11531,7 @@
         <v>1</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115">
         <v>5</v>
@@ -11667,7 +11667,7 @@
         <v>1</v>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O117">
         <v>10</v>
@@ -12007,7 +12007,7 @@
         <v>2</v>
       </c>
       <c r="N122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>3</v>
@@ -12483,7 +12483,7 @@
         <v>7</v>
       </c>
       <c r="N129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O129">
         <v>16</v>
@@ -12598,31 +12598,31 @@
         <v>255</v>
       </c>
       <c r="G131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
       <c r="I131">
+        <v>5</v>
+      </c>
+      <c r="J131">
         <v>4</v>
-      </c>
-      <c r="J131">
-        <v>2</v>
       </c>
       <c r="K131" t="s">
         <v>333</v>
       </c>
       <c r="L131">
+        <v>6</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>1</v>
+      </c>
+      <c r="O131">
         <v>5</v>
-      </c>
-      <c r="M131">
-        <v>1</v>
-      </c>
-      <c r="N131">
-        <v>2</v>
-      </c>
-      <c r="O131">
-        <v>4</v>
       </c>
       <c r="P131" t="s">
         <v>17</v>
@@ -12734,31 +12734,31 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J133">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K133" t="s">
         <v>333</v>
       </c>
       <c r="L133">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M133">
         <v>9</v>
       </c>
       <c r="N133">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O133">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P133" t="s">
         <v>17</v>
@@ -12802,7 +12802,7 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -12811,19 +12811,19 @@
         <v>31</v>
       </c>
       <c r="J134">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K134" t="s">
         <v>333</v>
       </c>
       <c r="L134">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M134">
         <v>8</v>
       </c>
       <c r="N134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O134">
         <v>31</v>
@@ -12891,7 +12891,7 @@
         <v>2</v>
       </c>
       <c r="N135">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O135">
         <v>24</v>
@@ -13163,7 +13163,7 @@
         <v>2</v>
       </c>
       <c r="N139">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O139">
         <v>10</v>
@@ -13414,13 +13414,13 @@
         <v>240</v>
       </c>
       <c r="G143">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -13429,16 +13429,16 @@
         <v>345</v>
       </c>
       <c r="L143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M143">
         <v>2</v>
       </c>
       <c r="N143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P143" t="s">
         <v>17</v>
@@ -13639,7 +13639,7 @@
         <v>0</v>
       </c>
       <c r="N146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146">
         <v>2</v>
@@ -13686,31 +13686,31 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J147">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K147" t="s">
         <v>333</v>
       </c>
       <c r="L147">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M147">
         <v>3</v>
       </c>
       <c r="N147">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O147">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P147" t="s">
         <v>17</v>
@@ -13754,13 +13754,13 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -13769,16 +13769,16 @@
         <v>345</v>
       </c>
       <c r="L148">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M148">
         <v>3</v>
       </c>
       <c r="N148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O148">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P148" t="s">
         <v>17</v>
@@ -13843,7 +13843,7 @@
         <v>3</v>
       </c>
       <c r="N149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O149">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>0</v>
       </c>
       <c r="N150">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O150">
         <v>16</v>
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="N151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151">
         <v>13</v>
@@ -15386,13 +15386,13 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -15401,16 +15401,16 @@
         <v>345</v>
       </c>
       <c r="L172">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M172">
         <v>2</v>
       </c>
       <c r="N172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O172">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P172" t="s">
         <v>17</v>
@@ -15460,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>2</v>
       </c>
       <c r="O173">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P173" t="s">
         <v>17</v>
@@ -15522,13 +15522,13 @@
         <v>245</v>
       </c>
       <c r="G174">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -15537,16 +15537,16 @@
         <v>345</v>
       </c>
       <c r="L174">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M174">
         <v>1</v>
       </c>
       <c r="N174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P174" t="s">
         <v>17</v>
@@ -15590,13 +15590,13 @@
         <v>250</v>
       </c>
       <c r="G175">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H175">
         <v>0</v>
       </c>
       <c r="I175">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -15605,16 +15605,16 @@
         <v>345</v>
       </c>
       <c r="L175">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M175">
         <v>2</v>
       </c>
       <c r="N175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O175">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P175" t="s">
         <v>17</v>
@@ -15679,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="N176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O176">
         <v>2</v>
@@ -16072,7 +16072,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -16090,7 +16090,7 @@
         <v>1</v>
       </c>
       <c r="O182">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P182" t="s">
         <v>17</v>
@@ -16155,7 +16155,7 @@
         <v>4</v>
       </c>
       <c r="N183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O183">
         <v>9</v>
@@ -16344,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="O186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P186" t="s">
         <v>17</v>
@@ -16631,7 +16631,7 @@
         <v>7</v>
       </c>
       <c r="N190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190">
         <v>3</v>
@@ -16835,7 +16835,7 @@
         <v>17</v>
       </c>
       <c r="N193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O193">
         <v>13</v>
@@ -16971,7 +16971,7 @@
         <v>8</v>
       </c>
       <c r="N195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O195">
         <v>12</v>
@@ -18467,7 +18467,7 @@
         <v>6</v>
       </c>
       <c r="N217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217">
         <v>5</v>
@@ -18535,7 +18535,7 @@
         <v>3</v>
       </c>
       <c r="N218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218">
         <v>5</v>
@@ -18875,7 +18875,7 @@
         <v>8</v>
       </c>
       <c r="N223">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O223">
         <v>17</v>
@@ -19283,7 +19283,7 @@
         <v>10</v>
       </c>
       <c r="N229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O229">
         <v>11</v>
@@ -19525,31 +19525,31 @@
         <v>123</v>
       </c>
       <c r="G233">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K233" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L233">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M233">
         <v>1</v>
       </c>
       <c r="N233">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O233">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="P233" t="s">
         <v>124</v>
@@ -19608,7 +19608,7 @@
         <v>0</v>
       </c>
       <c r="N234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O234">
         <v>7</v>
@@ -19649,13 +19649,13 @@
         <v>123</v>
       </c>
       <c r="G235">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H235">
         <v>0</v>
       </c>
       <c r="I235">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J235">
         <v>0</v>
@@ -19664,16 +19664,16 @@
         <v>345</v>
       </c>
       <c r="L235">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M235">
         <v>0</v>
       </c>
       <c r="N235">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O235">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P235" t="s">
         <v>124</v>
@@ -19732,7 +19732,7 @@
         <v>0</v>
       </c>
       <c r="N236">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O236">
         <v>10</v>
@@ -19918,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="N239">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O239">
         <v>22</v>
@@ -19959,13 +19959,13 @@
         <v>123</v>
       </c>
       <c r="G240">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H240">
         <v>0</v>
       </c>
       <c r="I240">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J240">
         <v>0</v>
@@ -19974,16 +19974,16 @@
         <v>345</v>
       </c>
       <c r="L240">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M240">
         <v>1</v>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O240">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P240" t="s">
         <v>124</v>
@@ -20042,7 +20042,7 @@
         <v>0</v>
       </c>
       <c r="N241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O241">
         <v>12</v>
@@ -20104,7 +20104,7 @@
         <v>0</v>
       </c>
       <c r="N242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O242">
         <v>21</v>
@@ -20228,7 +20228,7 @@
         <v>0</v>
       </c>
       <c r="N244">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O244">
         <v>19</v>
@@ -20269,13 +20269,13 @@
         <v>123</v>
       </c>
       <c r="G245">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H245">
         <v>0</v>
       </c>
       <c r="I245">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -20284,16 +20284,16 @@
         <v>345</v>
       </c>
       <c r="L245">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M245">
         <v>2</v>
       </c>
       <c r="N245">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O245">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P245" t="s">
         <v>124</v>
@@ -20331,13 +20331,13 @@
         <v>123</v>
       </c>
       <c r="G246">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H246">
         <v>0</v>
       </c>
       <c r="I246">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -20346,16 +20346,16 @@
         <v>345</v>
       </c>
       <c r="L246">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M246">
         <v>1</v>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P246" t="s">
         <v>124</v>
@@ -20538,7 +20538,7 @@
         <v>0</v>
       </c>
       <c r="N249">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O249">
         <v>15</v>
@@ -20579,13 +20579,13 @@
         <v>123</v>
       </c>
       <c r="G250">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -20594,16 +20594,16 @@
         <v>345</v>
       </c>
       <c r="L250">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M250">
         <v>1</v>
       </c>
       <c r="N250">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O250">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="P250" t="s">
         <v>124</v>
@@ -20662,7 +20662,7 @@
         <v>0</v>
       </c>
       <c r="N251">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O251">
         <v>18</v>
@@ -20724,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="N252">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O252">
         <v>18</v>
@@ -20827,13 +20827,13 @@
         <v>123</v>
       </c>
       <c r="G254">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H254">
         <v>0</v>
       </c>
       <c r="I254">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -20842,16 +20842,16 @@
         <v>345</v>
       </c>
       <c r="L254">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M254">
         <v>1</v>
       </c>
       <c r="N254">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O254">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P254" t="s">
         <v>124</v>
@@ -20951,13 +20951,13 @@
         <v>123</v>
       </c>
       <c r="G256">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H256">
         <v>0</v>
       </c>
       <c r="I256">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -20966,16 +20966,16 @@
         <v>345</v>
       </c>
       <c r="L256">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M256">
         <v>2</v>
       </c>
       <c r="N256">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O256">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P256" t="s">
         <v>124</v>
@@ -21137,13 +21137,13 @@
         <v>123</v>
       </c>
       <c r="G259">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H259">
         <v>0</v>
       </c>
       <c r="I259">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J259">
         <v>0</v>
@@ -21152,16 +21152,16 @@
         <v>345</v>
       </c>
       <c r="L259">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M259">
         <v>1</v>
       </c>
       <c r="N259">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O259">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P259" t="s">
         <v>124</v>
@@ -21202,10 +21202,10 @@
         <v>194</v>
       </c>
       <c r="G260">
-        <v>1948</v>
+        <v>1942</v>
       </c>
       <c r="I260">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -21214,16 +21214,16 @@
         <v>345</v>
       </c>
       <c r="L260">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M260">
         <v>0</v>
       </c>
       <c r="N260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O260">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="P260" t="s">
         <v>182</v>
@@ -21261,10 +21261,10 @@
         <v>181</v>
       </c>
       <c r="G261">
-        <v>1943</v>
+        <v>1925</v>
       </c>
       <c r="I261">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -21273,16 +21273,16 @@
         <v>345</v>
       </c>
       <c r="L261">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="M261">
         <v>0</v>
       </c>
       <c r="N261">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O261">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="P261" t="s">
         <v>182</v>
@@ -21320,10 +21320,10 @@
         <v>191</v>
       </c>
       <c r="G262">
-        <v>5920</v>
+        <v>5914</v>
       </c>
       <c r="I262">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -21332,16 +21332,16 @@
         <v>345</v>
       </c>
       <c r="L262">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M262">
         <v>0</v>
       </c>
       <c r="N262">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O262">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P262" t="s">
         <v>182</v>
@@ -21379,10 +21379,10 @@
         <v>193</v>
       </c>
       <c r="G263">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="I263">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -21391,16 +21391,16 @@
         <v>345</v>
       </c>
       <c r="L263">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="M263">
         <v>4</v>
       </c>
       <c r="N263">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O263">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="P263" t="s">
         <v>182</v>
@@ -21908,28 +21908,28 @@
         <v>123</v>
       </c>
       <c r="G274">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J274">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K274" t="s">
         <v>333</v>
       </c>
       <c r="L274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M274">
         <v>0</v>
       </c>
       <c r="N274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P274" t="s">
         <v>279</v>
@@ -22049,28 +22049,28 @@
         <v>123</v>
       </c>
       <c r="G277">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J277">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K277" t="s">
         <v>333</v>
       </c>
       <c r="L277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M277">
         <v>0</v>
       </c>
       <c r="N277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P277" t="s">
         <v>279</v>
@@ -22284,28 +22284,28 @@
         <v>123</v>
       </c>
       <c r="G282">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="I282">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J282">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K282" t="s">
         <v>333</v>
       </c>
       <c r="L282">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M282">
         <v>0</v>
       </c>
       <c r="N282">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O282">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P282" t="s">
         <v>279</v>
@@ -22331,28 +22331,28 @@
         <v>123</v>
       </c>
       <c r="G283">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="I283">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J283">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K283" t="s">
         <v>333</v>
       </c>
       <c r="L283">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M283">
         <v>0</v>
       </c>
       <c r="N283">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O283">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P283" t="s">
         <v>279</v>
@@ -22422,28 +22422,28 @@
         <v>123</v>
       </c>
       <c r="G285">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="I285">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J285">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K285" t="s">
         <v>333</v>
       </c>
       <c r="L285">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M285">
         <v>0</v>
       </c>
       <c r="N285">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O285">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P285" t="s">
         <v>279</v>
@@ -23147,28 +23147,28 @@
         <v>123</v>
       </c>
       <c r="G301">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I301">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J301">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K301" t="s">
         <v>333</v>
       </c>
       <c r="L301">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M301">
         <v>0</v>
       </c>
       <c r="N301">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O301">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P301" t="s">
         <v>279</v>
@@ -23367,10 +23367,10 @@
         <v>123</v>
       </c>
       <c r="G306">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I306">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -23379,16 +23379,16 @@
         <v>345</v>
       </c>
       <c r="L306">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M306">
         <v>0</v>
       </c>
       <c r="N306">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O306">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P306" t="s">
         <v>279</v>
@@ -23499,28 +23499,28 @@
         <v>123</v>
       </c>
       <c r="G309">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I309">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J309">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K309" t="s">
         <v>333</v>
       </c>
       <c r="L309">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M309">
         <v>0</v>
       </c>
       <c r="N309">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O309">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P309" t="s">
         <v>279</v>
@@ -23675,10 +23675,10 @@
         <v>123</v>
       </c>
       <c r="G313">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I313">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J313">
         <v>0</v>
@@ -23687,16 +23687,16 @@
         <v>345</v>
       </c>
       <c r="L313">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M313">
         <v>0</v>
       </c>
       <c r="N313">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O313">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P313" t="s">
         <v>279</v>
@@ -25083,28 +25083,28 @@
         <v>123</v>
       </c>
       <c r="G345">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="I345">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J345">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K345" t="s">
         <v>333</v>
       </c>
       <c r="L345">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M345">
         <v>0</v>
       </c>
       <c r="N345">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O345">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P345" t="s">
         <v>17</v>
@@ -25127,28 +25127,28 @@
         <v>123</v>
       </c>
       <c r="G346">
-        <v>-28</v>
+        <v>-34</v>
       </c>
       <c r="I346">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J346">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K346" t="s">
         <v>333</v>
       </c>
       <c r="L346">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M346">
         <v>0</v>
       </c>
       <c r="N346">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O346">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P346" t="s">
         <v>17</v>
@@ -25189,7 +25189,7 @@
         <v>0</v>
       </c>
       <c r="N347">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O347">
         <v>28</v>
@@ -25233,7 +25233,7 @@
         <v>0</v>
       </c>
       <c r="N348">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O348">
         <v>15</v>
@@ -25252,8 +25252,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{515F5B13-BD2A-4A64-BC32-3A315A2EF786}">
-  <dimension ref="A1:K1745"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F1ED83-4FE0-4CA4-B7EB-83BC91336899}">
+  <dimension ref="A1:K1796"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -86239,6 +86239,1791 @@
       </c>
       <c r="K1745">
         <v>35900</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1746" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1746" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1746" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1746">
+        <v>0</v>
+      </c>
+      <c r="H1746" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1746">
+        <v>2</v>
+      </c>
+      <c r="J1746" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1746">
+        <v>85800</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1747" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1747">
+        <v>0</v>
+      </c>
+      <c r="E1747" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1747" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1747">
+        <v>0</v>
+      </c>
+      <c r="H1747" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1747">
+        <v>1</v>
+      </c>
+      <c r="J1747" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1747">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1748" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1748">
+        <v>0</v>
+      </c>
+      <c r="E1748" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1748" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1748">
+        <v>0</v>
+      </c>
+      <c r="H1748" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1748">
+        <v>1</v>
+      </c>
+      <c r="J1748" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1748">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1749" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1749">
+        <v>0</v>
+      </c>
+      <c r="E1749" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1749" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1749">
+        <v>0</v>
+      </c>
+      <c r="H1749" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1749">
+        <v>1</v>
+      </c>
+      <c r="J1749" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1749">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1750" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1750">
+        <v>0</v>
+      </c>
+      <c r="E1750" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1750" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1750">
+        <v>0</v>
+      </c>
+      <c r="H1750" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1750">
+        <v>1</v>
+      </c>
+      <c r="J1750" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1750">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1751" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1751">
+        <v>0</v>
+      </c>
+      <c r="E1751" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1751" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1751">
+        <v>0</v>
+      </c>
+      <c r="H1751" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1751">
+        <v>1</v>
+      </c>
+      <c r="J1751" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1751">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1752" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1752">
+        <v>0</v>
+      </c>
+      <c r="E1752" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1752" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1752">
+        <v>0</v>
+      </c>
+      <c r="H1752" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1752">
+        <v>2</v>
+      </c>
+      <c r="J1752" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1752">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1753" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1753">
+        <v>0</v>
+      </c>
+      <c r="E1753" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1753" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1753">
+        <v>0</v>
+      </c>
+      <c r="H1753" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1753">
+        <v>1</v>
+      </c>
+      <c r="J1753" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1753">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1754" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1754">
+        <v>0</v>
+      </c>
+      <c r="E1754" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1754" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1754">
+        <v>0</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1754">
+        <v>1</v>
+      </c>
+      <c r="J1754" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1754">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1755" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1755">
+        <v>0</v>
+      </c>
+      <c r="E1755" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1755" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1755">
+        <v>0</v>
+      </c>
+      <c r="H1755" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1755">
+        <v>1</v>
+      </c>
+      <c r="J1755" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1755">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1756" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1756">
+        <v>0</v>
+      </c>
+      <c r="E1756" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1756" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1756">
+        <v>0</v>
+      </c>
+      <c r="H1756" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1756">
+        <v>1</v>
+      </c>
+      <c r="J1756" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1756">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1757" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1757">
+        <v>0</v>
+      </c>
+      <c r="E1757" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1757" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1757">
+        <v>0</v>
+      </c>
+      <c r="H1757" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1757">
+        <v>1</v>
+      </c>
+      <c r="J1757" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1757">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1758" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1758">
+        <v>0</v>
+      </c>
+      <c r="E1758" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1758" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1758">
+        <v>0</v>
+      </c>
+      <c r="H1758" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1758">
+        <v>1</v>
+      </c>
+      <c r="J1758" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1758">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1759" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1759">
+        <v>0</v>
+      </c>
+      <c r="E1759" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1759" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1759">
+        <v>0</v>
+      </c>
+      <c r="H1759" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1759">
+        <v>1</v>
+      </c>
+      <c r="J1759" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1759">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1760" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1760">
+        <v>0</v>
+      </c>
+      <c r="E1760" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1760" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1760">
+        <v>0</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1760">
+        <v>1</v>
+      </c>
+      <c r="J1760" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1760">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1761" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1761">
+        <v>0</v>
+      </c>
+      <c r="E1761" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1761" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1761">
+        <v>0</v>
+      </c>
+      <c r="H1761" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1761">
+        <v>1</v>
+      </c>
+      <c r="J1761" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1761">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1762" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1762">
+        <v>0</v>
+      </c>
+      <c r="E1762" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1762" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1762">
+        <v>0</v>
+      </c>
+      <c r="H1762" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1762">
+        <v>1</v>
+      </c>
+      <c r="J1762" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1762">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1763" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1763">
+        <v>0</v>
+      </c>
+      <c r="E1763" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1763" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1763">
+        <v>0</v>
+      </c>
+      <c r="H1763" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1763">
+        <v>1</v>
+      </c>
+      <c r="J1763" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1763">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1764" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1764">
+        <v>0</v>
+      </c>
+      <c r="E1764" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1764" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1764">
+        <v>0</v>
+      </c>
+      <c r="H1764" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1764">
+        <v>1</v>
+      </c>
+      <c r="J1764" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1764">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1765" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1765">
+        <v>0</v>
+      </c>
+      <c r="E1765" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1765" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1765">
+        <v>0</v>
+      </c>
+      <c r="H1765" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1765">
+        <v>1</v>
+      </c>
+      <c r="J1765" t="s">
+        <v>279</v>
+      </c>
+      <c r="K1765">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1766" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1766" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1766" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1766">
+        <v>0</v>
+      </c>
+      <c r="H1766" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1766">
+        <v>1</v>
+      </c>
+      <c r="J1766" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1766">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1767" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1767" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1767" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1767">
+        <v>0</v>
+      </c>
+      <c r="H1767" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1767">
+        <v>1</v>
+      </c>
+      <c r="J1767" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1767">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1768" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1768">
+        <v>0</v>
+      </c>
+      <c r="E1768" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1768" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1768">
+        <v>0</v>
+      </c>
+      <c r="H1768" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1768">
+        <v>1</v>
+      </c>
+      <c r="J1768" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1768">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1769" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1769" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1769" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1769">
+        <v>235</v>
+      </c>
+      <c r="H1769" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1769">
+        <v>1</v>
+      </c>
+      <c r="J1769" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1769">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1770" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1770">
+        <v>0</v>
+      </c>
+      <c r="E1770" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1770" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1770">
+        <v>0</v>
+      </c>
+      <c r="H1770" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1770">
+        <v>1</v>
+      </c>
+      <c r="J1770" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1770">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1771" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1771" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1771" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1771">
+        <v>250</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1771">
+        <v>1</v>
+      </c>
+      <c r="J1771" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1771">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1772" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1772">
+        <v>0</v>
+      </c>
+      <c r="E1772" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1772" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1772">
+        <v>0</v>
+      </c>
+      <c r="H1772" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1772">
+        <v>1</v>
+      </c>
+      <c r="J1772" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1772">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1773" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1773" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1773" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1773">
+        <v>245</v>
+      </c>
+      <c r="H1773" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1773">
+        <v>1</v>
+      </c>
+      <c r="J1773" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1773">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1774" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1774">
+        <v>0</v>
+      </c>
+      <c r="E1774" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1774" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1774">
+        <v>0</v>
+      </c>
+      <c r="H1774" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1774">
+        <v>1</v>
+      </c>
+      <c r="J1774" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1774">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1775" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1775" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1775" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1775">
+        <v>265</v>
+      </c>
+      <c r="H1775" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1775">
+        <v>1</v>
+      </c>
+      <c r="J1775" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1775">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1776" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1776">
+        <v>0</v>
+      </c>
+      <c r="E1776" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1776" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1776">
+        <v>0</v>
+      </c>
+      <c r="H1776" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1776">
+        <v>1</v>
+      </c>
+      <c r="J1776" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1776">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1777" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1777" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1777" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1777">
+        <v>245</v>
+      </c>
+      <c r="H1777" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1777">
+        <v>1</v>
+      </c>
+      <c r="J1777" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1777">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1778" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1778">
+        <v>0</v>
+      </c>
+      <c r="E1778" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1778" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1778">
+        <v>0</v>
+      </c>
+      <c r="H1778" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1778">
+        <v>1</v>
+      </c>
+      <c r="J1778" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1778">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1779" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1779" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1779" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1779">
+        <v>255</v>
+      </c>
+      <c r="H1779" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1779">
+        <v>1</v>
+      </c>
+      <c r="J1779" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1779">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1780" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1780">
+        <v>0</v>
+      </c>
+      <c r="E1780" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1780" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1780">
+        <v>0</v>
+      </c>
+      <c r="H1780" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1780">
+        <v>1</v>
+      </c>
+      <c r="J1780" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1780">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1781" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1781" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1781" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1781">
+        <v>235</v>
+      </c>
+      <c r="H1781" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1781">
+        <v>1</v>
+      </c>
+      <c r="J1781" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1781">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1782" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1782" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1782" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1782">
+        <v>240</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1782">
+        <v>1</v>
+      </c>
+      <c r="J1782" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1782">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1783" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1783" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1783" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1783">
+        <v>240</v>
+      </c>
+      <c r="H1783" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1783">
+        <v>1</v>
+      </c>
+      <c r="J1783" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1783">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1784" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1784" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1784" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1784">
+        <v>240</v>
+      </c>
+      <c r="H1784" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1784">
+        <v>1</v>
+      </c>
+      <c r="J1784" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1784">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1785" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1785" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1785" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1785">
+        <v>265</v>
+      </c>
+      <c r="H1785" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1785">
+        <v>1</v>
+      </c>
+      <c r="J1785" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1785">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1786" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1786" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1786" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1786" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1786" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1786">
+        <v>6</v>
+      </c>
+      <c r="J1786" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1786">
+        <v>41400</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1787" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1787" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1787" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1787" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1787" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1787">
+        <v>18</v>
+      </c>
+      <c r="J1787" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1787">
+        <v>151200</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1788" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1788" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1788" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1788" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1788" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1788">
+        <v>6</v>
+      </c>
+      <c r="J1788" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1788">
+        <v>59400</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1789" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1789" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1789" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1789" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1789" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1789">
+        <v>9</v>
+      </c>
+      <c r="J1789" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1789">
+        <v>80100</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1790" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1790" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1790" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1790">
+        <v>0</v>
+      </c>
+      <c r="H1790" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1790">
+        <v>3</v>
+      </c>
+      <c r="J1790" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1790">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1791" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1791" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1791" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1791">
+        <v>0</v>
+      </c>
+      <c r="H1791" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1791">
+        <v>4</v>
+      </c>
+      <c r="J1791" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1791">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1792" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1792" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1792" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1792">
+        <v>0</v>
+      </c>
+      <c r="H1792" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1792">
+        <v>3</v>
+      </c>
+      <c r="J1792" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1792">
+        <v>128700</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1793" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1793" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1793" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1793" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1793">
+        <v>0</v>
+      </c>
+      <c r="H1793" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1793">
+        <v>10</v>
+      </c>
+      <c r="J1793" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1793">
+        <v>429000</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1794" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1794" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1794" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1794">
+        <v>0</v>
+      </c>
+      <c r="H1794" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1794">
+        <v>5</v>
+      </c>
+      <c r="J1794" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1794">
+        <v>199500</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1795" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1795" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1795" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1795" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1795">
+        <v>0</v>
+      </c>
+      <c r="H1795" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1795">
+        <v>8</v>
+      </c>
+      <c r="J1795" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1795">
+        <v>287200</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1796" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1796" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1796" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1796" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1796" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1796">
+        <v>0</v>
+      </c>
+      <c r="H1796" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1796">
+        <v>6</v>
+      </c>
+      <c r="J1796" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1796">
+        <v>215400</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A38D47CB-2EDB-4CA5-AE49-A594CDA65D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15B039E7-D4B5-4150-921A-6F7D73FDEAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{171BDAA0-D1DC-4A4B-A56B-3BC7C1617239}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66F7B33F-6210-450D-A19A-957CEA30BD63}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17282" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17687" uniqueCount="1105">
   <si>
     <t>날짜</t>
   </si>
@@ -1071,6 +1071,9 @@
     <t>BUAG-151052</t>
   </si>
   <si>
+    <t>BJM845-WHNV275</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1492,9 +1495,6 @@
   </si>
   <si>
     <t>U-BJM845-131843</t>
-  </si>
-  <si>
-    <t>BJM845-WHNV275</t>
   </si>
   <si>
     <t>BJM845WHNV 바오지 남성 배드민턴화 화이트네이비 275</t>
@@ -3740,7 +3740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F58B30-65E5-4E35-A972-479A46FC138A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6C5CEA-1ADA-4749-AFED-4E4F5C694E2B}">
   <dimension ref="A1:V349"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3749,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3764,52 +3764,52 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="T1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="V1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -3817,7 +3817,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L2">
         <v>22</v>
@@ -3862,7 +3862,7 @@
         <v>17</v>
       </c>
       <c r="Q2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>59000</v>
       </c>
       <c r="U2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L3">
         <v>17</v>
@@ -3930,7 +3930,7 @@
         <v>17</v>
       </c>
       <c r="Q3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -3942,7 +3942,7 @@
         <v>59000</v>
       </c>
       <c r="U3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -3998,7 +3998,7 @@
         <v>17</v>
       </c>
       <c r="Q4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>59000</v>
       </c>
       <c r="U4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -4048,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L5">
         <v>13</v>
@@ -4066,7 +4066,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -4078,7 +4078,7 @@
         <v>59000</v>
       </c>
       <c r="U5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -4089,7 +4089,7 @@
         <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -4116,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -4134,7 +4134,7 @@
         <v>17</v>
       </c>
       <c r="Q6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>59000</v>
       </c>
       <c r="U6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -4157,7 +4157,7 @@
         <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -4202,7 +4202,7 @@
         <v>17</v>
       </c>
       <c r="Q7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -4214,7 +4214,7 @@
         <v>59000</v>
       </c>
       <c r="U7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -4270,7 +4270,7 @@
         <v>17</v>
       </c>
       <c r="Q8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>59000</v>
       </c>
       <c r="U8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -4293,7 +4293,7 @@
         <v>154</v>
       </c>
       <c r="B9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -4338,7 +4338,7 @@
         <v>17</v>
       </c>
       <c r="Q9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>59000</v>
       </c>
       <c r="U9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -4361,7 +4361,7 @@
         <v>155</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -4406,7 +4406,7 @@
         <v>17</v>
       </c>
       <c r="Q10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>59000</v>
       </c>
       <c r="U10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -4474,7 +4474,7 @@
         <v>17</v>
       </c>
       <c r="Q11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -4486,7 +4486,7 @@
         <v>59000</v>
       </c>
       <c r="U11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -4497,7 +4497,7 @@
         <v>313</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C12" t="s">
         <v>249</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L12">
         <v>2</v>
@@ -4542,7 +4542,7 @@
         <v>17</v>
       </c>
       <c r="Q12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -4554,7 +4554,7 @@
         <v>79000</v>
       </c>
       <c r="U12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>314</v>
       </c>
       <c r="B13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C13" t="s">
         <v>249</v>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L13">
         <v>2</v>
@@ -4610,7 +4610,7 @@
         <v>17</v>
       </c>
       <c r="Q13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>79000</v>
       </c>
       <c r="U13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>315</v>
       </c>
       <c r="B14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C14" t="s">
         <v>249</v>
@@ -4660,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -4678,7 +4678,7 @@
         <v>17</v>
       </c>
       <c r="Q14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>79000</v>
       </c>
       <c r="U14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4701,7 +4701,7 @@
         <v>316</v>
       </c>
       <c r="B15" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C15" t="s">
         <v>249</v>
@@ -4728,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -4746,7 +4746,7 @@
         <v>17</v>
       </c>
       <c r="Q15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4758,7 +4758,7 @@
         <v>79000</v>
       </c>
       <c r="U15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C16" t="s">
         <v>249</v>
@@ -4796,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>17</v>
       </c>
       <c r="Q16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         <v>79000</v>
       </c>
       <c r="U16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4837,7 +4837,7 @@
         <v>317</v>
       </c>
       <c r="B17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C17" t="s">
         <v>249</v>
@@ -4864,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L17">
         <v>4</v>
@@ -4882,7 +4882,7 @@
         <v>17</v>
       </c>
       <c r="Q17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4894,7 +4894,7 @@
         <v>79000</v>
       </c>
       <c r="U17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>268</v>
       </c>
       <c r="B18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C18" t="s">
         <v>249</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -4950,7 +4950,7 @@
         <v>17</v>
       </c>
       <c r="Q18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -4962,7 +4962,7 @@
         <v>79000</v>
       </c>
       <c r="U18" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>269</v>
       </c>
       <c r="B19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C19" t="s">
         <v>249</v>
@@ -5000,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L19">
         <v>3</v>
@@ -5018,7 +5018,7 @@
         <v>17</v>
       </c>
       <c r="Q19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>79000</v>
       </c>
       <c r="U19" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5041,7 +5041,7 @@
         <v>318</v>
       </c>
       <c r="B20" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C20" t="s">
         <v>249</v>
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L20">
         <v>2</v>
@@ -5086,7 +5086,7 @@
         <v>17</v>
       </c>
       <c r="Q20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5098,7 +5098,7 @@
         <v>79000</v>
       </c>
       <c r="U20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5109,7 +5109,7 @@
         <v>319</v>
       </c>
       <c r="B21" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C21" t="s">
         <v>249</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L21">
         <v>2</v>
@@ -5154,7 +5154,7 @@
         <v>17</v>
       </c>
       <c r="Q21" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>79000</v>
       </c>
       <c r="U21" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C22" t="s">
         <v>249</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -5222,7 +5222,7 @@
         <v>17</v>
       </c>
       <c r="Q22" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>79000</v>
       </c>
       <c r="U22" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5245,7 +5245,7 @@
         <v>253</v>
       </c>
       <c r="B23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C23" t="s">
         <v>249</v>
@@ -5272,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -5290,7 +5290,7 @@
         <v>17</v>
       </c>
       <c r="Q23" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -5302,7 +5302,7 @@
         <v>79000</v>
       </c>
       <c r="U23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5313,7 +5313,7 @@
         <v>320</v>
       </c>
       <c r="B24" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C24" t="s">
         <v>249</v>
@@ -5340,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -5358,7 +5358,7 @@
         <v>17</v>
       </c>
       <c r="Q24" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -5370,7 +5370,7 @@
         <v>79000</v>
       </c>
       <c r="U24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -5381,7 +5381,7 @@
         <v>321</v>
       </c>
       <c r="B25" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C25" t="s">
         <v>249</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -5426,7 +5426,7 @@
         <v>17</v>
       </c>
       <c r="Q25" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -5438,7 +5438,7 @@
         <v>79000</v>
       </c>
       <c r="U25" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C26" t="s">
         <v>249</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L26">
         <v>3</v>
@@ -5494,7 +5494,7 @@
         <v>17</v>
       </c>
       <c r="Q26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -5506,7 +5506,7 @@
         <v>79000</v>
       </c>
       <c r="U26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -5517,7 +5517,7 @@
         <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C27" t="s">
         <v>249</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L27">
         <v>6</v>
@@ -5562,7 +5562,7 @@
         <v>17</v>
       </c>
       <c r="Q27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>79000</v>
       </c>
       <c r="U27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -5585,7 +5585,7 @@
         <v>266</v>
       </c>
       <c r="B28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C28" t="s">
         <v>249</v>
@@ -5612,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -5630,7 +5630,7 @@
         <v>17</v>
       </c>
       <c r="Q28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>79000</v>
       </c>
       <c r="U28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>323</v>
       </c>
       <c r="B29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C29" t="s">
         <v>249</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L29">
         <v>3</v>
@@ -5698,7 +5698,7 @@
         <v>17</v>
       </c>
       <c r="Q29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>79000</v>
       </c>
       <c r="U29" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -5721,7 +5721,7 @@
         <v>267</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C30" t="s">
         <v>249</v>
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L30">
         <v>3</v>
@@ -5766,7 +5766,7 @@
         <v>17</v>
       </c>
       <c r="Q30" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -5778,7 +5778,7 @@
         <v>79000</v>
       </c>
       <c r="U30" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -5789,7 +5789,7 @@
         <v>324</v>
       </c>
       <c r="B31" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C31" t="s">
         <v>249</v>
@@ -5816,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L31">
         <v>2</v>
@@ -5834,7 +5834,7 @@
         <v>17</v>
       </c>
       <c r="Q31" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>79000</v>
       </c>
       <c r="U31" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B32" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C32" t="s">
         <v>249</v>
@@ -5884,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>17</v>
       </c>
       <c r="Q32" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -5914,7 +5914,7 @@
         <v>79000</v>
       </c>
       <c r="U32" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -5922,10 +5922,10 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B33" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C33" t="s">
         <v>249</v>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>17</v>
       </c>
       <c r="Q33" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -5982,7 +5982,7 @@
         <v>79000</v>
       </c>
       <c r="U33" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B34" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C34" t="s">
         <v>249</v>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>17</v>
       </c>
       <c r="Q34" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -6050,7 +6050,7 @@
         <v>79000</v>
       </c>
       <c r="U34" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B35" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C35" t="s">
         <v>249</v>
@@ -6088,7 +6088,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>17</v>
       </c>
       <c r="Q35" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
         <v>79000</v>
       </c>
       <c r="U35" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -6126,10 +6126,10 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B36" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C36" t="s">
         <v>249</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>17</v>
       </c>
       <c r="Q36" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -6186,7 +6186,7 @@
         <v>79000</v>
       </c>
       <c r="U36" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -6194,10 +6194,10 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B37" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C37" t="s">
         <v>249</v>
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         <v>17</v>
       </c>
       <c r="Q37" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>79000</v>
       </c>
       <c r="U37" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -6265,7 +6265,7 @@
         <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C38" t="s">
         <v>249</v>
@@ -6292,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         <v>17</v>
       </c>
       <c r="Q38" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>79000</v>
       </c>
       <c r="U38" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B39" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C39" t="s">
         <v>249</v>
@@ -6360,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>17</v>
       </c>
       <c r="Q39" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>79000</v>
       </c>
       <c r="U39" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B40" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C40" t="s">
         <v>249</v>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -6446,7 +6446,7 @@
         <v>17</v>
       </c>
       <c r="Q40" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -6458,7 +6458,7 @@
         <v>79000</v>
       </c>
       <c r="U40" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -6466,10 +6466,10 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B41" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C41" t="s">
         <v>249</v>
@@ -6496,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>17</v>
       </c>
       <c r="Q41" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -6526,7 +6526,7 @@
         <v>79000</v>
       </c>
       <c r="U41" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -6534,10 +6534,10 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B42" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C42" t="s">
         <v>249</v>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>17</v>
       </c>
       <c r="Q42" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -6594,7 +6594,7 @@
         <v>79000</v>
       </c>
       <c r="U42" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B43" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C43" t="s">
         <v>249</v>
@@ -6632,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -6650,7 +6650,7 @@
         <v>17</v>
       </c>
       <c r="Q43" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>79000</v>
       </c>
       <c r="U43" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -6670,10 +6670,10 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B44" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C44" t="s">
         <v>249</v>
@@ -6700,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
       <c r="Q44" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -6730,7 +6730,7 @@
         <v>79000</v>
       </c>
       <c r="U44" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B45" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C45" t="s">
         <v>249</v>
@@ -6768,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -6786,7 +6786,7 @@
         <v>17</v>
       </c>
       <c r="Q45" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -6798,7 +6798,7 @@
         <v>79000</v>
       </c>
       <c r="U45" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6806,10 +6806,10 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B46" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C46" t="s">
         <v>249</v>
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>17</v>
       </c>
       <c r="Q46" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>79000</v>
       </c>
       <c r="U46" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B47" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C47" t="s">
         <v>249</v>
@@ -6904,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -6922,7 +6922,7 @@
         <v>17</v>
       </c>
       <c r="Q47" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -6934,7 +6934,7 @@
         <v>79000</v>
       </c>
       <c r="U47" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -6942,10 +6942,10 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B48" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C48" t="s">
         <v>249</v>
@@ -6972,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -6990,7 +6990,7 @@
         <v>17</v>
       </c>
       <c r="Q48" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -7002,7 +7002,7 @@
         <v>79000</v>
       </c>
       <c r="U48" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B49" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C49" t="s">
         <v>249</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         <v>17</v>
       </c>
       <c r="Q49" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -7070,7 +7070,7 @@
         <v>79000</v>
       </c>
       <c r="U49" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>484</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s">
         <v>485</v>
@@ -7096,37 +7096,37 @@
         <v>275</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="s">
         <v>17</v>
       </c>
       <c r="Q50" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>17</v>
       </c>
       <c r="Q51" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -7516,7 +7516,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -7652,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -7720,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -7788,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -7856,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -8060,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L67">
         <v>17</v>
@@ -8332,7 +8332,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L68">
         <v>20</v>
@@ -8400,7 +8400,7 @@
         <v>13</v>
       </c>
       <c r="K69" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L69">
         <v>30</v>
@@ -8468,7 +8468,7 @@
         <v>8</v>
       </c>
       <c r="K70" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L70">
         <v>17</v>
@@ -8536,7 +8536,7 @@
         <v>8</v>
       </c>
       <c r="K71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L71">
         <v>11</v>
@@ -8604,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L73">
         <v>5</v>
@@ -8740,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -8876,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L76">
         <v>1</v>
@@ -8944,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L77">
         <v>4</v>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L78">
         <v>1</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L79">
         <v>3</v>
@@ -9148,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L80">
         <v>2</v>
@@ -9216,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L81">
         <v>3</v>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -9352,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L84">
         <v>1</v>
@@ -9488,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L85">
         <v>1</v>
@@ -9556,7 +9556,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L86">
         <v>1</v>
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L88">
         <v>5</v>
@@ -9760,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L89">
         <v>3</v>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L90">
         <v>3</v>
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -10032,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -10100,7 +10100,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L94">
         <v>1</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -10236,7 +10236,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L96">
         <v>3</v>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -10372,7 +10372,7 @@
         <v>4</v>
       </c>
       <c r="K98" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L98">
         <v>12</v>
@@ -10440,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L99">
         <v>5</v>
@@ -10508,7 +10508,7 @@
         <v>5</v>
       </c>
       <c r="K100" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L100">
         <v>8</v>
@@ -10576,7 +10576,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -10712,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L103">
         <v>4</v>
@@ -10780,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L104">
         <v>7</v>
@@ -10848,7 +10848,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -10916,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L106">
         <v>2</v>
@@ -10984,7 +10984,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -11040,31 +11040,31 @@
         <v>265</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>0</v>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L108">
+        <v>3</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
         <v>2</v>
       </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>1</v>
-      </c>
       <c r="O108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P108" t="s">
         <v>17</v>
@@ -11120,7 +11120,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -11188,7 +11188,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -11256,7 +11256,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -11324,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L112">
         <v>6</v>
@@ -11392,7 +11392,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L113">
         <v>16</v>
@@ -11460,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L114">
         <v>16</v>
@@ -11528,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L115">
         <v>8</v>
@@ -11596,7 +11596,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L116">
         <v>6</v>
@@ -11664,7 +11664,7 @@
         <v>8</v>
       </c>
       <c r="K117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L117">
         <v>12</v>
@@ -11732,7 +11732,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L118">
         <v>6</v>
@@ -11800,7 +11800,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L119">
         <v>7</v>
@@ -11868,7 +11868,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L120">
         <v>6</v>
@@ -11936,7 +11936,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -12004,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L122">
         <v>7</v>
@@ -12072,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L123">
         <v>3</v>
@@ -12140,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L124">
         <v>4</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L125">
         <v>2</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L126">
         <v>6</v>
@@ -12344,7 +12344,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L127">
         <v>19</v>
@@ -12412,7 +12412,7 @@
         <v>11</v>
       </c>
       <c r="K128" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L128">
         <v>32</v>
@@ -12480,7 +12480,7 @@
         <v>12</v>
       </c>
       <c r="K129" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L129">
         <v>23</v>
@@ -12548,7 +12548,7 @@
         <v>1</v>
       </c>
       <c r="K130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L130">
         <v>14</v>
@@ -12616,7 +12616,7 @@
         <v>4</v>
       </c>
       <c r="K131" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L131">
         <v>6</v>
@@ -12684,7 +12684,7 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L132">
         <v>43</v>
@@ -12752,7 +12752,7 @@
         <v>38</v>
       </c>
       <c r="K133" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L133">
         <v>47</v>
@@ -12808,31 +12808,31 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J134">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L134">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M134">
         <v>10</v>
       </c>
       <c r="N134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O134">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P134" t="s">
         <v>17</v>
@@ -12888,7 +12888,7 @@
         <v>26</v>
       </c>
       <c r="K135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L135">
         <v>32</v>
@@ -12956,7 +12956,7 @@
         <v>4</v>
       </c>
       <c r="K136" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L136">
         <v>9</v>
@@ -13012,31 +13012,31 @@
         <v>235</v>
       </c>
       <c r="G137">
+        <v>8</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
         <v>9</v>
       </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>8</v>
-      </c>
       <c r="J137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L137">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M137">
+        <v>4</v>
+      </c>
+      <c r="N137">
         <v>3</v>
       </c>
-      <c r="N137">
-        <v>2</v>
-      </c>
       <c r="O137">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P137" t="s">
         <v>17</v>
@@ -13080,31 +13080,31 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L138">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M138">
+        <v>6</v>
+      </c>
+      <c r="N138">
         <v>5</v>
       </c>
-      <c r="N138">
-        <v>4</v>
-      </c>
       <c r="O138">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P138" t="s">
         <v>17</v>
@@ -13160,7 +13160,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L139">
         <v>11</v>
@@ -13228,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L140">
         <v>15</v>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L141">
         <v>8</v>
@@ -13352,31 +13352,31 @@
         <v>235</v>
       </c>
       <c r="G142">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L142">
+        <v>5</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142">
         <v>4</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>3</v>
       </c>
       <c r="P142" t="s">
         <v>17</v>
@@ -13420,31 +13420,31 @@
         <v>240</v>
       </c>
       <c r="G143">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L143">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M143">
+        <v>4</v>
+      </c>
+      <c r="N143">
         <v>2</v>
       </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
       <c r="O143">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P143" t="s">
         <v>17</v>
@@ -13500,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L144">
         <v>3</v>
@@ -13568,7 +13568,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L145">
         <v>2</v>
@@ -13636,7 +13636,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L146">
         <v>2</v>
@@ -13692,31 +13692,31 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J147">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K147" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L147">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M147">
         <v>3</v>
       </c>
       <c r="N147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O147">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P147" t="s">
         <v>17</v>
@@ -13760,31 +13760,31 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J148">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K148" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L148">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M148">
         <v>3</v>
       </c>
       <c r="N148">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O148">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P148" t="s">
         <v>17</v>
@@ -13828,31 +13828,31 @@
         <v>245</v>
       </c>
       <c r="G149">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L149">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M149">
         <v>3</v>
       </c>
       <c r="N149">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O149">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P149" t="s">
         <v>17</v>
@@ -13908,7 +13908,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L150">
         <v>23</v>
@@ -13964,31 +13964,31 @@
         <v>255</v>
       </c>
       <c r="G151">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J151">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K151" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L151">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M151">
         <v>0</v>
       </c>
       <c r="N151">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O151">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P151" t="s">
         <v>17</v>
@@ -14044,7 +14044,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -14112,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -14180,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -14248,7 +14248,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -14384,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L157">
         <v>1</v>
@@ -14452,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="K158" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L158">
         <v>2</v>
@@ -14520,7 +14520,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -14588,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L162">
         <v>1</v>
@@ -14792,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -14860,7 +14860,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L164">
         <v>1</v>
@@ -14928,7 +14928,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -14996,7 +14996,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -15064,7 +15064,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L167">
         <v>4</v>
@@ -15132,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L168">
         <v>6</v>
@@ -15200,7 +15200,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L169">
         <v>4</v>
@@ -15268,7 +15268,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L170">
         <v>3</v>
@@ -15336,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="K171" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L171">
         <v>2</v>
@@ -15392,31 +15392,31 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J172">
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L172">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M172">
         <v>2</v>
       </c>
       <c r="N172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O172">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P172" t="s">
         <v>17</v>
@@ -15472,7 +15472,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L173">
         <v>18</v>
@@ -15528,31 +15528,31 @@
         <v>245</v>
       </c>
       <c r="G174">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J174">
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L174">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P174" t="s">
         <v>17</v>
@@ -15608,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L175">
         <v>11</v>
@@ -15676,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L176">
         <v>6</v>
@@ -15744,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L177">
         <v>5</v>
@@ -15800,31 +15800,31 @@
         <v>240</v>
       </c>
       <c r="G178">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
       <c r="I178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J178">
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L178">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P178" t="s">
         <v>17</v>
@@ -15880,7 +15880,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L179">
         <v>4</v>
@@ -15948,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L180">
         <v>7</v>
@@ -16016,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L181">
         <v>1</v>
@@ -16084,7 +16084,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L182">
         <v>13</v>
@@ -16140,31 +16140,31 @@
         <v>240</v>
       </c>
       <c r="G183">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H183">
         <v>0</v>
       </c>
       <c r="I183">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J183">
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L183">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M183">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N183">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O183">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P183" t="s">
         <v>17</v>
@@ -16208,31 +16208,31 @@
         <v>245</v>
       </c>
       <c r="G184">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J184">
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L184">
+        <v>6</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>1</v>
+      </c>
+      <c r="O184">
         <v>5</v>
-      </c>
-      <c r="M184">
-        <v>1</v>
-      </c>
-      <c r="N184">
-        <v>0</v>
-      </c>
-      <c r="O184">
-        <v>4</v>
       </c>
       <c r="P184" t="s">
         <v>17</v>
@@ -16288,7 +16288,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L185">
         <v>6</v>
@@ -16356,7 +16356,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -16424,7 +16424,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L187">
         <v>12</v>
@@ -16492,7 +16492,7 @@
         <v>5</v>
       </c>
       <c r="K188" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L188">
         <v>16</v>
@@ -16560,7 +16560,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L189">
         <v>10</v>
@@ -16628,7 +16628,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L190">
         <v>10</v>
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L191">
         <v>2</v>
@@ -16764,7 +16764,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L192">
         <v>17</v>
@@ -16832,7 +16832,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L193">
         <v>36</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L194">
         <v>32</v>
@@ -16968,7 +16968,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L195">
         <v>24</v>
@@ -17036,7 +17036,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L196">
         <v>10</v>
@@ -17104,7 +17104,7 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L197">
         <v>3</v>
@@ -17172,7 +17172,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L198">
         <v>10</v>
@@ -17240,7 +17240,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L199">
         <v>6</v>
@@ -17308,7 +17308,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -17376,7 +17376,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -17444,7 +17444,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L202">
         <v>1</v>
@@ -17512,7 +17512,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -17580,7 +17580,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L204">
         <v>2</v>
@@ -17648,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L205">
         <v>5</v>
@@ -17716,7 +17716,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -17784,7 +17784,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L207">
         <v>2</v>
@@ -17852,7 +17852,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L208">
         <v>2</v>
@@ -17920,7 +17920,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -17988,7 +17988,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L210">
         <v>6</v>
@@ -18056,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L211">
         <v>2</v>
@@ -18124,7 +18124,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L212">
         <v>1</v>
@@ -18192,7 +18192,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L213">
         <v>3</v>
@@ -18260,7 +18260,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L214">
         <v>4</v>
@@ -18328,7 +18328,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -18396,7 +18396,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L216">
         <v>1</v>
@@ -18464,7 +18464,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L217">
         <v>11</v>
@@ -18532,7 +18532,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L218">
         <v>10</v>
@@ -18600,7 +18600,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L219">
         <v>10</v>
@@ -18668,7 +18668,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L220">
         <v>10</v>
@@ -18736,7 +18736,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L221">
         <v>4</v>
@@ -18804,7 +18804,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L222">
         <v>5</v>
@@ -18872,7 +18872,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L223">
         <v>28</v>
@@ -18940,7 +18940,7 @@
         <v>3</v>
       </c>
       <c r="K224" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L224">
         <v>24</v>
@@ -19008,7 +19008,7 @@
         <v>6</v>
       </c>
       <c r="K225" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L225">
         <v>19</v>
@@ -19076,7 +19076,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -19144,7 +19144,7 @@
         <v>4</v>
       </c>
       <c r="K227" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L227">
         <v>27</v>
@@ -19212,7 +19212,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L228">
         <v>32</v>
@@ -19280,7 +19280,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L229">
         <v>22</v>
@@ -19348,7 +19348,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L230">
         <v>13</v>
@@ -19416,7 +19416,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L231">
         <v>2</v>
@@ -19481,7 +19481,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L232">
         <v>17</v>
@@ -19531,31 +19531,31 @@
         <v>123</v>
       </c>
       <c r="G233">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J233">
+        <v>4</v>
+      </c>
+      <c r="K233" t="s">
+        <v>349</v>
+      </c>
+      <c r="L233">
+        <v>54</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
         <v>2</v>
       </c>
-      <c r="K233" t="s">
-        <v>348</v>
-      </c>
-      <c r="L233">
-        <v>53</v>
-      </c>
-      <c r="M233">
-        <v>1</v>
-      </c>
-      <c r="N233">
-        <v>1</v>
-      </c>
       <c r="O233">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P233" t="s">
         <v>124</v>
@@ -19605,7 +19605,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L234">
         <v>7</v>
@@ -19667,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L235">
         <v>27</v>
@@ -19729,7 +19729,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L236">
         <v>11</v>
@@ -19791,7 +19791,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L237">
         <v>8</v>
@@ -19853,7 +19853,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L238">
         <v>7</v>
@@ -19915,7 +19915,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L239">
         <v>33</v>
@@ -19977,7 +19977,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L240">
         <v>17</v>
@@ -20039,7 +20039,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L241">
         <v>14</v>
@@ -20101,7 +20101,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L242">
         <v>21</v>
@@ -20163,7 +20163,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L243">
         <v>3</v>
@@ -20225,7 +20225,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L244">
         <v>19</v>
@@ -20287,7 +20287,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L245">
         <v>23</v>
@@ -20349,7 +20349,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L246">
         <v>10</v>
@@ -20411,7 +20411,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L247">
         <v>15</v>
@@ -20473,7 +20473,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L248">
         <v>5</v>
@@ -20535,7 +20535,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L249">
         <v>15</v>
@@ -20597,7 +20597,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L250">
         <v>35</v>
@@ -20659,7 +20659,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L251">
         <v>20</v>
@@ -20721,7 +20721,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L252">
         <v>18</v>
@@ -20783,7 +20783,7 @@
         <v>12</v>
       </c>
       <c r="K253" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L253">
         <v>57</v>
@@ -20845,7 +20845,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L254">
         <v>35</v>
@@ -20907,7 +20907,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L255">
         <v>27</v>
@@ -20969,7 +20969,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L256">
         <v>20</v>
@@ -21031,7 +21031,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L257">
         <v>8</v>
@@ -21093,7 +21093,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L258">
         <v>17</v>
@@ -21155,7 +21155,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L259">
         <v>21</v>
@@ -21217,7 +21217,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L260">
         <v>86</v>
@@ -21267,28 +21267,28 @@
         <v>181</v>
       </c>
       <c r="G261">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="I261">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J261">
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L261">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M261">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N261">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="O261">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P261" t="s">
         <v>182</v>
@@ -21335,7 +21335,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L262">
         <v>199</v>
@@ -21394,7 +21394,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L263">
         <v>142</v>
@@ -21450,7 +21450,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L264">
         <v>19</v>
@@ -21503,7 +21503,7 @@
         <v>0</v>
       </c>
       <c r="K265" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L265">
         <v>17</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L266">
         <v>11</v>
@@ -21603,7 +21603,7 @@
         <v>0</v>
       </c>
       <c r="K267" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L267">
         <v>11</v>
@@ -21650,7 +21650,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L268">
         <v>11</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L269">
         <v>11</v>
@@ -21744,7 +21744,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L270">
         <v>11</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L271">
         <v>11</v>
@@ -21835,7 +21835,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -21879,7 +21879,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -21914,28 +21914,28 @@
         <v>123</v>
       </c>
       <c r="G274">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="I274">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J274">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K274" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L274">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M274">
         <v>0</v>
       </c>
       <c r="N274">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O274">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P274" t="s">
         <v>279</v>
@@ -21961,28 +21961,28 @@
         <v>123</v>
       </c>
       <c r="G275">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="I275">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J275">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K275" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L275">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M275">
         <v>0</v>
       </c>
       <c r="N275">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O275">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P275" t="s">
         <v>279</v>
@@ -22017,7 +22017,7 @@
         <v>46</v>
       </c>
       <c r="K276" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L276">
         <v>23</v>
@@ -22055,28 +22055,28 @@
         <v>123</v>
       </c>
       <c r="G277">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="I277">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J277">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K277" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L277">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M277">
         <v>0</v>
       </c>
       <c r="N277">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O277">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P277" t="s">
         <v>279</v>
@@ -22111,7 +22111,7 @@
         <v>10</v>
       </c>
       <c r="K278" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L278">
         <v>5</v>
@@ -22149,28 +22149,28 @@
         <v>123</v>
       </c>
       <c r="G279">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="I279">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J279">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K279" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L279">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M279">
         <v>0</v>
       </c>
       <c r="N279">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O279">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P279" t="s">
         <v>279</v>
@@ -22205,7 +22205,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -22243,28 +22243,28 @@
         <v>123</v>
       </c>
       <c r="G281">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I281">
+        <v>16</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281" t="s">
+        <v>361</v>
+      </c>
+      <c r="L281">
+        <v>16</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
         <v>13</v>
       </c>
-      <c r="J281">
-        <v>0</v>
-      </c>
-      <c r="K281" t="s">
-        <v>360</v>
-      </c>
-      <c r="L281">
-        <v>13</v>
-      </c>
-      <c r="M281">
-        <v>0</v>
-      </c>
-      <c r="N281">
-        <v>10</v>
-      </c>
       <c r="O281">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P281" t="s">
         <v>279</v>
@@ -22290,28 +22290,28 @@
         <v>123</v>
       </c>
       <c r="G282">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="I282">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J282">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K282" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L282">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M282">
         <v>0</v>
       </c>
       <c r="N282">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O282">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P282" t="s">
         <v>279</v>
@@ -22337,28 +22337,28 @@
         <v>123</v>
       </c>
       <c r="G283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I283">
+        <v>29</v>
+      </c>
+      <c r="J283">
         <v>28</v>
       </c>
-      <c r="J283">
-        <v>26</v>
-      </c>
       <c r="K283" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L283">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M283">
         <v>0</v>
       </c>
       <c r="N283">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O283">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P283" t="s">
         <v>279</v>
@@ -22393,7 +22393,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L284">
         <v>0</v>
@@ -22428,28 +22428,28 @@
         <v>123</v>
       </c>
       <c r="G285">
-        <v>-39</v>
+        <v>-44</v>
       </c>
       <c r="I285">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J285">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K285" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L285">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M285">
         <v>0</v>
       </c>
       <c r="N285">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O285">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P285" t="s">
         <v>279</v>
@@ -22484,7 +22484,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L286">
         <v>0</v>
@@ -22528,7 +22528,7 @@
         <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L287">
         <v>0</v>
@@ -22566,28 +22566,28 @@
         <v>123</v>
       </c>
       <c r="G288">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I288">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J288">
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L288">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M288">
         <v>0</v>
       </c>
       <c r="N288">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O288">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P288" t="s">
         <v>279</v>
@@ -22613,28 +22613,28 @@
         <v>123</v>
       </c>
       <c r="G289">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I289">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J289">
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L289">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M289">
         <v>0</v>
       </c>
       <c r="N289">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O289">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P289" t="s">
         <v>279</v>
@@ -22669,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L290">
         <v>7</v>
@@ -22713,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L291">
         <v>8</v>
@@ -22757,7 +22757,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L292">
         <v>0</v>
@@ -22795,28 +22795,28 @@
         <v>123</v>
       </c>
       <c r="G293">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I293">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J293">
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L293">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M293">
         <v>0</v>
       </c>
       <c r="N293">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O293">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P293" t="s">
         <v>279</v>
@@ -22842,28 +22842,28 @@
         <v>123</v>
       </c>
       <c r="G294">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I294">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J294">
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L294">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M294">
         <v>0</v>
       </c>
       <c r="N294">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O294">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P294" t="s">
         <v>279</v>
@@ -22895,7 +22895,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L295">
         <v>9</v>
@@ -22939,7 +22939,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L296">
         <v>7</v>
@@ -22983,7 +22983,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L297">
         <v>9</v>
@@ -23021,28 +23021,28 @@
         <v>123</v>
       </c>
       <c r="G298">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I298">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J298">
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L298">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M298">
         <v>0</v>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O298">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P298" t="s">
         <v>279</v>
@@ -23074,7 +23074,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L299">
         <v>7</v>
@@ -23118,7 +23118,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L300">
         <v>4</v>
@@ -23153,28 +23153,28 @@
         <v>123</v>
       </c>
       <c r="G301">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I301">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J301">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K301" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L301">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M301">
         <v>0</v>
       </c>
       <c r="N301">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O301">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P301" t="s">
         <v>279</v>
@@ -23197,28 +23197,28 @@
         <v>123</v>
       </c>
       <c r="G302">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I302">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J302">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K302" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L302">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M302">
         <v>0</v>
       </c>
       <c r="N302">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O302">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P302" t="s">
         <v>279</v>
@@ -23250,7 +23250,7 @@
         <v>0</v>
       </c>
       <c r="K303" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L303">
         <v>11</v>
@@ -23285,28 +23285,28 @@
         <v>123</v>
       </c>
       <c r="G304">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I304">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J304">
         <v>0</v>
       </c>
       <c r="K304" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L304">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M304">
         <v>0</v>
       </c>
       <c r="N304">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O304">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P304" t="s">
         <v>279</v>
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L305">
         <v>13</v>
@@ -23373,28 +23373,28 @@
         <v>123</v>
       </c>
       <c r="G306">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I306">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J306">
         <v>0</v>
       </c>
       <c r="K306" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L306">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M306">
         <v>0</v>
       </c>
       <c r="N306">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O306">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P306" t="s">
         <v>279</v>
@@ -23426,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L307">
         <v>17</v>
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="K308" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L308">
         <v>0</v>
@@ -23505,28 +23505,28 @@
         <v>123</v>
       </c>
       <c r="G309">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I309">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J309">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K309" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L309">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M309">
         <v>0</v>
       </c>
       <c r="N309">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O309">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="P309" t="s">
         <v>279</v>
@@ -23558,7 +23558,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L310">
         <v>16</v>
@@ -23602,7 +23602,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L311">
         <v>15</v>
@@ -23637,28 +23637,28 @@
         <v>123</v>
       </c>
       <c r="G312">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I312">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J312">
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L312">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M312">
         <v>0</v>
       </c>
       <c r="N312">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O312">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P312" t="s">
         <v>279</v>
@@ -23690,7 +23690,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L313">
         <v>22</v>
@@ -23725,28 +23725,28 @@
         <v>123</v>
       </c>
       <c r="G314">
+        <v>20</v>
+      </c>
+      <c r="I314">
         <v>30</v>
       </c>
-      <c r="I314">
+      <c r="J314">
+        <v>10</v>
+      </c>
+      <c r="K314" t="s">
+        <v>349</v>
+      </c>
+      <c r="L314">
+        <v>30</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
+      </c>
+      <c r="N314">
         <v>20</v>
       </c>
-      <c r="J314">
-        <v>0</v>
-      </c>
-      <c r="K314" t="s">
-        <v>360</v>
-      </c>
-      <c r="L314">
-        <v>20</v>
-      </c>
-      <c r="M314">
-        <v>0</v>
-      </c>
-      <c r="N314">
-        <v>10</v>
-      </c>
       <c r="O314">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P314" t="s">
         <v>279</v>
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L315">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L316">
         <v>0</v>
@@ -23857,28 +23857,28 @@
         <v>123</v>
       </c>
       <c r="G317">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I317">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J317">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K317" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="L317">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="M317">
         <v>0</v>
       </c>
       <c r="N317">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O317">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="P317" t="s">
         <v>279</v>
@@ -23910,7 +23910,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L318">
         <v>15</v>
@@ -23954,7 +23954,7 @@
         <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L319">
         <v>21</v>
@@ -23998,7 +23998,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L320">
         <v>22</v>
@@ -24042,7 +24042,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L321">
         <v>0</v>
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L322">
         <v>0</v>
@@ -24130,7 +24130,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L323">
         <v>0</v>
@@ -24174,7 +24174,7 @@
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L324">
         <v>0</v>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L325">
         <v>0</v>
@@ -24262,7 +24262,7 @@
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L326">
         <v>0</v>
@@ -24306,7 +24306,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L327">
         <v>1</v>
@@ -24350,7 +24350,7 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L328">
         <v>0</v>
@@ -24394,7 +24394,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L329">
         <v>0</v>
@@ -24438,7 +24438,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L330">
         <v>0</v>
@@ -24482,7 +24482,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L331">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L332">
         <v>0</v>
@@ -24570,7 +24570,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L333">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L334">
         <v>0</v>
@@ -24658,7 +24658,7 @@
         <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L335">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L336">
         <v>0</v>
@@ -24746,7 +24746,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L337">
         <v>0</v>
@@ -24790,7 +24790,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L338">
         <v>0</v>
@@ -24834,7 +24834,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L339">
         <v>0</v>
@@ -24878,7 +24878,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L340">
         <v>0</v>
@@ -24922,7 +24922,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L341">
         <v>0</v>
@@ -24966,7 +24966,7 @@
         <v>0</v>
       </c>
       <c r="K342" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L342">
         <v>0</v>
@@ -25010,7 +25010,7 @@
         <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L343">
         <v>0</v>
@@ -25054,7 +25054,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L344">
         <v>0</v>
@@ -25089,28 +25089,28 @@
         <v>123</v>
       </c>
       <c r="G345">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="I345">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J345">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K345" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L345">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M345">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N345">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O345">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P345" t="s">
         <v>17</v>
@@ -25142,7 +25142,7 @@
         <v>81</v>
       </c>
       <c r="K346" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L346">
         <v>45</v>
@@ -25177,28 +25177,28 @@
         <v>123</v>
       </c>
       <c r="G347">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="I347">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J347">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K347" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L347">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M347">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N347">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O347">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P347" t="s">
         <v>17</v>
@@ -25221,28 +25221,28 @@
         <v>123</v>
       </c>
       <c r="G348">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="I348">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J348">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K348" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L348">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M348">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N348">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O348">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P348" t="s">
         <v>17</v>
@@ -25268,7 +25268,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L349">
         <v>0</v>
@@ -25296,8 +25296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4C77A0-3169-41F7-92B2-6B07E9EFAA33}">
-  <dimension ref="A1:K2097"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB23ABD-8D56-4B3C-B70A-D38D92E7A139}">
+  <dimension ref="A1:K2160"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -98602,6 +98602,2211 @@
         <v>17</v>
       </c>
       <c r="K2097">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2098" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2098" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2098">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2098" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2098">
+        <v>0</v>
+      </c>
+      <c r="H2098" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2098">
+        <v>3</v>
+      </c>
+      <c r="J2098" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2098">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2099" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2099" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2099">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2099" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2099">
+        <v>0</v>
+      </c>
+      <c r="H2099" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2099">
+        <v>8</v>
+      </c>
+      <c r="J2099" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2099">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2100" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2100" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2100">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2100" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2100">
+        <v>0</v>
+      </c>
+      <c r="H2100" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2100">
+        <v>6</v>
+      </c>
+      <c r="J2100" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2101" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2101" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2101">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2101" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2101">
+        <v>0</v>
+      </c>
+      <c r="H2101" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2101">
+        <v>10</v>
+      </c>
+      <c r="J2101" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2102" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2102" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2102">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2102" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2102">
+        <v>0</v>
+      </c>
+      <c r="H2102" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2102">
+        <v>10</v>
+      </c>
+      <c r="J2102" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2103" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>338</v>
+      </c>
+      <c r="C2103" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2103">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2103" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2103">
+        <v>0</v>
+      </c>
+      <c r="H2103" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2103">
+        <v>1</v>
+      </c>
+      <c r="J2103" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2104" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2104" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2104">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2104" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2104">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2104">
+        <v>1</v>
+      </c>
+      <c r="J2104" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2105" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2105" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2105">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2105" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2105">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2105">
+        <v>1</v>
+      </c>
+      <c r="J2105" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2106" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2106" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2106">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2106" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2106">
+        <v>0</v>
+      </c>
+      <c r="H2106" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2106">
+        <v>1</v>
+      </c>
+      <c r="J2106" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2107" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2107" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2107">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2107" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2107">
+        <v>0</v>
+      </c>
+      <c r="H2107" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2107">
+        <v>1</v>
+      </c>
+      <c r="J2107" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2108" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2108" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2108">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2108" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2108">
+        <v>0</v>
+      </c>
+      <c r="H2108" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2108">
+        <v>1</v>
+      </c>
+      <c r="J2108" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2109" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2109" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2109">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2109" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2109">
+        <v>0</v>
+      </c>
+      <c r="H2109" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2109">
+        <v>1</v>
+      </c>
+      <c r="J2109" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2110" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2110" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2110">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2110" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2110">
+        <v>0</v>
+      </c>
+      <c r="H2110" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2110">
+        <v>1</v>
+      </c>
+      <c r="J2110" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2111" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2111" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2111">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2111" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2111">
+        <v>0</v>
+      </c>
+      <c r="H2111" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2111">
+        <v>1</v>
+      </c>
+      <c r="J2111" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2112" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2112">
+        <v>0</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2112" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2112">
+        <v>0</v>
+      </c>
+      <c r="H2112" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2112">
+        <v>1</v>
+      </c>
+      <c r="J2112" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2113" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>296</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2113">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2113" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2113">
+        <v>0</v>
+      </c>
+      <c r="H2113" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2113">
+        <v>1</v>
+      </c>
+      <c r="J2113" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2114" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2114">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2114" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2114">
+        <v>0</v>
+      </c>
+      <c r="H2114" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2114">
+        <v>1</v>
+      </c>
+      <c r="J2114" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2115" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2115">
+        <v>0</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2115" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2115">
+        <v>0</v>
+      </c>
+      <c r="H2115" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2115">
+        <v>1</v>
+      </c>
+      <c r="J2115" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2116" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2116">
+        <v>0</v>
+      </c>
+      <c r="E2116" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2116" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2116">
+        <v>0</v>
+      </c>
+      <c r="H2116" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2116">
+        <v>1</v>
+      </c>
+      <c r="J2116" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2117" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2117">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2117" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2117">
+        <v>0</v>
+      </c>
+      <c r="H2117" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2117">
+        <v>1</v>
+      </c>
+      <c r="J2117" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2118" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2118">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2118" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2118">
+        <v>0</v>
+      </c>
+      <c r="H2118" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2118">
+        <v>1</v>
+      </c>
+      <c r="J2118" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2119" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2119">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2119">
+        <v>0</v>
+      </c>
+      <c r="H2119" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2119">
+        <v>1</v>
+      </c>
+      <c r="J2119" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2120" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2120">
+        <v>0</v>
+      </c>
+      <c r="E2120" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2120" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2120">
+        <v>0</v>
+      </c>
+      <c r="H2120" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2120">
+        <v>1</v>
+      </c>
+      <c r="J2120" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2121" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2121">
+        <v>0</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2121" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2121">
+        <v>0</v>
+      </c>
+      <c r="H2121" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2121">
+        <v>1</v>
+      </c>
+      <c r="J2121" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2122" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2122">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2122" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2122">
+        <v>0</v>
+      </c>
+      <c r="H2122" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2122">
+        <v>1</v>
+      </c>
+      <c r="J2122" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2123" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2123">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2123" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2123">
+        <v>0</v>
+      </c>
+      <c r="H2123" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2123">
+        <v>1</v>
+      </c>
+      <c r="J2123" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2124" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2124">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2124" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2124">
+        <v>0</v>
+      </c>
+      <c r="H2124" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2124">
+        <v>1</v>
+      </c>
+      <c r="J2124" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2125" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2125" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2125">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2125" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2125">
+        <v>0</v>
+      </c>
+      <c r="H2125" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2125">
+        <v>1</v>
+      </c>
+      <c r="J2125" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2126" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2126">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2126" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2126">
+        <v>0</v>
+      </c>
+      <c r="H2126" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2126">
+        <v>1</v>
+      </c>
+      <c r="J2126" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2127" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2127" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2127">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2127" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2127">
+        <v>0</v>
+      </c>
+      <c r="H2127" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2127">
+        <v>1</v>
+      </c>
+      <c r="J2127" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2128" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2128" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2128">
+        <v>0</v>
+      </c>
+      <c r="E2128" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2128" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2128">
+        <v>0</v>
+      </c>
+      <c r="H2128" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2128">
+        <v>1</v>
+      </c>
+      <c r="J2128" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2129" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2129" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2129">
+        <v>0</v>
+      </c>
+      <c r="E2129" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2129" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2129">
+        <v>0</v>
+      </c>
+      <c r="H2129" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2129">
+        <v>1</v>
+      </c>
+      <c r="J2129" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2130" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2130" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2130">
+        <v>0</v>
+      </c>
+      <c r="E2130" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2130" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2130">
+        <v>0</v>
+      </c>
+      <c r="H2130" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2130">
+        <v>1</v>
+      </c>
+      <c r="J2130" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2131" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2131" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2131" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2131" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2131">
+        <v>275</v>
+      </c>
+      <c r="H2131" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2131">
+        <v>1</v>
+      </c>
+      <c r="J2131" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2131">
+        <v>49900</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2132" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2132" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2132" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2132" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2132">
+        <v>255</v>
+      </c>
+      <c r="H2132" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2132">
+        <v>1</v>
+      </c>
+      <c r="J2132" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2132">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2133" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2133" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2133" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2133" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2133">
+        <v>255</v>
+      </c>
+      <c r="H2133" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2133">
+        <v>1</v>
+      </c>
+      <c r="J2133" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2133">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2134" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2134" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2134">
+        <v>0</v>
+      </c>
+      <c r="E2134" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2134" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2134">
+        <v>0</v>
+      </c>
+      <c r="H2134" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2134">
+        <v>1</v>
+      </c>
+      <c r="J2134" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2135" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2135" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2135">
+        <v>0</v>
+      </c>
+      <c r="E2135" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2135" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2135">
+        <v>0</v>
+      </c>
+      <c r="H2135" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2135">
+        <v>1</v>
+      </c>
+      <c r="J2135" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2136" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2136" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2136">
+        <v>0</v>
+      </c>
+      <c r="E2136" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2136" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2136">
+        <v>0</v>
+      </c>
+      <c r="H2136" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2136">
+        <v>1</v>
+      </c>
+      <c r="J2136" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2137" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2137" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2137">
+        <v>0</v>
+      </c>
+      <c r="E2137" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2137" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2137">
+        <v>0</v>
+      </c>
+      <c r="H2137" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2137">
+        <v>1</v>
+      </c>
+      <c r="J2137" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2138" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2138" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2138" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2138">
+        <v>0</v>
+      </c>
+      <c r="E2138" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2138" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2138">
+        <v>0</v>
+      </c>
+      <c r="H2138" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2138">
+        <v>1</v>
+      </c>
+      <c r="J2138" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2139" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2139" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2139" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2139">
+        <v>0</v>
+      </c>
+      <c r="E2139" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2139" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2139">
+        <v>0</v>
+      </c>
+      <c r="H2139" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2139">
+        <v>1</v>
+      </c>
+      <c r="J2139" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2140" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2140" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2140" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2140" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2140" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2140" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2140">
+        <v>235</v>
+      </c>
+      <c r="H2140" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2140">
+        <v>1</v>
+      </c>
+      <c r="J2140" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2140">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2141" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2141" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2141" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2141" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2141" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2141" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2141">
+        <v>235</v>
+      </c>
+      <c r="H2141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2141">
+        <v>1</v>
+      </c>
+      <c r="J2141" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2141">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2142" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2142" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2142" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2142" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2142" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2142">
+        <v>245</v>
+      </c>
+      <c r="H2142" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2142">
+        <v>1</v>
+      </c>
+      <c r="J2142" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2142">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2143" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2143" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2143" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2143" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2143" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2143" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2143">
+        <v>240</v>
+      </c>
+      <c r="H2143" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2143">
+        <v>1</v>
+      </c>
+      <c r="J2143" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2143">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2144" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2144" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2144" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2144" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2144" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2144" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2144" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2144" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2144">
+        <v>1</v>
+      </c>
+      <c r="J2144" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2144">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2145" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2145" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2145" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2145" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2145" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2145" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2145" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2145" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2145">
+        <v>1</v>
+      </c>
+      <c r="J2145" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2145">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2146" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2146" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2146" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2146" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2146" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2146" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2146" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2146" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2146">
+        <v>1</v>
+      </c>
+      <c r="J2146" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2146">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2147" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2147" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2147" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2147" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2147" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2147" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2147">
+        <v>0</v>
+      </c>
+      <c r="H2147" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2147">
+        <v>1</v>
+      </c>
+      <c r="J2147" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2147">
+        <v>35900</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2148" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2148" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2148" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2148" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2148" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2148" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2148">
+        <v>240</v>
+      </c>
+      <c r="H2148" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2148">
+        <v>1</v>
+      </c>
+      <c r="J2148" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2148">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2149" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2149" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2149" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2149" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2149" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2149">
+        <v>255</v>
+      </c>
+      <c r="H2149" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2149">
+        <v>1</v>
+      </c>
+      <c r="J2149" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2149">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2150" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2150" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2150" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2150" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2150" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2150" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2150">
+        <v>235</v>
+      </c>
+      <c r="H2150" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2150">
+        <v>1</v>
+      </c>
+      <c r="J2150" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2150">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2151" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2151" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2151" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2151" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2151" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2151" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2151">
+        <v>245</v>
+      </c>
+      <c r="H2151" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2151">
+        <v>1</v>
+      </c>
+      <c r="J2151" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2151">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2152" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2152" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2152" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2152" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2152" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2152" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2152">
+        <v>235</v>
+      </c>
+      <c r="H2152" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2152">
+        <v>1</v>
+      </c>
+      <c r="J2152" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2152">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2153" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2153" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2153" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2153" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2153" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2153" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2153">
+        <v>240</v>
+      </c>
+      <c r="H2153" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2153">
+        <v>1</v>
+      </c>
+      <c r="J2153" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2153">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2154" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2154" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2154" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2154" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2154" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2154" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2154">
+        <v>240</v>
+      </c>
+      <c r="H2154" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2154">
+        <v>1</v>
+      </c>
+      <c r="J2154" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2154">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2155" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2155" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2155" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2155" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2155" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2155" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2155">
+        <v>245</v>
+      </c>
+      <c r="H2155" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2155">
+        <v>1</v>
+      </c>
+      <c r="J2155" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2155">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2156" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2156" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2156" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2156" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2156" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2156" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2156">
+        <v>240</v>
+      </c>
+      <c r="H2156" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2156">
+        <v>1</v>
+      </c>
+      <c r="J2156" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2156">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2157" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2157" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2157" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2157" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2157" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2157" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2157">
+        <v>245</v>
+      </c>
+      <c r="H2157" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2157">
+        <v>1</v>
+      </c>
+      <c r="J2157" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2157">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2158" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2158" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2158" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2158" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2158" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2158" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2158">
+        <v>240</v>
+      </c>
+      <c r="H2158" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2158">
+        <v>1</v>
+      </c>
+      <c r="J2158" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2158">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2159" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2159" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2159" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2159" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2159" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2159" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2159">
+        <v>240</v>
+      </c>
+      <c r="H2159" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2159">
+        <v>1</v>
+      </c>
+      <c r="J2159" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2159">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2160" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2160" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2160" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2160" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2160" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2160" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2160">
+        <v>265</v>
+      </c>
+      <c r="H2160" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2160">
+        <v>1</v>
+      </c>
+      <c r="J2160" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2160">
         <v>44900</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1441705-5257-46E6-B80B-E40A988297A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D934C766-B8B9-4DB6-BC05-29B4BEBE554C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AD7059DE-073A-4FED-9BA0-E648BD3977A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{6F83EEB7-AD16-4C7F-96EB-F06D71E5DFAC}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18587" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19180" uniqueCount="1116">
   <si>
     <t>날짜</t>
   </si>
@@ -3066,61 +3066,61 @@
     <t>BUAG-151011</t>
   </si>
   <si>
-    <t>애견텐트 P 오렌지 S</t>
+    <t>뷰엔아미고 애견텐트 P 오렌지 S</t>
   </si>
   <si>
     <t>BUAG-151021</t>
   </si>
   <si>
-    <t>애견텐트 P 레드 S</t>
+    <t>뷰엔아미고 애견텐트 P 레드 S</t>
   </si>
   <si>
     <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/66840064ba7551ae92d1da8a09f9ef4f.jpg</t>
   </si>
   <si>
-    <t>애견텐트 P 라임 S</t>
+    <t>뷰엔아미고 애견텐트 P 라임 S</t>
   </si>
   <si>
     <t>https://idoogenkorea.cafe24.com/web/product/small/202608/f572abe28dcc14228d7dd27c14d11213.jpg</t>
   </si>
   <si>
-    <t>애견텐트 P 오렌지 M</t>
+    <t>뷰엔아미고 애견텐트 P 오렌지 M</t>
   </si>
   <si>
     <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/373fb4faf7d2be2987f178e41b456092.jpg</t>
   </si>
   <si>
-    <t>애견텐트 P 레드 M</t>
-  </si>
-  <si>
-    <t>애견텐트 P 라임 M</t>
+    <t>뷰엔아미고 애견텐트 P 레드 M</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 애견텐트 P 라임 M</t>
   </si>
   <si>
     <t>BUAG-151042</t>
   </si>
   <si>
-    <t>애견텐트 P 다크브라운 M</t>
+    <t>뷰엔아미고 애견텐트 P 다크브라운 M</t>
   </si>
   <si>
     <t>https://idoogenkorea.cafe24.com/web/product/small/202608/c8261dc0878da00ae4f87d32100ad707.jpg</t>
   </si>
   <si>
-    <t>애견텐트 P 브라운 M</t>
+    <t>뷰엔아미고 애견텐트 P 브라운 M</t>
   </si>
   <si>
     <t>https://idoogenkorea.cafe24.com/web/product/extra/big/202608/9babeca900a539bd3c00359b649e3f7e.jpg</t>
   </si>
   <si>
-    <t>애견텐트 P 오렌지 L</t>
-  </si>
-  <si>
-    <t>애견텐트 P 레드 L</t>
-  </si>
-  <si>
-    <t>애견텐트 P 라임 L</t>
-  </si>
-  <si>
-    <t>애견텐트 P 카키 L</t>
+    <t>뷰엔아미고 애견텐트 P 오렌지 L</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 애견텐트 P 레드 L</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 애견텐트 P 라임 L</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 애견텐트 P 카키 L</t>
   </si>
   <si>
     <t>https://idoogenkorea.cafe24.com/web/product/small/202608/21813b1588993306777bb07ce651de86.jpg</t>
@@ -3358,6 +3358,36 @@
   </si>
   <si>
     <t>차량용 맥세이프 거치대 블랙</t>
+  </si>
+  <si>
+    <t>BUAG-1121012</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 돔 4 라이트그레이</t>
+  </si>
+  <si>
+    <t>BUAG-1121022</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 돔 4 골드</t>
+  </si>
+  <si>
+    <t>BUAG-1121032</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 돔 4 그린</t>
+  </si>
+  <si>
+    <t>BUAG-1131012</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 돔 4 플러스 카키</t>
+  </si>
+  <si>
+    <t>BUAG-1131022</t>
+  </si>
+  <si>
+    <t>뷰엔아미고 돔 4 플러스 그레이</t>
   </si>
 </sst>
 </file>
@@ -3743,8 +3773,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB510FD5-36DE-4709-ACD1-E9B87E5486A5}">
-  <dimension ref="A1:V349"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8B97C3-4293-452A-86F2-AD937641AD30}">
+  <dimension ref="A1:V354"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
@@ -3856,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>16</v>
@@ -3977,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3995,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P4" t="s">
         <v>17</v>
@@ -4128,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -4400,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -8255,13 +8285,13 @@
         <v>260</v>
       </c>
       <c r="G67">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -8270,16 +8300,16 @@
         <v>362</v>
       </c>
       <c r="L67">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O67">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P67" t="s">
         <v>17</v>
@@ -8323,13 +8353,13 @@
         <v>265</v>
       </c>
       <c r="G68">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -8338,16 +8368,16 @@
         <v>362</v>
       </c>
       <c r="L68">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P68" t="s">
         <v>17</v>
@@ -8391,31 +8421,31 @@
         <v>270</v>
       </c>
       <c r="G69">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J69">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K69" t="s">
         <v>350</v>
       </c>
       <c r="L69">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69">
         <v>0</v>
       </c>
       <c r="O69">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P69" t="s">
         <v>17</v>
@@ -8480,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70">
         <v>15</v>
@@ -8548,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71">
         <v>9</v>
@@ -9003,13 +9033,13 @@
         <v>265</v>
       </c>
       <c r="G78">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H78">
         <v>0</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -9018,7 +9048,7 @@
         <v>362</v>
       </c>
       <c r="L78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78">
         <v>0</v>
@@ -9027,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="O78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P78" t="s">
         <v>17</v>
@@ -9479,13 +9509,13 @@
         <v>275</v>
       </c>
       <c r="G85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -9494,7 +9524,7 @@
         <v>362</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -9503,7 +9533,7 @@
         <v>0</v>
       </c>
       <c r="O85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P85" t="s">
         <v>17</v>
@@ -9683,13 +9713,13 @@
         <v>265</v>
       </c>
       <c r="G88">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -9698,7 +9728,7 @@
         <v>362</v>
       </c>
       <c r="L88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M88">
         <v>0</v>
@@ -9707,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="O88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P88" t="s">
         <v>17</v>
@@ -11389,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="I113">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -11407,7 +11437,7 @@
         <v>0</v>
       </c>
       <c r="O113">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P113" t="s">
         <v>17</v>
@@ -12335,13 +12365,13 @@
         <v>235</v>
       </c>
       <c r="G127">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
       <c r="I127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -12350,7 +12380,7 @@
         <v>362</v>
       </c>
       <c r="L127">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M127">
         <v>11</v>
@@ -12359,7 +12389,7 @@
         <v>5</v>
       </c>
       <c r="O127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P127" t="s">
         <v>17</v>
@@ -12403,22 +12433,22 @@
         <v>240</v>
       </c>
       <c r="G128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J128">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K128" t="s">
         <v>350</v>
       </c>
       <c r="L128">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M128">
         <v>13</v>
@@ -12427,7 +12457,7 @@
         <v>2</v>
       </c>
       <c r="O128">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P128" t="s">
         <v>17</v>
@@ -12471,22 +12501,22 @@
         <v>245</v>
       </c>
       <c r="G129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H129">
         <v>0</v>
       </c>
       <c r="I129">
+        <v>15</v>
+      </c>
+      <c r="J129">
         <v>14</v>
-      </c>
-      <c r="J129">
-        <v>12</v>
       </c>
       <c r="K129" t="s">
         <v>350</v>
       </c>
       <c r="L129">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M129">
         <v>7</v>
@@ -12495,7 +12525,7 @@
         <v>0</v>
       </c>
       <c r="O129">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P129" t="s">
         <v>17</v>
@@ -12539,22 +12569,22 @@
         <v>250</v>
       </c>
       <c r="G130">
+        <v>4</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>9</v>
+      </c>
+      <c r="J130">
         <v>5</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>8</v>
-      </c>
-      <c r="J130">
-        <v>3</v>
       </c>
       <c r="K130" t="s">
         <v>350</v>
       </c>
       <c r="L130">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M130">
         <v>7</v>
@@ -12563,7 +12593,7 @@
         <v>3</v>
       </c>
       <c r="O130">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P130" t="s">
         <v>17</v>
@@ -12681,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J132">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K132" t="s">
         <v>350</v>
@@ -12699,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="O132">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P132" t="s">
         <v>17</v>
@@ -12743,22 +12773,22 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J133">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K133" t="s">
         <v>350</v>
       </c>
       <c r="L133">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M133">
         <v>9</v>
@@ -12767,7 +12797,7 @@
         <v>0</v>
       </c>
       <c r="O133">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P133" t="s">
         <v>17</v>
@@ -12817,10 +12847,10 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J134">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K134" t="s">
         <v>350</v>
@@ -12835,7 +12865,7 @@
         <v>5</v>
       </c>
       <c r="O134">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P134" t="s">
         <v>17</v>
@@ -13036,7 +13066,7 @@
         <v>4</v>
       </c>
       <c r="N137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O137">
         <v>11</v>
@@ -13083,13 +13113,13 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -13098,7 +13128,7 @@
         <v>362</v>
       </c>
       <c r="L138">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M138">
         <v>6</v>
@@ -13107,7 +13137,7 @@
         <v>6</v>
       </c>
       <c r="O138">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P138" t="s">
         <v>17</v>
@@ -13151,13 +13181,13 @@
         <v>245</v>
       </c>
       <c r="G139">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J139">
         <v>0</v>
@@ -13166,16 +13196,16 @@
         <v>362</v>
       </c>
       <c r="L139">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N139">
         <v>0</v>
       </c>
       <c r="O139">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P139" t="s">
         <v>17</v>
@@ -13225,7 +13255,7 @@
         <v>0</v>
       </c>
       <c r="I140">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -13240,10 +13270,10 @@
         <v>3</v>
       </c>
       <c r="N140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O140">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P140" t="s">
         <v>17</v>
@@ -13355,13 +13385,13 @@
         <v>235</v>
       </c>
       <c r="G142">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -13370,7 +13400,7 @@
         <v>362</v>
       </c>
       <c r="L142">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M142">
         <v>1</v>
@@ -13379,7 +13409,7 @@
         <v>2</v>
       </c>
       <c r="O142">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P142" t="s">
         <v>17</v>
@@ -13695,31 +13725,31 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J147">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K147" t="s">
         <v>350</v>
       </c>
       <c r="L147">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M147">
         <v>3</v>
       </c>
       <c r="N147">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O147">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P147" t="s">
         <v>17</v>
@@ -13763,31 +13793,31 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J148">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K148" t="s">
         <v>350</v>
       </c>
       <c r="L148">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M148">
         <v>3</v>
       </c>
       <c r="N148">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O148">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P148" t="s">
         <v>17</v>
@@ -13852,7 +13882,7 @@
         <v>3</v>
       </c>
       <c r="N149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O149">
         <v>24</v>
@@ -13920,7 +13950,7 @@
         <v>0</v>
       </c>
       <c r="N150">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O150">
         <v>25</v>
@@ -13988,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="N151">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O151">
         <v>18</v>
@@ -15055,31 +15085,31 @@
         <v>235</v>
       </c>
       <c r="G167">
+        <v>4</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
         <v>5</v>
       </c>
-      <c r="H167">
-        <v>0</v>
-      </c>
-      <c r="I167">
-        <v>4</v>
-      </c>
       <c r="J167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="L167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N167">
         <v>0</v>
       </c>
       <c r="O167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P167" t="s">
         <v>17</v>
@@ -15144,7 +15174,7 @@
         <v>0</v>
       </c>
       <c r="N168">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O168">
         <v>6</v>
@@ -15191,13 +15221,13 @@
         <v>245</v>
       </c>
       <c r="G169">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -15206,16 +15236,16 @@
         <v>362</v>
       </c>
       <c r="L169">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N169">
         <v>0</v>
       </c>
       <c r="O169">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P169" t="s">
         <v>17</v>
@@ -15463,13 +15493,13 @@
         <v>240</v>
       </c>
       <c r="G173">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -15478,7 +15508,7 @@
         <v>362</v>
       </c>
       <c r="L173">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M173">
         <v>1</v>
@@ -15487,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="O173">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P173" t="s">
         <v>17</v>
@@ -15620,7 +15650,7 @@
         <v>2</v>
       </c>
       <c r="N175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O175">
         <v>11</v>
@@ -15939,13 +15969,13 @@
         <v>250</v>
       </c>
       <c r="G180">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H180">
         <v>0</v>
       </c>
       <c r="I180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -15954,16 +15984,16 @@
         <v>362</v>
       </c>
       <c r="L180">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M180">
         <v>3</v>
       </c>
       <c r="N180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P180" t="s">
         <v>17</v>
@@ -16075,13 +16105,13 @@
         <v>235</v>
       </c>
       <c r="G182">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
       <c r="I182">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -16090,7 +16120,7 @@
         <v>362</v>
       </c>
       <c r="L182">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M182">
         <v>4</v>
@@ -16099,7 +16129,7 @@
         <v>1</v>
       </c>
       <c r="O182">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P182" t="s">
         <v>17</v>
@@ -16483,22 +16513,22 @@
         <v>240</v>
       </c>
       <c r="G188">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H188">
         <v>0</v>
       </c>
       <c r="I188">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J188">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K188" t="s">
         <v>350</v>
       </c>
       <c r="L188">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M188">
         <v>7</v>
@@ -16507,7 +16537,7 @@
         <v>0</v>
       </c>
       <c r="O188">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P188" t="s">
         <v>17</v>
@@ -16959,13 +16989,13 @@
         <v>250</v>
       </c>
       <c r="G195">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H195">
         <v>0</v>
       </c>
       <c r="I195">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -16974,7 +17004,7 @@
         <v>362</v>
       </c>
       <c r="L195">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M195">
         <v>8</v>
@@ -16983,7 +17013,7 @@
         <v>1</v>
       </c>
       <c r="O195">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P195" t="s">
         <v>17</v>
@@ -18251,13 +18281,13 @@
         <v>245</v>
       </c>
       <c r="G214">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H214">
         <v>0</v>
       </c>
       <c r="I214">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J214">
         <v>0</v>
@@ -18266,7 +18296,7 @@
         <v>362</v>
       </c>
       <c r="L214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M214">
         <v>1</v>
@@ -18275,7 +18305,7 @@
         <v>1</v>
       </c>
       <c r="O214">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P214" t="s">
         <v>17</v>
@@ -18680,7 +18710,7 @@
         <v>2</v>
       </c>
       <c r="N220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O220">
         <v>6</v>
@@ -18863,22 +18893,22 @@
         <v>240</v>
       </c>
       <c r="G223">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J223">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K223" t="s">
         <v>350</v>
       </c>
       <c r="L223">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M223">
         <v>8</v>
@@ -18887,7 +18917,7 @@
         <v>1</v>
       </c>
       <c r="O223">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P223" t="s">
         <v>17</v>
@@ -18999,7 +19029,7 @@
         <v>250</v>
       </c>
       <c r="G225">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -19008,13 +19038,13 @@
         <v>9</v>
       </c>
       <c r="J225">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K225" t="s">
         <v>350</v>
       </c>
       <c r="L225">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M225">
         <v>8</v>
@@ -19156,7 +19186,7 @@
         <v>12</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227">
         <v>12</v>
@@ -19339,13 +19369,13 @@
         <v>250</v>
       </c>
       <c r="G230">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -19354,7 +19384,7 @@
         <v>362</v>
       </c>
       <c r="L230">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M230">
         <v>5</v>
@@ -19363,7 +19393,7 @@
         <v>1</v>
       </c>
       <c r="O230">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P230" t="s">
         <v>17</v>
@@ -19478,7 +19508,7 @@
         <v>0</v>
       </c>
       <c r="I232">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -19496,7 +19526,7 @@
         <v>1</v>
       </c>
       <c r="O232">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P232" t="s">
         <v>124</v>
@@ -19540,10 +19570,10 @@
         <v>0</v>
       </c>
       <c r="I233">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K233" t="s">
         <v>350</v>
@@ -19555,10 +19585,10 @@
         <v>1</v>
       </c>
       <c r="N233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O233">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P233" t="s">
         <v>124</v>
@@ -19658,13 +19688,13 @@
         <v>123</v>
       </c>
       <c r="G235">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H235">
         <v>0</v>
       </c>
       <c r="I235">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J235">
         <v>0</v>
@@ -19673,16 +19703,16 @@
         <v>362</v>
       </c>
       <c r="L235">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M235">
         <v>0</v>
       </c>
       <c r="N235">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O235">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P235" t="s">
         <v>124</v>
@@ -19720,13 +19750,13 @@
         <v>123</v>
       </c>
       <c r="G236">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H236">
         <v>0</v>
       </c>
       <c r="I236">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J236">
         <v>0</v>
@@ -19735,7 +19765,7 @@
         <v>362</v>
       </c>
       <c r="L236">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M236">
         <v>0</v>
@@ -19744,7 +19774,7 @@
         <v>1</v>
       </c>
       <c r="O236">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P236" t="s">
         <v>124</v>
@@ -19844,13 +19874,13 @@
         <v>123</v>
       </c>
       <c r="G238">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H238">
         <v>0</v>
       </c>
       <c r="I238">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J238">
         <v>0</v>
@@ -19859,7 +19889,7 @@
         <v>362</v>
       </c>
       <c r="L238">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M238">
         <v>1</v>
@@ -19868,7 +19898,7 @@
         <v>0</v>
       </c>
       <c r="O238">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P238" t="s">
         <v>124</v>
@@ -19906,13 +19936,13 @@
         <v>123</v>
       </c>
       <c r="G239">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H239">
         <v>0</v>
       </c>
       <c r="I239">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J239">
         <v>0</v>
@@ -19921,16 +19951,16 @@
         <v>362</v>
       </c>
       <c r="L239">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M239">
         <v>1</v>
       </c>
       <c r="N239">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O239">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P239" t="s">
         <v>124</v>
@@ -19989,7 +20019,7 @@
         <v>1</v>
       </c>
       <c r="N240">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O240">
         <v>15</v>
@@ -20030,13 +20060,13 @@
         <v>123</v>
       </c>
       <c r="G241">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H241">
         <v>0</v>
       </c>
       <c r="I241">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -20045,7 +20075,7 @@
         <v>362</v>
       </c>
       <c r="L241">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M241">
         <v>0</v>
@@ -20054,7 +20084,7 @@
         <v>1</v>
       </c>
       <c r="O241">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P241" t="s">
         <v>124</v>
@@ -20284,7 +20314,7 @@
         <v>0</v>
       </c>
       <c r="I245">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -20302,7 +20332,7 @@
         <v>0</v>
       </c>
       <c r="O245">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P245" t="s">
         <v>124</v>
@@ -20526,13 +20556,13 @@
         <v>123</v>
       </c>
       <c r="G249">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H249">
         <v>0</v>
       </c>
       <c r="I249">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -20541,7 +20571,7 @@
         <v>362</v>
       </c>
       <c r="L249">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M249">
         <v>0</v>
@@ -20550,7 +20580,7 @@
         <v>0</v>
       </c>
       <c r="O249">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P249" t="s">
         <v>124</v>
@@ -20588,13 +20618,13 @@
         <v>123</v>
       </c>
       <c r="G250">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -20603,16 +20633,16 @@
         <v>362</v>
       </c>
       <c r="L250">
+        <v>36</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250">
         <v>35</v>
-      </c>
-      <c r="M250">
-        <v>1</v>
-      </c>
-      <c r="N250">
-        <v>0</v>
-      </c>
-      <c r="O250">
-        <v>34</v>
       </c>
       <c r="P250" t="s">
         <v>124</v>
@@ -20671,7 +20701,7 @@
         <v>0</v>
       </c>
       <c r="N251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O251">
         <v>20</v>
@@ -20712,13 +20742,13 @@
         <v>123</v>
       </c>
       <c r="G252">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H252">
         <v>0</v>
       </c>
       <c r="I252">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J252">
         <v>0</v>
@@ -20727,7 +20757,7 @@
         <v>362</v>
       </c>
       <c r="L252">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M252">
         <v>1</v>
@@ -20736,7 +20766,7 @@
         <v>1</v>
       </c>
       <c r="O252">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P252" t="s">
         <v>124</v>
@@ -20774,31 +20804,31 @@
         <v>123</v>
       </c>
       <c r="G253">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H253">
         <v>0</v>
       </c>
       <c r="I253">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J253">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K253" t="s">
         <v>350</v>
       </c>
       <c r="L253">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M253">
         <v>3</v>
       </c>
       <c r="N253">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="O253">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P253" t="s">
         <v>124</v>
@@ -20836,13 +20866,13 @@
         <v>123</v>
       </c>
       <c r="G254">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H254">
         <v>0</v>
       </c>
       <c r="I254">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -20851,16 +20881,16 @@
         <v>362</v>
       </c>
       <c r="L254">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M254">
         <v>1</v>
       </c>
       <c r="N254">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O254">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P254" t="s">
         <v>124</v>
@@ -20898,13 +20928,13 @@
         <v>123</v>
       </c>
       <c r="G255">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H255">
         <v>0</v>
       </c>
       <c r="I255">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J255">
         <v>0</v>
@@ -20913,7 +20943,7 @@
         <v>362</v>
       </c>
       <c r="L255">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -20922,7 +20952,7 @@
         <v>0</v>
       </c>
       <c r="O255">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P255" t="s">
         <v>124</v>
@@ -21043,7 +21073,7 @@
         <v>1</v>
       </c>
       <c r="N257">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O257">
         <v>6</v>
@@ -21105,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="N258">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O258">
         <v>14</v>
@@ -21146,13 +21176,13 @@
         <v>123</v>
       </c>
       <c r="G259">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H259">
         <v>0</v>
       </c>
       <c r="I259">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J259">
         <v>0</v>
@@ -21161,7 +21191,7 @@
         <v>362</v>
       </c>
       <c r="L259">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M259">
         <v>1</v>
@@ -21170,7 +21200,7 @@
         <v>1</v>
       </c>
       <c r="O259">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P259" t="s">
         <v>124</v>
@@ -21211,10 +21241,10 @@
         <v>194</v>
       </c>
       <c r="G260">
-        <v>1902</v>
+        <v>1894</v>
       </c>
       <c r="I260">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -21223,16 +21253,16 @@
         <v>362</v>
       </c>
       <c r="L260">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M260">
         <v>0</v>
       </c>
       <c r="N260">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O260">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P260" t="s">
         <v>182</v>
@@ -21270,10 +21300,10 @@
         <v>181</v>
       </c>
       <c r="G261">
-        <v>1869</v>
+        <v>1852</v>
       </c>
       <c r="I261">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -21282,16 +21312,16 @@
         <v>362</v>
       </c>
       <c r="L261">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="M261">
         <v>4</v>
       </c>
       <c r="N261">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="O261">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="P261" t="s">
         <v>182</v>
@@ -21329,10 +21359,10 @@
         <v>191</v>
       </c>
       <c r="G262">
-        <v>5790</v>
+        <v>5776</v>
       </c>
       <c r="I262">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -21341,16 +21371,16 @@
         <v>362</v>
       </c>
       <c r="L262">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="M262">
         <v>0</v>
       </c>
       <c r="N262">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="O262">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="P262" t="s">
         <v>182</v>
@@ -21388,10 +21418,10 @@
         <v>193</v>
       </c>
       <c r="G263">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="I263">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -21400,16 +21430,16 @@
         <v>362</v>
       </c>
       <c r="L263">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M263">
         <v>4</v>
       </c>
       <c r="N263">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="O263">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="P263" t="s">
         <v>182</v>
@@ -21462,7 +21492,7 @@
         <v>0</v>
       </c>
       <c r="N264">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O264">
         <v>22</v>
@@ -21497,10 +21527,10 @@
         <v>123</v>
       </c>
       <c r="G265">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I265">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -21509,7 +21539,7 @@
         <v>362</v>
       </c>
       <c r="L265">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M265">
         <v>0</v>
@@ -21518,7 +21548,7 @@
         <v>0</v>
       </c>
       <c r="O265">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P265" t="s">
         <v>182</v>
@@ -21917,28 +21947,28 @@
         <v>123</v>
       </c>
       <c r="G274">
-        <v>-20</v>
+        <v>314</v>
       </c>
       <c r="I274">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J274">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K274" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="L274">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M274">
         <v>0</v>
       </c>
       <c r="N274">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O274">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P274" t="s">
         <v>279</v>
@@ -21964,16 +21994,16 @@
         <v>123</v>
       </c>
       <c r="G275">
-        <v>-29</v>
+        <v>83</v>
       </c>
       <c r="I275">
         <v>29</v>
       </c>
       <c r="J275">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K275" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="L275">
         <v>29</v>
@@ -21982,7 +22012,7 @@
         <v>0</v>
       </c>
       <c r="N275">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O275">
         <v>29</v>
@@ -22011,16 +22041,16 @@
         <v>123</v>
       </c>
       <c r="G276">
-        <v>-23</v>
+        <v>77</v>
       </c>
       <c r="I276">
         <v>23</v>
       </c>
       <c r="J276">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K276" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="L276">
         <v>23</v>
@@ -22029,7 +22059,7 @@
         <v>0</v>
       </c>
       <c r="N276">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O276">
         <v>23</v>
@@ -22058,28 +22088,28 @@
         <v>123</v>
       </c>
       <c r="G277">
-        <v>-31</v>
+        <v>10</v>
       </c>
       <c r="I277">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J277">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="K277" t="s">
         <v>350</v>
       </c>
       <c r="L277">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M277">
         <v>0</v>
       </c>
       <c r="N277">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O277">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P277" t="s">
         <v>279</v>
@@ -22105,28 +22135,28 @@
         <v>123</v>
       </c>
       <c r="G278">
-        <v>-8</v>
+        <v>45</v>
       </c>
       <c r="I278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J278">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K278" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="L278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M278">
         <v>0</v>
       </c>
       <c r="N278">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P278" t="s">
         <v>279</v>
@@ -22152,16 +22182,16 @@
         <v>123</v>
       </c>
       <c r="G279">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="I279">
         <v>21</v>
       </c>
       <c r="J279">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K279" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="L279">
         <v>21</v>
@@ -22170,7 +22200,7 @@
         <v>0</v>
       </c>
       <c r="N279">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="O279">
         <v>21</v>
@@ -22246,19 +22276,19 @@
         <v>123</v>
       </c>
       <c r="G281">
+        <v>18</v>
+      </c>
+      <c r="I281">
+        <v>32</v>
+      </c>
+      <c r="J281">
         <v>14</v>
-      </c>
-      <c r="I281">
-        <v>26</v>
-      </c>
-      <c r="J281">
-        <v>12</v>
       </c>
       <c r="K281" t="s">
         <v>350</v>
       </c>
       <c r="L281">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -22267,7 +22297,7 @@
         <v>23</v>
       </c>
       <c r="O281">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P281" t="s">
         <v>279</v>
@@ -22293,28 +22323,28 @@
         <v>123</v>
       </c>
       <c r="G282">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I282">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J282">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K282" t="s">
         <v>350</v>
       </c>
       <c r="L282">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M282">
         <v>0</v>
       </c>
       <c r="N282">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O282">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="P282" t="s">
         <v>279</v>
@@ -22340,28 +22370,28 @@
         <v>123</v>
       </c>
       <c r="G283">
-        <v>-9</v>
+        <v>12</v>
       </c>
       <c r="I283">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J283">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K283" t="s">
         <v>350</v>
       </c>
       <c r="L283">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="M283">
         <v>0</v>
       </c>
       <c r="N283">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="O283">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P283" t="s">
         <v>279</v>
@@ -22431,28 +22461,28 @@
         <v>123</v>
       </c>
       <c r="G285">
-        <v>-69</v>
+        <v>26</v>
       </c>
       <c r="I285">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J285">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="K285" t="s">
         <v>350</v>
       </c>
       <c r="L285">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M285">
         <v>0</v>
       </c>
       <c r="N285">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="O285">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P285" t="s">
         <v>279</v>
@@ -22863,7 +22893,7 @@
         <v>0</v>
       </c>
       <c r="N294">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O294">
         <v>13</v>
@@ -22907,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="N295">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O295">
         <v>9</v>
@@ -22995,7 +23025,7 @@
         <v>0</v>
       </c>
       <c r="N297">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O297">
         <v>10</v>
@@ -23024,10 +23054,10 @@
         <v>123</v>
       </c>
       <c r="G298">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I298">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J298">
         <v>0</v>
@@ -23036,7 +23066,7 @@
         <v>362</v>
       </c>
       <c r="L298">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M298">
         <v>0</v>
@@ -23045,7 +23075,7 @@
         <v>1</v>
       </c>
       <c r="O298">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P298" t="s">
         <v>279</v>
@@ -23068,10 +23098,10 @@
         <v>123</v>
       </c>
       <c r="G299">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I299">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J299">
         <v>0</v>
@@ -23080,7 +23110,7 @@
         <v>362</v>
       </c>
       <c r="L299">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M299">
         <v>0</v>
@@ -23089,7 +23119,7 @@
         <v>1</v>
       </c>
       <c r="O299">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P299" t="s">
         <v>279</v>
@@ -23218,7 +23248,7 @@
         <v>0</v>
       </c>
       <c r="N302">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O302">
         <v>31</v>
@@ -23288,28 +23318,28 @@
         <v>123</v>
       </c>
       <c r="G304">
+        <v>24</v>
+      </c>
+      <c r="I304">
         <v>26</v>
       </c>
-      <c r="I304">
-        <v>24</v>
-      </c>
       <c r="J304">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K304" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="L304">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M304">
         <v>0</v>
       </c>
       <c r="N304">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O304">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P304" t="s">
         <v>279</v>
@@ -23350,7 +23380,7 @@
         <v>0</v>
       </c>
       <c r="N305">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O305">
         <v>14</v>
@@ -23394,7 +23424,7 @@
         <v>0</v>
       </c>
       <c r="N306">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O306">
         <v>16</v>
@@ -23420,10 +23450,10 @@
         <v>123</v>
       </c>
       <c r="G307">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I307">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -23432,16 +23462,16 @@
         <v>362</v>
       </c>
       <c r="L307">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M307">
         <v>0</v>
       </c>
       <c r="N307">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O307">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P307" t="s">
         <v>279</v>
@@ -23508,28 +23538,28 @@
         <v>123</v>
       </c>
       <c r="G309">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I309">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J309">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K309" t="s">
         <v>350</v>
       </c>
       <c r="L309">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M309">
         <v>0</v>
       </c>
       <c r="N309">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O309">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P309" t="s">
         <v>279</v>
@@ -23596,10 +23626,10 @@
         <v>123</v>
       </c>
       <c r="G311">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I311">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -23608,7 +23638,7 @@
         <v>362</v>
       </c>
       <c r="L311">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M311">
         <v>0</v>
@@ -23617,7 +23647,7 @@
         <v>0</v>
       </c>
       <c r="O311">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P311" t="s">
         <v>279</v>
@@ -23966,7 +23996,7 @@
         <v>0</v>
       </c>
       <c r="N319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O319">
         <v>21</v>
@@ -23992,10 +24022,10 @@
         <v>123</v>
       </c>
       <c r="G320">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I320">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J320">
         <v>0</v>
@@ -24004,7 +24034,7 @@
         <v>362</v>
       </c>
       <c r="L320">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M320">
         <v>0</v>
@@ -24013,7 +24043,7 @@
         <v>0</v>
       </c>
       <c r="O320">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P320" t="s">
         <v>279</v>
@@ -24318,7 +24348,7 @@
         <v>0</v>
       </c>
       <c r="N327">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O327">
         <v>1</v>
@@ -25092,19 +25122,19 @@
         <v>123</v>
       </c>
       <c r="G345">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="I345">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J345">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K345" t="s">
         <v>350</v>
       </c>
       <c r="L345">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M345">
         <v>10</v>
@@ -25113,7 +25143,7 @@
         <v>10</v>
       </c>
       <c r="O345">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P345" t="s">
         <v>17</v>
@@ -25136,19 +25166,19 @@
         <v>123</v>
       </c>
       <c r="G346">
-        <v>-36</v>
+        <v>-42</v>
       </c>
       <c r="I346">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J346">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K346" t="s">
         <v>350</v>
       </c>
       <c r="L346">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M346">
         <v>0</v>
@@ -25157,7 +25187,7 @@
         <v>0</v>
       </c>
       <c r="O346">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="P346" t="s">
         <v>17</v>
@@ -25242,7 +25272,7 @@
         <v>6</v>
       </c>
       <c r="N348">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O348">
         <v>23</v>
@@ -25289,6 +25319,196 @@
         <v>14</v>
       </c>
       <c r="V349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G350">
+        <v>5</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350" t="s">
+        <v>362</v>
+      </c>
+      <c r="L350">
+        <v>0</v>
+      </c>
+      <c r="M350">
+        <v>0</v>
+      </c>
+      <c r="N350">
+        <v>0</v>
+      </c>
+      <c r="O350">
+        <v>0</v>
+      </c>
+      <c r="P350" t="s">
+        <v>279</v>
+      </c>
+      <c r="V350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G351">
+        <v>5</v>
+      </c>
+      <c r="I351">
+        <v>0</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351" t="s">
+        <v>362</v>
+      </c>
+      <c r="L351">
+        <v>0</v>
+      </c>
+      <c r="M351">
+        <v>0</v>
+      </c>
+      <c r="N351">
+        <v>0</v>
+      </c>
+      <c r="O351">
+        <v>0</v>
+      </c>
+      <c r="P351" t="s">
+        <v>279</v>
+      </c>
+      <c r="V351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G352">
+        <v>5</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352" t="s">
+        <v>362</v>
+      </c>
+      <c r="L352">
+        <v>0</v>
+      </c>
+      <c r="M352">
+        <v>0</v>
+      </c>
+      <c r="N352">
+        <v>0</v>
+      </c>
+      <c r="O352">
+        <v>0</v>
+      </c>
+      <c r="P352" t="s">
+        <v>279</v>
+      </c>
+      <c r="V352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G353">
+        <v>2</v>
+      </c>
+      <c r="I353">
+        <v>0</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353" t="s">
+        <v>362</v>
+      </c>
+      <c r="L353">
+        <v>0</v>
+      </c>
+      <c r="M353">
+        <v>0</v>
+      </c>
+      <c r="N353">
+        <v>0</v>
+      </c>
+      <c r="O353">
+        <v>0</v>
+      </c>
+      <c r="P353" t="s">
+        <v>279</v>
+      </c>
+      <c r="V353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G354">
+        <v>2</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354" t="s">
+        <v>362</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+      <c r="M354">
+        <v>0</v>
+      </c>
+      <c r="N354">
+        <v>0</v>
+      </c>
+      <c r="O354">
+        <v>0</v>
+      </c>
+      <c r="P354" t="s">
+        <v>279</v>
+      </c>
+      <c r="V354">
         <v>0</v>
       </c>
     </row>
@@ -25299,8 +25519,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B5BDEE-B1F0-4242-8B98-AFFE0F6046EB}">
-  <dimension ref="A1:K2301"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06772981-642D-4BD0-9C7E-8CF83FF72C60}">
+  <dimension ref="A1:K2387"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -105745,6 +105965,3016 @@
         <v>279</v>
       </c>
       <c r="K2301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2302" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2302">
+        <v>0</v>
+      </c>
+      <c r="E2302" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2302" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2302">
+        <v>0</v>
+      </c>
+      <c r="H2302" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2302">
+        <v>1</v>
+      </c>
+      <c r="J2302" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2303" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2303">
+        <v>0</v>
+      </c>
+      <c r="E2303" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2303" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2303">
+        <v>0</v>
+      </c>
+      <c r="H2303" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2303">
+        <v>1</v>
+      </c>
+      <c r="J2303" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2304" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2304">
+        <v>0</v>
+      </c>
+      <c r="E2304" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2304" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2304">
+        <v>0</v>
+      </c>
+      <c r="H2304" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2304">
+        <v>1</v>
+      </c>
+      <c r="J2304" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2305" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2305">
+        <v>0</v>
+      </c>
+      <c r="E2305" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2305" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2305">
+        <v>0</v>
+      </c>
+      <c r="H2305" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2305">
+        <v>1</v>
+      </c>
+      <c r="J2305" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2306" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2306">
+        <v>0</v>
+      </c>
+      <c r="E2306" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2306" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2306">
+        <v>0</v>
+      </c>
+      <c r="H2306" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2306">
+        <v>1</v>
+      </c>
+      <c r="J2306" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2307" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2307" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2307" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2307" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2307" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2307">
+        <v>4</v>
+      </c>
+      <c r="J2307" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2307">
+        <v>33600</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2308" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2308" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2308" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2308" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2308" t="s">
+        <v>191</v>
+      </c>
+      <c r="H2308" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2308">
+        <v>9</v>
+      </c>
+      <c r="J2308" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2308">
+        <v>89100</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2309" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2309" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2309" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2309">
+        <v>0</v>
+      </c>
+      <c r="H2309" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2309">
+        <v>2</v>
+      </c>
+      <c r="J2309" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2309">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2310" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2310" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2310" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2310" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2310">
+        <v>0</v>
+      </c>
+      <c r="H2310" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2310">
+        <v>1</v>
+      </c>
+      <c r="J2310" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2310">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2311" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2311" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2311" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2311">
+        <v>0</v>
+      </c>
+      <c r="H2311" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2311">
+        <v>1</v>
+      </c>
+      <c r="J2311" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2311">
+        <v>39900</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2312" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2312" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2312" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2312" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2312">
+        <v>0</v>
+      </c>
+      <c r="H2312" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2312">
+        <v>2</v>
+      </c>
+      <c r="J2312" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2312">
+        <v>79800</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2313" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2313" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2313" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2313">
+        <v>0</v>
+      </c>
+      <c r="H2313" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2313">
+        <v>5</v>
+      </c>
+      <c r="J2313" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2313">
+        <v>179500</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2314" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2314" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2314" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2314">
+        <v>0</v>
+      </c>
+      <c r="H2314" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2314">
+        <v>1</v>
+      </c>
+      <c r="J2314" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2314">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2315" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2315" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2315" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2315" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2315">
+        <v>8</v>
+      </c>
+      <c r="J2315" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2315">
+        <v>55200</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2316" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2316" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2316" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2316" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2316" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2316" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2316">
+        <v>13</v>
+      </c>
+      <c r="J2316" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2316">
+        <v>109200</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2317" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2317" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2317" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2317" t="s">
+        <v>191</v>
+      </c>
+      <c r="H2317" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2317">
+        <v>5</v>
+      </c>
+      <c r="J2317" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2317">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2318" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2318" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2318" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2318" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2318" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2318" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2318">
+        <v>6</v>
+      </c>
+      <c r="J2318" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2318">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2319" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2319" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2319" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2319">
+        <v>0</v>
+      </c>
+      <c r="H2319" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2319">
+        <v>3</v>
+      </c>
+      <c r="J2319" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2319">
+        <v>128700</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2320" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2320" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2320" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2320" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2320">
+        <v>0</v>
+      </c>
+      <c r="H2320" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2320">
+        <v>2</v>
+      </c>
+      <c r="J2320" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2320">
+        <v>79800</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2321" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2321" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2321" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2321">
+        <v>0</v>
+      </c>
+      <c r="H2321" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2321">
+        <v>6</v>
+      </c>
+      <c r="J2321" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2321">
+        <v>257400</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2322" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2322" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2322" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2322">
+        <v>0</v>
+      </c>
+      <c r="H2322" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2322">
+        <v>3</v>
+      </c>
+      <c r="J2322" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2322">
+        <v>128700</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2323" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2323" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2323" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2323">
+        <v>270</v>
+      </c>
+      <c r="H2323" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2323">
+        <v>1</v>
+      </c>
+      <c r="J2323" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2323">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2324" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2324" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2324" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2324">
+        <v>260</v>
+      </c>
+      <c r="H2324" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2324">
+        <v>1</v>
+      </c>
+      <c r="J2324" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2324">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2325" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2325" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2325" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2325" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2325">
+        <v>245</v>
+      </c>
+      <c r="H2325" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2325">
+        <v>1</v>
+      </c>
+      <c r="J2325" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2325">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2326" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2326" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2326" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2326" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2326">
+        <v>0</v>
+      </c>
+      <c r="H2326" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2326">
+        <v>3</v>
+      </c>
+      <c r="J2326" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2326">
+        <v>119700</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2327" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2327" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2327" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2327" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2327">
+        <v>0</v>
+      </c>
+      <c r="H2327" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2327">
+        <v>1</v>
+      </c>
+      <c r="J2327" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2327">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2328" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2328" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2328" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2328">
+        <v>0</v>
+      </c>
+      <c r="H2328" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2328">
+        <v>1</v>
+      </c>
+      <c r="J2328" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2328">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2329" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2329" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2329" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2329" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2329">
+        <v>250</v>
+      </c>
+      <c r="H2329" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2329">
+        <v>1</v>
+      </c>
+      <c r="J2329" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2329">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2330" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2330" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2330" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2330">
+        <v>245</v>
+      </c>
+      <c r="H2330" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2330">
+        <v>1</v>
+      </c>
+      <c r="J2330" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2330">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2331" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2331" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2331" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2331">
+        <v>240</v>
+      </c>
+      <c r="H2331" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2331">
+        <v>1</v>
+      </c>
+      <c r="J2331" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2331">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2332" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2332" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2332" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2332">
+        <v>235</v>
+      </c>
+      <c r="H2332" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2332">
+        <v>1</v>
+      </c>
+      <c r="J2332" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2332">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2333" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2333" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2333" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2333">
+        <v>240</v>
+      </c>
+      <c r="H2333" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2333">
+        <v>1</v>
+      </c>
+      <c r="J2333" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2333">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2334" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2334" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2334" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2334">
+        <v>250</v>
+      </c>
+      <c r="H2334" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2334">
+        <v>1</v>
+      </c>
+      <c r="J2334" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2334">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2335" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2335" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2335" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2335" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2335" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2335" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2335">
+        <v>240</v>
+      </c>
+      <c r="H2335" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2335">
+        <v>1</v>
+      </c>
+      <c r="J2335" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2335">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2336" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2336" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2336" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2336" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2336">
+        <v>240</v>
+      </c>
+      <c r="H2336" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2336">
+        <v>1</v>
+      </c>
+      <c r="J2336" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2336">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2337" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2337" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2337" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2337" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2337">
+        <v>235</v>
+      </c>
+      <c r="H2337" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2337">
+        <v>1</v>
+      </c>
+      <c r="J2337" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2337">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2338" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2338" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2338" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2338" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2338" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2338">
+        <v>265</v>
+      </c>
+      <c r="H2338" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2338">
+        <v>1</v>
+      </c>
+      <c r="J2338" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2338">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2339" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2339" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2339" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2339" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2339">
+        <v>265</v>
+      </c>
+      <c r="H2339" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2339">
+        <v>1</v>
+      </c>
+      <c r="J2339" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2339">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2340" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2340" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2340">
+        <v>0</v>
+      </c>
+      <c r="E2340" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2340" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2340">
+        <v>0</v>
+      </c>
+      <c r="H2340" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2340">
+        <v>1</v>
+      </c>
+      <c r="J2340" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2341" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2341" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2341" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2341" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2341">
+        <v>240</v>
+      </c>
+      <c r="H2341" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2341">
+        <v>1</v>
+      </c>
+      <c r="J2341" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2341">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2342" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2342" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2342" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2342">
+        <v>0</v>
+      </c>
+      <c r="E2342" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2342" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2342">
+        <v>0</v>
+      </c>
+      <c r="H2342" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2342">
+        <v>1</v>
+      </c>
+      <c r="J2342" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2343" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2343" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2343" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2343" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2343" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2343">
+        <v>250</v>
+      </c>
+      <c r="H2343" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2343">
+        <v>1</v>
+      </c>
+      <c r="J2343" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2343">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2344" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2344" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2344" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2344">
+        <v>0</v>
+      </c>
+      <c r="E2344" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2344" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2344">
+        <v>0</v>
+      </c>
+      <c r="H2344" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2344">
+        <v>1</v>
+      </c>
+      <c r="J2344" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2345" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2345" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2345" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2345">
+        <v>0</v>
+      </c>
+      <c r="E2345" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2345" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2345">
+        <v>0</v>
+      </c>
+      <c r="H2345" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2345">
+        <v>1</v>
+      </c>
+      <c r="J2345" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2346" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2346" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2346">
+        <v>0</v>
+      </c>
+      <c r="E2346" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2346" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2346">
+        <v>0</v>
+      </c>
+      <c r="H2346" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2346">
+        <v>1</v>
+      </c>
+      <c r="J2346" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2347" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2347" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2347" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2347" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2347" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2347" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2347">
+        <v>235</v>
+      </c>
+      <c r="H2347" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2347">
+        <v>1</v>
+      </c>
+      <c r="J2347" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2347">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2348" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2348" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2348">
+        <v>0</v>
+      </c>
+      <c r="E2348" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2348" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2348">
+        <v>0</v>
+      </c>
+      <c r="H2348" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2348">
+        <v>1</v>
+      </c>
+      <c r="J2348" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2349" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2349" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2349" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2349" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2349" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2349" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2349">
+        <v>250</v>
+      </c>
+      <c r="H2349" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2349">
+        <v>1</v>
+      </c>
+      <c r="J2349" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2349">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2350" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2350" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2350" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2350">
+        <v>0</v>
+      </c>
+      <c r="E2350" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2350" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2350">
+        <v>0</v>
+      </c>
+      <c r="H2350" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2350">
+        <v>1</v>
+      </c>
+      <c r="J2350" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2351" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2351" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2351" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2351" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2351" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2351" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2351">
+        <v>250</v>
+      </c>
+      <c r="H2351" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2351">
+        <v>1</v>
+      </c>
+      <c r="J2351" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2351">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2352" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2352" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2352">
+        <v>0</v>
+      </c>
+      <c r="E2352" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2352" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2352">
+        <v>0</v>
+      </c>
+      <c r="H2352" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2352">
+        <v>1</v>
+      </c>
+      <c r="J2352" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2353" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2353" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2353" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2353" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2353" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2353" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2353">
+        <v>275</v>
+      </c>
+      <c r="H2353" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2353">
+        <v>1</v>
+      </c>
+      <c r="J2353" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2353">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2354" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2354" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2354" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2354" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2354" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2354">
+        <v>235</v>
+      </c>
+      <c r="H2354" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2354">
+        <v>1</v>
+      </c>
+      <c r="J2354" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2354">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2355" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2355" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2355" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2355" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2355" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2355" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2355">
+        <v>235</v>
+      </c>
+      <c r="H2355" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2355">
+        <v>1</v>
+      </c>
+      <c r="J2355" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2355">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2356" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2356" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2356" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2356" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2356" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2356">
+        <v>240</v>
+      </c>
+      <c r="H2356" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2356">
+        <v>1</v>
+      </c>
+      <c r="J2356" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2356">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2357" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2357" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2357" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2357" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2357" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2357" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2357">
+        <v>245</v>
+      </c>
+      <c r="H2357" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2357">
+        <v>1</v>
+      </c>
+      <c r="J2357" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2357">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2358" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2358" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2358" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2358" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2358" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2358" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2358">
+        <v>235</v>
+      </c>
+      <c r="H2358" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2358">
+        <v>1</v>
+      </c>
+      <c r="J2358" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2358">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2359" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2359" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2359" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2359" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2359" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2359" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2359">
+        <v>235</v>
+      </c>
+      <c r="H2359" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2359">
+        <v>1</v>
+      </c>
+      <c r="J2359" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2359">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2360" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2360" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2360" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2360" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2360" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2360" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2360">
+        <v>245</v>
+      </c>
+      <c r="H2360" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2360">
+        <v>1</v>
+      </c>
+      <c r="J2360" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2360">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2361" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2361" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2361" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2361" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2361" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2361" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2361">
+        <v>240</v>
+      </c>
+      <c r="H2361" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2361">
+        <v>1</v>
+      </c>
+      <c r="J2361" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2361">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2362" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2362" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2362" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2362" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2362" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2362" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2362">
+        <v>245</v>
+      </c>
+      <c r="H2362" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2362">
+        <v>1</v>
+      </c>
+      <c r="J2362" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2362">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2363" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2363" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2363" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2363" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2363" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2363" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2363">
+        <v>0</v>
+      </c>
+      <c r="H2363" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2363">
+        <v>3</v>
+      </c>
+      <c r="J2363" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2363">
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2364" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2364" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2364" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2364">
+        <v>0</v>
+      </c>
+      <c r="E2364" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2364" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2364">
+        <v>0</v>
+      </c>
+      <c r="H2364" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2364">
+        <v>1</v>
+      </c>
+      <c r="J2364" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2365" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2365" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2365" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2365">
+        <v>0</v>
+      </c>
+      <c r="E2365" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2365" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2365">
+        <v>0</v>
+      </c>
+      <c r="H2365" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2365">
+        <v>1</v>
+      </c>
+      <c r="J2365" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2366" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2366" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2366" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2366">
+        <v>0</v>
+      </c>
+      <c r="E2366" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2366" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2366">
+        <v>0</v>
+      </c>
+      <c r="H2366" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2366">
+        <v>1</v>
+      </c>
+      <c r="J2366" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2367" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2367" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2367" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2367">
+        <v>0</v>
+      </c>
+      <c r="E2367" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2367" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2367">
+        <v>0</v>
+      </c>
+      <c r="H2367" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2367">
+        <v>2</v>
+      </c>
+      <c r="J2367" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2368" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2368" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2368" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2368">
+        <v>0</v>
+      </c>
+      <c r="E2368" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2368" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2368">
+        <v>0</v>
+      </c>
+      <c r="H2368" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2368">
+        <v>1</v>
+      </c>
+      <c r="J2368" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2369" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2369" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2369" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2369">
+        <v>0</v>
+      </c>
+      <c r="E2369" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2369" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2369">
+        <v>0</v>
+      </c>
+      <c r="H2369" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2369">
+        <v>1</v>
+      </c>
+      <c r="J2369" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2370" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2370" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2370" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2370">
+        <v>0</v>
+      </c>
+      <c r="E2370" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2370" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2370">
+        <v>0</v>
+      </c>
+      <c r="H2370" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2370">
+        <v>1</v>
+      </c>
+      <c r="J2370" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2371" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2371" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2371" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2371">
+        <v>0</v>
+      </c>
+      <c r="E2371" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2371" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2371">
+        <v>0</v>
+      </c>
+      <c r="H2371" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2371">
+        <v>1</v>
+      </c>
+      <c r="J2371" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2372" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2372" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2372" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2372">
+        <v>0</v>
+      </c>
+      <c r="E2372" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2372" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2372">
+        <v>0</v>
+      </c>
+      <c r="H2372" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2372">
+        <v>1</v>
+      </c>
+      <c r="J2372" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2373" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2373" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2373" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2373">
+        <v>0</v>
+      </c>
+      <c r="E2373" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2373" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2373">
+        <v>0</v>
+      </c>
+      <c r="H2373" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2373">
+        <v>1</v>
+      </c>
+      <c r="J2373" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2374" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2374" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2374">
+        <v>0</v>
+      </c>
+      <c r="E2374" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2374" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2374">
+        <v>0</v>
+      </c>
+      <c r="H2374" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2374">
+        <v>5</v>
+      </c>
+      <c r="J2374" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2375" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B2375" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2375" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2375">
+        <v>0</v>
+      </c>
+      <c r="E2375" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2375" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2375">
+        <v>0</v>
+      </c>
+      <c r="H2375" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2375">
+        <v>5</v>
+      </c>
+      <c r="J2375" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2376" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B2376" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2376" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2376">
+        <v>0</v>
+      </c>
+      <c r="E2376" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2376" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2376">
+        <v>0</v>
+      </c>
+      <c r="H2376" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2376">
+        <v>5</v>
+      </c>
+      <c r="J2376" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2377" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B2377" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2377" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2377">
+        <v>0</v>
+      </c>
+      <c r="E2377" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2377" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2377">
+        <v>0</v>
+      </c>
+      <c r="H2377" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2377">
+        <v>1</v>
+      </c>
+      <c r="J2377" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2378" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B2378" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2378" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2378">
+        <v>0</v>
+      </c>
+      <c r="E2378" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2378" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2378">
+        <v>0</v>
+      </c>
+      <c r="H2378" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2378">
+        <v>1</v>
+      </c>
+      <c r="J2378" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2379" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B2379" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2379" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2379">
+        <v>0</v>
+      </c>
+      <c r="E2379" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2379" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2379">
+        <v>0</v>
+      </c>
+      <c r="H2379" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2379">
+        <v>1</v>
+      </c>
+      <c r="J2379" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2380" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B2380" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2380" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2380">
+        <v>0</v>
+      </c>
+      <c r="E2380" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2380" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2380">
+        <v>0</v>
+      </c>
+      <c r="H2380" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2380">
+        <v>1</v>
+      </c>
+      <c r="J2380" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2381" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B2381" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2381" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2381">
+        <v>0</v>
+      </c>
+      <c r="E2381" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2381" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2381">
+        <v>0</v>
+      </c>
+      <c r="H2381" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2381">
+        <v>1</v>
+      </c>
+      <c r="J2381" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2382" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B2382" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2382" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2382">
+        <v>0</v>
+      </c>
+      <c r="E2382" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2382" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2382">
+        <v>0</v>
+      </c>
+      <c r="H2382" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2382">
+        <v>1</v>
+      </c>
+      <c r="J2382" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2383" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B2383" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2383" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2383" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2383" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2383" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2383">
+        <v>260</v>
+      </c>
+      <c r="H2383" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2383">
+        <v>4</v>
+      </c>
+      <c r="J2383" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2383">
+        <v>179600</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2384" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B2384" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2384" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2384" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2384" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2384" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2384">
+        <v>265</v>
+      </c>
+      <c r="H2384" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2384">
+        <v>5</v>
+      </c>
+      <c r="J2384" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2384">
+        <v>224500</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2385" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B2385" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2385" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2385">
+        <v>0</v>
+      </c>
+      <c r="E2385" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2385" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2385">
+        <v>0</v>
+      </c>
+      <c r="H2385" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2385">
+        <v>1</v>
+      </c>
+      <c r="J2385" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2386" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B2386" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2386" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2386">
+        <v>0</v>
+      </c>
+      <c r="E2386" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2386" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2386">
+        <v>0</v>
+      </c>
+      <c r="H2386" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2386">
+        <v>1</v>
+      </c>
+      <c r="J2386" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2387" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B2387" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2387" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2387">
+        <v>0</v>
+      </c>
+      <c r="E2387" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2387" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2387">
+        <v>0</v>
+      </c>
+      <c r="H2387" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2387">
+        <v>1</v>
+      </c>
+      <c r="J2387" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2387">
         <v>0</v>
       </c>
     </row>
